--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD17464-EA3B-DF4D-AF30-024C34A30372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21466243-053B-6C48-9718-0005C75F3104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="2700" windowWidth="24460" windowHeight="14820" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
   <sheets>
     <sheet name="promotoria" sheetId="2" r:id="rId1"/>
-    <sheet name="asesores" sheetId="1" r:id="rId2"/>
+    <sheet name="asesores" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="134">
   <si>
     <t>Asesor</t>
   </si>
@@ -411,36 +411,6 @@
     <t>a31</t>
   </si>
   <si>
-    <t>Columna1</t>
-  </si>
-  <si>
-    <t>Columna2</t>
-  </si>
-  <si>
-    <t>Columna3</t>
-  </si>
-  <si>
-    <t>Columna4</t>
-  </si>
-  <si>
-    <t>Columna5</t>
-  </si>
-  <si>
-    <t>Columna6</t>
-  </si>
-  <si>
-    <t>Columna7</t>
-  </si>
-  <si>
-    <t>Columna8</t>
-  </si>
-  <si>
-    <t>Columna9</t>
-  </si>
-  <si>
-    <t>Columna10</t>
-  </si>
-  <si>
     <t>GUADALAJARA</t>
   </si>
   <si>
@@ -466,6 +436,9 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>MONSERRAT VELASCO SANTOS</t>
   </si>
 </sst>
 </file>
@@ -474,9 +447,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -522,12 +495,6 @@
     <font>
       <sz val="10"/>
       <color indexed="9"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -661,14 +628,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="10" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -688,8 +647,16 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -698,7 +665,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="101">
+  <dxfs count="72">
     <dxf>
       <border>
         <left style="hair">
@@ -1832,289 +1799,10 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+      <border outline="0">
+        <top style="double">
+          <color indexed="22"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2122,13 +1810,6 @@
         <bottom style="double">
           <color indexed="22"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="double">
-          <color indexed="22"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -2167,266 +1848,6 @@
       </border>
       <protection locked="1" hidden="1"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="1" hidden="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="9"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="48"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="22"/>
-        </left>
-        <right style="double">
-          <color indexed="22"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="1"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2441,7 +1862,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="88" headerRowBorderDxfId="86" tableBorderDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="71" headerRowBorderDxfId="70" tableBorderDxfId="69">
   <autoFilter ref="A3:P5" xr:uid="{A29DCA76-5097-2F45-94DA-4B121F22F1F5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{A2D27468-D390-E245-85A6-B90C4BDF0CE1}" name="Polizas_Pagadas_Año_Anterior"/>
@@ -2460,25 +1881,6 @@
     <tableColumn id="14" xr3:uid="{2A0E0112-B35A-534F-9DD3-9201FF2483A4}" name="Prima_Pagada_Reclutas_Año_Actual"/>
     <tableColumn id="15" xr3:uid="{C1239651-E803-964C-BB42-9A34CDE98479}" name="Crec_Prima_Pagada_Reclutas"/>
     <tableColumn id="16" xr3:uid="{50F74EB1-98F8-F845-8CDC-6218380965BC}" name="%_Crec_Prima_Pagada_Reclutas"/>
-  </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{962EC2B3-BC50-FC4C-BE24-20259EE12B7C}" name="Tabla8" displayName="Tabla8" ref="A2:J60" totalsRowShown="0" headerRowDxfId="100" dataDxfId="99">
-  <autoFilter ref="A2:J60" xr:uid="{8E304F4B-C1E2-9E4A-98A7-5782F07B324B}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{D89C1F28-00A5-C64A-BF2B-07E04DA504ED}" name="Columna1" dataDxfId="98"/>
-    <tableColumn id="10" xr3:uid="{76B5DC48-4828-F349-A82C-3D351D77E39E}" name="Columna2" dataDxfId="97"/>
-    <tableColumn id="2" xr3:uid="{A9846CAA-A83F-764D-8AAF-14973DE1AB83}" name="Columna3" dataDxfId="96"/>
-    <tableColumn id="3" xr3:uid="{32B7138A-63DA-BD4E-A61A-C330594FB6B7}" name="Columna4" dataDxfId="95"/>
-    <tableColumn id="4" xr3:uid="{7C2BF043-FB3C-0147-84E0-8BC897AD5A93}" name="Columna5" dataDxfId="94"/>
-    <tableColumn id="5" xr3:uid="{8E0A6C37-C5BE-0B42-873E-3ED2518151E1}" name="Columna6" dataDxfId="93" dataCellStyle="Porcentaje"/>
-    <tableColumn id="6" xr3:uid="{D4964695-8B1F-8349-A532-BAD6BBED6FC2}" name="Columna7" dataDxfId="92"/>
-    <tableColumn id="7" xr3:uid="{722A7CA1-F9F1-0444-9E81-1150E24308F7}" name="Columna8" dataDxfId="91"/>
-    <tableColumn id="8" xr3:uid="{B2F3C962-80D5-084E-A7FB-214373672313}" name="Columna9" dataDxfId="90"/>
-    <tableColumn id="9" xr3:uid="{7C98A25B-479E-DF42-ACD4-50B64CAFB0DF}" name="Columna10" dataDxfId="89" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2801,9 +2203,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{405503AD-8A78-4740-A5ED-1A4F88DDAB00}">
-  <dimension ref="A3:P5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
+    <row r="1" spans="1:16" ht="32" x14ac:dyDescent="0.4">
+      <c r="A1" s="1">
+        <v>46081</v>
+      </c>
+    </row>
     <row r="3" spans="1:16" ht="46" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
@@ -2877,25 +2287,25 @@
         <v>78</v>
       </c>
       <c r="B5" s="15">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C5" s="15">
-        <v>-44</v>
+        <v>-40</v>
       </c>
       <c r="D5" s="16">
-        <v>-0.5641025641025641</v>
+        <v>-0.51282051282051277</v>
       </c>
       <c r="E5" s="15">
         <v>3065.09</v>
       </c>
       <c r="F5" s="15">
-        <v>1780.74</v>
+        <v>1888.59</v>
       </c>
       <c r="G5" s="15">
-        <v>-1284.3499999999999</v>
+        <v>-1176.5</v>
       </c>
       <c r="H5" s="16">
-        <v>-0.41902521622529842</v>
+        <v>-0.38383864747854068</v>
       </c>
       <c r="I5" s="15">
         <v>1</v>
@@ -2931,103 +2341,49 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB93031-4056-DB42-9AC4-133E99F52598}">
-  <sheetPr>
-    <tabColor theme="5" tint="0.39997558519241921"/>
-  </sheetPr>
-  <dimension ref="A1:AE64"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6395312-445F-3747-AD98-F1F037E33F44}">
+  <dimension ref="A1:AE65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="17.1640625" customWidth="1"/>
-    <col min="3" max="3" width="25.1640625" customWidth="1"/>
-    <col min="4" max="4" width="24.1640625" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="13" max="13" width="25.5" customWidth="1"/>
-    <col min="14" max="14" width="24.1640625" customWidth="1"/>
-    <col min="15" max="15" width="19.83203125" customWidth="1"/>
-    <col min="16" max="16" width="21.83203125" customWidth="1"/>
-    <col min="17" max="17" width="23.83203125" customWidth="1"/>
-    <col min="18" max="18" width="23.33203125" customWidth="1"/>
-    <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="20" customWidth="1"/>
-    <col min="21" max="21" width="19.33203125" customWidth="1"/>
-    <col min="22" max="22" width="18" customWidth="1"/>
-    <col min="23" max="23" width="13.5" customWidth="1"/>
-    <col min="24" max="24" width="15.5" customWidth="1"/>
-    <col min="25" max="25" width="31.1640625" customWidth="1"/>
-    <col min="26" max="26" width="29.83203125" customWidth="1"/>
-    <col min="27" max="27" width="25.33203125" customWidth="1"/>
-    <col min="28" max="28" width="27.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="33" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>46078</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="18" t="s">
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="17" t="s">
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="U2" s="17"/>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="17" t="s">
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25"/>
+      <c r="AA2" s="25"/>
+      <c r="AB2" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="AC2" s="17"/>
-      <c r="AD2" s="17"/>
-      <c r="AE2" s="17"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
     </row>
     <row r="3" spans="1:31" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -3063,16 +2419,16 @@
       <c r="K3" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="M3" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="N3" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="O3" s="20" t="s">
+      <c r="O3" s="18" t="s">
         <v>93</v>
       </c>
       <c r="P3" s="3" t="s">
@@ -3087,16 +2443,16 @@
       <c r="S3" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="T3" s="19" t="s">
+      <c r="T3" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="U3" s="19" t="s">
+      <c r="U3" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="V3" s="19" t="s">
+      <c r="V3" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="W3" s="20" t="s">
+      <c r="W3" s="18" t="s">
         <v>93</v>
       </c>
       <c r="X3" s="3" t="s">
@@ -3111,226 +2467,226 @@
       <c r="AA3" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="AB3" s="19" t="s">
+      <c r="AB3" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="AC3" s="19" t="s">
+      <c r="AC3" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="AD3" s="19" t="s">
+      <c r="AD3" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="AE3" s="20" t="s">
+      <c r="AE3" s="18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
-      <c r="O4" s="22"/>
+      <c r="O4" s="20"/>
       <c r="P4" s="13"/>
       <c r="Q4" s="13"/>
       <c r="R4" s="13"/>
-      <c r="S4" s="22"/>
+      <c r="S4" s="20"/>
       <c r="T4" s="13"/>
       <c r="U4" s="13"/>
       <c r="V4" s="13"/>
-      <c r="W4" s="22"/>
+      <c r="W4" s="20"/>
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
       <c r="Z4" s="13"/>
-      <c r="AA4" s="22"/>
+      <c r="AA4" s="20"/>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
       <c r="AD4" s="13"/>
-      <c r="AE4" s="22"/>
+      <c r="AE4" s="20"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
       <c r="L5" s="15">
         <v>87</v>
       </c>
       <c r="M5" s="15">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N5" s="15">
-        <v>-46</v>
+        <v>-43</v>
       </c>
       <c r="O5" s="16">
-        <v>-0.52873563218390807</v>
+        <v>-0.49425287356321834</v>
       </c>
       <c r="P5" s="15">
         <v>78</v>
       </c>
       <c r="Q5" s="15">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="R5" s="15">
-        <v>-44</v>
+        <v>-40</v>
       </c>
       <c r="S5" s="16">
-        <v>-0.5641025641025641</v>
+        <v>-0.51282051282051277</v>
       </c>
       <c r="T5" s="15">
         <v>3345.28</v>
       </c>
       <c r="U5" s="15">
-        <v>770.76</v>
+        <v>162.23999999999981</v>
       </c>
       <c r="V5" s="15">
-        <v>-2574.52</v>
+        <v>-3183.0400000000004</v>
       </c>
       <c r="W5" s="16">
-        <v>-0.7695977616223455</v>
+        <v>-0.95150181748612972</v>
       </c>
       <c r="X5" s="15">
         <v>3065.0899999999988</v>
       </c>
       <c r="Y5" s="15">
-        <v>1780.7400000000007</v>
+        <v>1888.5900000000001</v>
       </c>
       <c r="Z5" s="15">
-        <v>-1284.3499999999999</v>
+        <v>-1176.5000000000002</v>
       </c>
       <c r="AA5" s="16">
-        <v>-0.41902521622529798</v>
+        <v>-0.38383864747854035</v>
       </c>
       <c r="AB5" s="15">
         <v>21.1402</v>
       </c>
       <c r="AC5" s="15">
-        <v>28.482800000000005</v>
+        <v>31.525700000000001</v>
       </c>
       <c r="AD5" s="15">
-        <v>7.3426000000000018</v>
+        <v>10.3855</v>
       </c>
       <c r="AE5" s="16">
-        <v>0.34732878591498673</v>
+        <v>0.4912678214964854</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="J6" s="23" t="s">
+      <c r="J6" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="K6" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="L6" s="23" t="s">
+      <c r="L6" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M6" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="N6" s="23" t="s">
+      <c r="N6" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="O6" s="23" t="s">
+      <c r="O6" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="P6" s="23" t="s">
+      <c r="P6" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="Q6" s="23" t="s">
+      <c r="Q6" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="R6" s="23" t="s">
+      <c r="R6" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="S6" s="23" t="s">
+      <c r="S6" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="T6" s="23" t="s">
+      <c r="T6" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="U6" s="23" t="s">
+      <c r="U6" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="V6" s="23" t="s">
+      <c r="V6" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="W6" s="23" t="s">
+      <c r="W6" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="X6" s="23" t="s">
+      <c r="X6" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="Y6" s="23" t="s">
+      <c r="Y6" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="Z6" s="23" t="s">
+      <c r="Z6" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="AA6" s="23" t="s">
+      <c r="AA6" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="AB6" s="23" t="s">
+      <c r="AB6" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="AC6" s="23" t="s">
+      <c r="AC6" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="AD6" s="23" t="s">
+      <c r="AD6" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="AE6" s="23" t="s">
+      <c r="AE6" s="21" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C7" s="10">
         <v>2043</v>
@@ -3339,7 +2695,7 @@
         <v>2043</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F7" s="10">
         <v>47116</v>
@@ -3348,16 +2704,16 @@
         <v>17</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I7" s="24">
+        <v>127</v>
+      </c>
+      <c r="I7" s="22">
         <v>44616</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="22">
         <v>44616</v>
       </c>
-      <c r="K7" s="25" t="s">
-        <v>138</v>
+      <c r="K7" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L7" s="11">
         <v>3</v>
@@ -3387,45 +2743,45 @@
         <v>25.07</v>
       </c>
       <c r="U7" s="11">
-        <v>61.64</v>
+        <v>61.9</v>
       </c>
       <c r="V7" s="11">
-        <v>36.57</v>
+        <v>36.83</v>
       </c>
       <c r="W7" s="12">
-        <v>1.4587000000000001</v>
+        <v>1.4691000000000001</v>
       </c>
       <c r="X7" s="11">
         <v>96.36</v>
       </c>
       <c r="Y7" s="11">
-        <v>105.23</v>
+        <v>112.49</v>
       </c>
       <c r="Z7" s="11">
-        <v>8.8699999999999992</v>
+        <v>16.13</v>
       </c>
       <c r="AA7" s="12">
-        <v>9.2100000000000001E-2</v>
+        <v>0.16739999999999999</v>
       </c>
       <c r="AB7" s="11">
         <v>4.2222</v>
       </c>
       <c r="AC7" s="11">
-        <v>5.1172000000000004</v>
+        <v>5.1874000000000002</v>
       </c>
       <c r="AD7" s="11">
-        <v>0.89500000000000002</v>
+        <v>0.96519999999999995</v>
       </c>
       <c r="AE7" s="12">
-        <v>0.21199999999999999</v>
+        <v>0.2286</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C8" s="10">
         <v>2043</v>
@@ -3434,7 +2790,7 @@
         <v>2043</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F8" s="10">
         <v>49227</v>
@@ -3443,16 +2799,16 @@
         <v>18</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I8" s="24">
+        <v>129</v>
+      </c>
+      <c r="I8" s="22">
         <v>44377</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="22">
         <v>44377</v>
       </c>
-      <c r="K8" s="25" t="s">
-        <v>138</v>
+      <c r="K8" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L8" s="11">
         <v>0</v>
@@ -3517,10 +2873,10 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C9" s="10">
         <v>2043</v>
@@ -3529,7 +2885,7 @@
         <v>2511</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F9" s="10">
         <v>63441</v>
@@ -3538,16 +2894,16 @@
         <v>19</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I9" s="24">
+        <v>127</v>
+      </c>
+      <c r="I9" s="22">
         <v>44733</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="22">
         <v>44733</v>
       </c>
-      <c r="K9" s="25" t="s">
-        <v>138</v>
+      <c r="K9" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L9" s="11">
         <v>1</v>
@@ -3589,13 +2945,13 @@
         <v>23.41</v>
       </c>
       <c r="Y9" s="11">
-        <v>5.35</v>
+        <v>7.18</v>
       </c>
       <c r="Z9" s="11">
-        <v>-18.059999999999999</v>
+        <v>-16.23</v>
       </c>
       <c r="AA9" s="12">
-        <v>-0.77149999999999996</v>
+        <v>-0.69330000000000003</v>
       </c>
       <c r="AB9" s="11">
         <v>0</v>
@@ -3612,10 +2968,10 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C10" s="10">
         <v>2043</v>
@@ -3624,7 +2980,7 @@
         <v>2043</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F10" s="10">
         <v>65046</v>
@@ -3633,16 +2989,16 @@
         <v>20</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I10" s="24">
+        <v>127</v>
+      </c>
+      <c r="I10" s="22">
         <v>44763</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="22">
         <v>44763</v>
       </c>
-      <c r="K10" s="25" t="s">
-        <v>138</v>
+      <c r="K10" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L10" s="11">
         <v>1</v>
@@ -3707,10 +3063,10 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C11" s="10">
         <v>2043</v>
@@ -3719,7 +3075,7 @@
         <v>2511</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F11" s="10">
         <v>69684</v>
@@ -3728,16 +3084,16 @@
         <v>21</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I11" s="24">
+        <v>127</v>
+      </c>
+      <c r="I11" s="22">
         <v>44771</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="22">
         <v>44771</v>
       </c>
-      <c r="K11" s="25" t="s">
-        <v>138</v>
+      <c r="K11" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L11" s="11">
         <v>0</v>
@@ -3802,10 +3158,10 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C12" s="10">
         <v>2043</v>
@@ -3814,7 +3170,7 @@
         <v>2043</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F12" s="10">
         <v>80122</v>
@@ -3823,16 +3179,16 @@
         <v>22</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I12" s="24">
+        <v>127</v>
+      </c>
+      <c r="I12" s="22">
         <v>43371</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="22">
         <v>43371</v>
       </c>
-      <c r="K12" s="25" t="s">
-        <v>138</v>
+      <c r="K12" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L12" s="11">
         <v>6</v>
@@ -3850,57 +3206,57 @@
         <v>6</v>
       </c>
       <c r="Q12" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" s="11">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="S12" s="12">
-        <v>-0.83330000000000004</v>
+        <v>-0.66669999999999996</v>
       </c>
       <c r="T12" s="11">
         <v>149.66</v>
       </c>
       <c r="U12" s="11">
-        <v>44.57</v>
+        <v>44.67</v>
       </c>
       <c r="V12" s="11">
-        <v>-105.09</v>
+        <v>-104.99</v>
       </c>
       <c r="W12" s="12">
-        <v>-0.70220000000000005</v>
+        <v>-0.70150000000000001</v>
       </c>
       <c r="X12" s="11">
         <v>415.45</v>
       </c>
       <c r="Y12" s="11">
-        <v>34.340000000000003</v>
+        <v>58.56</v>
       </c>
       <c r="Z12" s="11">
-        <v>-381.11</v>
+        <v>-356.89</v>
       </c>
       <c r="AA12" s="12">
-        <v>-0.9173</v>
+        <v>-0.85899999999999999</v>
       </c>
       <c r="AB12" s="11">
         <v>2.6160999999999999</v>
       </c>
       <c r="AC12" s="11">
-        <v>7.9790999999999999</v>
+        <v>7.9966999999999997</v>
       </c>
       <c r="AD12" s="11">
-        <v>5.3630000000000004</v>
+        <v>5.3806000000000003</v>
       </c>
       <c r="AE12" s="12">
-        <v>2.0499999999999998</v>
+        <v>2.0567000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C13" s="10">
         <v>2043</v>
@@ -3909,7 +3265,7 @@
         <v>2043</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F13" s="10">
         <v>80925</v>
@@ -3918,16 +3274,16 @@
         <v>23</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I13" s="24">
+        <v>127</v>
+      </c>
+      <c r="I13" s="22">
         <v>43439</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="22">
         <v>43439</v>
       </c>
-      <c r="K13" s="25" t="s">
-        <v>138</v>
+      <c r="K13" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L13" s="11">
         <v>4</v>
@@ -3969,33 +3325,33 @@
         <v>74.97</v>
       </c>
       <c r="Y13" s="11">
-        <v>20.8</v>
+        <v>25.12</v>
       </c>
       <c r="Z13" s="11">
-        <v>-54.17</v>
+        <v>-49.85</v>
       </c>
       <c r="AA13" s="12">
-        <v>-0.72260000000000002</v>
+        <v>-0.66490000000000005</v>
       </c>
       <c r="AB13" s="11">
         <v>5.8438999999999997</v>
       </c>
       <c r="AC13" s="11">
-        <v>3.9723000000000002</v>
+        <v>3.9805999999999999</v>
       </c>
       <c r="AD13" s="11">
-        <v>-1.8715999999999999</v>
+        <v>-1.8633</v>
       </c>
       <c r="AE13" s="12">
-        <v>-0.32029999999999997</v>
+        <v>-0.31879999999999997</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C14" s="10">
         <v>2043</v>
@@ -4004,7 +3360,7 @@
         <v>2511</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F14" s="10">
         <v>81044</v>
@@ -4013,16 +3369,16 @@
         <v>24</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I14" s="24">
+        <v>127</v>
+      </c>
+      <c r="I14" s="22">
         <v>44872</v>
       </c>
-      <c r="J14" s="24">
+      <c r="J14" s="22">
         <v>44872</v>
       </c>
-      <c r="K14" s="25" t="s">
-        <v>138</v>
+      <c r="K14" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L14" s="11">
         <v>0</v>
@@ -4087,10 +3443,10 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C15" s="10">
         <v>2043</v>
@@ -4099,7 +3455,7 @@
         <v>2043</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F15" s="10">
         <v>81618</v>
@@ -4108,16 +3464,16 @@
         <v>25</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I15" s="24">
+        <v>127</v>
+      </c>
+      <c r="I15" s="22">
         <v>43447</v>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="22">
         <v>43447</v>
       </c>
-      <c r="K15" s="25" t="s">
-        <v>138</v>
+      <c r="K15" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L15" s="11">
         <v>0</v>
@@ -4159,22 +3515,22 @@
         <v>2.87</v>
       </c>
       <c r="Y15" s="11">
-        <v>14.89</v>
+        <v>14.95</v>
       </c>
       <c r="Z15" s="11">
-        <v>12.02</v>
+        <v>12.08</v>
       </c>
       <c r="AA15" s="12">
-        <v>4.1882000000000001</v>
+        <v>4.2091000000000003</v>
       </c>
       <c r="AB15" s="11">
         <v>0</v>
       </c>
       <c r="AC15" s="11">
-        <v>2.4923999999999999</v>
+        <v>2.5028000000000001</v>
       </c>
       <c r="AD15" s="11">
-        <v>2.4923999999999999</v>
+        <v>2.5028000000000001</v>
       </c>
       <c r="AE15" s="12">
         <v>1</v>
@@ -4182,10 +3538,10 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C16" s="10">
         <v>2043</v>
@@ -4194,7 +3550,7 @@
         <v>2043</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F16" s="10">
         <v>83407</v>
@@ -4203,16 +3559,16 @@
         <v>26</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I16" s="24">
+        <v>129</v>
+      </c>
+      <c r="I16" s="22">
         <v>43488</v>
       </c>
-      <c r="J16" s="24">
+      <c r="J16" s="22">
         <v>43497</v>
       </c>
-      <c r="K16" s="25" t="s">
-        <v>138</v>
+      <c r="K16" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L16" s="11">
         <v>0</v>
@@ -4277,10 +3633,10 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C17" s="10">
         <v>2043</v>
@@ -4289,7 +3645,7 @@
         <v>2043</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F17" s="10">
         <v>87538</v>
@@ -4298,84 +3654,84 @@
         <v>27</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I17" s="24">
+        <v>127</v>
+      </c>
+      <c r="I17" s="22">
         <v>43731</v>
       </c>
-      <c r="J17" s="24">
+      <c r="J17" s="22">
         <v>43731</v>
       </c>
-      <c r="K17" s="25" t="s">
-        <v>138</v>
+      <c r="K17" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L17" s="11">
         <v>4</v>
       </c>
       <c r="M17" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N17" s="11">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="O17" s="12">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="P17" s="11">
         <v>6</v>
       </c>
       <c r="Q17" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R17" s="11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="S17" s="12">
-        <v>-0.66669999999999996</v>
+        <v>-0.5</v>
       </c>
       <c r="T17" s="11">
         <v>855.64</v>
       </c>
       <c r="U17" s="11">
-        <v>59.87</v>
+        <v>109.49</v>
       </c>
       <c r="V17" s="11">
-        <v>-795.77</v>
+        <v>-746.15</v>
       </c>
       <c r="W17" s="12">
-        <v>-0.93</v>
+        <v>-0.872</v>
       </c>
       <c r="X17" s="11">
         <v>571.64</v>
       </c>
       <c r="Y17" s="11">
-        <v>235.15</v>
+        <v>238.29</v>
       </c>
       <c r="Z17" s="11">
-        <v>-336.49</v>
+        <v>-333.35</v>
       </c>
       <c r="AA17" s="12">
-        <v>-0.58860000000000001</v>
+        <v>-0.58309999999999995</v>
       </c>
       <c r="AB17" s="11">
         <v>0.28599999999999998</v>
       </c>
       <c r="AC17" s="11">
-        <v>0.69679999999999997</v>
+        <v>0.74060000000000004</v>
       </c>
       <c r="AD17" s="11">
-        <v>0.4108</v>
+        <v>0.4546</v>
       </c>
       <c r="AE17" s="12">
-        <v>1.4363999999999999</v>
+        <v>1.5894999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C18" s="10">
         <v>2043</v>
@@ -4384,7 +3740,7 @@
         <v>2043</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F18" s="10">
         <v>88234</v>
@@ -4393,16 +3749,16 @@
         <v>28</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I18" s="24">
+        <v>127</v>
+      </c>
+      <c r="I18" s="22">
         <v>43794</v>
       </c>
-      <c r="J18" s="24">
+      <c r="J18" s="22">
         <v>43794</v>
       </c>
-      <c r="K18" s="25" t="s">
-        <v>138</v>
+      <c r="K18" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L18" s="11">
         <v>1</v>
@@ -4444,33 +3800,33 @@
         <v>22.54</v>
       </c>
       <c r="Y18" s="11">
-        <v>8.39</v>
+        <v>8.4</v>
       </c>
       <c r="Z18" s="11">
-        <v>-14.15</v>
+        <v>-14.14</v>
       </c>
       <c r="AA18" s="12">
-        <v>-0.62780000000000002</v>
+        <v>-0.62729999999999997</v>
       </c>
       <c r="AB18" s="11">
         <v>0.81110000000000004</v>
       </c>
       <c r="AC18" s="11">
-        <v>0.83930000000000005</v>
+        <v>0.84189999999999998</v>
       </c>
       <c r="AD18" s="11">
-        <v>2.8199999999999999E-2</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="AE18" s="12">
-        <v>3.4799999999999998E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C19" s="10">
         <v>2043</v>
@@ -4479,7 +3835,7 @@
         <v>2043</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F19" s="10">
         <v>90177</v>
@@ -4488,16 +3844,16 @@
         <v>29</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I19" s="24">
+        <v>127</v>
+      </c>
+      <c r="I19" s="22">
         <v>43949</v>
       </c>
-      <c r="J19" s="24">
+      <c r="J19" s="22">
         <v>43949</v>
       </c>
-      <c r="K19" s="25" t="s">
-        <v>138</v>
+      <c r="K19" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L19" s="11">
         <v>0</v>
@@ -4539,13 +3895,13 @@
         <v>4.34</v>
       </c>
       <c r="Y19" s="11">
-        <v>10.28</v>
+        <v>10.3</v>
       </c>
       <c r="Z19" s="11">
-        <v>5.94</v>
+        <v>5.96</v>
       </c>
       <c r="AA19" s="12">
-        <v>1.3687</v>
+        <v>1.3733</v>
       </c>
       <c r="AB19" s="11">
         <v>0</v>
@@ -4562,10 +3918,10 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C20" s="10">
         <v>2043</v>
@@ -4574,7 +3930,7 @@
         <v>2043</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F20" s="10">
         <v>90355</v>
@@ -4583,16 +3939,16 @@
         <v>30</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I20" s="24">
+        <v>127</v>
+      </c>
+      <c r="I20" s="22">
         <v>43949</v>
       </c>
-      <c r="J20" s="24">
+      <c r="J20" s="22">
         <v>43949</v>
       </c>
-      <c r="K20" s="25" t="s">
-        <v>138</v>
+      <c r="K20" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L20" s="11">
         <v>9</v>
@@ -4622,25 +3978,25 @@
         <v>328.85</v>
       </c>
       <c r="U20" s="11">
-        <v>199.35</v>
+        <v>199.88</v>
       </c>
       <c r="V20" s="11">
-        <v>-129.5</v>
+        <v>-128.97</v>
       </c>
       <c r="W20" s="12">
-        <v>-0.39379999999999998</v>
+        <v>-0.39219999999999999</v>
       </c>
       <c r="X20" s="11">
         <v>259.25</v>
       </c>
       <c r="Y20" s="11">
-        <v>198.99</v>
+        <v>202.83</v>
       </c>
       <c r="Z20" s="11">
-        <v>-60.26</v>
+        <v>-56.42</v>
       </c>
       <c r="AA20" s="12">
-        <v>-0.2324</v>
+        <v>-0.21759999999999999</v>
       </c>
       <c r="AB20" s="11">
         <v>0.01</v>
@@ -4657,10 +4013,10 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C21" s="10">
         <v>2043</v>
@@ -4669,7 +4025,7 @@
         <v>2043</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F21" s="10">
         <v>94156</v>
@@ -4678,16 +4034,16 @@
         <v>31</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I21" s="24">
+        <v>127</v>
+      </c>
+      <c r="I21" s="22">
         <v>44159</v>
       </c>
-      <c r="J21" s="24">
+      <c r="J21" s="22">
         <v>44159</v>
       </c>
-      <c r="K21" s="25" t="s">
-        <v>138</v>
+      <c r="K21" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L21" s="11">
         <v>0</v>
@@ -4717,10 +4073,10 @@
         <v>0</v>
       </c>
       <c r="U21" s="11">
-        <v>111.32</v>
+        <v>111.57</v>
       </c>
       <c r="V21" s="11">
-        <v>111.32</v>
+        <v>111.57</v>
       </c>
       <c r="W21" s="12">
         <v>1</v>
@@ -4729,33 +4085,33 @@
         <v>7.7</v>
       </c>
       <c r="Y21" s="11">
-        <v>59.82</v>
+        <v>59.85</v>
       </c>
       <c r="Z21" s="11">
-        <v>52.12</v>
+        <v>52.15</v>
       </c>
       <c r="AA21" s="12">
-        <v>6.7687999999999997</v>
+        <v>6.7727000000000004</v>
       </c>
       <c r="AB21" s="11">
         <v>0.20960000000000001</v>
       </c>
       <c r="AC21" s="11">
-        <v>0.77739999999999998</v>
+        <v>0.7792</v>
       </c>
       <c r="AD21" s="11">
-        <v>0.56779999999999997</v>
+        <v>0.5696</v>
       </c>
       <c r="AE21" s="12">
-        <v>2.7090000000000001</v>
+        <v>2.7176</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C22" s="10">
         <v>2043</v>
@@ -4764,7 +4120,7 @@
         <v>2043</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F22" s="10">
         <v>94205</v>
@@ -4773,16 +4129,16 @@
         <v>32</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I22" s="24">
+        <v>127</v>
+      </c>
+      <c r="I22" s="22">
         <v>44116</v>
       </c>
-      <c r="J22" s="24">
+      <c r="J22" s="22">
         <v>44116</v>
       </c>
-      <c r="K22" s="25" t="s">
-        <v>138</v>
+      <c r="K22" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L22" s="11">
         <v>0</v>
@@ -4847,10 +4203,10 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C23" s="10">
         <v>2043</v>
@@ -4859,7 +4215,7 @@
         <v>2043</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F23" s="10">
         <v>95148</v>
@@ -4868,16 +4224,16 @@
         <v>33</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I23" s="24">
+        <v>127</v>
+      </c>
+      <c r="I23" s="22">
         <v>44916</v>
       </c>
-      <c r="J23" s="24">
+      <c r="J23" s="22">
         <v>44916</v>
       </c>
-      <c r="K23" s="25" t="s">
-        <v>138</v>
+      <c r="K23" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L23" s="11">
         <v>1</v>
@@ -4919,13 +4275,13 @@
         <v>5.81</v>
       </c>
       <c r="Y23" s="11">
-        <v>16.309999999999999</v>
+        <v>16.34</v>
       </c>
       <c r="Z23" s="11">
-        <v>10.5</v>
+        <v>10.53</v>
       </c>
       <c r="AA23" s="12">
-        <v>1.8071999999999999</v>
+        <v>1.8124</v>
       </c>
       <c r="AB23" s="11">
         <v>0</v>
@@ -4942,10 +4298,10 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C24" s="10">
         <v>2043</v>
@@ -4954,7 +4310,7 @@
         <v>2043</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F24" s="10">
         <v>98797</v>
@@ -4963,16 +4319,16 @@
         <v>34</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I24" s="24">
+        <v>127</v>
+      </c>
+      <c r="I24" s="22">
         <v>44342</v>
       </c>
-      <c r="J24" s="24">
+      <c r="J24" s="22">
         <v>44342</v>
       </c>
-      <c r="K24" s="25" t="s">
-        <v>138</v>
+      <c r="K24" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L24" s="11">
         <v>0</v>
@@ -5037,10 +4393,10 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C25" s="10">
         <v>2043</v>
@@ -5049,7 +4405,7 @@
         <v>2043</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F25" s="10">
         <v>100323</v>
@@ -5058,16 +4414,16 @@
         <v>35</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="I25" s="24">
+        <v>130</v>
+      </c>
+      <c r="I25" s="22">
         <v>45042</v>
       </c>
-      <c r="J25" s="24">
+      <c r="J25" s="22">
         <v>45042</v>
       </c>
-      <c r="K25" s="25" t="s">
-        <v>141</v>
+      <c r="K25" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="L25" s="11">
         <v>0</v>
@@ -5132,10 +4488,10 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C26" s="10">
         <v>2043</v>
@@ -5144,7 +4500,7 @@
         <v>2043</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F26" s="10">
         <v>100677</v>
@@ -5153,16 +4509,16 @@
         <v>36</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I26" s="24">
+        <v>127</v>
+      </c>
+      <c r="I26" s="22">
         <v>44999</v>
       </c>
-      <c r="J26" s="24">
+      <c r="J26" s="22">
         <v>44999</v>
       </c>
-      <c r="K26" s="25" t="s">
-        <v>141</v>
+      <c r="K26" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="L26" s="11">
         <v>4</v>
@@ -5204,13 +4560,13 @@
         <v>64.19</v>
       </c>
       <c r="Y26" s="11">
-        <v>39.619999999999997</v>
+        <v>42.45</v>
       </c>
       <c r="Z26" s="11">
-        <v>-24.57</v>
+        <v>-21.74</v>
       </c>
       <c r="AA26" s="12">
-        <v>-0.38279999999999997</v>
+        <v>-0.3387</v>
       </c>
       <c r="AB26" s="11">
         <v>0.5141</v>
@@ -5227,10 +4583,10 @@
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C27" s="10">
         <v>2043</v>
@@ -5239,7 +4595,7 @@
         <v>2043</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F27" s="10">
         <v>101640</v>
@@ -5248,16 +4604,16 @@
         <v>37</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I27" s="24">
+        <v>127</v>
+      </c>
+      <c r="I27" s="22">
         <v>45104</v>
       </c>
-      <c r="J27" s="24">
+      <c r="J27" s="22">
         <v>45104</v>
       </c>
-      <c r="K27" s="25" t="s">
-        <v>141</v>
+      <c r="K27" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="L27" s="11">
         <v>2</v>
@@ -5299,13 +4655,13 @@
         <v>23.02</v>
       </c>
       <c r="Y27" s="11">
-        <v>13.36</v>
+        <v>17.43</v>
       </c>
       <c r="Z27" s="11">
-        <v>-9.66</v>
+        <v>-5.59</v>
       </c>
       <c r="AA27" s="12">
-        <v>-0.41959999999999997</v>
+        <v>-0.24279999999999999</v>
       </c>
       <c r="AB27" s="11">
         <v>0</v>
@@ -5322,10 +4678,10 @@
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C28" s="10">
         <v>2043</v>
@@ -5334,7 +4690,7 @@
         <v>2043</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F28" s="10">
         <v>102825</v>
@@ -5343,16 +4699,16 @@
         <v>38</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I28" s="24">
+        <v>127</v>
+      </c>
+      <c r="I28" s="22">
         <v>45117</v>
       </c>
-      <c r="J28" s="24">
+      <c r="J28" s="22">
         <v>45139</v>
       </c>
-      <c r="K28" s="25" t="s">
-        <v>141</v>
+      <c r="K28" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="L28" s="11">
         <v>0</v>
@@ -5394,13 +4750,13 @@
         <v>1.54</v>
       </c>
       <c r="Y28" s="11">
-        <v>9.69</v>
+        <v>9.73</v>
       </c>
       <c r="Z28" s="11">
-        <v>8.15</v>
+        <v>8.19</v>
       </c>
       <c r="AA28" s="12">
-        <v>5.2922000000000002</v>
+        <v>5.3182</v>
       </c>
       <c r="AB28" s="11">
         <v>0</v>
@@ -5417,10 +4773,10 @@
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C29" s="10">
         <v>2043</v>
@@ -5429,7 +4785,7 @@
         <v>2043</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F29" s="10">
         <v>104343</v>
@@ -5438,16 +4794,16 @@
         <v>39</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I29" s="24">
+        <v>127</v>
+      </c>
+      <c r="I29" s="22">
         <v>45201</v>
       </c>
-      <c r="J29" s="24">
+      <c r="J29" s="22">
         <v>45201</v>
       </c>
-      <c r="K29" s="25" t="s">
-        <v>141</v>
+      <c r="K29" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="L29" s="11">
         <v>3</v>
@@ -5489,33 +4845,33 @@
         <v>94.31</v>
       </c>
       <c r="Y29" s="11">
-        <v>22.44</v>
+        <v>24.18</v>
       </c>
       <c r="Z29" s="11">
-        <v>-71.87</v>
+        <v>-70.13</v>
       </c>
       <c r="AA29" s="12">
-        <v>-0.7621</v>
+        <v>-0.74360000000000004</v>
       </c>
       <c r="AB29" s="11">
         <v>0.15720000000000001</v>
       </c>
       <c r="AC29" s="11">
-        <v>0.67920000000000003</v>
+        <v>1.5749</v>
       </c>
       <c r="AD29" s="11">
-        <v>0.52200000000000002</v>
+        <v>1.4177</v>
       </c>
       <c r="AE29" s="12">
-        <v>3.3206000000000002</v>
+        <v>9.0183999999999997</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C30" s="10">
         <v>2043</v>
@@ -5524,7 +4880,7 @@
         <v>2692</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F30" s="10">
         <v>104718</v>
@@ -5533,16 +4889,16 @@
         <v>40</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I30" s="24">
+        <v>127</v>
+      </c>
+      <c r="I30" s="22">
         <v>45264</v>
       </c>
-      <c r="J30" s="24">
+      <c r="J30" s="22">
         <v>45264</v>
       </c>
-      <c r="K30" s="25" t="s">
-        <v>141</v>
+      <c r="K30" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="L30" s="11">
         <v>4</v>
@@ -5572,45 +4928,45 @@
         <v>107.55</v>
       </c>
       <c r="U30" s="11">
-        <v>85.96</v>
+        <v>86.32</v>
       </c>
       <c r="V30" s="11">
-        <v>-21.59</v>
+        <v>-21.23</v>
       </c>
       <c r="W30" s="12">
-        <v>-0.20069999999999999</v>
+        <v>-0.19739999999999999</v>
       </c>
       <c r="X30" s="11">
         <v>109.35</v>
       </c>
       <c r="Y30" s="11">
-        <v>61.1</v>
+        <v>67.709999999999994</v>
       </c>
       <c r="Z30" s="11">
-        <v>-48.25</v>
+        <v>-41.64</v>
       </c>
       <c r="AA30" s="12">
-        <v>-0.44119999999999998</v>
+        <v>-0.38080000000000003</v>
       </c>
       <c r="AB30" s="11">
         <v>3.8600000000000002E-2</v>
       </c>
       <c r="AC30" s="11">
-        <v>0.34399999999999997</v>
+        <v>0.56420000000000003</v>
       </c>
       <c r="AD30" s="11">
-        <v>0.3054</v>
+        <v>0.52559999999999996</v>
       </c>
       <c r="AE30" s="12">
-        <v>7.9119000000000002</v>
+        <v>13.6166</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C31" s="10">
         <v>2043</v>
@@ -5619,7 +4975,7 @@
         <v>2692</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F31" s="10">
         <v>104750</v>
@@ -5628,16 +4984,16 @@
         <v>41</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I31" s="24">
+        <v>127</v>
+      </c>
+      <c r="I31" s="22">
         <v>45236</v>
       </c>
-      <c r="J31" s="24">
+      <c r="J31" s="22">
         <v>45236</v>
       </c>
-      <c r="K31" s="25" t="s">
-        <v>141</v>
+      <c r="K31" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="L31" s="11">
         <v>3</v>
@@ -5655,57 +5011,57 @@
         <v>3</v>
       </c>
       <c r="Q31" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R31" s="11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="12">
-        <v>-0.33329999999999999</v>
+        <v>0</v>
       </c>
       <c r="T31" s="11">
         <v>121.6</v>
       </c>
       <c r="U31" s="11">
-        <v>43.87</v>
+        <v>44.05</v>
       </c>
       <c r="V31" s="11">
-        <v>-77.73</v>
+        <v>-77.55</v>
       </c>
       <c r="W31" s="12">
-        <v>-0.63919999999999999</v>
+        <v>-0.63770000000000004</v>
       </c>
       <c r="X31" s="11">
         <v>121.85</v>
       </c>
       <c r="Y31" s="11">
-        <v>43.63</v>
+        <v>49.24</v>
       </c>
       <c r="Z31" s="11">
-        <v>-78.22</v>
+        <v>-72.61</v>
       </c>
       <c r="AA31" s="12">
-        <v>-0.64190000000000003</v>
+        <v>-0.59589999999999999</v>
       </c>
       <c r="AB31" s="11">
         <v>0.35880000000000001</v>
       </c>
       <c r="AC31" s="11">
-        <v>0.72170000000000001</v>
+        <v>0.72289999999999999</v>
       </c>
       <c r="AD31" s="11">
-        <v>0.3629</v>
+        <v>0.36409999999999998</v>
       </c>
       <c r="AE31" s="12">
-        <v>1.0114000000000001</v>
+        <v>1.0147999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C32" s="10">
         <v>2043</v>
@@ -5714,7 +5070,7 @@
         <v>2043</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F32" s="10">
         <v>105696</v>
@@ -5723,16 +5079,16 @@
         <v>42</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I32" s="24">
+        <v>127</v>
+      </c>
+      <c r="I32" s="22">
         <v>45279</v>
       </c>
-      <c r="J32" s="24">
+      <c r="J32" s="22">
         <v>45279</v>
       </c>
-      <c r="K32" s="25" t="s">
-        <v>141</v>
+      <c r="K32" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="L32" s="11">
         <v>0</v>
@@ -5774,22 +5130,22 @@
         <v>20.77</v>
       </c>
       <c r="Y32" s="11">
-        <v>22.52</v>
+        <v>24.37</v>
       </c>
       <c r="Z32" s="11">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA32" s="12">
-        <v>8.43E-2</v>
+        <v>0.17330000000000001</v>
       </c>
       <c r="AB32" s="11">
         <v>0</v>
       </c>
       <c r="AC32" s="11">
-        <v>0.57909999999999995</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="AD32" s="11">
-        <v>0.57909999999999995</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="AE32" s="12">
         <v>1</v>
@@ -5797,10 +5153,10 @@
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C33" s="10">
         <v>2043</v>
@@ -5809,7 +5165,7 @@
         <v>2043</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F33" s="10">
         <v>106018</v>
@@ -5818,16 +5174,16 @@
         <v>43</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I33" s="24">
+        <v>127</v>
+      </c>
+      <c r="I33" s="22">
         <v>45344</v>
       </c>
-      <c r="J33" s="24">
+      <c r="J33" s="22">
         <v>45344</v>
       </c>
-      <c r="K33" s="25" t="s">
-        <v>137</v>
+      <c r="K33" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L33" s="11">
         <v>1</v>
@@ -5869,13 +5225,13 @@
         <v>54.74</v>
       </c>
       <c r="Y33" s="11">
-        <v>19.68</v>
+        <v>19.7</v>
       </c>
       <c r="Z33" s="11">
-        <v>-35.06</v>
+        <v>-35.04</v>
       </c>
       <c r="AA33" s="12">
-        <v>-0.64049999999999996</v>
+        <v>-0.6401</v>
       </c>
       <c r="AB33" s="11">
         <v>3.1772999999999998</v>
@@ -5892,10 +5248,10 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C34" s="10">
         <v>2043</v>
@@ -5904,7 +5260,7 @@
         <v>2043</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F34" s="10">
         <v>107488</v>
@@ -5913,16 +5269,16 @@
         <v>44</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I34" s="24">
+        <v>127</v>
+      </c>
+      <c r="I34" s="22">
         <v>45440</v>
       </c>
-      <c r="J34" s="24">
+      <c r="J34" s="22">
         <v>45440</v>
       </c>
-      <c r="K34" s="25" t="s">
-        <v>137</v>
+      <c r="K34" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L34" s="11">
         <v>4</v>
@@ -5952,25 +5308,25 @@
         <v>191.52</v>
       </c>
       <c r="U34" s="11">
-        <v>-599.82000000000005</v>
+        <v>-1319.02</v>
       </c>
       <c r="V34" s="11">
-        <v>-791.34</v>
+        <v>-1510.54</v>
       </c>
       <c r="W34" s="12">
-        <v>-4.1318999999999999</v>
+        <v>-7.8871000000000002</v>
       </c>
       <c r="X34" s="11">
         <v>25.02</v>
       </c>
       <c r="Y34" s="11">
-        <v>66.08</v>
+        <v>66.02</v>
       </c>
       <c r="Z34" s="11">
-        <v>41.06</v>
+        <v>41</v>
       </c>
       <c r="AA34" s="12">
-        <v>1.6411</v>
+        <v>1.6387</v>
       </c>
       <c r="AB34" s="11">
         <v>0</v>
@@ -5987,10 +5343,10 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C35" s="10">
         <v>2043</v>
@@ -5999,7 +5355,7 @@
         <v>2692</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F35" s="10">
         <v>107660</v>
@@ -6008,16 +5364,16 @@
         <v>45</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="I35" s="24">
+        <v>130</v>
+      </c>
+      <c r="I35" s="22">
         <v>45471</v>
       </c>
-      <c r="J35" s="24">
+      <c r="J35" s="22">
         <v>45471</v>
       </c>
-      <c r="K35" s="25" t="s">
-        <v>137</v>
+      <c r="K35" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L35" s="11">
         <v>0</v>
@@ -6082,10 +5438,10 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C36" s="10">
         <v>2043</v>
@@ -6094,7 +5450,7 @@
         <v>2692</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F36" s="10">
         <v>108404</v>
@@ -6103,16 +5459,16 @@
         <v>46</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I36" s="24">
+        <v>127</v>
+      </c>
+      <c r="I36" s="22">
         <v>45467</v>
       </c>
-      <c r="J36" s="24">
+      <c r="J36" s="22">
         <v>45467</v>
       </c>
-      <c r="K36" s="25" t="s">
-        <v>137</v>
+      <c r="K36" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L36" s="11">
         <v>6</v>
@@ -6142,45 +5498,45 @@
         <v>203.63</v>
       </c>
       <c r="U36" s="11">
-        <v>36.78</v>
+        <v>36.93</v>
       </c>
       <c r="V36" s="11">
-        <v>-166.85</v>
+        <v>-166.7</v>
       </c>
       <c r="W36" s="12">
-        <v>-0.81940000000000002</v>
+        <v>-0.81859999999999999</v>
       </c>
       <c r="X36" s="11">
         <v>250.75</v>
       </c>
       <c r="Y36" s="11">
-        <v>57.18</v>
+        <v>59.09</v>
       </c>
       <c r="Z36" s="11">
-        <v>-193.57</v>
+        <v>-191.66</v>
       </c>
       <c r="AA36" s="12">
-        <v>-0.77200000000000002</v>
+        <v>-0.76429999999999998</v>
       </c>
       <c r="AB36" s="11">
         <v>2.6915</v>
       </c>
       <c r="AC36" s="11">
-        <v>1.3966000000000001</v>
+        <v>2.7980999999999998</v>
       </c>
       <c r="AD36" s="11">
-        <v>-1.2948999999999999</v>
+        <v>0.1066</v>
       </c>
       <c r="AE36" s="12">
-        <v>-0.48110000000000003</v>
+        <v>3.9600000000000003E-2</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C37" s="10">
         <v>2043</v>
@@ -6189,7 +5545,7 @@
         <v>2692</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F37" s="10">
         <v>108405</v>
@@ -6198,16 +5554,16 @@
         <v>47</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I37" s="24">
+        <v>127</v>
+      </c>
+      <c r="I37" s="22">
         <v>45471</v>
       </c>
-      <c r="J37" s="24">
+      <c r="J37" s="22">
         <v>45471</v>
       </c>
-      <c r="K37" s="25" t="s">
-        <v>137</v>
+      <c r="K37" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L37" s="11">
         <v>4</v>
@@ -6249,13 +5605,13 @@
         <v>53.59</v>
       </c>
       <c r="Y37" s="11">
-        <v>110.71</v>
+        <v>112.26</v>
       </c>
       <c r="Z37" s="11">
-        <v>57.12</v>
+        <v>58.67</v>
       </c>
       <c r="AA37" s="12">
-        <v>1.0659000000000001</v>
+        <v>1.0948</v>
       </c>
       <c r="AB37" s="11">
         <v>0</v>
@@ -6272,10 +5628,10 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C38" s="10">
         <v>2043</v>
@@ -6284,7 +5640,7 @@
         <v>2043</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F38" s="10">
         <v>108658</v>
@@ -6293,16 +5649,16 @@
         <v>48</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I38" s="24">
+        <v>127</v>
+      </c>
+      <c r="I38" s="22">
         <v>45497</v>
       </c>
-      <c r="J38" s="24">
+      <c r="J38" s="22">
         <v>45497</v>
       </c>
-      <c r="K38" s="25" t="s">
-        <v>137</v>
+      <c r="K38" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L38" s="11">
         <v>0</v>
@@ -6344,13 +5700,13 @@
         <v>42.18</v>
       </c>
       <c r="Y38" s="11">
-        <v>7.28</v>
+        <v>8.83</v>
       </c>
       <c r="Z38" s="11">
-        <v>-34.9</v>
+        <v>-33.35</v>
       </c>
       <c r="AA38" s="12">
-        <v>-0.82740000000000002</v>
+        <v>-0.79069999999999996</v>
       </c>
       <c r="AB38" s="11">
         <v>8.9999999999999998E-4</v>
@@ -6367,10 +5723,10 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C39" s="10">
         <v>2043</v>
@@ -6379,7 +5735,7 @@
         <v>2692</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F39" s="10">
         <v>108920</v>
@@ -6388,16 +5744,16 @@
         <v>49</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="I39" s="24">
+        <v>130</v>
+      </c>
+      <c r="I39" s="22">
         <v>45526</v>
       </c>
-      <c r="J39" s="24">
+      <c r="J39" s="22">
         <v>45526</v>
       </c>
-      <c r="K39" s="25" t="s">
-        <v>137</v>
+      <c r="K39" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L39" s="11">
         <v>3</v>
@@ -6462,10 +5818,10 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C40" s="10">
         <v>2043</v>
@@ -6474,7 +5830,7 @@
         <v>2043</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F40" s="10">
         <v>109007</v>
@@ -6483,16 +5839,16 @@
         <v>50</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I40" s="24">
+        <v>127</v>
+      </c>
+      <c r="I40" s="22">
         <v>45525</v>
       </c>
-      <c r="J40" s="24">
+      <c r="J40" s="22">
         <v>45525</v>
       </c>
-      <c r="K40" s="25" t="s">
-        <v>137</v>
+      <c r="K40" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L40" s="11">
         <v>1</v>
@@ -6534,13 +5890,13 @@
         <v>18.02</v>
       </c>
       <c r="Y40" s="11">
-        <v>15.93</v>
+        <v>15.96</v>
       </c>
       <c r="Z40" s="11">
-        <v>-2.09</v>
+        <v>-2.06</v>
       </c>
       <c r="AA40" s="12">
-        <v>-0.11600000000000001</v>
+        <v>-0.1143</v>
       </c>
       <c r="AB40" s="11">
         <v>0</v>
@@ -6557,10 +5913,10 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C41" s="10">
         <v>2043</v>
@@ -6569,7 +5925,7 @@
         <v>2043</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F41" s="10">
         <v>109141</v>
@@ -6578,16 +5934,16 @@
         <v>51</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I41" s="24">
+        <v>129</v>
+      </c>
+      <c r="I41" s="22">
         <v>45453</v>
       </c>
-      <c r="J41" s="24">
+      <c r="J41" s="22">
         <v>45474</v>
       </c>
-      <c r="K41" s="25" t="s">
-        <v>138</v>
+      <c r="K41" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L41" s="11">
         <v>0</v>
@@ -6652,10 +6008,10 @@
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C42" s="10">
         <v>2043</v>
@@ -6664,7 +6020,7 @@
         <v>2856</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F42" s="10">
         <v>109819</v>
@@ -6673,16 +6029,16 @@
         <v>52</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I42" s="24">
+        <v>127</v>
+      </c>
+      <c r="I42" s="22">
         <v>45562</v>
       </c>
-      <c r="J42" s="24">
+      <c r="J42" s="22">
         <v>45562</v>
       </c>
-      <c r="K42" s="25" t="s">
-        <v>137</v>
+      <c r="K42" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L42" s="11">
         <v>0</v>
@@ -6747,10 +6103,10 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C43" s="10">
         <v>2043</v>
@@ -6759,7 +6115,7 @@
         <v>2043</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F43" s="10">
         <v>109998</v>
@@ -6768,28 +6124,28 @@
         <v>53</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I43" s="24">
+        <v>127</v>
+      </c>
+      <c r="I43" s="22">
         <v>45596</v>
       </c>
-      <c r="J43" s="24">
+      <c r="J43" s="22">
         <v>45596</v>
       </c>
-      <c r="K43" s="25" t="s">
-        <v>137</v>
+      <c r="K43" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L43" s="11">
         <v>3</v>
       </c>
       <c r="M43" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" s="11">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="O43" s="12">
-        <v>-1</v>
+        <v>-0.66669999999999996</v>
       </c>
       <c r="P43" s="11">
         <v>2</v>
@@ -6807,34 +6163,34 @@
         <v>-3.19</v>
       </c>
       <c r="U43" s="11">
-        <v>0</v>
+        <v>28.7</v>
       </c>
       <c r="V43" s="11">
-        <v>3.19</v>
+        <v>31.89</v>
       </c>
       <c r="W43" s="12">
-        <v>1</v>
+        <v>9.9969000000000001</v>
       </c>
       <c r="X43" s="11">
         <v>52.34</v>
       </c>
       <c r="Y43" s="11">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="Z43" s="11">
-        <v>-46.67</v>
+        <v>-46.66</v>
       </c>
       <c r="AA43" s="12">
-        <v>-0.89170000000000005</v>
+        <v>-0.89149999999999996</v>
       </c>
       <c r="AB43" s="11">
         <v>0</v>
       </c>
       <c r="AC43" s="11">
-        <v>0.13519999999999999</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="AD43" s="11">
-        <v>0.13519999999999999</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="AE43" s="12">
         <v>1</v>
@@ -6842,10 +6198,10 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C44" s="10">
         <v>2043</v>
@@ -6854,7 +6210,7 @@
         <v>2043</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F44" s="10">
         <v>110105</v>
@@ -6863,16 +6219,16 @@
         <v>54</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I44" s="24">
+        <v>127</v>
+      </c>
+      <c r="I44" s="22">
         <v>45560</v>
       </c>
-      <c r="J44" s="24">
+      <c r="J44" s="22">
         <v>45560</v>
       </c>
-      <c r="K44" s="25" t="s">
-        <v>137</v>
+      <c r="K44" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L44" s="11">
         <v>1</v>
@@ -6914,13 +6270,13 @@
         <v>34.43</v>
       </c>
       <c r="Y44" s="11">
-        <v>17.64</v>
+        <v>17.68</v>
       </c>
       <c r="Z44" s="11">
-        <v>-16.79</v>
+        <v>-16.75</v>
       </c>
       <c r="AA44" s="12">
-        <v>-0.48770000000000002</v>
+        <v>-0.48649999999999999</v>
       </c>
       <c r="AB44" s="11">
         <v>0</v>
@@ -6937,10 +6293,10 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C45" s="10">
         <v>2043</v>
@@ -6949,7 +6305,7 @@
         <v>2856</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F45" s="10">
         <v>110453</v>
@@ -6958,16 +6314,16 @@
         <v>55</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I45" s="24">
+        <v>127</v>
+      </c>
+      <c r="I45" s="22">
         <v>45600</v>
       </c>
-      <c r="J45" s="24">
+      <c r="J45" s="22">
         <v>45600</v>
       </c>
-      <c r="K45" s="25" t="s">
-        <v>137</v>
+      <c r="K45" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L45" s="11">
         <v>9</v>
@@ -6985,37 +6341,37 @@
         <v>9</v>
       </c>
       <c r="Q45" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R45" s="11">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="S45" s="12">
-        <v>-0.55559999999999998</v>
+        <v>-0.44440000000000002</v>
       </c>
       <c r="T45" s="11">
         <v>219.18</v>
       </c>
       <c r="U45" s="11">
-        <v>180.97</v>
+        <v>181.35</v>
       </c>
       <c r="V45" s="11">
-        <v>-38.21</v>
+        <v>-37.83</v>
       </c>
       <c r="W45" s="12">
-        <v>-0.17430000000000001</v>
+        <v>-0.1726</v>
       </c>
       <c r="X45" s="11">
         <v>129.72</v>
       </c>
       <c r="Y45" s="11">
-        <v>87.06</v>
+        <v>89.24</v>
       </c>
       <c r="Z45" s="11">
-        <v>-42.66</v>
+        <v>-40.479999999999997</v>
       </c>
       <c r="AA45" s="12">
-        <v>-0.32890000000000003</v>
+        <v>-0.31209999999999999</v>
       </c>
       <c r="AB45" s="11">
         <v>0.2029</v>
@@ -7032,10 +6388,10 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C46" s="10">
         <v>2043</v>
@@ -7044,7 +6400,7 @@
         <v>2692</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F46" s="10">
         <v>110575</v>
@@ -7053,16 +6409,16 @@
         <v>56</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I46" s="24">
+        <v>127</v>
+      </c>
+      <c r="I46" s="22">
         <v>45583</v>
       </c>
-      <c r="J46" s="24">
+      <c r="J46" s="22">
         <v>45583</v>
       </c>
-      <c r="K46" s="25" t="s">
-        <v>137</v>
+      <c r="K46" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L46" s="11">
         <v>1</v>
@@ -7104,13 +6460,13 @@
         <v>140.16</v>
       </c>
       <c r="Y46" s="11">
-        <v>28.44</v>
+        <v>28.49</v>
       </c>
       <c r="Z46" s="11">
-        <v>-111.72</v>
+        <v>-111.67</v>
       </c>
       <c r="AA46" s="12">
-        <v>-0.79710000000000003</v>
+        <v>-0.79669999999999996</v>
       </c>
       <c r="AB46" s="11">
         <v>0</v>
@@ -7127,10 +6483,10 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C47" s="10">
         <v>2043</v>
@@ -7139,7 +6495,7 @@
         <v>2043</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F47" s="10">
         <v>110740</v>
@@ -7148,16 +6504,16 @@
         <v>57</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I47" s="24">
+        <v>129</v>
+      </c>
+      <c r="I47" s="22">
         <v>45616</v>
       </c>
-      <c r="J47" s="24">
+      <c r="J47" s="22">
         <v>45616</v>
       </c>
-      <c r="K47" s="25" t="s">
-        <v>137</v>
+      <c r="K47" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L47" s="11">
         <v>0</v>
@@ -7222,10 +6578,10 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C48" s="10">
         <v>2043</v>
@@ -7234,7 +6590,7 @@
         <v>2692</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F48" s="10">
         <v>111056</v>
@@ -7243,16 +6599,16 @@
         <v>58</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I48" s="24">
+        <v>127</v>
+      </c>
+      <c r="I48" s="22">
         <v>45639</v>
       </c>
-      <c r="J48" s="24">
+      <c r="J48" s="22">
         <v>45639</v>
       </c>
-      <c r="K48" s="25" t="s">
-        <v>137</v>
+      <c r="K48" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="L48" s="11">
         <v>2</v>
@@ -7294,13 +6650,13 @@
         <v>16.75</v>
       </c>
       <c r="Y48" s="11">
-        <v>22.96</v>
+        <v>23.01</v>
       </c>
       <c r="Z48" s="11">
-        <v>6.21</v>
+        <v>6.26</v>
       </c>
       <c r="AA48" s="12">
-        <v>0.37069999999999997</v>
+        <v>0.37369999999999998</v>
       </c>
       <c r="AB48" s="11">
         <v>0</v>
@@ -7317,10 +6673,10 @@
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C49" s="10">
         <v>2043</v>
@@ -7329,7 +6685,7 @@
         <v>2856</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F49" s="10">
         <v>111960</v>
@@ -7338,16 +6694,16 @@
         <v>59</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I49" s="24">
+        <v>127</v>
+      </c>
+      <c r="I49" s="22">
         <v>45707</v>
       </c>
-      <c r="J49" s="24">
+      <c r="J49" s="22">
         <v>45707</v>
       </c>
-      <c r="K49" s="25" t="s">
-        <v>142</v>
+      <c r="K49" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L49" s="11">
         <v>3</v>
@@ -7389,13 +6745,13 @@
         <v>141.97</v>
       </c>
       <c r="Y49" s="11">
-        <v>13.49</v>
+        <v>13.5</v>
       </c>
       <c r="Z49" s="11">
-        <v>-128.47999999999999</v>
+        <v>-128.47</v>
       </c>
       <c r="AA49" s="12">
-        <v>-0.90500000000000003</v>
+        <v>-0.90490000000000004</v>
       </c>
       <c r="AB49" s="11">
         <v>0</v>
@@ -7412,10 +6768,10 @@
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C50" s="10">
         <v>2043</v>
@@ -7424,7 +6780,7 @@
         <v>2043</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F50" s="10">
         <v>112083</v>
@@ -7433,16 +6789,16 @@
         <v>60</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I50" s="24">
+        <v>127</v>
+      </c>
+      <c r="I50" s="22">
         <v>45736</v>
       </c>
-      <c r="J50" s="24">
+      <c r="J50" s="22">
         <v>45736</v>
       </c>
-      <c r="K50" s="25" t="s">
-        <v>142</v>
+      <c r="K50" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L50" s="11">
         <v>2</v>
@@ -7507,10 +6863,10 @@
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C51" s="10">
         <v>2043</v>
@@ -7519,7 +6875,7 @@
         <v>2692</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F51" s="10">
         <v>112192</v>
@@ -7528,16 +6884,16 @@
         <v>61</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I51" s="24">
+        <v>129</v>
+      </c>
+      <c r="I51" s="22">
         <v>45660</v>
       </c>
-      <c r="J51" s="24">
+      <c r="J51" s="22">
         <v>45691</v>
       </c>
-      <c r="K51" s="25" t="s">
-        <v>138</v>
+      <c r="K51" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L51" s="11">
         <v>1</v>
@@ -7602,10 +6958,10 @@
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C52" s="10">
         <v>2043</v>
@@ -7614,7 +6970,7 @@
         <v>2856</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F52" s="10">
         <v>112522</v>
@@ -7623,16 +6979,16 @@
         <v>62</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I52" s="24">
+        <v>127</v>
+      </c>
+      <c r="I52" s="22">
         <v>45776</v>
       </c>
-      <c r="J52" s="24">
+      <c r="J52" s="22">
         <v>45776</v>
       </c>
-      <c r="K52" s="25" t="s">
-        <v>142</v>
+      <c r="K52" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L52" s="11">
         <v>0</v>
@@ -7674,10 +7030,10 @@
         <v>0</v>
       </c>
       <c r="Y52" s="11">
-        <v>13.28</v>
+        <v>13.31</v>
       </c>
       <c r="Z52" s="11">
-        <v>13.28</v>
+        <v>13.31</v>
       </c>
       <c r="AA52" s="12">
         <v>1</v>
@@ -7697,10 +7053,10 @@
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C53" s="10">
         <v>2043</v>
@@ -7709,7 +7065,7 @@
         <v>2043</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F53" s="10">
         <v>113076</v>
@@ -7718,16 +7074,16 @@
         <v>63</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I53" s="24">
+        <v>127</v>
+      </c>
+      <c r="I53" s="22">
         <v>45806</v>
       </c>
-      <c r="J53" s="24">
+      <c r="J53" s="22">
         <v>45806</v>
       </c>
-      <c r="K53" s="25" t="s">
-        <v>142</v>
+      <c r="K53" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L53" s="11">
         <v>0</v>
@@ -7769,10 +7125,10 @@
         <v>0</v>
       </c>
       <c r="Y53" s="11">
-        <v>8.82</v>
+        <v>13.16</v>
       </c>
       <c r="Z53" s="11">
-        <v>8.82</v>
+        <v>13.16</v>
       </c>
       <c r="AA53" s="12">
         <v>1</v>
@@ -7792,10 +7148,10 @@
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C54" s="10">
         <v>2043</v>
@@ -7804,7 +7160,7 @@
         <v>2692</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F54" s="10">
         <v>113450</v>
@@ -7813,16 +7169,16 @@
         <v>64</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I54" s="24">
+        <v>127</v>
+      </c>
+      <c r="I54" s="22">
         <v>45852</v>
       </c>
-      <c r="J54" s="24">
+      <c r="J54" s="22">
         <v>45852</v>
       </c>
-      <c r="K54" s="25" t="s">
-        <v>142</v>
+      <c r="K54" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L54" s="11">
         <v>0</v>
@@ -7864,10 +7220,10 @@
         <v>0</v>
       </c>
       <c r="Y54" s="11">
-        <v>61.13</v>
+        <v>84.11</v>
       </c>
       <c r="Z54" s="11">
-        <v>61.13</v>
+        <v>84.11</v>
       </c>
       <c r="AA54" s="12">
         <v>1</v>
@@ -7887,10 +7243,10 @@
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C55" s="10">
         <v>2043</v>
@@ -7899,7 +7255,7 @@
         <v>2856</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F55" s="10">
         <v>114100</v>
@@ -7908,16 +7264,16 @@
         <v>65</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I55" s="24">
+        <v>127</v>
+      </c>
+      <c r="I55" s="22">
         <v>45863</v>
       </c>
-      <c r="J55" s="24">
+      <c r="J55" s="22">
         <v>45863</v>
       </c>
-      <c r="K55" s="25" t="s">
-        <v>142</v>
+      <c r="K55" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L55" s="11">
         <v>0</v>
@@ -7959,10 +7315,10 @@
         <v>0</v>
       </c>
       <c r="Y55" s="11">
-        <v>37.06</v>
+        <v>37.08</v>
       </c>
       <c r="Z55" s="11">
-        <v>37.06</v>
+        <v>37.08</v>
       </c>
       <c r="AA55" s="12">
         <v>1</v>
@@ -7982,10 +7338,10 @@
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C56" s="10">
         <v>2043</v>
@@ -7994,7 +7350,7 @@
         <v>2692</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F56" s="10">
         <v>114157</v>
@@ -8003,16 +7359,16 @@
         <v>66</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I56" s="24">
+        <v>127</v>
+      </c>
+      <c r="I56" s="22">
         <v>45904</v>
       </c>
-      <c r="J56" s="24">
+      <c r="J56" s="22">
         <v>45904</v>
       </c>
-      <c r="K56" s="25" t="s">
-        <v>142</v>
+      <c r="K56" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L56" s="11">
         <v>0</v>
@@ -8054,10 +7410,10 @@
         <v>0</v>
       </c>
       <c r="Y56" s="11">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="Z56" s="11">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="AA56" s="12">
         <v>1</v>
@@ -8077,10 +7433,10 @@
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C57" s="10">
         <v>2043</v>
@@ -8089,7 +7445,7 @@
         <v>2692</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F57" s="10">
         <v>114431</v>
@@ -8098,16 +7454,16 @@
         <v>67</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I57" s="24">
+        <v>127</v>
+      </c>
+      <c r="I57" s="22">
         <v>45930</v>
       </c>
-      <c r="J57" s="24">
+      <c r="J57" s="22">
         <v>45930</v>
       </c>
-      <c r="K57" s="25" t="s">
-        <v>142</v>
+      <c r="K57" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L57" s="11">
         <v>0</v>
@@ -8149,10 +7505,10 @@
         <v>0</v>
       </c>
       <c r="Y57" s="11">
-        <v>17.16</v>
+        <v>18.93</v>
       </c>
       <c r="Z57" s="11">
-        <v>17.16</v>
+        <v>18.93</v>
       </c>
       <c r="AA57" s="12">
         <v>1</v>
@@ -8172,10 +7528,10 @@
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C58" s="10">
         <v>2043</v>
@@ -8184,7 +7540,7 @@
         <v>2692</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F58" s="10">
         <v>114664</v>
@@ -8193,16 +7549,16 @@
         <v>68</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I58" s="24">
+        <v>129</v>
+      </c>
+      <c r="I58" s="22">
         <v>45950</v>
       </c>
-      <c r="J58" s="24">
+      <c r="J58" s="22">
         <v>45950</v>
       </c>
-      <c r="K58" s="25" t="s">
-        <v>142</v>
+      <c r="K58" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L58" s="11">
         <v>0</v>
@@ -8267,10 +7623,10 @@
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A59" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C59" s="10">
         <v>2043</v>
@@ -8279,7 +7635,7 @@
         <v>2856</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F59" s="10">
         <v>115047</v>
@@ -8288,16 +7644,16 @@
         <v>69</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I59" s="24">
+        <v>127</v>
+      </c>
+      <c r="I59" s="22">
         <v>45944</v>
       </c>
-      <c r="J59" s="24">
+      <c r="J59" s="22">
         <v>45944</v>
       </c>
-      <c r="K59" s="25" t="s">
-        <v>142</v>
+      <c r="K59" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L59" s="11">
         <v>0</v>
@@ -8339,10 +7695,10 @@
         <v>0</v>
       </c>
       <c r="Y59" s="11">
-        <v>90.72</v>
+        <v>90.8</v>
       </c>
       <c r="Z59" s="11">
-        <v>90.72</v>
+        <v>90.8</v>
       </c>
       <c r="AA59" s="12">
         <v>1</v>
@@ -8351,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="AC59" s="11">
-        <v>0.23180000000000001</v>
+        <v>0.46429999999999999</v>
       </c>
       <c r="AD59" s="11">
-        <v>0.23180000000000001</v>
+        <v>0.46429999999999999</v>
       </c>
       <c r="AE59" s="12">
         <v>1</v>
@@ -8362,10 +7718,10 @@
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A60" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C60" s="10">
         <v>2043</v>
@@ -8374,7 +7730,7 @@
         <v>2043</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F60" s="10">
         <v>115404</v>
@@ -8383,16 +7739,16 @@
         <v>70</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I60" s="24">
+        <v>127</v>
+      </c>
+      <c r="I60" s="22">
         <v>45986</v>
       </c>
-      <c r="J60" s="24">
+      <c r="J60" s="22">
         <v>45986</v>
       </c>
-      <c r="K60" s="25" t="s">
-        <v>142</v>
+      <c r="K60" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L60" s="11">
         <v>0</v>
@@ -8422,10 +7778,10 @@
         <v>0</v>
       </c>
       <c r="U60" s="11">
-        <v>29.75</v>
+        <v>29.87</v>
       </c>
       <c r="V60" s="11">
-        <v>29.75</v>
+        <v>29.87</v>
       </c>
       <c r="W60" s="12">
         <v>1</v>
@@ -8434,10 +7790,10 @@
         <v>0</v>
       </c>
       <c r="Y60" s="11">
-        <v>17.239999999999998</v>
+        <v>19.03</v>
       </c>
       <c r="Z60" s="11">
-        <v>17.239999999999998</v>
+        <v>19.03</v>
       </c>
       <c r="AA60" s="12">
         <v>1</v>
@@ -8457,10 +7813,10 @@
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A61" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C61" s="10">
         <v>2043</v>
@@ -8469,7 +7825,7 @@
         <v>2856</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F61" s="10">
         <v>116060</v>
@@ -8478,16 +7834,16 @@
         <v>71</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I61" s="24">
+        <v>127</v>
+      </c>
+      <c r="I61" s="22">
         <v>46010</v>
       </c>
-      <c r="J61" s="24">
+      <c r="J61" s="22">
         <v>46010</v>
       </c>
-      <c r="K61" s="25" t="s">
-        <v>142</v>
+      <c r="K61" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="L61" s="11">
         <v>0</v>
@@ -8517,10 +7873,10 @@
         <v>0</v>
       </c>
       <c r="U61" s="11">
-        <v>52.01</v>
+        <v>52.1</v>
       </c>
       <c r="V61" s="11">
-        <v>52.01</v>
+        <v>52.1</v>
       </c>
       <c r="W61" s="12">
         <v>1</v>
@@ -8529,10 +7885,10 @@
         <v>0</v>
       </c>
       <c r="Y61" s="11">
-        <v>56.96</v>
+        <v>58.67</v>
       </c>
       <c r="Z61" s="11">
-        <v>56.96</v>
+        <v>58.67</v>
       </c>
       <c r="AA61" s="12">
         <v>1</v>
@@ -8552,10 +7908,10 @@
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A62" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C62" s="10">
         <v>2043</v>
@@ -8564,7 +7920,7 @@
         <v>2043</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F62" s="10">
         <v>116795</v>
@@ -8573,16 +7929,16 @@
         <v>72</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I62" s="24">
+        <v>127</v>
+      </c>
+      <c r="I62" s="22">
         <v>46000</v>
       </c>
-      <c r="J62" s="24">
+      <c r="J62" s="22">
         <v>46023</v>
       </c>
-      <c r="K62" s="25" t="s">
-        <v>138</v>
+      <c r="K62" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L62" s="11">
         <v>0</v>
@@ -8624,10 +7980,10 @@
         <v>0</v>
       </c>
       <c r="Y62" s="11">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="Z62" s="11">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="AA62" s="12">
         <v>1</v>
@@ -8647,10 +8003,10 @@
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A63" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C63" s="10">
         <v>2043</v>
@@ -8659,7 +8015,7 @@
         <v>2856</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F63" s="10">
         <v>116876</v>
@@ -8668,16 +8024,16 @@
         <v>73</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I63" s="24">
+        <v>127</v>
+      </c>
+      <c r="I63" s="22">
         <v>46006</v>
       </c>
-      <c r="J63" s="24">
+      <c r="J63" s="22">
         <v>46023</v>
       </c>
-      <c r="K63" s="25" t="s">
-        <v>138</v>
+      <c r="K63" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L63" s="11">
         <v>0</v>
@@ -8707,10 +8063,10 @@
         <v>0</v>
       </c>
       <c r="U63" s="11">
-        <v>118.67</v>
+        <v>118.98</v>
       </c>
       <c r="V63" s="11">
-        <v>118.67</v>
+        <v>118.98</v>
       </c>
       <c r="W63" s="12">
         <v>1</v>
@@ -8719,10 +8075,10 @@
         <v>0</v>
       </c>
       <c r="Y63" s="11">
-        <v>67.790000000000006</v>
+        <v>68.010000000000005</v>
       </c>
       <c r="Z63" s="11">
-        <v>67.790000000000006</v>
+        <v>68.010000000000005</v>
       </c>
       <c r="AA63" s="12">
         <v>1</v>
@@ -8742,10 +8098,10 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A64" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C64" s="10">
         <v>2043</v>
@@ -8754,7 +8110,7 @@
         <v>2856</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F64" s="10">
         <v>116883</v>
@@ -8763,16 +8119,16 @@
         <v>74</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I64" s="24">
+        <v>127</v>
+      </c>
+      <c r="I64" s="22">
         <v>46007</v>
       </c>
-      <c r="J64" s="24">
+      <c r="J64" s="22">
         <v>46023</v>
       </c>
-      <c r="K64" s="25" t="s">
-        <v>138</v>
+      <c r="K64" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="L64" s="11">
         <v>0</v>
@@ -8802,10 +8158,10 @@
         <v>0</v>
       </c>
       <c r="U64" s="11">
-        <v>99.18</v>
+        <v>99.46</v>
       </c>
       <c r="V64" s="11">
-        <v>99.18</v>
+        <v>99.46</v>
       </c>
       <c r="W64" s="12">
         <v>1</v>
@@ -8814,10 +8170,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="11">
-        <v>20.2</v>
+        <v>20.22</v>
       </c>
       <c r="Z64" s="11">
-        <v>20.2</v>
+        <v>20.22</v>
       </c>
       <c r="AA64" s="12">
         <v>1</v>
@@ -8832,6 +8188,101 @@
         <v>0</v>
       </c>
       <c r="AE64" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A65" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C65" s="10">
+        <v>2043</v>
+      </c>
+      <c r="D65" s="10">
+        <v>2043</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F65" s="10">
+        <v>117440</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="I65" s="22">
+        <v>46059</v>
+      </c>
+      <c r="J65" s="22">
+        <v>46083</v>
+      </c>
+      <c r="K65" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="L65" s="11">
+        <v>0</v>
+      </c>
+      <c r="M65" s="11">
+        <v>1</v>
+      </c>
+      <c r="N65" s="11">
+        <v>1</v>
+      </c>
+      <c r="O65" s="12">
+        <v>1</v>
+      </c>
+      <c r="P65" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="11">
+        <v>0</v>
+      </c>
+      <c r="R65" s="11">
+        <v>0</v>
+      </c>
+      <c r="S65" s="12">
+        <v>0</v>
+      </c>
+      <c r="T65" s="11">
+        <v>0</v>
+      </c>
+      <c r="U65" s="11">
+        <v>29.35</v>
+      </c>
+      <c r="V65" s="11">
+        <v>29.35</v>
+      </c>
+      <c r="W65" s="12">
+        <v>1</v>
+      </c>
+      <c r="X65" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="12">
         <v>0</v>
       </c>
     </row>
@@ -8843,320 +8294,316 @@
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="AD7:AE64 N7:O64 R7:S64 V7:W64 Z7:AA64">
+  <conditionalFormatting sqref="AD7:AE65 N7:O65 R7:S65 V7:W65 Z7:AA65">
     <cfRule type="cellIs" dxfId="61" priority="40" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B64">
+  <conditionalFormatting sqref="A7:B65">
     <cfRule type="expression" dxfId="60" priority="61" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C64">
+  <conditionalFormatting sqref="C7:C65">
     <cfRule type="expression" dxfId="59" priority="60" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D64">
+  <conditionalFormatting sqref="D7:D65">
     <cfRule type="expression" dxfId="58" priority="59" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E64">
+  <conditionalFormatting sqref="E7:E65">
     <cfRule type="expression" dxfId="57" priority="58" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F64">
+  <conditionalFormatting sqref="F7:F65">
     <cfRule type="expression" dxfId="56" priority="57" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G64">
+  <conditionalFormatting sqref="G7:G65">
     <cfRule type="expression" dxfId="55" priority="56" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H64">
+  <conditionalFormatting sqref="H7:H65">
     <cfRule type="expression" dxfId="54" priority="55" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I64">
+  <conditionalFormatting sqref="I7:I65">
     <cfRule type="expression" dxfId="53" priority="54" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J64">
+  <conditionalFormatting sqref="J7:J65">
     <cfRule type="expression" dxfId="52" priority="53" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K7:K64">
+  <conditionalFormatting sqref="K7:K65">
     <cfRule type="expression" dxfId="51" priority="52" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L7:L64">
+  <conditionalFormatting sqref="L7:L65">
     <cfRule type="expression" dxfId="50" priority="51" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M64">
+  <conditionalFormatting sqref="M7:M65">
     <cfRule type="expression" dxfId="49" priority="50" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N7:N64">
+  <conditionalFormatting sqref="N7:N65">
     <cfRule type="expression" dxfId="48" priority="49" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O7:O64">
+  <conditionalFormatting sqref="O7:O65">
     <cfRule type="expression" dxfId="47" priority="48" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P7:P64">
+  <conditionalFormatting sqref="P7:P65">
     <cfRule type="expression" dxfId="46" priority="47" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q7:Q64">
+  <conditionalFormatting sqref="Q7:Q65">
     <cfRule type="expression" dxfId="45" priority="46" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R7:R64">
+  <conditionalFormatting sqref="R7:R65">
     <cfRule type="expression" dxfId="44" priority="45" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S7:S64">
+  <conditionalFormatting sqref="S7:S65">
     <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T7:T64">
+  <conditionalFormatting sqref="T7:T65">
     <cfRule type="expression" dxfId="42" priority="43" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U7:U64">
+  <conditionalFormatting sqref="U7:U65">
     <cfRule type="expression" dxfId="41" priority="42" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V7:V64">
+  <conditionalFormatting sqref="V7:V65">
     <cfRule type="expression" dxfId="40" priority="41" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W7:W64">
+  <conditionalFormatting sqref="W7:W65">
     <cfRule type="expression" dxfId="39" priority="62" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X7:X64">
+  <conditionalFormatting sqref="X7:X65">
     <cfRule type="expression" dxfId="38" priority="39" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Y64">
+  <conditionalFormatting sqref="Y7:Y65">
     <cfRule type="expression" dxfId="37" priority="38" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z7:Z64">
+  <conditionalFormatting sqref="Z7:Z65">
     <cfRule type="expression" dxfId="36" priority="37" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA64">
+  <conditionalFormatting sqref="AA7:AA65">
     <cfRule type="expression" dxfId="35" priority="36" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB7:AB64">
+  <conditionalFormatting sqref="AB7:AB65">
     <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC7:AC64">
+  <conditionalFormatting sqref="AC7:AC65">
     <cfRule type="expression" dxfId="33" priority="34" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AD64">
+  <conditionalFormatting sqref="AD7:AD65">
     <cfRule type="expression" dxfId="32" priority="33" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE7:AE64">
+  <conditionalFormatting sqref="AE7:AE65">
     <cfRule type="expression" dxfId="31" priority="32" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AE64 N7:O64 R7:S64 V7:W64 Z7:AA64">
+  <conditionalFormatting sqref="AD7:AE65 N7:O65 R7:S65 V7:W65 Z7:AA65">
     <cfRule type="cellIs" dxfId="30" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B64">
+  <conditionalFormatting sqref="A7:B65">
     <cfRule type="expression" dxfId="29" priority="30" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C64">
+  <conditionalFormatting sqref="C7:C65">
     <cfRule type="expression" dxfId="28" priority="29" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D64">
+  <conditionalFormatting sqref="D7:D65">
     <cfRule type="expression" dxfId="27" priority="28">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E64">
+  <conditionalFormatting sqref="E7:E65">
     <cfRule type="expression" dxfId="26" priority="27">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F64">
+  <conditionalFormatting sqref="F7:F65">
     <cfRule type="expression" dxfId="25" priority="26">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G64">
+  <conditionalFormatting sqref="G7:G65">
     <cfRule type="expression" dxfId="24" priority="25">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H64">
+  <conditionalFormatting sqref="H7:H65">
     <cfRule type="expression" dxfId="23" priority="24">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I64">
+  <conditionalFormatting sqref="I7:I65">
     <cfRule type="expression" dxfId="22" priority="23">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J64">
+  <conditionalFormatting sqref="J7:J65">
     <cfRule type="expression" dxfId="21" priority="22">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K7:K64">
+  <conditionalFormatting sqref="K7:K65">
     <cfRule type="expression" dxfId="20" priority="21">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L7:L64">
+  <conditionalFormatting sqref="L7:L65">
     <cfRule type="expression" dxfId="19" priority="20">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M64">
+  <conditionalFormatting sqref="M7:M65">
     <cfRule type="expression" dxfId="18" priority="19">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N7:N64">
+  <conditionalFormatting sqref="N7:N65">
     <cfRule type="expression" dxfId="17" priority="18">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O7:O64">
+  <conditionalFormatting sqref="O7:O65">
     <cfRule type="expression" dxfId="16" priority="17">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P7:P64">
+  <conditionalFormatting sqref="P7:P65">
     <cfRule type="expression" dxfId="15" priority="16">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q7:Q64">
+  <conditionalFormatting sqref="Q7:Q65">
     <cfRule type="expression" dxfId="14" priority="15">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R7:R64">
+  <conditionalFormatting sqref="R7:R65">
     <cfRule type="expression" dxfId="13" priority="14">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S7:S64">
+  <conditionalFormatting sqref="S7:S65">
     <cfRule type="expression" dxfId="12" priority="13">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T7:T64">
+  <conditionalFormatting sqref="T7:T65">
     <cfRule type="expression" dxfId="11" priority="12">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U7:U64">
+  <conditionalFormatting sqref="U7:U65">
     <cfRule type="expression" dxfId="10" priority="11">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V7:V64">
+  <conditionalFormatting sqref="V7:V65">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W7:W64">
+  <conditionalFormatting sqref="W7:W65">
     <cfRule type="expression" dxfId="8" priority="31" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X7:X64">
+  <conditionalFormatting sqref="X7:X65">
     <cfRule type="expression" dxfId="7" priority="8">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Y64">
+  <conditionalFormatting sqref="Y7:Y65">
     <cfRule type="expression" dxfId="6" priority="7">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z7:Z64">
+  <conditionalFormatting sqref="Z7:Z65">
     <cfRule type="expression" dxfId="5" priority="6">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA64">
+  <conditionalFormatting sqref="AA7:AA65">
     <cfRule type="expression" dxfId="4" priority="5">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB7:AB64">
+  <conditionalFormatting sqref="AB7:AB65">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC7:AC64">
+  <conditionalFormatting sqref="AC7:AC65">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AD64">
+  <conditionalFormatting sqref="AD7:AD65">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE7:AE64">
+  <conditionalFormatting sqref="AE7:AE65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21466243-053B-6C48-9718-0005C75F3104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D258E3D-6714-DC4C-ACEA-69B5465EB99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
+    <workbookView xWindow="1340" yWindow="900" windowWidth="24460" windowHeight="16380" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
   <sheets>
     <sheet name="promotoria" sheetId="2" r:id="rId1"/>
@@ -2211,7 +2211,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="1">
-        <v>46081</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="46" thickBot="1" x14ac:dyDescent="0.25">
@@ -2284,49 +2284,49 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="15">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="B5" s="15">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C5" s="15">
-        <v>-40</v>
+        <v>-77</v>
       </c>
       <c r="D5" s="16">
-        <v>-0.51282051282051277</v>
+        <v>-0.63114754098360648</v>
       </c>
       <c r="E5" s="15">
-        <v>3065.09</v>
+        <v>4684.3999999999996</v>
       </c>
       <c r="F5" s="15">
-        <v>1888.59</v>
+        <v>2468.83</v>
       </c>
       <c r="G5" s="15">
-        <v>-1176.5</v>
+        <v>-2215.5700000000002</v>
       </c>
       <c r="H5" s="16">
-        <v>-0.38383864747854068</v>
+        <v>-0.47296772265391507</v>
       </c>
       <c r="I5" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="15">
         <v>0</v>
       </c>
       <c r="K5" s="15">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="16">
         <v>-1</v>
       </c>
       <c r="M5" s="15">
-        <v>141.97</v>
+        <v>313.24</v>
       </c>
       <c r="N5" s="15">
         <v>0</v>
       </c>
       <c r="O5" s="15">
-        <v>-141.97</v>
+        <v>-313.24</v>
       </c>
       <c r="P5" s="16">
         <v>-1</v>
@@ -2716,64 +2716,64 @@
         <v>128</v>
       </c>
       <c r="L7" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7" s="11">
         <v>2</v>
       </c>
       <c r="N7" s="11">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O7" s="12">
-        <v>-0.33329999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="P7" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="11">
         <v>2</v>
       </c>
       <c r="R7" s="11">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S7" s="12">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T7" s="11">
-        <v>25.07</v>
+        <v>134.32</v>
       </c>
       <c r="U7" s="11">
         <v>61.9</v>
       </c>
       <c r="V7" s="11">
-        <v>36.83</v>
+        <v>-72.42</v>
       </c>
       <c r="W7" s="12">
-        <v>1.4691000000000001</v>
+        <v>-0.53920000000000001</v>
       </c>
       <c r="X7" s="11">
-        <v>96.36</v>
+        <v>238.93</v>
       </c>
       <c r="Y7" s="11">
-        <v>112.49</v>
+        <v>115.62</v>
       </c>
       <c r="Z7" s="11">
-        <v>16.13</v>
+        <v>-123.31</v>
       </c>
       <c r="AA7" s="12">
-        <v>0.16739999999999999</v>
+        <v>-0.5161</v>
       </c>
       <c r="AB7" s="11">
-        <v>4.2222</v>
+        <v>5.3364000000000003</v>
       </c>
       <c r="AC7" s="11">
-        <v>5.1874000000000002</v>
+        <v>6.3615000000000004</v>
       </c>
       <c r="AD7" s="11">
-        <v>0.96519999999999995</v>
+        <v>1.0250999999999999</v>
       </c>
       <c r="AE7" s="12">
-        <v>0.2286</v>
+        <v>0.19209999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
@@ -2847,13 +2847,13 @@
         <v>0</v>
       </c>
       <c r="X8" s="11">
-        <v>22.53</v>
+        <v>40.71</v>
       </c>
       <c r="Y8" s="11">
         <v>0</v>
       </c>
       <c r="Z8" s="11">
-        <v>-22.53</v>
+        <v>-40.71</v>
       </c>
       <c r="AA8" s="12">
         <v>-1</v>
@@ -2942,16 +2942,16 @@
         <v>-1</v>
       </c>
       <c r="X9" s="11">
-        <v>23.41</v>
+        <v>31.29</v>
       </c>
       <c r="Y9" s="11">
         <v>7.18</v>
       </c>
       <c r="Z9" s="11">
-        <v>-16.23</v>
+        <v>-24.11</v>
       </c>
       <c r="AA9" s="12">
-        <v>-0.69330000000000003</v>
+        <v>-0.77049999999999996</v>
       </c>
       <c r="AB9" s="11">
         <v>0</v>
@@ -3013,16 +3013,16 @@
         <v>-1</v>
       </c>
       <c r="P10" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="11">
         <v>0</v>
       </c>
       <c r="R10" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S10" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T10" s="11">
         <v>29.23</v>
@@ -3037,16 +3037,16 @@
         <v>-1</v>
       </c>
       <c r="X10" s="11">
-        <v>1.85</v>
+        <v>31.17</v>
       </c>
       <c r="Y10" s="11">
-        <v>2.75</v>
+        <v>5.51</v>
       </c>
       <c r="Z10" s="11">
-        <v>0.9</v>
+        <v>-25.66</v>
       </c>
       <c r="AA10" s="12">
-        <v>0.48649999999999999</v>
+        <v>-0.82320000000000004</v>
       </c>
       <c r="AB10" s="11">
         <v>0</v>
@@ -3132,13 +3132,13 @@
         <v>0</v>
       </c>
       <c r="X11" s="11">
-        <v>8.8699999999999992</v>
+        <v>13.32</v>
       </c>
       <c r="Y11" s="11">
         <v>0</v>
       </c>
       <c r="Z11" s="11">
-        <v>-8.8699999999999992</v>
+        <v>-13.32</v>
       </c>
       <c r="AA11" s="12">
         <v>-1</v>
@@ -3191,64 +3191,64 @@
         <v>128</v>
       </c>
       <c r="L12" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M12" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" s="11">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O12" s="12">
-        <v>-0.66669999999999996</v>
+        <v>-0.625</v>
       </c>
       <c r="P12" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q12" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" s="11">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="S12" s="12">
-        <v>-0.66669999999999996</v>
+        <v>-0.625</v>
       </c>
       <c r="T12" s="11">
-        <v>149.66</v>
+        <v>279.27999999999997</v>
       </c>
       <c r="U12" s="11">
-        <v>44.67</v>
+        <v>75.27</v>
       </c>
       <c r="V12" s="11">
-        <v>-104.99</v>
+        <v>-204.01</v>
       </c>
       <c r="W12" s="12">
-        <v>-0.70150000000000001</v>
+        <v>-0.73050000000000004</v>
       </c>
       <c r="X12" s="11">
-        <v>415.45</v>
+        <v>574.09</v>
       </c>
       <c r="Y12" s="11">
-        <v>58.56</v>
+        <v>65.709999999999994</v>
       </c>
       <c r="Z12" s="11">
-        <v>-356.89</v>
+        <v>-508.38</v>
       </c>
       <c r="AA12" s="12">
-        <v>-0.85899999999999999</v>
+        <v>-0.88549999999999995</v>
       </c>
       <c r="AB12" s="11">
-        <v>2.6160999999999999</v>
+        <v>3.1593</v>
       </c>
       <c r="AC12" s="11">
-        <v>7.9966999999999997</v>
+        <v>17.5944</v>
       </c>
       <c r="AD12" s="11">
-        <v>5.3806000000000003</v>
+        <v>14.4351</v>
       </c>
       <c r="AE12" s="12">
-        <v>2.0567000000000002</v>
+        <v>4.5690999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
@@ -3322,28 +3322,28 @@
         <v>-1</v>
       </c>
       <c r="X13" s="11">
-        <v>74.97</v>
+        <v>99.88</v>
       </c>
       <c r="Y13" s="11">
-        <v>25.12</v>
+        <v>30.24</v>
       </c>
       <c r="Z13" s="11">
-        <v>-49.85</v>
+        <v>-69.64</v>
       </c>
       <c r="AA13" s="12">
-        <v>-0.66490000000000005</v>
+        <v>-0.69720000000000004</v>
       </c>
       <c r="AB13" s="11">
-        <v>5.8438999999999997</v>
+        <v>6.0643000000000002</v>
       </c>
       <c r="AC13" s="11">
-        <v>3.9805999999999999</v>
+        <v>4.0369999999999999</v>
       </c>
       <c r="AD13" s="11">
-        <v>-1.8633</v>
+        <v>-2.0272999999999999</v>
       </c>
       <c r="AE13" s="12">
-        <v>-0.31879999999999997</v>
+        <v>-0.33429999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
@@ -3417,13 +3417,13 @@
         <v>0</v>
       </c>
       <c r="X14" s="11">
-        <v>21.7</v>
+        <v>27.86</v>
       </c>
       <c r="Y14" s="11">
         <v>0</v>
       </c>
       <c r="Z14" s="11">
-        <v>-21.7</v>
+        <v>-27.86</v>
       </c>
       <c r="AA14" s="12">
         <v>-1</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AC15" s="11">
-        <v>2.5028000000000001</v>
+        <v>3.2017000000000002</v>
       </c>
       <c r="AD15" s="11">
-        <v>2.5028000000000001</v>
+        <v>3.2017000000000002</v>
       </c>
       <c r="AE15" s="12">
         <v>1</v>
@@ -3669,61 +3669,61 @@
         <v>4</v>
       </c>
       <c r="M17" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N17" s="11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O17" s="12">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="P17" s="11">
         <v>6</v>
       </c>
       <c r="Q17" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R17" s="11">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="S17" s="12">
-        <v>-0.5</v>
+        <v>-0.16669999999999999</v>
       </c>
       <c r="T17" s="11">
         <v>855.64</v>
       </c>
       <c r="U17" s="11">
-        <v>109.49</v>
+        <v>433.01</v>
       </c>
       <c r="V17" s="11">
-        <v>-746.15</v>
+        <v>-422.63</v>
       </c>
       <c r="W17" s="12">
-        <v>-0.872</v>
+        <v>-0.49390000000000001</v>
       </c>
       <c r="X17" s="11">
-        <v>571.64</v>
+        <v>588.49</v>
       </c>
       <c r="Y17" s="11">
-        <v>238.29</v>
+        <v>633.39</v>
       </c>
       <c r="Z17" s="11">
-        <v>-333.35</v>
+        <v>44.9</v>
       </c>
       <c r="AA17" s="12">
-        <v>-0.58309999999999995</v>
+        <v>7.6300000000000007E-2</v>
       </c>
       <c r="AB17" s="11">
-        <v>0.28599999999999998</v>
+        <v>0.69879999999999998</v>
       </c>
       <c r="AC17" s="11">
-        <v>0.74060000000000004</v>
+        <v>0.86550000000000005</v>
       </c>
       <c r="AD17" s="11">
-        <v>0.4546</v>
+        <v>0.16669999999999999</v>
       </c>
       <c r="AE17" s="12">
-        <v>1.5894999999999999</v>
+        <v>0.23860000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -3797,28 +3797,28 @@
         <v>-1</v>
       </c>
       <c r="X18" s="11">
-        <v>22.54</v>
+        <v>25.91</v>
       </c>
       <c r="Y18" s="11">
-        <v>8.4</v>
+        <v>12.61</v>
       </c>
       <c r="Z18" s="11">
-        <v>-14.14</v>
+        <v>-13.3</v>
       </c>
       <c r="AA18" s="12">
-        <v>-0.62729999999999997</v>
+        <v>-0.51329999999999998</v>
       </c>
       <c r="AB18" s="11">
-        <v>0.81110000000000004</v>
+        <v>1.4147000000000001</v>
       </c>
       <c r="AC18" s="11">
-        <v>0.84189999999999998</v>
+        <v>1.4668000000000001</v>
       </c>
       <c r="AD18" s="11">
-        <v>3.0800000000000001E-2</v>
+        <v>5.21E-2</v>
       </c>
       <c r="AE18" s="12">
-        <v>3.7999999999999999E-2</v>
+        <v>3.6799999999999999E-2</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.2">
@@ -3987,28 +3987,28 @@
         <v>-0.39219999999999999</v>
       </c>
       <c r="X20" s="11">
-        <v>259.25</v>
+        <v>353.8</v>
       </c>
       <c r="Y20" s="11">
         <v>202.83</v>
       </c>
       <c r="Z20" s="11">
-        <v>-56.42</v>
+        <v>-150.97</v>
       </c>
       <c r="AA20" s="12">
-        <v>-0.21759999999999999</v>
+        <v>-0.42670000000000002</v>
       </c>
       <c r="AB20" s="11">
-        <v>0.01</v>
+        <v>1.8688</v>
       </c>
       <c r="AC20" s="11">
-        <v>3.0000000000000001E-3</v>
+        <v>0.36919999999999997</v>
       </c>
       <c r="AD20" s="11">
-        <v>-7.0000000000000001E-3</v>
+        <v>-1.4996</v>
       </c>
       <c r="AE20" s="12">
-        <v>-0.7</v>
+        <v>-0.8024</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.2">
@@ -4082,28 +4082,28 @@
         <v>1</v>
       </c>
       <c r="X21" s="11">
-        <v>7.7</v>
+        <v>11.56</v>
       </c>
       <c r="Y21" s="11">
         <v>59.85</v>
       </c>
       <c r="Z21" s="11">
-        <v>52.15</v>
+        <v>48.29</v>
       </c>
       <c r="AA21" s="12">
-        <v>6.7727000000000004</v>
+        <v>4.1772999999999998</v>
       </c>
       <c r="AB21" s="11">
-        <v>0.20960000000000001</v>
+        <v>0.31490000000000001</v>
       </c>
       <c r="AC21" s="11">
-        <v>0.7792</v>
+        <v>1.1247</v>
       </c>
       <c r="AD21" s="11">
-        <v>0.5696</v>
+        <v>0.80979999999999996</v>
       </c>
       <c r="AE21" s="12">
-        <v>2.7176</v>
+        <v>2.5716000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.2">
@@ -4180,13 +4180,13 @@
         <v>11.23</v>
       </c>
       <c r="Y22" s="11">
-        <v>0</v>
+        <v>10.14</v>
       </c>
       <c r="Z22" s="11">
-        <v>-11.23</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="AA22" s="12">
-        <v>-1</v>
+        <v>-9.7100000000000006E-2</v>
       </c>
       <c r="AB22" s="11">
         <v>0</v>
@@ -4236,52 +4236,52 @@
         <v>128</v>
       </c>
       <c r="L23" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M23" s="11">
         <v>1</v>
       </c>
       <c r="N23" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O23" s="12">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="P23" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="11">
         <v>1</v>
       </c>
       <c r="R23" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S23" s="12">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T23" s="11">
-        <v>45.49</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="U23" s="11">
         <v>46.1</v>
       </c>
       <c r="V23" s="11">
-        <v>0.61</v>
+        <v>-26.8</v>
       </c>
       <c r="W23" s="12">
-        <v>1.34E-2</v>
+        <v>-0.36759999999999998</v>
       </c>
       <c r="X23" s="11">
-        <v>5.81</v>
+        <v>11.9</v>
       </c>
       <c r="Y23" s="11">
         <v>16.34</v>
       </c>
       <c r="Z23" s="11">
-        <v>10.53</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="AA23" s="12">
-        <v>1.8124</v>
+        <v>0.37309999999999999</v>
       </c>
       <c r="AB23" s="11">
         <v>0</v>
@@ -4367,13 +4367,13 @@
         <v>0</v>
       </c>
       <c r="X24" s="11">
-        <v>5.42</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="Y24" s="11">
         <v>0</v>
       </c>
       <c r="Z24" s="11">
-        <v>-5.42</v>
+        <v>-8.3800000000000008</v>
       </c>
       <c r="AA24" s="12">
         <v>-1</v>
@@ -4462,13 +4462,13 @@
         <v>0</v>
       </c>
       <c r="X25" s="11">
-        <v>2.2000000000000002</v>
+        <v>4.42</v>
       </c>
       <c r="Y25" s="11">
         <v>0</v>
       </c>
       <c r="Z25" s="11">
-        <v>-2.2000000000000002</v>
+        <v>-4.42</v>
       </c>
       <c r="AA25" s="12">
         <v>-1</v>
@@ -4557,16 +4557,16 @@
         <v>-0.58879999999999999</v>
       </c>
       <c r="X26" s="11">
-        <v>64.19</v>
+        <v>78.84</v>
       </c>
       <c r="Y26" s="11">
-        <v>42.45</v>
+        <v>46.37</v>
       </c>
       <c r="Z26" s="11">
-        <v>-21.74</v>
+        <v>-32.47</v>
       </c>
       <c r="AA26" s="12">
-        <v>-0.3387</v>
+        <v>-0.4118</v>
       </c>
       <c r="AB26" s="11">
         <v>0.5141</v>
@@ -4628,40 +4628,40 @@
         <v>-1</v>
       </c>
       <c r="P27" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="11">
         <v>0</v>
       </c>
       <c r="R27" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S27" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T27" s="11">
-        <v>39.299999999999997</v>
+        <v>9.4</v>
       </c>
       <c r="U27" s="11">
         <v>0</v>
       </c>
       <c r="V27" s="11">
-        <v>-39.299999999999997</v>
+        <v>-9.4</v>
       </c>
       <c r="W27" s="12">
         <v>-1</v>
       </c>
       <c r="X27" s="11">
-        <v>23.02</v>
+        <v>46.3</v>
       </c>
       <c r="Y27" s="11">
-        <v>17.43</v>
+        <v>19.75</v>
       </c>
       <c r="Z27" s="11">
-        <v>-5.59</v>
+        <v>-26.55</v>
       </c>
       <c r="AA27" s="12">
-        <v>-0.24279999999999999</v>
+        <v>-0.57340000000000002</v>
       </c>
       <c r="AB27" s="11">
         <v>0</v>
@@ -4747,16 +4747,16 @@
         <v>0</v>
       </c>
       <c r="X28" s="11">
-        <v>1.54</v>
+        <v>3.09</v>
       </c>
       <c r="Y28" s="11">
-        <v>9.73</v>
+        <v>11.47</v>
       </c>
       <c r="Z28" s="11">
-        <v>8.19</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="AA28" s="12">
-        <v>5.3182</v>
+        <v>2.7120000000000002</v>
       </c>
       <c r="AB28" s="11">
         <v>0</v>
@@ -4806,64 +4806,64 @@
         <v>131</v>
       </c>
       <c r="L29" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M29" s="11">
         <v>0</v>
       </c>
       <c r="N29" s="11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O29" s="12">
         <v>-1</v>
       </c>
       <c r="P29" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q29" s="11">
         <v>0</v>
       </c>
       <c r="R29" s="11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="S29" s="12">
         <v>-1</v>
       </c>
       <c r="T29" s="11">
-        <v>93.83</v>
+        <v>175.1</v>
       </c>
       <c r="U29" s="11">
         <v>0</v>
       </c>
       <c r="V29" s="11">
-        <v>-93.83</v>
+        <v>-175.1</v>
       </c>
       <c r="W29" s="12">
         <v>-1</v>
       </c>
       <c r="X29" s="11">
-        <v>94.31</v>
+        <v>215.39</v>
       </c>
       <c r="Y29" s="11">
-        <v>24.18</v>
+        <v>28.61</v>
       </c>
       <c r="Z29" s="11">
-        <v>-70.13</v>
+        <v>-186.78</v>
       </c>
       <c r="AA29" s="12">
-        <v>-0.74360000000000004</v>
+        <v>-0.86719999999999997</v>
       </c>
       <c r="AB29" s="11">
-        <v>0.15720000000000001</v>
+        <v>1.528</v>
       </c>
       <c r="AC29" s="11">
-        <v>1.5749</v>
+        <v>2.7492999999999999</v>
       </c>
       <c r="AD29" s="11">
-        <v>1.4177</v>
+        <v>1.2213000000000001</v>
       </c>
       <c r="AE29" s="12">
-        <v>9.0183999999999997</v>
+        <v>0.79930000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.2">
@@ -4901,64 +4901,64 @@
         <v>131</v>
       </c>
       <c r="L30" s="11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M30" s="11">
         <v>3</v>
       </c>
       <c r="N30" s="11">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="O30" s="12">
-        <v>-0.25</v>
+        <v>-0.625</v>
       </c>
       <c r="P30" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q30" s="11">
         <v>3</v>
       </c>
       <c r="R30" s="11">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="S30" s="12">
-        <v>-0.25</v>
+        <v>-0.57140000000000002</v>
       </c>
       <c r="T30" s="11">
-        <v>107.55</v>
+        <v>224.88</v>
       </c>
       <c r="U30" s="11">
         <v>86.32</v>
       </c>
       <c r="V30" s="11">
-        <v>-21.23</v>
+        <v>-138.56</v>
       </c>
       <c r="W30" s="12">
-        <v>-0.19739999999999999</v>
+        <v>-0.61619999999999997</v>
       </c>
       <c r="X30" s="11">
-        <v>109.35</v>
+        <v>227.28</v>
       </c>
       <c r="Y30" s="11">
-        <v>67.709999999999994</v>
+        <v>79.98</v>
       </c>
       <c r="Z30" s="11">
-        <v>-41.64</v>
+        <v>-147.30000000000001</v>
       </c>
       <c r="AA30" s="12">
-        <v>-0.38080000000000003</v>
+        <v>-0.64810000000000001</v>
       </c>
       <c r="AB30" s="11">
-        <v>3.8600000000000002E-2</v>
+        <v>0.1235</v>
       </c>
       <c r="AC30" s="11">
         <v>0.56420000000000003</v>
       </c>
       <c r="AD30" s="11">
-        <v>0.52559999999999996</v>
+        <v>0.44069999999999998</v>
       </c>
       <c r="AE30" s="12">
-        <v>13.6166</v>
+        <v>3.5684</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.2">
@@ -4996,64 +4996,64 @@
         <v>131</v>
       </c>
       <c r="L31" s="11">
+        <v>7</v>
+      </c>
+      <c r="M31" s="11">
         <v>3</v>
       </c>
-      <c r="M31" s="11">
-        <v>2</v>
-      </c>
       <c r="N31" s="11">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="O31" s="12">
-        <v>-0.33329999999999999</v>
+        <v>-0.57140000000000002</v>
       </c>
       <c r="P31" s="11">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q31" s="11">
         <v>3</v>
       </c>
       <c r="R31" s="11">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="S31" s="12">
-        <v>0</v>
+        <v>-0.57140000000000002</v>
       </c>
       <c r="T31" s="11">
-        <v>121.6</v>
+        <v>212.51</v>
       </c>
       <c r="U31" s="11">
-        <v>44.05</v>
+        <v>68.92</v>
       </c>
       <c r="V31" s="11">
-        <v>-77.55</v>
+        <v>-143.59</v>
       </c>
       <c r="W31" s="12">
-        <v>-0.63770000000000004</v>
+        <v>-0.67569999999999997</v>
       </c>
       <c r="X31" s="11">
-        <v>121.85</v>
+        <v>187.2</v>
       </c>
       <c r="Y31" s="11">
-        <v>49.24</v>
+        <v>58.89</v>
       </c>
       <c r="Z31" s="11">
-        <v>-72.61</v>
+        <v>-128.31</v>
       </c>
       <c r="AA31" s="12">
-        <v>-0.59589999999999999</v>
+        <v>-0.68540000000000001</v>
       </c>
       <c r="AB31" s="11">
-        <v>0.35880000000000001</v>
+        <v>0.79920000000000002</v>
       </c>
       <c r="AC31" s="11">
-        <v>0.72289999999999999</v>
+        <v>1.1778999999999999</v>
       </c>
       <c r="AD31" s="11">
-        <v>0.36409999999999998</v>
+        <v>0.37869999999999998</v>
       </c>
       <c r="AE31" s="12">
-        <v>1.0147999999999999</v>
+        <v>0.4738</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.2">
@@ -5091,52 +5091,52 @@
         <v>131</v>
       </c>
       <c r="L32" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N32" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="11">
         <v>1</v>
       </c>
       <c r="R32" s="11">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S32" s="12">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="T32" s="11">
-        <v>0</v>
+        <v>49.3</v>
       </c>
       <c r="U32" s="11">
-        <v>30.84</v>
+        <v>61.31</v>
       </c>
       <c r="V32" s="11">
-        <v>30.84</v>
+        <v>12.01</v>
       </c>
       <c r="W32" s="12">
-        <v>1</v>
+        <v>0.24360000000000001</v>
       </c>
       <c r="X32" s="11">
-        <v>20.77</v>
+        <v>80.510000000000005</v>
       </c>
       <c r="Y32" s="11">
-        <v>24.37</v>
+        <v>26.09</v>
       </c>
       <c r="Z32" s="11">
-        <v>3.6</v>
+        <v>-54.42</v>
       </c>
       <c r="AA32" s="12">
-        <v>0.17330000000000001</v>
+        <v>-0.67589999999999995</v>
       </c>
       <c r="AB32" s="11">
         <v>0</v>
@@ -5186,64 +5186,64 @@
         <v>127</v>
       </c>
       <c r="L33" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="11">
         <v>0</v>
       </c>
       <c r="N33" s="11">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O33" s="12">
         <v>-1</v>
       </c>
       <c r="P33" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="11">
         <v>0</v>
       </c>
       <c r="R33" s="11">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S33" s="12">
         <v>-1</v>
       </c>
       <c r="T33" s="11">
-        <v>49.01</v>
+        <v>67.260000000000005</v>
       </c>
       <c r="U33" s="11">
         <v>0</v>
       </c>
       <c r="V33" s="11">
-        <v>-49.01</v>
+        <v>-67.260000000000005</v>
       </c>
       <c r="W33" s="12">
         <v>-1</v>
       </c>
       <c r="X33" s="11">
-        <v>54.74</v>
+        <v>73</v>
       </c>
       <c r="Y33" s="11">
-        <v>19.7</v>
+        <v>22.78</v>
       </c>
       <c r="Z33" s="11">
-        <v>-35.04</v>
+        <v>-50.22</v>
       </c>
       <c r="AA33" s="12">
-        <v>-0.6401</v>
+        <v>-0.68789999999999996</v>
       </c>
       <c r="AB33" s="11">
-        <v>3.1772999999999998</v>
+        <v>3.1848999999999998</v>
       </c>
       <c r="AC33" s="11">
         <v>0.71109999999999995</v>
       </c>
       <c r="AD33" s="11">
-        <v>-2.4662000000000002</v>
+        <v>-2.4738000000000002</v>
       </c>
       <c r="AE33" s="12">
-        <v>-0.7762</v>
+        <v>-0.77669999999999995</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
@@ -5281,52 +5281,52 @@
         <v>127</v>
       </c>
       <c r="L34" s="11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M34" s="11">
         <v>1</v>
       </c>
       <c r="N34" s="11">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="O34" s="12">
-        <v>-0.75</v>
+        <v>-0.875</v>
       </c>
       <c r="P34" s="11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q34" s="11">
         <v>0</v>
       </c>
       <c r="R34" s="11">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="S34" s="12">
         <v>-1</v>
       </c>
       <c r="T34" s="11">
-        <v>191.52</v>
+        <v>406.35</v>
       </c>
       <c r="U34" s="11">
         <v>-1319.02</v>
       </c>
       <c r="V34" s="11">
-        <v>-1510.54</v>
+        <v>-1725.37</v>
       </c>
       <c r="W34" s="12">
-        <v>-7.8871000000000002</v>
+        <v>-4.2460000000000004</v>
       </c>
       <c r="X34" s="11">
-        <v>25.02</v>
+        <v>63.59</v>
       </c>
       <c r="Y34" s="11">
-        <v>66.02</v>
+        <v>72.59</v>
       </c>
       <c r="Z34" s="11">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="AA34" s="12">
-        <v>1.6387</v>
+        <v>0.14149999999999999</v>
       </c>
       <c r="AB34" s="11">
         <v>0</v>
@@ -5471,64 +5471,64 @@
         <v>127</v>
       </c>
       <c r="L36" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M36" s="11">
         <v>1</v>
       </c>
       <c r="N36" s="11">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O36" s="12">
-        <v>-0.83330000000000004</v>
+        <v>-0.85709999999999997</v>
       </c>
       <c r="P36" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q36" s="11">
         <v>1</v>
       </c>
       <c r="R36" s="11">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="S36" s="12">
-        <v>-0.8</v>
+        <v>-0.83330000000000004</v>
       </c>
       <c r="T36" s="11">
-        <v>203.63</v>
+        <v>223.13</v>
       </c>
       <c r="U36" s="11">
         <v>36.93</v>
       </c>
       <c r="V36" s="11">
-        <v>-166.7</v>
+        <v>-186.2</v>
       </c>
       <c r="W36" s="12">
-        <v>-0.81859999999999999</v>
+        <v>-0.83450000000000002</v>
       </c>
       <c r="X36" s="11">
-        <v>250.75</v>
+        <v>303.52999999999997</v>
       </c>
       <c r="Y36" s="11">
-        <v>59.09</v>
+        <v>64.94</v>
       </c>
       <c r="Z36" s="11">
-        <v>-191.66</v>
+        <v>-238.59</v>
       </c>
       <c r="AA36" s="12">
-        <v>-0.76429999999999998</v>
+        <v>-0.78610000000000002</v>
       </c>
       <c r="AB36" s="11">
-        <v>2.6915</v>
+        <v>4.0427</v>
       </c>
       <c r="AC36" s="11">
         <v>2.7980999999999998</v>
       </c>
       <c r="AD36" s="11">
-        <v>0.1066</v>
+        <v>-1.2445999999999999</v>
       </c>
       <c r="AE36" s="12">
-        <v>3.9600000000000003E-2</v>
+        <v>-0.30790000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.2">
@@ -5566,52 +5566,52 @@
         <v>127</v>
       </c>
       <c r="L37" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M37" s="11">
         <v>1</v>
       </c>
       <c r="N37" s="11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O37" s="12">
-        <v>-0.75</v>
+        <v>-0.8</v>
       </c>
       <c r="P37" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q37" s="11">
         <v>1</v>
       </c>
       <c r="R37" s="11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="S37" s="12">
-        <v>-0.75</v>
+        <v>-0.8</v>
       </c>
       <c r="T37" s="11">
-        <v>114.51</v>
+        <v>149.02000000000001</v>
       </c>
       <c r="U37" s="11">
         <v>36.159999999999997</v>
       </c>
       <c r="V37" s="11">
-        <v>-78.349999999999994</v>
+        <v>-112.86</v>
       </c>
       <c r="W37" s="12">
-        <v>-0.68420000000000003</v>
+        <v>-0.75729999999999997</v>
       </c>
       <c r="X37" s="11">
-        <v>53.59</v>
+        <v>86.18</v>
       </c>
       <c r="Y37" s="11">
-        <v>112.26</v>
+        <v>119.74</v>
       </c>
       <c r="Z37" s="11">
-        <v>58.67</v>
+        <v>33.56</v>
       </c>
       <c r="AA37" s="12">
-        <v>1.0948</v>
+        <v>0.38940000000000002</v>
       </c>
       <c r="AB37" s="11">
         <v>0</v>
@@ -5661,61 +5661,61 @@
         <v>127</v>
       </c>
       <c r="L38" s="11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="11">
         <v>0</v>
       </c>
       <c r="N38" s="11">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="O38" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P38" s="11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q38" s="11">
         <v>0</v>
       </c>
       <c r="R38" s="11">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="S38" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T38" s="11">
-        <v>0</v>
+        <v>90.67</v>
       </c>
       <c r="U38" s="11">
         <v>0</v>
       </c>
       <c r="V38" s="11">
-        <v>0</v>
+        <v>-90.67</v>
       </c>
       <c r="W38" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X38" s="11">
-        <v>42.18</v>
+        <v>103.45</v>
       </c>
       <c r="Y38" s="11">
         <v>8.83</v>
       </c>
       <c r="Z38" s="11">
-        <v>-33.35</v>
+        <v>-94.62</v>
       </c>
       <c r="AA38" s="12">
-        <v>-0.79069999999999996</v>
+        <v>-0.91459999999999997</v>
       </c>
       <c r="AB38" s="11">
-        <v>8.9999999999999998E-4</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="AC38" s="11">
         <v>0</v>
       </c>
       <c r="AD38" s="11">
-        <v>-8.9999999999999998E-4</v>
+        <v>-3.3999999999999998E-3</v>
       </c>
       <c r="AE38" s="12">
         <v>-1</v>
@@ -5768,13 +5768,13 @@
         <v>-1</v>
       </c>
       <c r="P39" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="11">
         <v>0</v>
       </c>
       <c r="R39" s="11">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="S39" s="12">
         <v>-1</v>
@@ -5792,28 +5792,28 @@
         <v>-1</v>
       </c>
       <c r="X39" s="11">
-        <v>19.489999999999998</v>
+        <v>44.5</v>
       </c>
       <c r="Y39" s="11">
         <v>0</v>
       </c>
       <c r="Z39" s="11">
-        <v>-19.489999999999998</v>
+        <v>-44.5</v>
       </c>
       <c r="AA39" s="12">
         <v>-1</v>
       </c>
       <c r="AB39" s="11">
-        <v>0</v>
+        <v>9.8100000000000007E-2</v>
       </c>
       <c r="AC39" s="11">
         <v>0</v>
       </c>
       <c r="AD39" s="11">
-        <v>0</v>
+        <v>-9.8100000000000007E-2</v>
       </c>
       <c r="AE39" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.2">
@@ -5887,16 +5887,16 @@
         <v>-1</v>
       </c>
       <c r="X40" s="11">
-        <v>18.02</v>
+        <v>29.29</v>
       </c>
       <c r="Y40" s="11">
-        <v>15.96</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="Z40" s="11">
-        <v>-2.06</v>
+        <v>-12.48</v>
       </c>
       <c r="AA40" s="12">
-        <v>-0.1143</v>
+        <v>-0.42609999999999998</v>
       </c>
       <c r="AB40" s="11">
         <v>0</v>
@@ -5982,13 +5982,13 @@
         <v>0</v>
       </c>
       <c r="X41" s="11">
-        <v>2.97</v>
+        <v>4.46</v>
       </c>
       <c r="Y41" s="11">
         <v>0</v>
       </c>
       <c r="Z41" s="11">
-        <v>-2.97</v>
+        <v>-4.46</v>
       </c>
       <c r="AA41" s="12">
         <v>-1</v>
@@ -6041,49 +6041,49 @@
         <v>127</v>
       </c>
       <c r="L42" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" s="11">
         <v>0</v>
       </c>
       <c r="N42" s="11">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="O42" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P42" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42" s="11">
         <v>0</v>
       </c>
       <c r="R42" s="11">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S42" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T42" s="11">
-        <v>0</v>
+        <v>97.1</v>
       </c>
       <c r="U42" s="11">
         <v>0</v>
       </c>
       <c r="V42" s="11">
-        <v>0</v>
+        <v>-97.1</v>
       </c>
       <c r="W42" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X42" s="11">
-        <v>19.25</v>
+        <v>140.68</v>
       </c>
       <c r="Y42" s="11">
         <v>0</v>
       </c>
       <c r="Z42" s="11">
-        <v>-19.25</v>
+        <v>-140.68</v>
       </c>
       <c r="AA42" s="12">
         <v>-1</v>
@@ -6160,28 +6160,28 @@
         <v>-1</v>
       </c>
       <c r="T43" s="11">
-        <v>-3.19</v>
+        <v>-35.53</v>
       </c>
       <c r="U43" s="11">
         <v>28.7</v>
       </c>
       <c r="V43" s="11">
-        <v>31.89</v>
+        <v>64.23</v>
       </c>
       <c r="W43" s="12">
-        <v>9.9969000000000001</v>
+        <v>1.8078000000000001</v>
       </c>
       <c r="X43" s="11">
-        <v>52.34</v>
+        <v>62.03</v>
       </c>
       <c r="Y43" s="11">
         <v>5.68</v>
       </c>
       <c r="Z43" s="11">
-        <v>-46.66</v>
+        <v>-56.35</v>
       </c>
       <c r="AA43" s="12">
-        <v>-0.89149999999999996</v>
+        <v>-0.90839999999999999</v>
       </c>
       <c r="AB43" s="11">
         <v>0</v>
@@ -6231,52 +6231,52 @@
         <v>127</v>
       </c>
       <c r="L44" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="11">
         <v>0</v>
       </c>
       <c r="N44" s="11">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O44" s="12">
         <v>-1</v>
       </c>
       <c r="P44" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" s="11">
         <v>0</v>
       </c>
       <c r="R44" s="11">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S44" s="12">
         <v>-1</v>
       </c>
       <c r="T44" s="11">
-        <v>30.34</v>
+        <v>50.61</v>
       </c>
       <c r="U44" s="11">
         <v>0</v>
       </c>
       <c r="V44" s="11">
-        <v>-30.34</v>
+        <v>-50.61</v>
       </c>
       <c r="W44" s="12">
         <v>-1</v>
       </c>
       <c r="X44" s="11">
-        <v>34.43</v>
+        <v>44.35</v>
       </c>
       <c r="Y44" s="11">
         <v>17.68</v>
       </c>
       <c r="Z44" s="11">
-        <v>-16.75</v>
+        <v>-26.67</v>
       </c>
       <c r="AA44" s="12">
-        <v>-0.48649999999999999</v>
+        <v>-0.60140000000000005</v>
       </c>
       <c r="AB44" s="11">
         <v>0</v>
@@ -6326,64 +6326,64 @@
         <v>127</v>
       </c>
       <c r="L45" s="11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M45" s="11">
+        <v>7</v>
+      </c>
+      <c r="N45" s="11">
+        <v>-5</v>
+      </c>
+      <c r="O45" s="12">
+        <v>-0.41670000000000001</v>
+      </c>
+      <c r="P45" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q45" s="11">
         <v>6</v>
       </c>
-      <c r="N45" s="11">
-        <v>-3</v>
-      </c>
-      <c r="O45" s="12">
-        <v>-0.33329999999999999</v>
-      </c>
-      <c r="P45" s="11">
-        <v>9</v>
-      </c>
-      <c r="Q45" s="11">
-        <v>5</v>
-      </c>
       <c r="R45" s="11">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="S45" s="12">
-        <v>-0.44440000000000002</v>
+        <v>-0.5</v>
       </c>
       <c r="T45" s="11">
-        <v>219.18</v>
+        <v>272.62</v>
       </c>
       <c r="U45" s="11">
-        <v>181.35</v>
+        <v>227.64</v>
       </c>
       <c r="V45" s="11">
-        <v>-37.83</v>
+        <v>-44.98</v>
       </c>
       <c r="W45" s="12">
-        <v>-0.1726</v>
+        <v>-0.16500000000000001</v>
       </c>
       <c r="X45" s="11">
-        <v>129.72</v>
+        <v>156.13999999999999</v>
       </c>
       <c r="Y45" s="11">
-        <v>89.24</v>
+        <v>144.81</v>
       </c>
       <c r="Z45" s="11">
-        <v>-40.479999999999997</v>
+        <v>-11.33</v>
       </c>
       <c r="AA45" s="12">
-        <v>-0.31209999999999999</v>
+        <v>-7.2599999999999998E-2</v>
       </c>
       <c r="AB45" s="11">
         <v>0.2029</v>
       </c>
       <c r="AC45" s="11">
-        <v>0.30380000000000001</v>
+        <v>0.4355</v>
       </c>
       <c r="AD45" s="11">
-        <v>0.1009</v>
+        <v>0.2326</v>
       </c>
       <c r="AE45" s="12">
-        <v>0.49730000000000002</v>
+        <v>1.1464000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
@@ -6457,16 +6457,16 @@
         <v>-1</v>
       </c>
       <c r="X46" s="11">
-        <v>140.16</v>
+        <v>208.83</v>
       </c>
       <c r="Y46" s="11">
         <v>28.49</v>
       </c>
       <c r="Z46" s="11">
-        <v>-111.67</v>
+        <v>-180.34</v>
       </c>
       <c r="AA46" s="12">
-        <v>-0.79669999999999996</v>
+        <v>-0.86360000000000003</v>
       </c>
       <c r="AB46" s="11">
         <v>0</v>
@@ -6552,13 +6552,13 @@
         <v>0</v>
       </c>
       <c r="X47" s="11">
-        <v>6.2</v>
+        <v>9.74</v>
       </c>
       <c r="Y47" s="11">
         <v>0</v>
       </c>
       <c r="Z47" s="11">
-        <v>-6.2</v>
+        <v>-9.74</v>
       </c>
       <c r="AA47" s="12">
         <v>-1</v>
@@ -6611,52 +6611,52 @@
         <v>127</v>
       </c>
       <c r="L48" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M48" s="11">
         <v>0</v>
       </c>
       <c r="N48" s="11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O48" s="12">
         <v>-1</v>
       </c>
       <c r="P48" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q48" s="11">
         <v>0</v>
       </c>
       <c r="R48" s="11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="S48" s="12">
         <v>-1</v>
       </c>
       <c r="T48" s="11">
-        <v>106.85</v>
+        <v>169.31</v>
       </c>
       <c r="U48" s="11">
         <v>0</v>
       </c>
       <c r="V48" s="11">
-        <v>-106.85</v>
+        <v>-169.31</v>
       </c>
       <c r="W48" s="12">
         <v>-1</v>
       </c>
       <c r="X48" s="11">
-        <v>16.75</v>
+        <v>86.46</v>
       </c>
       <c r="Y48" s="11">
-        <v>23.01</v>
+        <v>28.41</v>
       </c>
       <c r="Z48" s="11">
-        <v>6.26</v>
+        <v>-58.05</v>
       </c>
       <c r="AA48" s="12">
-        <v>0.37369999999999998</v>
+        <v>-0.6714</v>
       </c>
       <c r="AB48" s="11">
         <v>0</v>
@@ -6706,52 +6706,52 @@
         <v>132</v>
       </c>
       <c r="L49" s="11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M49" s="11">
         <v>0</v>
       </c>
       <c r="N49" s="11">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="O49" s="12">
         <v>-1</v>
       </c>
       <c r="P49" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q49" s="11">
         <v>0</v>
       </c>
       <c r="R49" s="11">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="S49" s="12">
         <v>-1</v>
       </c>
       <c r="T49" s="11">
-        <v>142.29</v>
+        <v>228.19</v>
       </c>
       <c r="U49" s="11">
         <v>0</v>
       </c>
       <c r="V49" s="11">
-        <v>-142.29</v>
+        <v>-228.19</v>
       </c>
       <c r="W49" s="12">
         <v>-1</v>
       </c>
       <c r="X49" s="11">
-        <v>141.97</v>
+        <v>181.68</v>
       </c>
       <c r="Y49" s="11">
         <v>13.5</v>
       </c>
       <c r="Z49" s="11">
-        <v>-128.47</v>
+        <v>-168.18</v>
       </c>
       <c r="AA49" s="12">
-        <v>-0.90490000000000004</v>
+        <v>-0.92569999999999997</v>
       </c>
       <c r="AB49" s="11">
         <v>0</v>
@@ -6789,7 +6789,7 @@
         <v>60</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I50" s="22">
         <v>45736</v>
@@ -6801,49 +6801,49 @@
         <v>132</v>
       </c>
       <c r="L50" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M50" s="11">
         <v>0</v>
       </c>
       <c r="N50" s="11">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="O50" s="12">
         <v>-1</v>
       </c>
       <c r="P50" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q50" s="11">
         <v>0</v>
       </c>
       <c r="R50" s="11">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="S50" s="12">
         <v>-1</v>
       </c>
       <c r="T50" s="11">
-        <v>44.44</v>
+        <v>133.03</v>
       </c>
       <c r="U50" s="11">
         <v>0</v>
       </c>
       <c r="V50" s="11">
-        <v>-44.44</v>
+        <v>-133.03</v>
       </c>
       <c r="W50" s="12">
         <v>-1</v>
       </c>
       <c r="X50" s="11">
-        <v>44.44</v>
+        <v>131.56</v>
       </c>
       <c r="Y50" s="11">
         <v>0</v>
       </c>
       <c r="Z50" s="11">
-        <v>-44.44</v>
+        <v>-131.56</v>
       </c>
       <c r="AA50" s="12">
         <v>-1</v>
@@ -6991,52 +6991,52 @@
         <v>132</v>
       </c>
       <c r="L52" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" s="11">
         <v>0</v>
       </c>
       <c r="N52" s="11">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="O52" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P52" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="11">
         <v>0</v>
       </c>
       <c r="R52" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S52" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T52" s="11">
-        <v>0</v>
+        <v>53.09</v>
       </c>
       <c r="U52" s="11">
         <v>0</v>
       </c>
       <c r="V52" s="11">
-        <v>0</v>
+        <v>-53.09</v>
       </c>
       <c r="W52" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X52" s="11">
-        <v>0</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="Y52" s="11">
         <v>13.31</v>
       </c>
       <c r="Z52" s="11">
-        <v>13.31</v>
+        <v>10.86</v>
       </c>
       <c r="AA52" s="12">
-        <v>1</v>
+        <v>4.4326999999999996</v>
       </c>
       <c r="AB52" s="11">
         <v>0</v>
@@ -7086,52 +7086,52 @@
         <v>132</v>
       </c>
       <c r="L53" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="11">
         <v>0</v>
       </c>
       <c r="N53" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O53" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P53" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="11">
         <v>0</v>
       </c>
       <c r="R53" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S53" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T53" s="11">
-        <v>0</v>
+        <v>27.65</v>
       </c>
       <c r="U53" s="11">
         <v>0</v>
       </c>
       <c r="V53" s="11">
-        <v>0</v>
+        <v>-27.65</v>
       </c>
       <c r="W53" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X53" s="11">
-        <v>0</v>
+        <v>13.82</v>
       </c>
       <c r="Y53" s="11">
-        <v>13.16</v>
+        <v>17.690000000000001</v>
       </c>
       <c r="Z53" s="11">
-        <v>13.16</v>
+        <v>3.87</v>
       </c>
       <c r="AA53" s="12">
-        <v>1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AB53" s="11">
         <v>0</v>
@@ -7220,10 +7220,10 @@
         <v>0</v>
       </c>
       <c r="Y54" s="11">
-        <v>84.11</v>
+        <v>67.709999999999994</v>
       </c>
       <c r="Z54" s="11">
-        <v>84.11</v>
+        <v>67.709999999999994</v>
       </c>
       <c r="AA54" s="12">
         <v>1</v>
@@ -7315,10 +7315,10 @@
         <v>0</v>
       </c>
       <c r="Y55" s="11">
-        <v>37.08</v>
+        <v>39.47</v>
       </c>
       <c r="Z55" s="11">
-        <v>37.08</v>
+        <v>39.47</v>
       </c>
       <c r="AA55" s="12">
         <v>1</v>
@@ -7410,10 +7410,10 @@
         <v>0</v>
       </c>
       <c r="Y56" s="11">
-        <v>10.48</v>
+        <v>15.97</v>
       </c>
       <c r="Z56" s="11">
-        <v>10.48</v>
+        <v>15.97</v>
       </c>
       <c r="AA56" s="12">
         <v>1</v>
@@ -7659,10 +7659,10 @@
         <v>0</v>
       </c>
       <c r="M59" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N59" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O59" s="12">
         <v>1</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="U59" s="11">
-        <v>51.35</v>
+        <v>75.849999999999994</v>
       </c>
       <c r="V59" s="11">
-        <v>51.35</v>
+        <v>75.849999999999994</v>
       </c>
       <c r="W59" s="12">
         <v>1</v>
@@ -7695,10 +7695,10 @@
         <v>0</v>
       </c>
       <c r="Y59" s="11">
-        <v>90.8</v>
+        <v>110.56</v>
       </c>
       <c r="Z59" s="11">
-        <v>90.8</v>
+        <v>110.56</v>
       </c>
       <c r="AA59" s="12">
         <v>1</v>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="AC59" s="11">
-        <v>0.46429999999999999</v>
+        <v>1.1674</v>
       </c>
       <c r="AD59" s="11">
-        <v>0.46429999999999999</v>
+        <v>1.1674</v>
       </c>
       <c r="AE59" s="12">
         <v>1</v>
@@ -7790,10 +7790,10 @@
         <v>0</v>
       </c>
       <c r="Y60" s="11">
-        <v>19.03</v>
+        <v>19.690000000000001</v>
       </c>
       <c r="Z60" s="11">
-        <v>19.03</v>
+        <v>19.690000000000001</v>
       </c>
       <c r="AA60" s="12">
         <v>1</v>
@@ -7885,10 +7885,10 @@
         <v>0</v>
       </c>
       <c r="Y61" s="11">
-        <v>58.67</v>
+        <v>61.83</v>
       </c>
       <c r="Z61" s="11">
-        <v>58.67</v>
+        <v>61.83</v>
       </c>
       <c r="AA61" s="12">
         <v>1</v>
@@ -7929,7 +7929,7 @@
         <v>72</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I62" s="22">
         <v>46000</v>
@@ -8075,10 +8075,10 @@
         <v>0</v>
       </c>
       <c r="Y63" s="11">
-        <v>68.010000000000005</v>
+        <v>70.02</v>
       </c>
       <c r="Z63" s="11">
-        <v>68.010000000000005</v>
+        <v>70.02</v>
       </c>
       <c r="AA63" s="12">
         <v>1</v>
@@ -8134,10 +8134,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N64" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O64" s="12">
         <v>1</v>
@@ -8146,10 +8146,10 @@
         <v>0</v>
       </c>
       <c r="Q64" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R64" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S64" s="12">
         <v>1</v>
@@ -8158,10 +8158,10 @@
         <v>0</v>
       </c>
       <c r="U64" s="11">
-        <v>99.46</v>
+        <v>121.31</v>
       </c>
       <c r="V64" s="11">
-        <v>99.46</v>
+        <v>121.31</v>
       </c>
       <c r="W64" s="12">
         <v>1</v>
@@ -8170,10 +8170,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="11">
-        <v>20.22</v>
+        <v>25.41</v>
       </c>
       <c r="Z64" s="11">
-        <v>20.22</v>
+        <v>25.41</v>
       </c>
       <c r="AA64" s="12">
         <v>1</v>
@@ -8229,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="M65" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N65" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O65" s="12">
         <v>1</v>
@@ -8241,22 +8241,22 @@
         <v>0</v>
       </c>
       <c r="Q65" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R65" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S65" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="11">
         <v>0</v>
       </c>
       <c r="U65" s="11">
-        <v>29.35</v>
+        <v>119.03</v>
       </c>
       <c r="V65" s="11">
-        <v>29.35</v>
+        <v>119.03</v>
       </c>
       <c r="W65" s="12">
         <v>1</v>
@@ -8265,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="Y65" s="11">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="Z65" s="11">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="AA65" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB65" s="11">
         <v>0</v>
@@ -8294,12 +8294,22 @@
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A7:A65">
+    <cfRule type="expression" dxfId="68" priority="91" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:A65">
+    <cfRule type="expression" dxfId="67" priority="103" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AD7:AE65 N7:O65 R7:S65 V7:W65 Z7:AA65">
     <cfRule type="cellIs" dxfId="61" priority="40" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B65">
+  <conditionalFormatting sqref="B7:B65">
     <cfRule type="expression" dxfId="60" priority="61" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
@@ -8454,7 +8464,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B65">
+  <conditionalFormatting sqref="B7:B65">
     <cfRule type="expression" dxfId="29" priority="30" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>

--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5B6BD3-AA51-4149-976E-5C6B39C5D120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02ABF1C4-BD9E-A846-8D24-F3E21D4C21E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16380" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
+    <workbookView xWindow="2720" yWindow="500" windowWidth="24460" windowHeight="16360" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
   <sheets>
     <sheet name="promotoria" sheetId="2" r:id="rId1"/>
@@ -665,7 +665,981 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="70">
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <left style="hair">
@@ -856,7 +1830,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="69" headerRowBorderDxfId="68" tableBorderDxfId="67">
   <autoFilter ref="A3:P5" xr:uid="{A29DCA76-5097-2F45-94DA-4B121F22F1F5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{A2D27468-D390-E245-85A6-B90C4BDF0CE1}" name="Polizas_Pagadas_Año_Anterior"/>
@@ -1205,7 +2179,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="1">
-        <v>46092</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="46" thickBot="1" x14ac:dyDescent="0.25">
@@ -1281,25 +2255,25 @@
         <v>122</v>
       </c>
       <c r="B5" s="15">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C5" s="15">
-        <v>-77</v>
+        <v>-72</v>
       </c>
       <c r="D5" s="16">
-        <v>-0.63114754098360648</v>
+        <v>-0.5901639344262295</v>
       </c>
       <c r="E5" s="15">
         <v>4684.3999999999996</v>
       </c>
       <c r="F5" s="15">
-        <v>2468.83</v>
+        <v>2670.98</v>
       </c>
       <c r="G5" s="15">
-        <v>-2215.5700000000002</v>
+        <v>-2013.42</v>
       </c>
       <c r="H5" s="16">
-        <v>-0.47296772265391507</v>
+        <v>-0.42981385022628293</v>
       </c>
       <c r="I5" s="15">
         <v>2</v>
@@ -1344,7 +2318,7 @@
   <sheetData>
     <row r="1" spans="1:31" ht="33" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>46092</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1761,13 +2735,13 @@
         <v>5.3364000000000003</v>
       </c>
       <c r="AC7" s="11">
-        <v>6.3615000000000004</v>
+        <v>6.8959000000000001</v>
       </c>
       <c r="AD7" s="11">
-        <v>1.0250999999999999</v>
+        <v>1.5595000000000001</v>
       </c>
       <c r="AE7" s="12">
-        <v>0.19209999999999999</v>
+        <v>0.29220000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
@@ -1998,13 +2972,13 @@
         <v>1</v>
       </c>
       <c r="M10" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="11">
         <v>1</v>
@@ -2022,13 +2996,13 @@
         <v>29.23</v>
       </c>
       <c r="U10" s="11">
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="V10" s="11">
-        <v>-29.23</v>
+        <v>-4.03</v>
       </c>
       <c r="W10" s="12">
-        <v>-1</v>
+        <v>-0.13789999999999999</v>
       </c>
       <c r="X10" s="11">
         <v>31.17</v>
@@ -2188,13 +3162,13 @@
         <v>8</v>
       </c>
       <c r="M12" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N12" s="11">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="O12" s="12">
-        <v>-0.625</v>
+        <v>-0.5</v>
       </c>
       <c r="P12" s="11">
         <v>8</v>
@@ -2212,37 +3186,37 @@
         <v>279.27999999999997</v>
       </c>
       <c r="U12" s="11">
-        <v>75.27</v>
+        <v>179.67</v>
       </c>
       <c r="V12" s="11">
-        <v>-204.01</v>
+        <v>-99.61</v>
       </c>
       <c r="W12" s="12">
-        <v>-0.73050000000000004</v>
+        <v>-0.35670000000000002</v>
       </c>
       <c r="X12" s="11">
         <v>574.09</v>
       </c>
       <c r="Y12" s="11">
-        <v>65.709999999999994</v>
+        <v>73.45</v>
       </c>
       <c r="Z12" s="11">
-        <v>-508.38</v>
+        <v>-500.64</v>
       </c>
       <c r="AA12" s="12">
-        <v>-0.88549999999999995</v>
+        <v>-0.87209999999999999</v>
       </c>
       <c r="AB12" s="11">
         <v>3.1593</v>
       </c>
       <c r="AC12" s="11">
-        <v>17.5944</v>
+        <v>17.987200000000001</v>
       </c>
       <c r="AD12" s="11">
-        <v>14.4351</v>
+        <v>14.8279</v>
       </c>
       <c r="AE12" s="12">
-        <v>4.5690999999999997</v>
+        <v>4.6933999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
@@ -2331,13 +3305,13 @@
         <v>6.0643000000000002</v>
       </c>
       <c r="AC13" s="11">
-        <v>4.0369999999999999</v>
+        <v>4.2088000000000001</v>
       </c>
       <c r="AD13" s="11">
-        <v>-2.0272999999999999</v>
+        <v>-1.8554999999999999</v>
       </c>
       <c r="AE13" s="12">
-        <v>-0.33429999999999999</v>
+        <v>-0.30599999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
@@ -2414,13 +3388,13 @@
         <v>27.86</v>
       </c>
       <c r="Y14" s="11">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Z14" s="11">
-        <v>-27.86</v>
+        <v>-25.47</v>
       </c>
       <c r="AA14" s="12">
-        <v>-1</v>
+        <v>-0.91420000000000001</v>
       </c>
       <c r="AB14" s="11">
         <v>0</v>
@@ -2458,7 +3432,7 @@
         <v>25</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I15" s="22">
         <v>43447</v>
@@ -2663,61 +3637,61 @@
         <v>4</v>
       </c>
       <c r="M17" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N17" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="12">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P17" s="11">
         <v>6</v>
       </c>
       <c r="Q17" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R17" s="11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S17" s="12">
-        <v>-0.16669999999999999</v>
+        <v>0</v>
       </c>
       <c r="T17" s="11">
         <v>855.64</v>
       </c>
       <c r="U17" s="11">
-        <v>433.01</v>
+        <v>560.76</v>
       </c>
       <c r="V17" s="11">
-        <v>-422.63</v>
+        <v>-294.88</v>
       </c>
       <c r="W17" s="12">
-        <v>-0.49390000000000001</v>
+        <v>-0.34460000000000002</v>
       </c>
       <c r="X17" s="11">
         <v>588.49</v>
       </c>
       <c r="Y17" s="11">
-        <v>633.39</v>
+        <v>699.82</v>
       </c>
       <c r="Z17" s="11">
-        <v>44.9</v>
+        <v>111.33</v>
       </c>
       <c r="AA17" s="12">
-        <v>7.6300000000000007E-2</v>
+        <v>0.18920000000000001</v>
       </c>
       <c r="AB17" s="11">
         <v>0.69879999999999998</v>
       </c>
       <c r="AC17" s="11">
-        <v>0.86550000000000005</v>
+        <v>1.4301999999999999</v>
       </c>
       <c r="AD17" s="11">
-        <v>0.16669999999999999</v>
+        <v>0.73140000000000005</v>
       </c>
       <c r="AE17" s="12">
-        <v>0.23860000000000001</v>
+        <v>1.0467</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -2889,13 +3863,13 @@
         <v>4.34</v>
       </c>
       <c r="Y19" s="11">
-        <v>10.3</v>
+        <v>15.46</v>
       </c>
       <c r="Z19" s="11">
-        <v>5.96</v>
+        <v>11.12</v>
       </c>
       <c r="AA19" s="12">
-        <v>1.3733</v>
+        <v>2.5621999999999998</v>
       </c>
       <c r="AB19" s="11">
         <v>0</v>
@@ -2972,25 +3946,25 @@
         <v>328.85</v>
       </c>
       <c r="U20" s="11">
-        <v>199.88</v>
+        <v>126.73</v>
       </c>
       <c r="V20" s="11">
-        <v>-128.97</v>
+        <v>-202.12</v>
       </c>
       <c r="W20" s="12">
-        <v>-0.39219999999999999</v>
+        <v>-0.61460000000000004</v>
       </c>
       <c r="X20" s="11">
         <v>353.8</v>
       </c>
       <c r="Y20" s="11">
-        <v>202.83</v>
+        <v>216.24</v>
       </c>
       <c r="Z20" s="11">
-        <v>-150.97</v>
+        <v>-137.56</v>
       </c>
       <c r="AA20" s="12">
-        <v>-0.42670000000000002</v>
+        <v>-0.38879999999999998</v>
       </c>
       <c r="AB20" s="11">
         <v>1.8688</v>
@@ -3091,13 +4065,13 @@
         <v>0.31490000000000001</v>
       </c>
       <c r="AC21" s="11">
-        <v>1.1247</v>
+        <v>1.4286000000000001</v>
       </c>
       <c r="AD21" s="11">
-        <v>0.80979999999999996</v>
+        <v>1.1136999999999999</v>
       </c>
       <c r="AE21" s="12">
-        <v>2.5716000000000001</v>
+        <v>3.5367000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.2">
@@ -3269,13 +4243,13 @@
         <v>11.9</v>
       </c>
       <c r="Y23" s="11">
-        <v>16.34</v>
+        <v>20.2</v>
       </c>
       <c r="Z23" s="11">
-        <v>4.4400000000000004</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AA23" s="12">
-        <v>0.37309999999999999</v>
+        <v>0.69750000000000001</v>
       </c>
       <c r="AB23" s="11">
         <v>0</v>
@@ -3542,25 +4516,25 @@
         <v>58.68</v>
       </c>
       <c r="U26" s="11">
-        <v>24.13</v>
+        <v>-0.1</v>
       </c>
       <c r="V26" s="11">
-        <v>-34.549999999999997</v>
+        <v>-58.78</v>
       </c>
       <c r="W26" s="12">
-        <v>-0.58879999999999999</v>
+        <v>-1.0017</v>
       </c>
       <c r="X26" s="11">
         <v>78.84</v>
       </c>
       <c r="Y26" s="11">
-        <v>46.37</v>
+        <v>48.79</v>
       </c>
       <c r="Z26" s="11">
-        <v>-32.47</v>
+        <v>-30.05</v>
       </c>
       <c r="AA26" s="12">
-        <v>-0.4118</v>
+        <v>-0.38119999999999998</v>
       </c>
       <c r="AB26" s="11">
         <v>0.5141</v>
@@ -3898,61 +4872,61 @@
         <v>8</v>
       </c>
       <c r="M30" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N30" s="11">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="O30" s="12">
-        <v>-0.625</v>
+        <v>-0.5</v>
       </c>
       <c r="P30" s="11">
         <v>7</v>
       </c>
       <c r="Q30" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R30" s="11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="S30" s="12">
-        <v>-0.57140000000000002</v>
+        <v>-0.42859999999999998</v>
       </c>
       <c r="T30" s="11">
         <v>224.88</v>
       </c>
       <c r="U30" s="11">
-        <v>86.32</v>
+        <v>112.38</v>
       </c>
       <c r="V30" s="11">
-        <v>-138.56</v>
+        <v>-112.5</v>
       </c>
       <c r="W30" s="12">
-        <v>-0.61619999999999997</v>
+        <v>-0.50029999999999997</v>
       </c>
       <c r="X30" s="11">
         <v>227.28</v>
       </c>
       <c r="Y30" s="11">
-        <v>79.98</v>
+        <v>97.57</v>
       </c>
       <c r="Z30" s="11">
-        <v>-147.30000000000001</v>
+        <v>-129.71</v>
       </c>
       <c r="AA30" s="12">
-        <v>-0.64810000000000001</v>
+        <v>-0.57069999999999999</v>
       </c>
       <c r="AB30" s="11">
         <v>0.1235</v>
       </c>
       <c r="AC30" s="11">
-        <v>0.56420000000000003</v>
+        <v>3.3443000000000001</v>
       </c>
       <c r="AD30" s="11">
-        <v>0.44069999999999998</v>
+        <v>3.2208000000000001</v>
       </c>
       <c r="AE30" s="12">
-        <v>3.5684</v>
+        <v>26.0794</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.2">
@@ -3993,13 +4967,13 @@
         <v>7</v>
       </c>
       <c r="M31" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N31" s="11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="O31" s="12">
-        <v>-0.57140000000000002</v>
+        <v>-0.42859999999999998</v>
       </c>
       <c r="P31" s="11">
         <v>7</v>
@@ -4017,37 +4991,37 @@
         <v>212.51</v>
       </c>
       <c r="U31" s="11">
-        <v>68.92</v>
+        <v>96.98</v>
       </c>
       <c r="V31" s="11">
-        <v>-143.59</v>
+        <v>-115.53</v>
       </c>
       <c r="W31" s="12">
-        <v>-0.67569999999999997</v>
+        <v>-0.54359999999999997</v>
       </c>
       <c r="X31" s="11">
         <v>187.2</v>
       </c>
       <c r="Y31" s="11">
-        <v>58.89</v>
+        <v>56.92</v>
       </c>
       <c r="Z31" s="11">
-        <v>-128.31</v>
+        <v>-130.28</v>
       </c>
       <c r="AA31" s="12">
-        <v>-0.68540000000000001</v>
+        <v>-0.69589999999999996</v>
       </c>
       <c r="AB31" s="11">
         <v>0.79920000000000002</v>
       </c>
       <c r="AC31" s="11">
-        <v>1.1778999999999999</v>
+        <v>1.3084</v>
       </c>
       <c r="AD31" s="11">
-        <v>0.37869999999999998</v>
+        <v>0.50919999999999999</v>
       </c>
       <c r="AE31" s="12">
-        <v>0.4738</v>
+        <v>0.6371</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.2">
@@ -4112,34 +5086,34 @@
         <v>49.3</v>
       </c>
       <c r="U32" s="11">
-        <v>61.31</v>
+        <v>62.71</v>
       </c>
       <c r="V32" s="11">
-        <v>12.01</v>
+        <v>13.41</v>
       </c>
       <c r="W32" s="12">
-        <v>0.24360000000000001</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="X32" s="11">
         <v>80.510000000000005</v>
       </c>
       <c r="Y32" s="11">
-        <v>26.09</v>
+        <v>30.65</v>
       </c>
       <c r="Z32" s="11">
-        <v>-54.42</v>
+        <v>-49.86</v>
       </c>
       <c r="AA32" s="12">
-        <v>-0.67589999999999995</v>
+        <v>-0.61929999999999996</v>
       </c>
       <c r="AB32" s="11">
         <v>0</v>
       </c>
       <c r="AC32" s="11">
-        <v>0.58040000000000003</v>
+        <v>0.89339999999999997</v>
       </c>
       <c r="AD32" s="11">
-        <v>0.58040000000000003</v>
+        <v>0.89339999999999997</v>
       </c>
       <c r="AE32" s="12">
         <v>1</v>
@@ -4183,49 +5157,49 @@
         <v>2</v>
       </c>
       <c r="M33" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" s="11">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="O33" s="12">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="P33" s="11">
         <v>2</v>
       </c>
       <c r="Q33" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="11">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="S33" s="12">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="T33" s="11">
         <v>67.260000000000005</v>
       </c>
       <c r="U33" s="11">
-        <v>0</v>
+        <v>34.11</v>
       </c>
       <c r="V33" s="11">
-        <v>-67.260000000000005</v>
+        <v>-33.15</v>
       </c>
       <c r="W33" s="12">
-        <v>-1</v>
+        <v>-0.4929</v>
       </c>
       <c r="X33" s="11">
         <v>73</v>
       </c>
       <c r="Y33" s="11">
-        <v>22.78</v>
+        <v>26.42</v>
       </c>
       <c r="Z33" s="11">
-        <v>-50.22</v>
+        <v>-46.58</v>
       </c>
       <c r="AA33" s="12">
-        <v>-0.68789999999999996</v>
+        <v>-0.6381</v>
       </c>
       <c r="AB33" s="11">
         <v>3.1848999999999998</v>
@@ -4314,13 +5288,13 @@
         <v>63.59</v>
       </c>
       <c r="Y34" s="11">
-        <v>72.59</v>
+        <v>98.63</v>
       </c>
       <c r="Z34" s="11">
-        <v>9</v>
+        <v>35.04</v>
       </c>
       <c r="AA34" s="12">
-        <v>0.14149999999999999</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="AB34" s="11">
         <v>0</v>
@@ -5169,13 +6143,13 @@
         <v>62.03</v>
       </c>
       <c r="Y43" s="11">
-        <v>5.68</v>
+        <v>8.52</v>
       </c>
       <c r="Z43" s="11">
-        <v>-56.35</v>
+        <v>-53.51</v>
       </c>
       <c r="AA43" s="12">
-        <v>-0.90839999999999999</v>
+        <v>-0.86260000000000003</v>
       </c>
       <c r="AB43" s="11">
         <v>0</v>
@@ -5264,13 +6238,13 @@
         <v>44.35</v>
       </c>
       <c r="Y44" s="11">
-        <v>17.68</v>
+        <v>19.739999999999998</v>
       </c>
       <c r="Z44" s="11">
-        <v>-26.67</v>
+        <v>-24.61</v>
       </c>
       <c r="AA44" s="12">
-        <v>-0.60140000000000005</v>
+        <v>-0.55489999999999995</v>
       </c>
       <c r="AB44" s="11">
         <v>0</v>
@@ -5359,25 +6333,25 @@
         <v>156.13999999999999</v>
       </c>
       <c r="Y45" s="11">
-        <v>144.81</v>
+        <v>167.4</v>
       </c>
       <c r="Z45" s="11">
-        <v>-11.33</v>
+        <v>11.26</v>
       </c>
       <c r="AA45" s="12">
-        <v>-7.2599999999999998E-2</v>
+        <v>7.2099999999999997E-2</v>
       </c>
       <c r="AB45" s="11">
         <v>0.2029</v>
       </c>
       <c r="AC45" s="11">
-        <v>0.4355</v>
+        <v>0.4365</v>
       </c>
       <c r="AD45" s="11">
-        <v>0.2326</v>
+        <v>0.2336</v>
       </c>
       <c r="AE45" s="12">
-        <v>1.1464000000000001</v>
+        <v>1.1513</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
@@ -6309,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="Y55" s="11">
-        <v>39.47</v>
+        <v>42.53</v>
       </c>
       <c r="Z55" s="11">
-        <v>39.47</v>
+        <v>42.53</v>
       </c>
       <c r="AA55" s="12">
         <v>1</v>
@@ -6368,13 +7342,13 @@
         <v>0</v>
       </c>
       <c r="M56" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P56" s="11">
         <v>0</v>
@@ -6392,22 +7366,22 @@
         <v>0</v>
       </c>
       <c r="U56" s="11">
-        <v>0</v>
+        <v>20.22</v>
       </c>
       <c r="V56" s="11">
-        <v>0</v>
+        <v>20.22</v>
       </c>
       <c r="W56" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56" s="11">
         <v>0</v>
       </c>
       <c r="Y56" s="11">
-        <v>15.97</v>
+        <v>23.77</v>
       </c>
       <c r="Z56" s="11">
-        <v>15.97</v>
+        <v>23.77</v>
       </c>
       <c r="AA56" s="12">
         <v>1</v>
@@ -6879,10 +7853,10 @@
         <v>0</v>
       </c>
       <c r="Y61" s="11">
-        <v>61.83</v>
+        <v>63.6</v>
       </c>
       <c r="Z61" s="11">
-        <v>61.83</v>
+        <v>63.6</v>
       </c>
       <c r="AA61" s="12">
         <v>1</v>
@@ -7113,7 +8087,7 @@
         <v>74</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I64" s="22">
         <v>46007</v>
@@ -7140,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="Q64" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R64" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S64" s="12">
         <v>1</v>
@@ -7164,10 +8138,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="11">
-        <v>25.41</v>
+        <v>31.24</v>
       </c>
       <c r="Z64" s="11">
-        <v>25.41</v>
+        <v>31.24</v>
       </c>
       <c r="AA64" s="12">
         <v>1</v>
@@ -7235,10 +8209,10 @@
         <v>0</v>
       </c>
       <c r="Q65" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R65" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S65" s="12">
         <v>1</v>
@@ -7259,10 +8233,10 @@
         <v>0</v>
       </c>
       <c r="Y65" s="11">
-        <v>4.99</v>
+        <v>9.92</v>
       </c>
       <c r="Z65" s="11">
-        <v>4.99</v>
+        <v>9.92</v>
       </c>
       <c r="AA65" s="12">
         <v>1</v>
@@ -7288,37 +8262,312 @@
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A7:W65">
-    <cfRule type="expression" dxfId="6" priority="41" stopIfTrue="1">
+  <conditionalFormatting sqref="A7:B65">
+    <cfRule type="expression" dxfId="66" priority="101" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:C65">
-    <cfRule type="expression" dxfId="5" priority="29" stopIfTrue="1">
+  <conditionalFormatting sqref="B7:B65">
+    <cfRule type="expression" dxfId="65" priority="89" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:V65">
-    <cfRule type="expression" dxfId="4" priority="10">
+  <conditionalFormatting sqref="AD7:AE65 N7:O65 R7:S65 V7:W65 Z7:AA65">
+    <cfRule type="cellIs" dxfId="59" priority="39" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C65">
+    <cfRule type="expression" dxfId="58" priority="59" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N7:O65 R7:S65 V7:W65 Z7:AA65 AD7:AE65">
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="lessThan">
+  <conditionalFormatting sqref="D7:D65">
+    <cfRule type="expression" dxfId="57" priority="58" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E65">
+    <cfRule type="expression" dxfId="56" priority="57" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F65">
+    <cfRule type="expression" dxfId="55" priority="56" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G65">
+    <cfRule type="expression" dxfId="54" priority="55" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H65">
+    <cfRule type="expression" dxfId="53" priority="54" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7:I65">
+    <cfRule type="expression" dxfId="52" priority="53" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7:J65">
+    <cfRule type="expression" dxfId="51" priority="52" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:K65">
+    <cfRule type="expression" dxfId="50" priority="51" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:L65">
+    <cfRule type="expression" dxfId="49" priority="50" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M65">
+    <cfRule type="expression" dxfId="48" priority="49" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:N65">
+    <cfRule type="expression" dxfId="47" priority="48" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O7:O65">
+    <cfRule type="expression" dxfId="46" priority="47" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:P65">
+    <cfRule type="expression" dxfId="45" priority="46" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q7:Q65">
+    <cfRule type="expression" dxfId="44" priority="45" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R7:R65">
+    <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S65">
+    <cfRule type="expression" dxfId="42" priority="43" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T7:T65">
+    <cfRule type="expression" dxfId="41" priority="42" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U7:U65">
+    <cfRule type="expression" dxfId="40" priority="41" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V7:V65">
+    <cfRule type="expression" dxfId="39" priority="40" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W7:W65">
+    <cfRule type="expression" dxfId="38" priority="60" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X7:X65">
+    <cfRule type="expression" dxfId="37" priority="38" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Y65">
+    <cfRule type="expression" dxfId="36" priority="37" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z7:Z65">
+    <cfRule type="expression" dxfId="35" priority="36" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA65">
+    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB7:AB65">
+    <cfRule type="expression" dxfId="33" priority="34" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC65">
+    <cfRule type="expression" dxfId="32" priority="33" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD65">
+    <cfRule type="expression" dxfId="31" priority="32" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AE65">
+    <cfRule type="expression" dxfId="30" priority="31" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AE65 N7:O65 R7:S65 V7:W65 Z7:AA65">
+    <cfRule type="cellIs" dxfId="29" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V7:W65 Z7:AA65 AD7:AE65 N7:O65 R7:S65">
-    <cfRule type="cellIs" dxfId="2" priority="40" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W7:AE65">
-    <cfRule type="expression" dxfId="1" priority="31" stopIfTrue="1">
+  <conditionalFormatting sqref="C7:C65">
+    <cfRule type="expression" dxfId="28" priority="29" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X7:AE65">
+  <conditionalFormatting sqref="D7:D65">
+    <cfRule type="expression" dxfId="27" priority="28">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E65">
+    <cfRule type="expression" dxfId="26" priority="27">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F65">
+    <cfRule type="expression" dxfId="25" priority="26">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G65">
+    <cfRule type="expression" dxfId="24" priority="25">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H65">
+    <cfRule type="expression" dxfId="23" priority="24">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7:I65">
+    <cfRule type="expression" dxfId="22" priority="23">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7:J65">
+    <cfRule type="expression" dxfId="21" priority="22">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:K65">
+    <cfRule type="expression" dxfId="20" priority="21">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:L65">
+    <cfRule type="expression" dxfId="19" priority="20">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M65">
+    <cfRule type="expression" dxfId="18" priority="19">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:N65">
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O7:O65">
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:P65">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q7:Q65">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R7:R65">
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S65">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T7:T65">
+    <cfRule type="expression" dxfId="11" priority="12">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U7:U65">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V7:V65">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W7:W65">
+    <cfRule type="expression" dxfId="8" priority="30" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X7:X65">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Y65">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z7:Z65">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA65">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB7:AB65">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC65">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD65">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AE65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>

--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02ABF1C4-BD9E-A846-8D24-F3E21D4C21E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB99C0D9-F878-1842-BB47-DE1D0141D6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2720" yWindow="500" windowWidth="24460" windowHeight="16360" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
   <sheets>
     <sheet name="promotoria" sheetId="2" r:id="rId1"/>
@@ -665,7 +665,23 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="70">
+  <dxfs count="72">
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <left style="hair">
@@ -1138,6 +1154,22 @@
         <extend val="0"/>
         <color indexed="10"/>
       </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <left style="hair">
           <color indexed="64"/>
@@ -1830,7 +1862,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="69" headerRowBorderDxfId="68" tableBorderDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="71" headerRowBorderDxfId="70" tableBorderDxfId="69">
   <autoFilter ref="A3:P5" xr:uid="{A29DCA76-5097-2F45-94DA-4B121F22F1F5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{A2D27468-D390-E245-85A6-B90C4BDF0CE1}" name="Polizas_Pagadas_Año_Anterior"/>
@@ -2179,7 +2211,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="1">
-        <v>46099</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="46" thickBot="1" x14ac:dyDescent="0.25">
@@ -2255,25 +2287,25 @@
         <v>122</v>
       </c>
       <c r="B5" s="15">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C5" s="15">
-        <v>-72</v>
+        <v>-66</v>
       </c>
       <c r="D5" s="16">
-        <v>-0.5901639344262295</v>
+        <v>-0.54098360655737698</v>
       </c>
       <c r="E5" s="15">
         <v>4684.3999999999996</v>
       </c>
       <c r="F5" s="15">
-        <v>2670.98</v>
+        <v>2927.66</v>
       </c>
       <c r="G5" s="15">
-        <v>-2013.42</v>
+        <v>-1756.74</v>
       </c>
       <c r="H5" s="16">
-        <v>-0.42981385022628293</v>
+        <v>-0.37501921270600291</v>
       </c>
       <c r="I5" s="15">
         <v>2</v>
@@ -2318,7 +2350,7 @@
   <sheetData>
     <row r="1" spans="1:31" ht="33" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>46099</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2494,64 +2526,64 @@
       <c r="J5" s="19"/>
       <c r="K5" s="19"/>
       <c r="L5" s="15">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="M5" s="15">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="N5" s="15">
-        <v>-43</v>
+        <v>-63</v>
       </c>
       <c r="O5" s="16">
-        <v>-0.49425287356321834</v>
+        <v>-0.49606299212598426</v>
       </c>
       <c r="P5" s="15">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="Q5" s="15">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="R5" s="15">
-        <v>-40</v>
+        <v>-66</v>
       </c>
       <c r="S5" s="16">
-        <v>-0.51282051282051277</v>
+        <v>-0.54098360655737698</v>
       </c>
       <c r="T5" s="15">
-        <v>3345.28</v>
+        <v>4754.3900000000003</v>
       </c>
       <c r="U5" s="15">
-        <v>162.23999999999981</v>
+        <v>1112.4400000000003</v>
       </c>
       <c r="V5" s="15">
-        <v>-3183.0400000000004</v>
+        <v>-3641.9499999999994</v>
       </c>
       <c r="W5" s="16">
-        <v>-0.95150181748612972</v>
+        <v>-0.76601835356375891</v>
       </c>
       <c r="X5" s="15">
-        <v>3065.0899999999988</v>
+        <v>4684.4000000000005</v>
       </c>
       <c r="Y5" s="15">
-        <v>1888.5900000000001</v>
+        <v>2927.6599999999994</v>
       </c>
       <c r="Z5" s="15">
-        <v>-1176.5000000000002</v>
+        <v>-1756.7399999999998</v>
       </c>
       <c r="AA5" s="16">
-        <v>-0.38383864747854035</v>
+        <v>-0.37501921270600314</v>
       </c>
       <c r="AB5" s="15">
-        <v>21.1402</v>
+        <v>29.353999999999996</v>
       </c>
       <c r="AC5" s="15">
-        <v>31.525700000000001</v>
+        <v>57.281699999999994</v>
       </c>
       <c r="AD5" s="15">
-        <v>10.3855</v>
+        <v>27.927700000000005</v>
       </c>
       <c r="AE5" s="16">
-        <v>0.4912678214964854</v>
+        <v>0.95141036996661454</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
@@ -3162,49 +3194,49 @@
         <v>8</v>
       </c>
       <c r="M12" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N12" s="11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="O12" s="12">
-        <v>-0.5</v>
+        <v>-0.375</v>
       </c>
       <c r="P12" s="11">
         <v>8</v>
       </c>
       <c r="Q12" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R12" s="11">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="S12" s="12">
-        <v>-0.625</v>
+        <v>-0.5</v>
       </c>
       <c r="T12" s="11">
         <v>279.27999999999997</v>
       </c>
       <c r="U12" s="11">
-        <v>179.67</v>
+        <v>205.06</v>
       </c>
       <c r="V12" s="11">
-        <v>-99.61</v>
+        <v>-74.22</v>
       </c>
       <c r="W12" s="12">
-        <v>-0.35670000000000002</v>
+        <v>-0.26579999999999998</v>
       </c>
       <c r="X12" s="11">
         <v>574.09</v>
       </c>
       <c r="Y12" s="11">
-        <v>73.45</v>
+        <v>170.7</v>
       </c>
       <c r="Z12" s="11">
-        <v>-500.64</v>
+        <v>-403.39</v>
       </c>
       <c r="AA12" s="12">
-        <v>-0.87209999999999999</v>
+        <v>-0.70269999999999999</v>
       </c>
       <c r="AB12" s="11">
         <v>3.1593</v>
@@ -3673,13 +3705,13 @@
         <v>588.49</v>
       </c>
       <c r="Y17" s="11">
-        <v>699.82</v>
+        <v>702.8</v>
       </c>
       <c r="Z17" s="11">
-        <v>111.33</v>
+        <v>114.31</v>
       </c>
       <c r="AA17" s="12">
-        <v>0.18920000000000001</v>
+        <v>0.19420000000000001</v>
       </c>
       <c r="AB17" s="11">
         <v>0.69879999999999998</v>
@@ -4017,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="M21" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N21" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O21" s="12">
         <v>1</v>
@@ -4041,10 +4073,10 @@
         <v>0</v>
       </c>
       <c r="U21" s="11">
-        <v>111.57</v>
+        <v>139</v>
       </c>
       <c r="V21" s="11">
-        <v>111.57</v>
+        <v>139</v>
       </c>
       <c r="W21" s="12">
         <v>1</v>
@@ -4908,13 +4940,13 @@
         <v>227.28</v>
       </c>
       <c r="Y30" s="11">
-        <v>97.57</v>
+        <v>99.18</v>
       </c>
       <c r="Z30" s="11">
-        <v>-129.71</v>
+        <v>-128.1</v>
       </c>
       <c r="AA30" s="12">
-        <v>-0.57069999999999999</v>
+        <v>-0.56359999999999999</v>
       </c>
       <c r="AB30" s="11">
         <v>0.1235</v>
@@ -4967,61 +4999,61 @@
         <v>7</v>
       </c>
       <c r="M31" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N31" s="11">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="O31" s="12">
-        <v>-0.42859999999999998</v>
+        <v>-0.28570000000000001</v>
       </c>
       <c r="P31" s="11">
         <v>7</v>
       </c>
       <c r="Q31" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R31" s="11">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="S31" s="12">
-        <v>-0.57140000000000002</v>
+        <v>-0.28570000000000001</v>
       </c>
       <c r="T31" s="11">
         <v>212.51</v>
       </c>
       <c r="U31" s="11">
-        <v>96.98</v>
+        <v>132.76</v>
       </c>
       <c r="V31" s="11">
-        <v>-115.53</v>
+        <v>-79.75</v>
       </c>
       <c r="W31" s="12">
-        <v>-0.54359999999999997</v>
+        <v>-0.37530000000000002</v>
       </c>
       <c r="X31" s="11">
         <v>187.2</v>
       </c>
       <c r="Y31" s="11">
-        <v>56.92</v>
+        <v>122.51</v>
       </c>
       <c r="Z31" s="11">
-        <v>-130.28</v>
+        <v>-64.69</v>
       </c>
       <c r="AA31" s="12">
-        <v>-0.69589999999999996</v>
+        <v>-0.34560000000000002</v>
       </c>
       <c r="AB31" s="11">
         <v>0.79920000000000002</v>
       </c>
       <c r="AC31" s="11">
-        <v>1.3084</v>
+        <v>1.4389000000000001</v>
       </c>
       <c r="AD31" s="11">
-        <v>0.50919999999999999</v>
+        <v>0.63970000000000005</v>
       </c>
       <c r="AE31" s="12">
-        <v>0.6371</v>
+        <v>0.8004</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.2">
@@ -5074,13 +5106,13 @@
         <v>2</v>
       </c>
       <c r="Q32" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32" s="11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S32" s="12">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="T32" s="11">
         <v>49.3</v>
@@ -5098,13 +5130,13 @@
         <v>80.510000000000005</v>
       </c>
       <c r="Y32" s="11">
-        <v>30.65</v>
+        <v>65.56</v>
       </c>
       <c r="Z32" s="11">
-        <v>-49.86</v>
+        <v>-14.95</v>
       </c>
       <c r="AA32" s="12">
-        <v>-0.61929999999999996</v>
+        <v>-0.1857</v>
       </c>
       <c r="AB32" s="11">
         <v>0</v>
@@ -5193,13 +5225,13 @@
         <v>73</v>
       </c>
       <c r="Y33" s="11">
-        <v>26.42</v>
+        <v>28.89</v>
       </c>
       <c r="Z33" s="11">
-        <v>-46.58</v>
+        <v>-44.11</v>
       </c>
       <c r="AA33" s="12">
-        <v>-0.6381</v>
+        <v>-0.60419999999999996</v>
       </c>
       <c r="AB33" s="11">
         <v>3.1848999999999998</v>
@@ -5288,13 +5320,13 @@
         <v>63.59</v>
       </c>
       <c r="Y34" s="11">
-        <v>98.63</v>
+        <v>104.69</v>
       </c>
       <c r="Z34" s="11">
-        <v>35.04</v>
+        <v>41.1</v>
       </c>
       <c r="AA34" s="12">
-        <v>0.55100000000000005</v>
+        <v>0.64629999999999999</v>
       </c>
       <c r="AB34" s="11">
         <v>0</v>
@@ -5490,13 +5522,13 @@
         <v>4.0427</v>
       </c>
       <c r="AC36" s="11">
-        <v>2.7980999999999998</v>
+        <v>7.7786</v>
       </c>
       <c r="AD36" s="11">
-        <v>-1.2445999999999999</v>
+        <v>3.7359</v>
       </c>
       <c r="AE36" s="12">
-        <v>-0.30790000000000001</v>
+        <v>0.92410000000000003</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.2">
@@ -5858,13 +5890,13 @@
         <v>29.29</v>
       </c>
       <c r="Y40" s="11">
-        <v>16.809999999999999</v>
+        <v>18.170000000000002</v>
       </c>
       <c r="Z40" s="11">
-        <v>-12.48</v>
+        <v>-11.12</v>
       </c>
       <c r="AA40" s="12">
-        <v>-0.42609999999999998</v>
+        <v>-0.37969999999999998</v>
       </c>
       <c r="AB40" s="11">
         <v>0</v>
@@ -6238,13 +6270,13 @@
         <v>44.35</v>
       </c>
       <c r="Y44" s="11">
-        <v>19.739999999999998</v>
+        <v>26.54</v>
       </c>
       <c r="Z44" s="11">
-        <v>-24.61</v>
+        <v>-17.809999999999999</v>
       </c>
       <c r="AA44" s="12">
-        <v>-0.55489999999999995</v>
+        <v>-0.40160000000000001</v>
       </c>
       <c r="AB44" s="11">
         <v>0</v>
@@ -6998,13 +7030,13 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="Y52" s="11">
-        <v>13.31</v>
+        <v>15.04</v>
       </c>
       <c r="Z52" s="11">
-        <v>10.86</v>
+        <v>12.59</v>
       </c>
       <c r="AA52" s="12">
-        <v>4.4326999999999996</v>
+        <v>5.1387999999999998</v>
       </c>
       <c r="AB52" s="11">
         <v>0</v>
@@ -7188,10 +7220,10 @@
         <v>0</v>
       </c>
       <c r="Y54" s="11">
-        <v>67.709999999999994</v>
+        <v>69.489999999999995</v>
       </c>
       <c r="Z54" s="11">
-        <v>67.709999999999994</v>
+        <v>69.489999999999995</v>
       </c>
       <c r="AA54" s="12">
         <v>1</v>
@@ -7283,10 +7315,10 @@
         <v>0</v>
       </c>
       <c r="Y55" s="11">
-        <v>42.53</v>
+        <v>45.5</v>
       </c>
       <c r="Z55" s="11">
-        <v>42.53</v>
+        <v>45.5</v>
       </c>
       <c r="AA55" s="12">
         <v>1</v>
@@ -7354,13 +7386,13 @@
         <v>0</v>
       </c>
       <c r="Q56" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="11">
         <v>0</v>
@@ -7378,10 +7410,10 @@
         <v>0</v>
       </c>
       <c r="Y56" s="11">
-        <v>23.77</v>
+        <v>25.46</v>
       </c>
       <c r="Z56" s="11">
-        <v>23.77</v>
+        <v>25.46</v>
       </c>
       <c r="AA56" s="12">
         <v>1</v>
@@ -7473,10 +7505,10 @@
         <v>0</v>
       </c>
       <c r="Y57" s="11">
-        <v>18.93</v>
+        <v>20.6</v>
       </c>
       <c r="Z57" s="11">
-        <v>18.93</v>
+        <v>20.6</v>
       </c>
       <c r="AA57" s="12">
         <v>1</v>
@@ -7639,10 +7671,10 @@
         <v>0</v>
       </c>
       <c r="Q59" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R59" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S59" s="12">
         <v>1</v>
@@ -7663,10 +7695,10 @@
         <v>0</v>
       </c>
       <c r="Y59" s="11">
-        <v>110.56</v>
+        <v>136.78</v>
       </c>
       <c r="Z59" s="11">
-        <v>110.56</v>
+        <v>136.78</v>
       </c>
       <c r="AA59" s="12">
         <v>1</v>
@@ -7948,10 +7980,10 @@
         <v>0</v>
       </c>
       <c r="Y62" s="11">
-        <v>3.16</v>
+        <v>4.75</v>
       </c>
       <c r="Z62" s="11">
-        <v>3.16</v>
+        <v>4.75</v>
       </c>
       <c r="AA62" s="12">
         <v>1</v>
@@ -8087,7 +8119,7 @@
         <v>74</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I64" s="22">
         <v>46007</v>
@@ -8262,169 +8294,169 @@
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
   </mergeCells>
+  <conditionalFormatting sqref="AD7:AE65 N7:O65 R7:S65 V7:W65 Z7:AA65">
+    <cfRule type="cellIs" dxfId="61" priority="40" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A7:B65">
-    <cfRule type="expression" dxfId="66" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="61" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B65">
-    <cfRule type="expression" dxfId="65" priority="89" stopIfTrue="1">
+  <conditionalFormatting sqref="C7:C65">
+    <cfRule type="expression" dxfId="59" priority="60" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7:D65">
+    <cfRule type="expression" dxfId="58" priority="59" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E65">
+    <cfRule type="expression" dxfId="57" priority="58" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F65">
+    <cfRule type="expression" dxfId="56" priority="57" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G65">
+    <cfRule type="expression" dxfId="55" priority="56" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H65">
+    <cfRule type="expression" dxfId="54" priority="55" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7:I65">
+    <cfRule type="expression" dxfId="53" priority="54" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7:J65">
+    <cfRule type="expression" dxfId="52" priority="53" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:K65">
+    <cfRule type="expression" dxfId="51" priority="52" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:L65">
+    <cfRule type="expression" dxfId="50" priority="51" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M65">
+    <cfRule type="expression" dxfId="49" priority="50" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:N65">
+    <cfRule type="expression" dxfId="48" priority="49" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O7:O65">
+    <cfRule type="expression" dxfId="47" priority="48" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:P65">
+    <cfRule type="expression" dxfId="46" priority="47" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q7:Q65">
+    <cfRule type="expression" dxfId="45" priority="46" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R7:R65">
+    <cfRule type="expression" dxfId="44" priority="45" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S65">
+    <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T7:T65">
+    <cfRule type="expression" dxfId="42" priority="43" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U7:U65">
+    <cfRule type="expression" dxfId="41" priority="42" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V7:V65">
+    <cfRule type="expression" dxfId="40" priority="41" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W7:W65">
+    <cfRule type="expression" dxfId="39" priority="62" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X7:X65">
+    <cfRule type="expression" dxfId="38" priority="39" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Y65">
+    <cfRule type="expression" dxfId="37" priority="38" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z7:Z65">
+    <cfRule type="expression" dxfId="36" priority="37" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA65">
+    <cfRule type="expression" dxfId="35" priority="36" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB7:AB65">
+    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC65">
+    <cfRule type="expression" dxfId="33" priority="34" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD65">
+    <cfRule type="expression" dxfId="32" priority="33" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AE65">
+    <cfRule type="expression" dxfId="31" priority="32" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD7:AE65 N7:O65 R7:S65 V7:W65 Z7:AA65">
-    <cfRule type="cellIs" dxfId="59" priority="39" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C65">
-    <cfRule type="expression" dxfId="58" priority="59" stopIfTrue="1">
+  <conditionalFormatting sqref="A7:B65">
+    <cfRule type="expression" dxfId="29" priority="30" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D65">
-    <cfRule type="expression" dxfId="57" priority="58" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E65">
-    <cfRule type="expression" dxfId="56" priority="57" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F65">
-    <cfRule type="expression" dxfId="55" priority="56" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G65">
-    <cfRule type="expression" dxfId="54" priority="55" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H65">
-    <cfRule type="expression" dxfId="53" priority="54" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I65">
-    <cfRule type="expression" dxfId="52" priority="53" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J65">
-    <cfRule type="expression" dxfId="51" priority="52" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7:K65">
-    <cfRule type="expression" dxfId="50" priority="51" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L7:L65">
-    <cfRule type="expression" dxfId="49" priority="50" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M65">
-    <cfRule type="expression" dxfId="48" priority="49" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N7:N65">
-    <cfRule type="expression" dxfId="47" priority="48" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O7:O65">
-    <cfRule type="expression" dxfId="46" priority="47" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P7:P65">
-    <cfRule type="expression" dxfId="45" priority="46" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q7:Q65">
-    <cfRule type="expression" dxfId="44" priority="45" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R7:R65">
-    <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S7:S65">
-    <cfRule type="expression" dxfId="42" priority="43" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T7:T65">
-    <cfRule type="expression" dxfId="41" priority="42" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U7:U65">
-    <cfRule type="expression" dxfId="40" priority="41" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V7:V65">
-    <cfRule type="expression" dxfId="39" priority="40" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W7:W65">
-    <cfRule type="expression" dxfId="38" priority="60" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X7:X65">
-    <cfRule type="expression" dxfId="37" priority="38" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Y65">
-    <cfRule type="expression" dxfId="36" priority="37" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z7:Z65">
-    <cfRule type="expression" dxfId="35" priority="36" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA65">
-    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB7:AB65">
-    <cfRule type="expression" dxfId="33" priority="34" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC7:AC65">
-    <cfRule type="expression" dxfId="32" priority="33" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AD65">
-    <cfRule type="expression" dxfId="31" priority="32" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE7:AE65">
-    <cfRule type="expression" dxfId="30" priority="31" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AE65 N7:O65 R7:S65 V7:W65 Z7:AA65">
-    <cfRule type="cellIs" dxfId="29" priority="9" operator="lessThan">
-      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C65">
@@ -8528,7 +8560,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W7:W65">
-    <cfRule type="expression" dxfId="8" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="31" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>

--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB99C0D9-F878-1842-BB47-DE1D0141D6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76F1B9D-9BAB-5F4A-B99D-8F494D9AD651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
   <sheets>
     <sheet name="promotoria" sheetId="2" r:id="rId1"/>
@@ -665,1013 +665,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="72">
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <border>
         <left style="hair">
@@ -1862,7 +856,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="71" headerRowBorderDxfId="70" tableBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
   <autoFilter ref="A3:P5" xr:uid="{A29DCA76-5097-2F45-94DA-4B121F22F1F5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{A2D27468-D390-E245-85A6-B90C4BDF0CE1}" name="Polizas_Pagadas_Año_Anterior"/>
@@ -8294,312 +7288,37 @@
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
   </mergeCells>
-  <conditionalFormatting sqref="AD7:AE65 N7:O65 R7:S65 V7:W65 Z7:AA65">
-    <cfRule type="cellIs" dxfId="61" priority="40" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="A7:C65">
+    <cfRule type="expression" dxfId="6" priority="29" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:W65">
+    <cfRule type="expression" dxfId="5" priority="41" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7:V65">
+    <cfRule type="expression" dxfId="4" priority="10">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:O65 R7:S65 V7:W65 Z7:AA65 AD7:AE65">
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B65">
-    <cfRule type="expression" dxfId="60" priority="61" stopIfTrue="1">
+  <conditionalFormatting sqref="V7:W65 Z7:AA65 AD7:AE65 N7:O65 R7:S65">
+    <cfRule type="cellIs" dxfId="2" priority="40" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W7:AE65">
+    <cfRule type="expression" dxfId="1" priority="31" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C65">
-    <cfRule type="expression" dxfId="59" priority="60" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D65">
-    <cfRule type="expression" dxfId="58" priority="59" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E65">
-    <cfRule type="expression" dxfId="57" priority="58" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F65">
-    <cfRule type="expression" dxfId="56" priority="57" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G65">
-    <cfRule type="expression" dxfId="55" priority="56" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H65">
-    <cfRule type="expression" dxfId="54" priority="55" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I65">
-    <cfRule type="expression" dxfId="53" priority="54" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J65">
-    <cfRule type="expression" dxfId="52" priority="53" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7:K65">
-    <cfRule type="expression" dxfId="51" priority="52" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L7:L65">
-    <cfRule type="expression" dxfId="50" priority="51" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M65">
-    <cfRule type="expression" dxfId="49" priority="50" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N7:N65">
-    <cfRule type="expression" dxfId="48" priority="49" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O7:O65">
-    <cfRule type="expression" dxfId="47" priority="48" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P7:P65">
-    <cfRule type="expression" dxfId="46" priority="47" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q7:Q65">
-    <cfRule type="expression" dxfId="45" priority="46" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R7:R65">
-    <cfRule type="expression" dxfId="44" priority="45" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S7:S65">
-    <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T7:T65">
-    <cfRule type="expression" dxfId="42" priority="43" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U7:U65">
-    <cfRule type="expression" dxfId="41" priority="42" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V7:V65">
-    <cfRule type="expression" dxfId="40" priority="41" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W7:W65">
-    <cfRule type="expression" dxfId="39" priority="62" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X7:X65">
-    <cfRule type="expression" dxfId="38" priority="39" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Y65">
-    <cfRule type="expression" dxfId="37" priority="38" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z7:Z65">
-    <cfRule type="expression" dxfId="36" priority="37" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA65">
-    <cfRule type="expression" dxfId="35" priority="36" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB7:AB65">
-    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC7:AC65">
-    <cfRule type="expression" dxfId="33" priority="34" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AD65">
-    <cfRule type="expression" dxfId="32" priority="33" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE7:AE65">
-    <cfRule type="expression" dxfId="31" priority="32" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AE65 N7:O65 R7:S65 V7:W65 Z7:AA65">
-    <cfRule type="cellIs" dxfId="30" priority="9" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B65">
-    <cfRule type="expression" dxfId="29" priority="30" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C65">
-    <cfRule type="expression" dxfId="28" priority="29" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D65">
-    <cfRule type="expression" dxfId="27" priority="28">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E65">
-    <cfRule type="expression" dxfId="26" priority="27">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F65">
-    <cfRule type="expression" dxfId="25" priority="26">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G65">
-    <cfRule type="expression" dxfId="24" priority="25">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H65">
-    <cfRule type="expression" dxfId="23" priority="24">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I65">
-    <cfRule type="expression" dxfId="22" priority="23">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J65">
-    <cfRule type="expression" dxfId="21" priority="22">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7:K65">
-    <cfRule type="expression" dxfId="20" priority="21">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L7:L65">
-    <cfRule type="expression" dxfId="19" priority="20">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M65">
-    <cfRule type="expression" dxfId="18" priority="19">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N7:N65">
-    <cfRule type="expression" dxfId="17" priority="18">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O7:O65">
-    <cfRule type="expression" dxfId="16" priority="17">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P7:P65">
-    <cfRule type="expression" dxfId="15" priority="16">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q7:Q65">
-    <cfRule type="expression" dxfId="14" priority="15">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R7:R65">
-    <cfRule type="expression" dxfId="13" priority="14">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S7:S65">
-    <cfRule type="expression" dxfId="12" priority="13">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T7:T65">
-    <cfRule type="expression" dxfId="11" priority="12">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U7:U65">
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V7:V65">
-    <cfRule type="expression" dxfId="9" priority="10">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W7:W65">
-    <cfRule type="expression" dxfId="8" priority="31" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X7:X65">
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Y65">
-    <cfRule type="expression" dxfId="6" priority="7">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z7:Z65">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA65">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB7:AB65">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC7:AC65">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AD65">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE7:AE65">
+  <conditionalFormatting sqref="X7:AE65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>

--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76F1B9D-9BAB-5F4A-B99D-8F494D9AD651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8E8360-929D-C74A-BB41-15CF60D3ADB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
+    <workbookView xWindow="100" yWindow="500" windowWidth="24460" windowHeight="16320" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
   <sheets>
     <sheet name="promotoria" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="136">
   <si>
     <t>Asesor</t>
   </si>
@@ -439,6 +439,12 @@
   </si>
   <si>
     <t>MONSERRAT VELASCO SANTOS</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>MARIO IVAN ROMERO GONZALEZ</t>
   </si>
 </sst>
 </file>
@@ -449,7 +455,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -495,6 +501,12 @@
     <font>
       <sz val="10"/>
       <color indexed="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -665,7 +677,455 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="136">
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <left style="hair">
@@ -722,6 +1182,486 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -793,17 +1733,1007 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="double">
+          <color indexed="22"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="double">
           <color indexed="22"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="double">
-          <color indexed="22"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -842,6 +2772,132 @@
       </border>
       <protection locked="1" hidden="1"/>
     </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -856,7 +2912,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="128" headerRowBorderDxfId="126" tableBorderDxfId="127">
   <autoFilter ref="A3:P5" xr:uid="{A29DCA76-5097-2F45-94DA-4B121F22F1F5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{A2D27468-D390-E245-85A6-B90C4BDF0CE1}" name="Polizas_Pagadas_Año_Anterior"/>
@@ -1205,7 +3261,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="1">
-        <v>46101</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="46" thickBot="1" x14ac:dyDescent="0.25">
@@ -1281,52 +3337,53 @@
         <v>122</v>
       </c>
       <c r="B5" s="15">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C5" s="15">
-        <v>-66</v>
+        <v>-56</v>
       </c>
       <c r="D5" s="16">
-        <v>-0.54098360655737698</v>
+        <v>-0.45901639344262291</v>
       </c>
       <c r="E5" s="15">
         <v>4684.3999999999996</v>
       </c>
       <c r="F5" s="15">
-        <v>2927.66</v>
+        <v>3371.71</v>
       </c>
       <c r="G5" s="15">
-        <v>-1756.74</v>
+        <v>-1312.69</v>
       </c>
       <c r="H5" s="16">
-        <v>-0.37501921270600291</v>
+        <v>-0.2802258560327896</v>
       </c>
       <c r="I5" s="15">
         <v>2</v>
       </c>
       <c r="J5" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="15">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="16">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="M5" s="15">
         <v>313.24</v>
       </c>
       <c r="N5" s="15">
-        <v>0</v>
+        <v>72.052099999999996</v>
       </c>
       <c r="O5" s="15">
-        <v>-313.24</v>
+        <v>-241.18790000000001</v>
       </c>
       <c r="P5" s="16">
-        <v>-1</v>
+        <v>-0.76997797216192065</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -1336,7 +3393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6395312-445F-3747-AD98-F1F037E33F44}">
-  <dimension ref="A1:AE65"/>
+  <dimension ref="A1:AE66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
@@ -1344,7 +3401,7 @@
   <sheetData>
     <row r="1" spans="1:31" ht="33" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>46101</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1713,61 +3770,61 @@
         <v>4</v>
       </c>
       <c r="M7" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N7" s="11">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="O7" s="12">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="P7" s="11">
         <v>4</v>
       </c>
       <c r="Q7" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" s="11">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="S7" s="12">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="T7" s="11">
         <v>134.32</v>
       </c>
       <c r="U7" s="11">
-        <v>61.9</v>
+        <v>134.38999999999999</v>
       </c>
       <c r="V7" s="11">
-        <v>-72.42</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="W7" s="12">
-        <v>-0.53920000000000001</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="X7" s="11">
         <v>238.93</v>
       </c>
       <c r="Y7" s="11">
-        <v>115.62</v>
+        <v>178.07</v>
       </c>
       <c r="Z7" s="11">
-        <v>-123.31</v>
+        <v>-60.86</v>
       </c>
       <c r="AA7" s="12">
-        <v>-0.5161</v>
+        <v>-0.25469999999999998</v>
       </c>
       <c r="AB7" s="11">
         <v>5.3364000000000003</v>
       </c>
       <c r="AC7" s="11">
-        <v>6.8959000000000001</v>
+        <v>8.8035999999999994</v>
       </c>
       <c r="AD7" s="11">
-        <v>1.5595000000000001</v>
+        <v>3.4672000000000001</v>
       </c>
       <c r="AE7" s="12">
-        <v>0.29220000000000002</v>
+        <v>0.64970000000000006</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
@@ -1939,13 +3996,13 @@
         <v>31.29</v>
       </c>
       <c r="Y9" s="11">
-        <v>7.18</v>
+        <v>9.02</v>
       </c>
       <c r="Z9" s="11">
-        <v>-24.11</v>
+        <v>-22.27</v>
       </c>
       <c r="AA9" s="12">
-        <v>-0.77049999999999996</v>
+        <v>-0.7117</v>
       </c>
       <c r="AB9" s="11">
         <v>0</v>
@@ -2010,37 +4067,37 @@
         <v>1</v>
       </c>
       <c r="Q10" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T10" s="11">
         <v>29.23</v>
       </c>
       <c r="U10" s="11">
-        <v>25.2</v>
+        <v>25.39</v>
       </c>
       <c r="V10" s="11">
-        <v>-4.03</v>
+        <v>-3.84</v>
       </c>
       <c r="W10" s="12">
-        <v>-0.13789999999999999</v>
+        <v>-0.13139999999999999</v>
       </c>
       <c r="X10" s="11">
         <v>31.17</v>
       </c>
       <c r="Y10" s="11">
-        <v>5.51</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="Z10" s="11">
-        <v>-25.66</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="AA10" s="12">
-        <v>-0.82320000000000004</v>
+        <v>8.1199999999999994E-2</v>
       </c>
       <c r="AB10" s="11">
         <v>0</v>
@@ -2188,61 +4245,61 @@
         <v>8</v>
       </c>
       <c r="M12" s="11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N12" s="11">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="O12" s="12">
-        <v>-0.375</v>
+        <v>0</v>
       </c>
       <c r="P12" s="11">
         <v>8</v>
       </c>
       <c r="Q12" s="11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R12" s="11">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="S12" s="12">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="T12" s="11">
         <v>279.27999999999997</v>
       </c>
       <c r="U12" s="11">
-        <v>205.06</v>
+        <v>357.98</v>
       </c>
       <c r="V12" s="11">
-        <v>-74.22</v>
+        <v>78.7</v>
       </c>
       <c r="W12" s="12">
-        <v>-0.26579999999999998</v>
+        <v>0.28179999999999999</v>
       </c>
       <c r="X12" s="11">
         <v>574.09</v>
       </c>
       <c r="Y12" s="11">
-        <v>170.7</v>
+        <v>249.15</v>
       </c>
       <c r="Z12" s="11">
-        <v>-403.39</v>
+        <v>-324.94</v>
       </c>
       <c r="AA12" s="12">
-        <v>-0.70269999999999999</v>
+        <v>-0.56599999999999995</v>
       </c>
       <c r="AB12" s="11">
         <v>3.1593</v>
       </c>
       <c r="AC12" s="11">
-        <v>17.987200000000001</v>
+        <v>19.947700000000001</v>
       </c>
       <c r="AD12" s="11">
-        <v>14.8279</v>
+        <v>16.788399999999999</v>
       </c>
       <c r="AE12" s="12">
-        <v>4.6933999999999996</v>
+        <v>5.3140000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
@@ -2319,25 +4376,25 @@
         <v>99.88</v>
       </c>
       <c r="Y13" s="11">
-        <v>30.24</v>
+        <v>39.76</v>
       </c>
       <c r="Z13" s="11">
-        <v>-69.64</v>
+        <v>-60.12</v>
       </c>
       <c r="AA13" s="12">
-        <v>-0.69720000000000004</v>
+        <v>-0.60189999999999999</v>
       </c>
       <c r="AB13" s="11">
         <v>6.0643000000000002</v>
       </c>
       <c r="AC13" s="11">
-        <v>4.2088000000000001</v>
+        <v>6.2045000000000003</v>
       </c>
       <c r="AD13" s="11">
-        <v>-1.8554999999999999</v>
+        <v>0.14019999999999999</v>
       </c>
       <c r="AE13" s="12">
-        <v>-0.30599999999999999</v>
+        <v>2.3099999999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
@@ -2414,13 +4471,13 @@
         <v>27.86</v>
       </c>
       <c r="Y14" s="11">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Z14" s="11">
-        <v>-25.47</v>
+        <v>-25.46</v>
       </c>
       <c r="AA14" s="12">
-        <v>-0.91420000000000001</v>
+        <v>-0.91390000000000005</v>
       </c>
       <c r="AB14" s="11">
         <v>0</v>
@@ -2521,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="AC15" s="11">
-        <v>3.2017000000000002</v>
+        <v>6.7150999999999996</v>
       </c>
       <c r="AD15" s="11">
-        <v>3.2017000000000002</v>
+        <v>6.7150999999999996</v>
       </c>
       <c r="AE15" s="12">
         <v>1</v>
@@ -2663,61 +4720,61 @@
         <v>4</v>
       </c>
       <c r="M17" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N17" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O17" s="12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P17" s="11">
         <v>6</v>
       </c>
       <c r="Q17" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R17" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="12">
-        <v>0</v>
+        <v>0.16669999999999999</v>
       </c>
       <c r="T17" s="11">
         <v>855.64</v>
       </c>
       <c r="U17" s="11">
-        <v>560.76</v>
+        <v>670.28</v>
       </c>
       <c r="V17" s="11">
-        <v>-294.88</v>
+        <v>-185.36</v>
       </c>
       <c r="W17" s="12">
-        <v>-0.34460000000000002</v>
+        <v>-0.21659999999999999</v>
       </c>
       <c r="X17" s="11">
         <v>588.49</v>
       </c>
       <c r="Y17" s="11">
-        <v>702.8</v>
+        <v>760.86</v>
       </c>
       <c r="Z17" s="11">
-        <v>114.31</v>
+        <v>172.37</v>
       </c>
       <c r="AA17" s="12">
-        <v>0.19420000000000001</v>
+        <v>0.29289999999999999</v>
       </c>
       <c r="AB17" s="11">
         <v>0.69879999999999998</v>
       </c>
       <c r="AC17" s="11">
-        <v>1.4301999999999999</v>
+        <v>1.8223</v>
       </c>
       <c r="AD17" s="11">
-        <v>0.73140000000000005</v>
+        <v>1.1234999999999999</v>
       </c>
       <c r="AE17" s="12">
-        <v>1.0467</v>
+        <v>1.6077999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -2794,25 +4851,25 @@
         <v>25.91</v>
       </c>
       <c r="Y18" s="11">
-        <v>12.61</v>
+        <v>12.65</v>
       </c>
       <c r="Z18" s="11">
-        <v>-13.3</v>
+        <v>-13.26</v>
       </c>
       <c r="AA18" s="12">
-        <v>-0.51329999999999998</v>
+        <v>-0.51180000000000003</v>
       </c>
       <c r="AB18" s="11">
         <v>1.4147000000000001</v>
       </c>
       <c r="AC18" s="11">
-        <v>1.4668000000000001</v>
+        <v>1.4715</v>
       </c>
       <c r="AD18" s="11">
-        <v>5.21E-2</v>
+        <v>5.6800000000000003E-2</v>
       </c>
       <c r="AE18" s="12">
-        <v>3.6799999999999999E-2</v>
+        <v>4.0099999999999997E-2</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.2">
@@ -2889,13 +4946,13 @@
         <v>4.34</v>
       </c>
       <c r="Y19" s="11">
-        <v>15.46</v>
+        <v>15.5</v>
       </c>
       <c r="Z19" s="11">
-        <v>11.12</v>
+        <v>11.16</v>
       </c>
       <c r="AA19" s="12">
-        <v>2.5621999999999998</v>
+        <v>2.5714000000000001</v>
       </c>
       <c r="AB19" s="11">
         <v>0</v>
@@ -2972,37 +5029,37 @@
         <v>328.85</v>
       </c>
       <c r="U20" s="11">
-        <v>126.73</v>
+        <v>126.17</v>
       </c>
       <c r="V20" s="11">
-        <v>-202.12</v>
+        <v>-202.68</v>
       </c>
       <c r="W20" s="12">
-        <v>-0.61460000000000004</v>
+        <v>-0.61629999999999996</v>
       </c>
       <c r="X20" s="11">
         <v>353.8</v>
       </c>
       <c r="Y20" s="11">
-        <v>216.24</v>
+        <v>219.62</v>
       </c>
       <c r="Z20" s="11">
-        <v>-137.56</v>
+        <v>-134.18</v>
       </c>
       <c r="AA20" s="12">
-        <v>-0.38879999999999998</v>
+        <v>-0.37930000000000003</v>
       </c>
       <c r="AB20" s="11">
         <v>1.8688</v>
       </c>
       <c r="AC20" s="11">
-        <v>0.36919999999999997</v>
+        <v>0.37190000000000001</v>
       </c>
       <c r="AD20" s="11">
-        <v>-1.4996</v>
+        <v>-1.4968999999999999</v>
       </c>
       <c r="AE20" s="12">
-        <v>-0.8024</v>
+        <v>-0.80100000000000005</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.2">
@@ -3055,10 +5112,10 @@
         <v>0</v>
       </c>
       <c r="Q21" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R21" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S21" s="12">
         <v>1</v>
@@ -3067,10 +5124,10 @@
         <v>0</v>
       </c>
       <c r="U21" s="11">
-        <v>139</v>
+        <v>139.21</v>
       </c>
       <c r="V21" s="11">
-        <v>139</v>
+        <v>139.21</v>
       </c>
       <c r="W21" s="12">
         <v>1</v>
@@ -3079,25 +5136,25 @@
         <v>11.56</v>
       </c>
       <c r="Y21" s="11">
-        <v>59.85</v>
+        <v>66.790000000000006</v>
       </c>
       <c r="Z21" s="11">
-        <v>48.29</v>
+        <v>55.23</v>
       </c>
       <c r="AA21" s="12">
-        <v>4.1772999999999998</v>
+        <v>4.7777000000000003</v>
       </c>
       <c r="AB21" s="11">
         <v>0.31490000000000001</v>
       </c>
       <c r="AC21" s="11">
-        <v>1.4286000000000001</v>
+        <v>1.4336</v>
       </c>
       <c r="AD21" s="11">
-        <v>1.1136999999999999</v>
+        <v>1.1187</v>
       </c>
       <c r="AE21" s="12">
-        <v>3.5367000000000002</v>
+        <v>3.5526</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.2">
@@ -3174,13 +5231,13 @@
         <v>11.23</v>
       </c>
       <c r="Y22" s="11">
-        <v>10.14</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="Z22" s="11">
-        <v>-1.0900000000000001</v>
+        <v>-1.02</v>
       </c>
       <c r="AA22" s="12">
-        <v>-9.7100000000000006E-2</v>
+        <v>-9.0800000000000006E-2</v>
       </c>
       <c r="AB22" s="11">
         <v>0</v>
@@ -3269,13 +5326,13 @@
         <v>11.9</v>
       </c>
       <c r="Y23" s="11">
-        <v>20.2</v>
+        <v>20.23</v>
       </c>
       <c r="Z23" s="11">
-        <v>8.3000000000000007</v>
+        <v>8.33</v>
       </c>
       <c r="AA23" s="12">
-        <v>0.69750000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AB23" s="11">
         <v>0</v>
@@ -3542,25 +5599,25 @@
         <v>58.68</v>
       </c>
       <c r="U26" s="11">
-        <v>-0.1</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="V26" s="11">
-        <v>-58.78</v>
+        <v>-58.97</v>
       </c>
       <c r="W26" s="12">
-        <v>-1.0017</v>
+        <v>-1.0048999999999999</v>
       </c>
       <c r="X26" s="11">
         <v>78.84</v>
       </c>
       <c r="Y26" s="11">
-        <v>48.79</v>
+        <v>53.4</v>
       </c>
       <c r="Z26" s="11">
-        <v>-30.05</v>
+        <v>-25.44</v>
       </c>
       <c r="AA26" s="12">
-        <v>-0.38119999999999998</v>
+        <v>-0.32269999999999999</v>
       </c>
       <c r="AB26" s="11">
         <v>0.5141</v>
@@ -3649,13 +5706,13 @@
         <v>46.3</v>
       </c>
       <c r="Y27" s="11">
-        <v>19.75</v>
+        <v>23.85</v>
       </c>
       <c r="Z27" s="11">
-        <v>-26.55</v>
+        <v>-22.45</v>
       </c>
       <c r="AA27" s="12">
-        <v>-0.57340000000000002</v>
+        <v>-0.4849</v>
       </c>
       <c r="AB27" s="11">
         <v>0</v>
@@ -3744,13 +5801,13 @@
         <v>3.09</v>
       </c>
       <c r="Y28" s="11">
-        <v>11.47</v>
+        <v>13.24</v>
       </c>
       <c r="Z28" s="11">
-        <v>8.3800000000000008</v>
+        <v>10.15</v>
       </c>
       <c r="AA28" s="12">
-        <v>2.7120000000000002</v>
+        <v>3.2848000000000002</v>
       </c>
       <c r="AB28" s="11">
         <v>0</v>
@@ -3803,61 +5860,61 @@
         <v>4</v>
       </c>
       <c r="M29" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="O29" s="12">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="P29" s="11">
         <v>4</v>
       </c>
       <c r="Q29" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="S29" s="12">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="T29" s="11">
         <v>175.1</v>
       </c>
       <c r="U29" s="11">
-        <v>0</v>
+        <v>20.6</v>
       </c>
       <c r="V29" s="11">
-        <v>-175.1</v>
+        <v>-154.5</v>
       </c>
       <c r="W29" s="12">
-        <v>-1</v>
+        <v>-0.88239999999999996</v>
       </c>
       <c r="X29" s="11">
         <v>215.39</v>
       </c>
       <c r="Y29" s="11">
-        <v>28.61</v>
+        <v>39.979999999999997</v>
       </c>
       <c r="Z29" s="11">
-        <v>-186.78</v>
+        <v>-175.41</v>
       </c>
       <c r="AA29" s="12">
-        <v>-0.86719999999999997</v>
+        <v>-0.81440000000000001</v>
       </c>
       <c r="AB29" s="11">
         <v>1.528</v>
       </c>
       <c r="AC29" s="11">
-        <v>2.7492999999999999</v>
+        <v>3.9302000000000001</v>
       </c>
       <c r="AD29" s="11">
-        <v>1.2213000000000001</v>
+        <v>2.4022000000000001</v>
       </c>
       <c r="AE29" s="12">
-        <v>0.79930000000000001</v>
+        <v>1.5721000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.2">
@@ -3922,37 +5979,37 @@
         <v>224.88</v>
       </c>
       <c r="U30" s="11">
-        <v>112.38</v>
+        <v>112.57</v>
       </c>
       <c r="V30" s="11">
-        <v>-112.5</v>
+        <v>-112.31</v>
       </c>
       <c r="W30" s="12">
-        <v>-0.50029999999999997</v>
+        <v>-0.49940000000000001</v>
       </c>
       <c r="X30" s="11">
         <v>227.28</v>
       </c>
       <c r="Y30" s="11">
-        <v>99.18</v>
+        <v>107.29</v>
       </c>
       <c r="Z30" s="11">
-        <v>-128.1</v>
+        <v>-119.99</v>
       </c>
       <c r="AA30" s="12">
-        <v>-0.56359999999999999</v>
+        <v>-0.52790000000000004</v>
       </c>
       <c r="AB30" s="11">
         <v>0.1235</v>
       </c>
       <c r="AC30" s="11">
-        <v>3.3443000000000001</v>
+        <v>3.3654000000000002</v>
       </c>
       <c r="AD30" s="11">
-        <v>3.2208000000000001</v>
+        <v>3.2418999999999998</v>
       </c>
       <c r="AE30" s="12">
-        <v>26.0794</v>
+        <v>26.2502</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.2">
@@ -3993,13 +6050,13 @@
         <v>7</v>
       </c>
       <c r="M31" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N31" s="11">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="O31" s="12">
-        <v>-0.28570000000000001</v>
+        <v>0</v>
       </c>
       <c r="P31" s="11">
         <v>7</v>
@@ -4017,37 +6074,37 @@
         <v>212.51</v>
       </c>
       <c r="U31" s="11">
-        <v>132.76</v>
+        <v>185.33</v>
       </c>
       <c r="V31" s="11">
-        <v>-79.75</v>
+        <v>-27.18</v>
       </c>
       <c r="W31" s="12">
-        <v>-0.37530000000000002</v>
+        <v>-0.12790000000000001</v>
       </c>
       <c r="X31" s="11">
         <v>187.2</v>
       </c>
       <c r="Y31" s="11">
-        <v>122.51</v>
+        <v>126.07</v>
       </c>
       <c r="Z31" s="11">
-        <v>-64.69</v>
+        <v>-61.13</v>
       </c>
       <c r="AA31" s="12">
-        <v>-0.34560000000000002</v>
+        <v>-0.32650000000000001</v>
       </c>
       <c r="AB31" s="11">
         <v>0.79920000000000002</v>
       </c>
       <c r="AC31" s="11">
-        <v>1.4389000000000001</v>
+        <v>1.8523000000000001</v>
       </c>
       <c r="AD31" s="11">
-        <v>0.63970000000000005</v>
+        <v>1.0530999999999999</v>
       </c>
       <c r="AE31" s="12">
-        <v>0.8004</v>
+        <v>1.3177000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.2">
@@ -4088,13 +6145,13 @@
         <v>2</v>
       </c>
       <c r="M32" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P32" s="11">
         <v>2</v>
@@ -4112,34 +6169,34 @@
         <v>49.3</v>
       </c>
       <c r="U32" s="11">
-        <v>62.71</v>
+        <v>99.07</v>
       </c>
       <c r="V32" s="11">
-        <v>13.41</v>
+        <v>49.77</v>
       </c>
       <c r="W32" s="12">
-        <v>0.27200000000000002</v>
+        <v>1.0095000000000001</v>
       </c>
       <c r="X32" s="11">
         <v>80.510000000000005</v>
       </c>
       <c r="Y32" s="11">
-        <v>65.56</v>
+        <v>71.16</v>
       </c>
       <c r="Z32" s="11">
-        <v>-14.95</v>
+        <v>-9.35</v>
       </c>
       <c r="AA32" s="12">
-        <v>-0.1857</v>
+        <v>-0.11609999999999999</v>
       </c>
       <c r="AB32" s="11">
         <v>0</v>
       </c>
       <c r="AC32" s="11">
-        <v>0.89339999999999997</v>
+        <v>0.89580000000000004</v>
       </c>
       <c r="AD32" s="11">
-        <v>0.89339999999999997</v>
+        <v>0.89580000000000004</v>
       </c>
       <c r="AE32" s="12">
         <v>1</v>
@@ -4207,25 +6264,25 @@
         <v>67.260000000000005</v>
       </c>
       <c r="U33" s="11">
-        <v>34.11</v>
+        <v>34.369999999999997</v>
       </c>
       <c r="V33" s="11">
-        <v>-33.15</v>
+        <v>-32.89</v>
       </c>
       <c r="W33" s="12">
-        <v>-0.4929</v>
+        <v>-0.48899999999999999</v>
       </c>
       <c r="X33" s="11">
         <v>73</v>
       </c>
       <c r="Y33" s="11">
-        <v>28.89</v>
+        <v>32.06</v>
       </c>
       <c r="Z33" s="11">
-        <v>-44.11</v>
+        <v>-40.94</v>
       </c>
       <c r="AA33" s="12">
-        <v>-0.60419999999999996</v>
+        <v>-0.56079999999999997</v>
       </c>
       <c r="AB33" s="11">
         <v>3.1848999999999998</v>
@@ -4314,13 +6371,13 @@
         <v>63.59</v>
       </c>
       <c r="Y34" s="11">
-        <v>104.69</v>
+        <v>132.61000000000001</v>
       </c>
       <c r="Z34" s="11">
-        <v>41.1</v>
+        <v>69.02</v>
       </c>
       <c r="AA34" s="12">
-        <v>0.64629999999999999</v>
+        <v>1.0853999999999999</v>
       </c>
       <c r="AB34" s="11">
         <v>0</v>
@@ -4504,25 +6561,25 @@
         <v>303.52999999999997</v>
       </c>
       <c r="Y36" s="11">
-        <v>64.94</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="Z36" s="11">
-        <v>-238.59</v>
+        <v>-238.54</v>
       </c>
       <c r="AA36" s="12">
-        <v>-0.78610000000000002</v>
+        <v>-0.78590000000000004</v>
       </c>
       <c r="AB36" s="11">
         <v>4.0427</v>
       </c>
       <c r="AC36" s="11">
-        <v>7.7786</v>
+        <v>9.2260000000000009</v>
       </c>
       <c r="AD36" s="11">
-        <v>3.7359</v>
+        <v>5.1833</v>
       </c>
       <c r="AE36" s="12">
-        <v>0.92410000000000003</v>
+        <v>1.2821</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.2">
@@ -4599,13 +6656,13 @@
         <v>86.18</v>
       </c>
       <c r="Y37" s="11">
-        <v>119.74</v>
+        <v>145.55000000000001</v>
       </c>
       <c r="Z37" s="11">
-        <v>33.56</v>
+        <v>59.37</v>
       </c>
       <c r="AA37" s="12">
-        <v>0.38940000000000002</v>
+        <v>0.68889999999999996</v>
       </c>
       <c r="AB37" s="11">
         <v>0</v>
@@ -4694,13 +6751,13 @@
         <v>103.45</v>
       </c>
       <c r="Y38" s="11">
-        <v>8.83</v>
+        <v>10.45</v>
       </c>
       <c r="Z38" s="11">
-        <v>-94.62</v>
+        <v>-93</v>
       </c>
       <c r="AA38" s="12">
-        <v>-0.91459999999999997</v>
+        <v>-0.89900000000000002</v>
       </c>
       <c r="AB38" s="11">
         <v>3.3999999999999998E-3</v>
@@ -4801,13 +6858,13 @@
         <v>9.8100000000000007E-2</v>
       </c>
       <c r="AC39" s="11">
-        <v>0</v>
+        <v>0.1643</v>
       </c>
       <c r="AD39" s="11">
-        <v>-9.8100000000000007E-2</v>
+        <v>6.6199999999999995E-2</v>
       </c>
       <c r="AE39" s="12">
-        <v>-1</v>
+        <v>0.67479999999999996</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.2">
@@ -4884,13 +6941,13 @@
         <v>29.29</v>
       </c>
       <c r="Y40" s="11">
-        <v>18.170000000000002</v>
+        <v>23.88</v>
       </c>
       <c r="Z40" s="11">
-        <v>-11.12</v>
+        <v>-5.41</v>
       </c>
       <c r="AA40" s="12">
-        <v>-0.37969999999999998</v>
+        <v>-0.1847</v>
       </c>
       <c r="AB40" s="11">
         <v>0</v>
@@ -5169,13 +7226,13 @@
         <v>62.03</v>
       </c>
       <c r="Y43" s="11">
-        <v>8.52</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="Z43" s="11">
-        <v>-53.51</v>
+        <v>-53.49</v>
       </c>
       <c r="AA43" s="12">
-        <v>-0.86260000000000003</v>
+        <v>-0.86229999999999996</v>
       </c>
       <c r="AB43" s="11">
         <v>0</v>
@@ -5264,13 +7321,13 @@
         <v>44.35</v>
       </c>
       <c r="Y44" s="11">
-        <v>26.54</v>
+        <v>26.61</v>
       </c>
       <c r="Z44" s="11">
-        <v>-17.809999999999999</v>
+        <v>-17.739999999999998</v>
       </c>
       <c r="AA44" s="12">
-        <v>-0.40160000000000001</v>
+        <v>-0.4</v>
       </c>
       <c r="AB44" s="11">
         <v>0</v>
@@ -5347,37 +7404,37 @@
         <v>272.62</v>
       </c>
       <c r="U45" s="11">
-        <v>227.64</v>
+        <v>227.99</v>
       </c>
       <c r="V45" s="11">
-        <v>-44.98</v>
+        <v>-44.63</v>
       </c>
       <c r="W45" s="12">
-        <v>-0.16500000000000001</v>
+        <v>-0.16370000000000001</v>
       </c>
       <c r="X45" s="11">
         <v>156.13999999999999</v>
       </c>
       <c r="Y45" s="11">
-        <v>167.4</v>
+        <v>172.46</v>
       </c>
       <c r="Z45" s="11">
-        <v>11.26</v>
+        <v>16.32</v>
       </c>
       <c r="AA45" s="12">
-        <v>7.2099999999999997E-2</v>
+        <v>0.1045</v>
       </c>
       <c r="AB45" s="11">
         <v>0.2029</v>
       </c>
       <c r="AC45" s="11">
-        <v>0.4365</v>
+        <v>0.4375</v>
       </c>
       <c r="AD45" s="11">
-        <v>0.2336</v>
+        <v>0.2346</v>
       </c>
       <c r="AE45" s="12">
-        <v>1.1513</v>
+        <v>1.1561999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
@@ -5454,13 +7511,13 @@
         <v>208.83</v>
       </c>
       <c r="Y46" s="11">
-        <v>28.49</v>
+        <v>42.88</v>
       </c>
       <c r="Z46" s="11">
-        <v>-180.34</v>
+        <v>-165.95</v>
       </c>
       <c r="AA46" s="12">
-        <v>-0.86360000000000003</v>
+        <v>-0.79469999999999996</v>
       </c>
       <c r="AB46" s="11">
         <v>0</v>
@@ -5644,13 +7701,13 @@
         <v>86.46</v>
       </c>
       <c r="Y48" s="11">
-        <v>28.41</v>
+        <v>33.9</v>
       </c>
       <c r="Z48" s="11">
-        <v>-58.05</v>
+        <v>-52.56</v>
       </c>
       <c r="AA48" s="12">
-        <v>-0.6714</v>
+        <v>-0.6079</v>
       </c>
       <c r="AB48" s="11">
         <v>0</v>
@@ -5783,7 +7840,7 @@
         <v>60</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I50" s="22">
         <v>45736</v>
@@ -5798,13 +7855,13 @@
         <v>4</v>
       </c>
       <c r="M50" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" s="11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="O50" s="12">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="P50" s="11">
         <v>4</v>
@@ -5822,13 +7879,13 @@
         <v>133.03</v>
       </c>
       <c r="U50" s="11">
-        <v>0</v>
+        <v>20.48</v>
       </c>
       <c r="V50" s="11">
-        <v>-133.03</v>
+        <v>-112.55</v>
       </c>
       <c r="W50" s="12">
-        <v>-1</v>
+        <v>-0.84599999999999997</v>
       </c>
       <c r="X50" s="11">
         <v>131.56</v>
@@ -6024,13 +8081,13 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="Y52" s="11">
-        <v>15.04</v>
+        <v>15.06</v>
       </c>
       <c r="Z52" s="11">
-        <v>12.59</v>
+        <v>12.61</v>
       </c>
       <c r="AA52" s="12">
-        <v>5.1387999999999998</v>
+        <v>5.1468999999999996</v>
       </c>
       <c r="AB52" s="11">
         <v>0</v>
@@ -6119,13 +8176,13 @@
         <v>13.82</v>
       </c>
       <c r="Y53" s="11">
-        <v>17.690000000000001</v>
+        <v>22.09</v>
       </c>
       <c r="Z53" s="11">
-        <v>3.87</v>
+        <v>8.27</v>
       </c>
       <c r="AA53" s="12">
-        <v>0.28000000000000003</v>
+        <v>0.59840000000000004</v>
       </c>
       <c r="AB53" s="11">
         <v>0</v>
@@ -6214,10 +8271,10 @@
         <v>0</v>
       </c>
       <c r="Y54" s="11">
-        <v>69.489999999999995</v>
+        <v>69.42</v>
       </c>
       <c r="Z54" s="11">
-        <v>69.489999999999995</v>
+        <v>69.42</v>
       </c>
       <c r="AA54" s="12">
         <v>1</v>
@@ -6309,10 +8366,10 @@
         <v>0</v>
       </c>
       <c r="Y55" s="11">
-        <v>45.5</v>
+        <v>47.98</v>
       </c>
       <c r="Z55" s="11">
-        <v>45.5</v>
+        <v>47.98</v>
       </c>
       <c r="AA55" s="12">
         <v>1</v>
@@ -6392,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="U56" s="11">
-        <v>20.22</v>
+        <v>20.37</v>
       </c>
       <c r="V56" s="11">
-        <v>20.22</v>
+        <v>20.37</v>
       </c>
       <c r="W56" s="12">
         <v>1</v>
@@ -6404,10 +8461,10 @@
         <v>0</v>
       </c>
       <c r="Y56" s="11">
-        <v>25.46</v>
+        <v>27.97</v>
       </c>
       <c r="Z56" s="11">
-        <v>25.46</v>
+        <v>27.97</v>
       </c>
       <c r="AA56" s="12">
         <v>1</v>
@@ -6499,10 +8556,10 @@
         <v>0</v>
       </c>
       <c r="Y57" s="11">
-        <v>20.6</v>
+        <v>22.36</v>
       </c>
       <c r="Z57" s="11">
-        <v>20.6</v>
+        <v>22.36</v>
       </c>
       <c r="AA57" s="12">
         <v>1</v>
@@ -6677,10 +8734,10 @@
         <v>0</v>
       </c>
       <c r="U59" s="11">
-        <v>75.849999999999994</v>
+        <v>76.040000000000006</v>
       </c>
       <c r="V59" s="11">
-        <v>75.849999999999994</v>
+        <v>76.040000000000006</v>
       </c>
       <c r="W59" s="12">
         <v>1</v>
@@ -6689,10 +8746,10 @@
         <v>0</v>
       </c>
       <c r="Y59" s="11">
-        <v>136.78</v>
+        <v>143.38</v>
       </c>
       <c r="Z59" s="11">
-        <v>136.78</v>
+        <v>143.38</v>
       </c>
       <c r="AA59" s="12">
         <v>1</v>
@@ -6701,10 +8758,10 @@
         <v>0</v>
       </c>
       <c r="AC59" s="11">
-        <v>1.1674</v>
+        <v>1.407</v>
       </c>
       <c r="AD59" s="11">
-        <v>1.1674</v>
+        <v>1.407</v>
       </c>
       <c r="AE59" s="12">
         <v>1</v>
@@ -6784,10 +8841,10 @@
         <v>0</v>
       </c>
       <c r="Y60" s="11">
-        <v>19.690000000000001</v>
+        <v>53.86</v>
       </c>
       <c r="Z60" s="11">
-        <v>19.690000000000001</v>
+        <v>53.86</v>
       </c>
       <c r="AA60" s="12">
         <v>1</v>
@@ -6879,10 +8936,10 @@
         <v>0</v>
       </c>
       <c r="Y61" s="11">
-        <v>63.6</v>
+        <v>67.16</v>
       </c>
       <c r="Z61" s="11">
-        <v>63.6</v>
+        <v>67.16</v>
       </c>
       <c r="AA61" s="12">
         <v>1</v>
@@ -6974,10 +9031,10 @@
         <v>0</v>
       </c>
       <c r="Y62" s="11">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="Z62" s="11">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="AA62" s="12">
         <v>1</v>
@@ -7021,13 +9078,13 @@
         <v>127</v>
       </c>
       <c r="I63" s="22">
-        <v>46006</v>
+        <v>46111</v>
       </c>
       <c r="J63" s="22">
-        <v>46023</v>
+        <v>46111</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="L63" s="11">
         <v>0</v>
@@ -7069,10 +9126,10 @@
         <v>0</v>
       </c>
       <c r="Y63" s="11">
-        <v>70.02</v>
+        <v>72.05</v>
       </c>
       <c r="Z63" s="11">
-        <v>70.02</v>
+        <v>72.05</v>
       </c>
       <c r="AA63" s="12">
         <v>1</v>
@@ -7128,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N64" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O64" s="12">
         <v>1</v>
@@ -7140,10 +9197,10 @@
         <v>0</v>
       </c>
       <c r="Q64" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R64" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S64" s="12">
         <v>1</v>
@@ -7152,10 +9209,10 @@
         <v>0</v>
       </c>
       <c r="U64" s="11">
-        <v>121.31</v>
+        <v>142.31</v>
       </c>
       <c r="V64" s="11">
-        <v>121.31</v>
+        <v>142.31</v>
       </c>
       <c r="W64" s="12">
         <v>1</v>
@@ -7164,10 +9221,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="11">
-        <v>31.24</v>
+        <v>33.06</v>
       </c>
       <c r="Z64" s="11">
-        <v>31.24</v>
+        <v>33.06</v>
       </c>
       <c r="AA64" s="12">
         <v>1</v>
@@ -7223,10 +9280,10 @@
         <v>0</v>
       </c>
       <c r="M65" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N65" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O65" s="12">
         <v>1</v>
@@ -7235,10 +9292,10 @@
         <v>0</v>
       </c>
       <c r="Q65" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R65" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S65" s="12">
         <v>1</v>
@@ -7247,10 +9304,10 @@
         <v>0</v>
       </c>
       <c r="U65" s="11">
-        <v>119.03</v>
+        <v>155.6</v>
       </c>
       <c r="V65" s="11">
-        <v>119.03</v>
+        <v>155.6</v>
       </c>
       <c r="W65" s="12">
         <v>1</v>
@@ -7259,10 +9316,10 @@
         <v>0</v>
       </c>
       <c r="Y65" s="11">
-        <v>9.92</v>
+        <v>15.45</v>
       </c>
       <c r="Z65" s="11">
-        <v>9.92</v>
+        <v>15.45</v>
       </c>
       <c r="AA65" s="12">
         <v>1</v>
@@ -7277,6 +9334,101 @@
         <v>0</v>
       </c>
       <c r="AE65" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A66" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C66" s="10">
+        <v>2043</v>
+      </c>
+      <c r="D66" s="10">
+        <v>2856</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F66" s="10">
+        <v>118069</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="I66" s="22">
+        <v>46105</v>
+      </c>
+      <c r="J66" s="22">
+        <v>46113</v>
+      </c>
+      <c r="K66" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="L66" s="11">
+        <v>0</v>
+      </c>
+      <c r="M66" s="11">
+        <v>1</v>
+      </c>
+      <c r="N66" s="11">
+        <v>1</v>
+      </c>
+      <c r="O66" s="12">
+        <v>1</v>
+      </c>
+      <c r="P66" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="11">
+        <v>1</v>
+      </c>
+      <c r="R66" s="11">
+        <v>1</v>
+      </c>
+      <c r="S66" s="12">
+        <v>1</v>
+      </c>
+      <c r="T66" s="11">
+        <v>0</v>
+      </c>
+      <c r="U66" s="11">
+        <v>21.34</v>
+      </c>
+      <c r="V66" s="11">
+        <v>21.34</v>
+      </c>
+      <c r="W66" s="12">
+        <v>1</v>
+      </c>
+      <c r="X66" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="11">
+        <v>1.78</v>
+      </c>
+      <c r="Z66" s="11">
+        <v>1.78</v>
+      </c>
+      <c r="AA66" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="12">
         <v>0</v>
       </c>
     </row>
@@ -7288,37 +9440,312 @@
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A7:C65">
-    <cfRule type="expression" dxfId="6" priority="29" stopIfTrue="1">
+  <conditionalFormatting sqref="AD7:AE66 N7:O66 R7:S66 V7:W66 Z7:AA66">
+    <cfRule type="cellIs" dxfId="61" priority="40" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:B66">
+    <cfRule type="expression" dxfId="60" priority="61" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:W65">
-    <cfRule type="expression" dxfId="5" priority="41" stopIfTrue="1">
+  <conditionalFormatting sqref="C7:C66">
+    <cfRule type="expression" dxfId="59" priority="60" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:V65">
-    <cfRule type="expression" dxfId="4" priority="10">
+  <conditionalFormatting sqref="D7:D66">
+    <cfRule type="expression" dxfId="58" priority="59" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N7:O65 R7:S65 V7:W65 Z7:AA65 AD7:AE65">
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="lessThan">
+  <conditionalFormatting sqref="E7:E66">
+    <cfRule type="expression" dxfId="57" priority="58" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F66">
+    <cfRule type="expression" dxfId="56" priority="57" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G66">
+    <cfRule type="expression" dxfId="55" priority="56" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H66">
+    <cfRule type="expression" dxfId="54" priority="55" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7:I66">
+    <cfRule type="expression" dxfId="53" priority="54" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7:J66">
+    <cfRule type="expression" dxfId="52" priority="53" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:K66">
+    <cfRule type="expression" dxfId="51" priority="52" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:L66">
+    <cfRule type="expression" dxfId="50" priority="51" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M66">
+    <cfRule type="expression" dxfId="49" priority="50" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:N66">
+    <cfRule type="expression" dxfId="48" priority="49" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O7:O66">
+    <cfRule type="expression" dxfId="47" priority="48" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:P66">
+    <cfRule type="expression" dxfId="46" priority="47" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q7:Q66">
+    <cfRule type="expression" dxfId="45" priority="46" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R7:R66">
+    <cfRule type="expression" dxfId="44" priority="45" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S66">
+    <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T7:T66">
+    <cfRule type="expression" dxfId="42" priority="43" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U7:U66">
+    <cfRule type="expression" dxfId="41" priority="42" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V7:V66">
+    <cfRule type="expression" dxfId="40" priority="41" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W7:W66">
+    <cfRule type="expression" dxfId="39" priority="62" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X7:X66">
+    <cfRule type="expression" dxfId="38" priority="39" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Y66">
+    <cfRule type="expression" dxfId="37" priority="38" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z7:Z66">
+    <cfRule type="expression" dxfId="36" priority="37" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA66">
+    <cfRule type="expression" dxfId="35" priority="36" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB7:AB66">
+    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC66">
+    <cfRule type="expression" dxfId="33" priority="34" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD66">
+    <cfRule type="expression" dxfId="32" priority="33" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AE66">
+    <cfRule type="expression" dxfId="31" priority="32" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AE66 N7:O66 R7:S66 V7:W66 Z7:AA66">
+    <cfRule type="cellIs" dxfId="30" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V7:W65 Z7:AA65 AD7:AE65 N7:O65 R7:S65">
-    <cfRule type="cellIs" dxfId="2" priority="40" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W7:AE65">
-    <cfRule type="expression" dxfId="1" priority="31" stopIfTrue="1">
+  <conditionalFormatting sqref="A7:B66">
+    <cfRule type="expression" dxfId="29" priority="30" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X7:AE65">
+  <conditionalFormatting sqref="C7:C66">
+    <cfRule type="expression" dxfId="28" priority="29" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7:D66">
+    <cfRule type="expression" dxfId="27" priority="28">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E66">
+    <cfRule type="expression" dxfId="26" priority="27">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F66">
+    <cfRule type="expression" dxfId="25" priority="26">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G66">
+    <cfRule type="expression" dxfId="24" priority="25">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H66">
+    <cfRule type="expression" dxfId="23" priority="24">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7:I66">
+    <cfRule type="expression" dxfId="22" priority="23">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7:J66">
+    <cfRule type="expression" dxfId="21" priority="22">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:K66">
+    <cfRule type="expression" dxfId="20" priority="21">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:L66">
+    <cfRule type="expression" dxfId="19" priority="20">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M66">
+    <cfRule type="expression" dxfId="18" priority="19">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:N66">
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O7:O66">
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:P66">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q7:Q66">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R7:R66">
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S66">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T7:T66">
+    <cfRule type="expression" dxfId="11" priority="12">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U7:U66">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V7:V66">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W7:W66">
+    <cfRule type="expression" dxfId="8" priority="31" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X7:X66">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Y66">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z7:Z66">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA66">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB7:AB66">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC66">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD66">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AE66">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>

--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8E8360-929D-C74A-BB41-15CF60D3ADB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99484549-DB6B-D94E-9138-9FD40A100275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="500" windowWidth="24460" windowHeight="16320" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
   <sheets>
     <sheet name="promotoria" sheetId="2" r:id="rId1"/>
@@ -677,2101 +677,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="136">
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="double">
-          <color indexed="22"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="double">
-          <color indexed="22"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="9"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="18"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="22"/>
-        </left>
-        <right style="double">
-          <color indexed="22"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="1"/>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <border>
         <left style="hair">
@@ -2898,6 +804,56 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="double">
+          <color indexed="22"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="double">
+          <color indexed="22"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="9"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="18"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="22"/>
+        </left>
+        <right style="double">
+          <color indexed="22"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="1"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2912,7 +868,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="128" headerRowBorderDxfId="126" tableBorderDxfId="127">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
   <autoFilter ref="A3:P5" xr:uid="{A29DCA76-5097-2F45-94DA-4B121F22F1F5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{A2D27468-D390-E245-85A6-B90C4BDF0CE1}" name="Polizas_Pagadas_Año_Anterior"/>
@@ -9440,312 +7396,37 @@
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
   </mergeCells>
-  <conditionalFormatting sqref="AD7:AE66 N7:O66 R7:S66 V7:W66 Z7:AA66">
-    <cfRule type="cellIs" dxfId="61" priority="40" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="A7:C66">
+    <cfRule type="expression" dxfId="6" priority="29" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:W66">
+    <cfRule type="expression" dxfId="5" priority="41" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7:V66">
+    <cfRule type="expression" dxfId="4" priority="10">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:O66 R7:S66 V7:W66 Z7:AA66 AD7:AE66">
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B66">
-    <cfRule type="expression" dxfId="60" priority="61" stopIfTrue="1">
+  <conditionalFormatting sqref="V7:W66 Z7:AA66 AD7:AE66 N7:O66 R7:S66">
+    <cfRule type="cellIs" dxfId="2" priority="40" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W7:AE66">
+    <cfRule type="expression" dxfId="1" priority="31" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C66">
-    <cfRule type="expression" dxfId="59" priority="60" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D66">
-    <cfRule type="expression" dxfId="58" priority="59" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E66">
-    <cfRule type="expression" dxfId="57" priority="58" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F66">
-    <cfRule type="expression" dxfId="56" priority="57" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G66">
-    <cfRule type="expression" dxfId="55" priority="56" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H66">
-    <cfRule type="expression" dxfId="54" priority="55" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I66">
-    <cfRule type="expression" dxfId="53" priority="54" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J66">
-    <cfRule type="expression" dxfId="52" priority="53" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7:K66">
-    <cfRule type="expression" dxfId="51" priority="52" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L7:L66">
-    <cfRule type="expression" dxfId="50" priority="51" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M66">
-    <cfRule type="expression" dxfId="49" priority="50" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N7:N66">
-    <cfRule type="expression" dxfId="48" priority="49" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O7:O66">
-    <cfRule type="expression" dxfId="47" priority="48" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P7:P66">
-    <cfRule type="expression" dxfId="46" priority="47" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q7:Q66">
-    <cfRule type="expression" dxfId="45" priority="46" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R7:R66">
-    <cfRule type="expression" dxfId="44" priority="45" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S7:S66">
-    <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T7:T66">
-    <cfRule type="expression" dxfId="42" priority="43" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U7:U66">
-    <cfRule type="expression" dxfId="41" priority="42" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V7:V66">
-    <cfRule type="expression" dxfId="40" priority="41" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W7:W66">
-    <cfRule type="expression" dxfId="39" priority="62" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X7:X66">
-    <cfRule type="expression" dxfId="38" priority="39" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Y66">
-    <cfRule type="expression" dxfId="37" priority="38" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z7:Z66">
-    <cfRule type="expression" dxfId="36" priority="37" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA66">
-    <cfRule type="expression" dxfId="35" priority="36" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB7:AB66">
-    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC7:AC66">
-    <cfRule type="expression" dxfId="33" priority="34" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AD66">
-    <cfRule type="expression" dxfId="32" priority="33" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE7:AE66">
-    <cfRule type="expression" dxfId="31" priority="32" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AE66 N7:O66 R7:S66 V7:W66 Z7:AA66">
-    <cfRule type="cellIs" dxfId="30" priority="9" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B66">
-    <cfRule type="expression" dxfId="29" priority="30" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C66">
-    <cfRule type="expression" dxfId="28" priority="29" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D66">
-    <cfRule type="expression" dxfId="27" priority="28">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E66">
-    <cfRule type="expression" dxfId="26" priority="27">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F66">
-    <cfRule type="expression" dxfId="25" priority="26">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G66">
-    <cfRule type="expression" dxfId="24" priority="25">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H66">
-    <cfRule type="expression" dxfId="23" priority="24">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I66">
-    <cfRule type="expression" dxfId="22" priority="23">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J66">
-    <cfRule type="expression" dxfId="21" priority="22">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7:K66">
-    <cfRule type="expression" dxfId="20" priority="21">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L7:L66">
-    <cfRule type="expression" dxfId="19" priority="20">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M66">
-    <cfRule type="expression" dxfId="18" priority="19">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N7:N66">
-    <cfRule type="expression" dxfId="17" priority="18">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O7:O66">
-    <cfRule type="expression" dxfId="16" priority="17">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P7:P66">
-    <cfRule type="expression" dxfId="15" priority="16">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q7:Q66">
-    <cfRule type="expression" dxfId="14" priority="15">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R7:R66">
-    <cfRule type="expression" dxfId="13" priority="14">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S7:S66">
-    <cfRule type="expression" dxfId="12" priority="13">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T7:T66">
-    <cfRule type="expression" dxfId="11" priority="12">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U7:U66">
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V7:V66">
-    <cfRule type="expression" dxfId="9" priority="10">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W7:W66">
-    <cfRule type="expression" dxfId="8" priority="31" stopIfTrue="1">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X7:X66">
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Y66">
-    <cfRule type="expression" dxfId="6" priority="7">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z7:Z66">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA66">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB7:AB66">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC7:AC66">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AD66">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$B7&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE7:AE66">
+  <conditionalFormatting sqref="X7:AE66">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>

--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99484549-DB6B-D94E-9138-9FD40A100275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C41DBC-0F85-2547-AD45-E499275A69B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
   <sheets>
     <sheet name="promotoria" sheetId="2" r:id="rId1"/>

--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C41DBC-0F85-2547-AD45-E499275A69B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBB7603-FB08-1E41-86E5-4FB497F2845E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>

--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBB7603-FB08-1E41-86E5-4FB497F2845E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4E8461-310D-5344-AC16-5637620BBD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
   <sheets>
     <sheet name="promotoria" sheetId="2" r:id="rId1"/>

--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4E8461-310D-5344-AC16-5637620BBD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925BE45E-FFF4-F940-8C22-AC81EADFF646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
   <sheets>
     <sheet name="promotoria" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="137">
   <si>
     <t>Asesor</t>
   </si>
@@ -445,6 +445,9 @@
   </si>
   <si>
     <t>MARIO IVAN ROMERO GONZALEZ</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -512,7 +515,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -528,6 +531,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="48"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,7 +583,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -671,13 +680,474 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="72">
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <left style="hair">
@@ -734,6 +1204,486 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -757,50 +1707,9 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
+      <border outline="0">
+        <bottom style="double">
+          <color indexed="22"/>
         </bottom>
       </border>
     </dxf>
@@ -809,13 +1718,6 @@
         <top style="double">
           <color indexed="22"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="double">
-          <color indexed="22"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -854,6 +1756,132 @@
       </border>
       <protection locked="1" hidden="1"/>
     </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -868,7 +1896,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="64" headerRowBorderDxfId="62" tableBorderDxfId="63">
   <autoFilter ref="A3:P5" xr:uid="{A29DCA76-5097-2F45-94DA-4B121F22F1F5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{A2D27468-D390-E245-85A6-B90C4BDF0CE1}" name="Polizas_Pagadas_Año_Anterior"/>
@@ -1217,7 +2245,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="1">
-        <v>46112</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="46" thickBot="1" x14ac:dyDescent="0.25">
@@ -1290,52 +2318,52 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="15">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="B5" s="15">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C5" s="15">
-        <v>-56</v>
+        <v>-82</v>
       </c>
       <c r="D5" s="16">
-        <v>-0.45901639344262291</v>
+        <v>-0.48809523809523814</v>
       </c>
       <c r="E5" s="15">
-        <v>4684.3999999999996</v>
+        <v>8098.38</v>
       </c>
       <c r="F5" s="15">
-        <v>3371.71</v>
+        <v>4179.3500000000004</v>
       </c>
       <c r="G5" s="15">
-        <v>-1312.69</v>
+        <v>-3919.03</v>
       </c>
       <c r="H5" s="16">
-        <v>-0.2802258560327896</v>
+        <v>-0.48392764972747637</v>
       </c>
       <c r="I5" s="15">
+        <v>3</v>
+      </c>
+      <c r="J5" s="15">
         <v>2</v>
-      </c>
-      <c r="J5" s="15">
-        <v>1</v>
       </c>
       <c r="K5" s="15">
         <v>-1</v>
       </c>
       <c r="L5" s="16">
-        <v>-0.5</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="M5" s="15">
-        <v>313.24</v>
+        <v>372.32</v>
       </c>
       <c r="N5" s="15">
-        <v>72.052099999999996</v>
+        <v>106.9436</v>
       </c>
       <c r="O5" s="15">
-        <v>-241.18790000000001</v>
+        <v>-265.37639999999999</v>
       </c>
       <c r="P5" s="16">
-        <v>-0.76997797216192065</v>
+        <v>-0.7127642887838419</v>
       </c>
     </row>
   </sheetData>
@@ -1349,7 +2377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6395312-445F-3747-AD98-F1F037E33F44}">
-  <dimension ref="A1:AE66"/>
+  <dimension ref="A1:AE67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
@@ -1357,7 +2385,7 @@
   <sheetData>
     <row r="1" spans="1:31" ht="33" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>46112</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1520,78 +2548,38 @@
       <c r="AD4" s="13"/>
       <c r="AE4" s="20"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="15">
-        <v>127</v>
-      </c>
-      <c r="M5" s="15">
-        <v>64</v>
-      </c>
-      <c r="N5" s="15">
-        <v>-63</v>
-      </c>
-      <c r="O5" s="16">
-        <v>-0.49606299212598426</v>
-      </c>
-      <c r="P5" s="15">
-        <v>122</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>56</v>
-      </c>
-      <c r="R5" s="15">
-        <v>-66</v>
-      </c>
-      <c r="S5" s="16">
-        <v>-0.54098360655737698</v>
-      </c>
-      <c r="T5" s="15">
-        <v>4754.3900000000003</v>
-      </c>
-      <c r="U5" s="15">
-        <v>1112.4400000000003</v>
-      </c>
-      <c r="V5" s="15">
-        <v>-3641.9499999999994</v>
-      </c>
-      <c r="W5" s="16">
-        <v>-0.76601835356375891</v>
-      </c>
-      <c r="X5" s="15">
-        <v>4684.4000000000005</v>
-      </c>
-      <c r="Y5" s="15">
-        <v>2927.6599999999994</v>
-      </c>
-      <c r="Z5" s="15">
-        <v>-1756.7399999999998</v>
-      </c>
-      <c r="AA5" s="16">
-        <v>-0.37501921270600314</v>
-      </c>
-      <c r="AB5" s="15">
-        <v>29.353999999999996</v>
-      </c>
-      <c r="AC5" s="15">
-        <v>57.281699999999994</v>
-      </c>
-      <c r="AD5" s="15">
-        <v>27.927700000000005</v>
-      </c>
-      <c r="AE5" s="16">
-        <v>0.95141036996661454</v>
-      </c>
+    <row r="5" spans="1:31" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="27"/>
+      <c r="AC5" s="27"/>
+      <c r="AD5" s="27"/>
+      <c r="AE5" s="28"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
@@ -1723,64 +2711,64 @@
         <v>128</v>
       </c>
       <c r="L7" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M7" s="11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N7" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O7" s="12">
-        <v>0</v>
+        <v>-0.1429</v>
       </c>
       <c r="P7" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q7" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R7" s="11">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S7" s="12">
-        <v>-0.25</v>
+        <v>-0.28570000000000001</v>
       </c>
       <c r="T7" s="11">
-        <v>134.32</v>
+        <v>278.72000000000003</v>
       </c>
       <c r="U7" s="11">
-        <v>134.38999999999999</v>
+        <v>186.68</v>
       </c>
       <c r="V7" s="11">
-        <v>7.0000000000000007E-2</v>
+        <v>-92.04</v>
       </c>
       <c r="W7" s="12">
-        <v>5.0000000000000001E-4</v>
+        <v>-0.33019999999999999</v>
       </c>
       <c r="X7" s="11">
-        <v>238.93</v>
+        <v>326.55</v>
       </c>
       <c r="Y7" s="11">
-        <v>178.07</v>
+        <v>215.54</v>
       </c>
       <c r="Z7" s="11">
-        <v>-60.86</v>
+        <v>-111.01</v>
       </c>
       <c r="AA7" s="12">
-        <v>-0.25469999999999998</v>
+        <v>-0.33989999999999998</v>
       </c>
       <c r="AB7" s="11">
-        <v>5.3364000000000003</v>
+        <v>8.8199000000000005</v>
       </c>
       <c r="AC7" s="11">
-        <v>8.8035999999999994</v>
+        <v>17.076799999999999</v>
       </c>
       <c r="AD7" s="11">
-        <v>3.4672000000000001</v>
+        <v>8.2568999999999999</v>
       </c>
       <c r="AE7" s="12">
-        <v>0.64970000000000006</v>
+        <v>0.93620000000000003</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
@@ -1949,16 +2937,16 @@
         <v>-1</v>
       </c>
       <c r="X9" s="11">
-        <v>31.29</v>
+        <v>38.99</v>
       </c>
       <c r="Y9" s="11">
         <v>9.02</v>
       </c>
       <c r="Z9" s="11">
-        <v>-22.27</v>
+        <v>-29.97</v>
       </c>
       <c r="AA9" s="12">
-        <v>-0.7117</v>
+        <v>-0.76870000000000005</v>
       </c>
       <c r="AB9" s="11">
         <v>0</v>
@@ -2059,13 +3047,13 @@
         <v>0</v>
       </c>
       <c r="AC10" s="11">
-        <v>0</v>
+        <v>0.2135</v>
       </c>
       <c r="AD10" s="11">
-        <v>0</v>
+        <v>0.2135</v>
       </c>
       <c r="AE10" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
@@ -2139,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="X11" s="11">
-        <v>13.32</v>
+        <v>15.2</v>
       </c>
       <c r="Y11" s="11">
         <v>0</v>
       </c>
       <c r="Z11" s="11">
-        <v>-13.32</v>
+        <v>-15.2</v>
       </c>
       <c r="AA11" s="12">
         <v>-1</v>
@@ -2198,64 +3186,64 @@
         <v>128</v>
       </c>
       <c r="L12" s="11">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M12" s="11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N12" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O12" s="12">
-        <v>0</v>
+        <v>-7.6899999999999996E-2</v>
       </c>
       <c r="P12" s="11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q12" s="11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R12" s="11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="S12" s="12">
         <v>-0.25</v>
       </c>
       <c r="T12" s="11">
-        <v>279.27999999999997</v>
+        <v>619.97</v>
       </c>
       <c r="U12" s="11">
-        <v>357.98</v>
+        <v>570.01</v>
       </c>
       <c r="V12" s="11">
-        <v>78.7</v>
+        <v>-49.96</v>
       </c>
       <c r="W12" s="12">
-        <v>0.28179999999999999</v>
+        <v>-8.0600000000000005E-2</v>
       </c>
       <c r="X12" s="11">
-        <v>574.09</v>
+        <v>876.03</v>
       </c>
       <c r="Y12" s="11">
-        <v>249.15</v>
+        <v>394.8</v>
       </c>
       <c r="Z12" s="11">
-        <v>-324.94</v>
+        <v>-481.23</v>
       </c>
       <c r="AA12" s="12">
-        <v>-0.56599999999999995</v>
+        <v>-0.54930000000000001</v>
       </c>
       <c r="AB12" s="11">
-        <v>3.1593</v>
+        <v>11.831099999999999</v>
       </c>
       <c r="AC12" s="11">
-        <v>19.947700000000001</v>
+        <v>21.471900000000002</v>
       </c>
       <c r="AD12" s="11">
-        <v>16.788399999999999</v>
+        <v>9.6408000000000005</v>
       </c>
       <c r="AE12" s="12">
-        <v>5.3140000000000001</v>
+        <v>0.81489999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
@@ -2329,28 +3317,28 @@
         <v>-1</v>
       </c>
       <c r="X13" s="11">
-        <v>99.88</v>
+        <v>116.4</v>
       </c>
       <c r="Y13" s="11">
-        <v>39.76</v>
+        <v>44.91</v>
       </c>
       <c r="Z13" s="11">
-        <v>-60.12</v>
+        <v>-71.489999999999995</v>
       </c>
       <c r="AA13" s="12">
-        <v>-0.60189999999999999</v>
+        <v>-0.61419999999999997</v>
       </c>
       <c r="AB13" s="11">
-        <v>6.0643000000000002</v>
+        <v>6.7163000000000004</v>
       </c>
       <c r="AC13" s="11">
-        <v>6.2045000000000003</v>
+        <v>8.6708999999999996</v>
       </c>
       <c r="AD13" s="11">
-        <v>0.14019999999999999</v>
+        <v>1.9545999999999999</v>
       </c>
       <c r="AE13" s="12">
-        <v>2.3099999999999999E-2</v>
+        <v>0.29099999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
@@ -2424,16 +3412,16 @@
         <v>0</v>
       </c>
       <c r="X14" s="11">
-        <v>27.86</v>
+        <v>30.5</v>
       </c>
       <c r="Y14" s="11">
         <v>2.4</v>
       </c>
       <c r="Z14" s="11">
-        <v>-25.46</v>
+        <v>-28.1</v>
       </c>
       <c r="AA14" s="12">
-        <v>-0.91390000000000005</v>
+        <v>-0.92130000000000001</v>
       </c>
       <c r="AB14" s="11">
         <v>0</v>
@@ -2673,64 +3661,64 @@
         <v>128</v>
       </c>
       <c r="L17" s="11">
+        <v>7</v>
+      </c>
+      <c r="M17" s="11">
+        <v>12</v>
+      </c>
+      <c r="N17" s="11">
+        <v>5</v>
+      </c>
+      <c r="O17" s="12">
+        <v>0.71430000000000005</v>
+      </c>
+      <c r="P17" s="11">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>12</v>
+      </c>
+      <c r="R17" s="11">
         <v>4</v>
       </c>
-      <c r="M17" s="11">
-        <v>8</v>
-      </c>
-      <c r="N17" s="11">
-        <v>4</v>
-      </c>
-      <c r="O17" s="12">
-        <v>1</v>
-      </c>
-      <c r="P17" s="11">
-        <v>6</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>7</v>
-      </c>
-      <c r="R17" s="11">
-        <v>1</v>
-      </c>
       <c r="S17" s="12">
-        <v>0.16669999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="T17" s="11">
-        <v>855.64</v>
+        <v>1032.33</v>
       </c>
       <c r="U17" s="11">
-        <v>670.28</v>
+        <v>788.19</v>
       </c>
       <c r="V17" s="11">
-        <v>-185.36</v>
+        <v>-244.14</v>
       </c>
       <c r="W17" s="12">
-        <v>-0.21659999999999999</v>
+        <v>-0.23649999999999999</v>
       </c>
       <c r="X17" s="11">
-        <v>588.49</v>
+        <v>820.67</v>
       </c>
       <c r="Y17" s="11">
-        <v>760.86</v>
+        <v>941.95</v>
       </c>
       <c r="Z17" s="11">
-        <v>172.37</v>
+        <v>121.28</v>
       </c>
       <c r="AA17" s="12">
-        <v>0.29289999999999999</v>
+        <v>0.14779999999999999</v>
       </c>
       <c r="AB17" s="11">
-        <v>0.69879999999999998</v>
+        <v>1.9245000000000001</v>
       </c>
       <c r="AC17" s="11">
-        <v>1.8223</v>
+        <v>4.5960000000000001</v>
       </c>
       <c r="AD17" s="11">
-        <v>1.1234999999999999</v>
+        <v>2.6715</v>
       </c>
       <c r="AE17" s="12">
-        <v>1.6077999999999999</v>
+        <v>1.3882000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -2771,13 +3759,13 @@
         <v>1</v>
       </c>
       <c r="M18" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="11">
         <v>1</v>
@@ -2795,37 +3783,37 @@
         <v>19.260000000000002</v>
       </c>
       <c r="U18" s="11">
-        <v>0</v>
+        <v>41.45</v>
       </c>
       <c r="V18" s="11">
-        <v>-19.260000000000002</v>
+        <v>22.19</v>
       </c>
       <c r="W18" s="12">
-        <v>-1</v>
+        <v>1.1520999999999999</v>
       </c>
       <c r="X18" s="11">
-        <v>25.91</v>
+        <v>29.28</v>
       </c>
       <c r="Y18" s="11">
-        <v>12.65</v>
+        <v>16.89</v>
       </c>
       <c r="Z18" s="11">
-        <v>-13.26</v>
+        <v>-12.39</v>
       </c>
       <c r="AA18" s="12">
-        <v>-0.51180000000000003</v>
+        <v>-0.42320000000000002</v>
       </c>
       <c r="AB18" s="11">
-        <v>1.4147000000000001</v>
+        <v>2.0203000000000002</v>
       </c>
       <c r="AC18" s="11">
-        <v>1.4715</v>
+        <v>2.1012</v>
       </c>
       <c r="AD18" s="11">
-        <v>5.6800000000000003E-2</v>
+        <v>8.09E-2</v>
       </c>
       <c r="AE18" s="12">
-        <v>4.0099999999999997E-2</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.2">
@@ -2899,16 +3887,16 @@
         <v>0</v>
       </c>
       <c r="X19" s="11">
-        <v>4.34</v>
+        <v>6.52</v>
       </c>
       <c r="Y19" s="11">
-        <v>15.5</v>
+        <v>20.7</v>
       </c>
       <c r="Z19" s="11">
-        <v>11.16</v>
+        <v>14.18</v>
       </c>
       <c r="AA19" s="12">
-        <v>2.5714000000000001</v>
+        <v>2.1747999999999998</v>
       </c>
       <c r="AB19" s="11">
         <v>0</v>
@@ -2958,64 +3946,64 @@
         <v>128</v>
       </c>
       <c r="L20" s="11">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M20" s="11">
+        <v>8</v>
+      </c>
+      <c r="N20" s="11">
+        <v>-3</v>
+      </c>
+      <c r="O20" s="12">
+        <v>-0.2727</v>
+      </c>
+      <c r="P20" s="11">
+        <v>11</v>
+      </c>
+      <c r="Q20" s="11">
         <v>4</v>
       </c>
-      <c r="N20" s="11">
-        <v>-5</v>
-      </c>
-      <c r="O20" s="12">
-        <v>-0.55559999999999998</v>
-      </c>
-      <c r="P20" s="11">
-        <v>9</v>
-      </c>
-      <c r="Q20" s="11">
-        <v>3</v>
-      </c>
       <c r="R20" s="11">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="S20" s="12">
-        <v>-0.66669999999999996</v>
+        <v>-0.63639999999999997</v>
       </c>
       <c r="T20" s="11">
-        <v>328.85</v>
+        <v>429.71</v>
       </c>
       <c r="U20" s="11">
-        <v>126.17</v>
+        <v>360.76</v>
       </c>
       <c r="V20" s="11">
-        <v>-202.68</v>
+        <v>-68.95</v>
       </c>
       <c r="W20" s="12">
-        <v>-0.61629999999999996</v>
+        <v>-0.1605</v>
       </c>
       <c r="X20" s="11">
-        <v>353.8</v>
+        <v>513.05999999999995</v>
       </c>
       <c r="Y20" s="11">
-        <v>219.62</v>
+        <v>243.25</v>
       </c>
       <c r="Z20" s="11">
-        <v>-134.18</v>
+        <v>-269.81</v>
       </c>
       <c r="AA20" s="12">
-        <v>-0.37930000000000003</v>
+        <v>-0.52590000000000003</v>
       </c>
       <c r="AB20" s="11">
         <v>1.8688</v>
       </c>
       <c r="AC20" s="11">
-        <v>0.37190000000000001</v>
+        <v>0.62990000000000002</v>
       </c>
       <c r="AD20" s="11">
-        <v>-1.4968999999999999</v>
+        <v>-1.2388999999999999</v>
       </c>
       <c r="AE20" s="12">
-        <v>-0.80100000000000005</v>
+        <v>-0.66290000000000004</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.2">
@@ -3089,28 +4077,28 @@
         <v>1</v>
       </c>
       <c r="X21" s="11">
-        <v>11.56</v>
+        <v>15.44</v>
       </c>
       <c r="Y21" s="11">
-        <v>66.790000000000006</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="Z21" s="11">
-        <v>55.23</v>
+        <v>53.66</v>
       </c>
       <c r="AA21" s="12">
-        <v>4.7777000000000003</v>
+        <v>3.4754</v>
       </c>
       <c r="AB21" s="11">
-        <v>0.31490000000000001</v>
+        <v>0.42049999999999998</v>
       </c>
       <c r="AC21" s="11">
-        <v>1.4336</v>
+        <v>5.0438999999999998</v>
       </c>
       <c r="AD21" s="11">
-        <v>1.1187</v>
+        <v>4.6234000000000002</v>
       </c>
       <c r="AE21" s="12">
-        <v>3.5526</v>
+        <v>10.994999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.2">
@@ -3243,52 +4231,52 @@
         <v>128</v>
       </c>
       <c r="L23" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M23" s="11">
         <v>1</v>
       </c>
       <c r="N23" s="11">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O23" s="12">
-        <v>-0.5</v>
+        <v>-0.66669999999999996</v>
       </c>
       <c r="P23" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" s="11">
         <v>1</v>
       </c>
       <c r="R23" s="11">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S23" s="12">
-        <v>-0.5</v>
+        <v>-0.66669999999999996</v>
       </c>
       <c r="T23" s="11">
-        <v>72.900000000000006</v>
+        <v>1620.14</v>
       </c>
       <c r="U23" s="11">
         <v>46.1</v>
       </c>
       <c r="V23" s="11">
-        <v>-26.8</v>
+        <v>-1574.04</v>
       </c>
       <c r="W23" s="12">
-        <v>-0.36759999999999998</v>
+        <v>-0.97150000000000003</v>
       </c>
       <c r="X23" s="11">
-        <v>11.9</v>
+        <v>1468.63</v>
       </c>
       <c r="Y23" s="11">
-        <v>20.23</v>
+        <v>24.11</v>
       </c>
       <c r="Z23" s="11">
-        <v>8.33</v>
+        <v>-1444.52</v>
       </c>
       <c r="AA23" s="12">
-        <v>0.7</v>
+        <v>-0.98360000000000003</v>
       </c>
       <c r="AB23" s="11">
         <v>0</v>
@@ -3338,49 +4326,49 @@
         <v>128</v>
       </c>
       <c r="L24" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="11">
         <v>0</v>
       </c>
       <c r="N24" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O24" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P24" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="11">
         <v>0</v>
       </c>
       <c r="R24" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S24" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T24" s="11">
-        <v>0</v>
+        <v>63.72</v>
       </c>
       <c r="U24" s="11">
         <v>0</v>
       </c>
       <c r="V24" s="11">
-        <v>0</v>
+        <v>-63.72</v>
       </c>
       <c r="W24" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X24" s="11">
-        <v>8.3800000000000008</v>
+        <v>109.19</v>
       </c>
       <c r="Y24" s="11">
         <v>0</v>
       </c>
       <c r="Z24" s="11">
-        <v>-8.3800000000000008</v>
+        <v>-109.19</v>
       </c>
       <c r="AA24" s="12">
         <v>-1</v>
@@ -3528,64 +4516,64 @@
         <v>131</v>
       </c>
       <c r="L26" s="11">
+        <v>5</v>
+      </c>
+      <c r="M26" s="11">
+        <v>1</v>
+      </c>
+      <c r="N26" s="11">
+        <v>-4</v>
+      </c>
+      <c r="O26" s="12">
+        <v>-0.8</v>
+      </c>
+      <c r="P26" s="11">
         <v>4</v>
       </c>
-      <c r="M26" s="11">
-        <v>1</v>
-      </c>
-      <c r="N26" s="11">
-        <v>-3</v>
-      </c>
-      <c r="O26" s="12">
-        <v>-0.75</v>
-      </c>
-      <c r="P26" s="11">
-        <v>3</v>
-      </c>
       <c r="Q26" s="11">
         <v>0</v>
       </c>
       <c r="R26" s="11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="S26" s="12">
         <v>-1</v>
       </c>
       <c r="T26" s="11">
-        <v>58.68</v>
+        <v>78.38</v>
       </c>
       <c r="U26" s="11">
         <v>-0.28999999999999998</v>
       </c>
       <c r="V26" s="11">
-        <v>-58.97</v>
+        <v>-78.67</v>
       </c>
       <c r="W26" s="12">
-        <v>-1.0048999999999999</v>
+        <v>-1.0037</v>
       </c>
       <c r="X26" s="11">
-        <v>78.84</v>
+        <v>85.04</v>
       </c>
       <c r="Y26" s="11">
-        <v>53.4</v>
+        <v>59.82</v>
       </c>
       <c r="Z26" s="11">
-        <v>-25.44</v>
+        <v>-25.22</v>
       </c>
       <c r="AA26" s="12">
-        <v>-0.32269999999999999</v>
+        <v>-0.29659999999999997</v>
       </c>
       <c r="AB26" s="11">
-        <v>0.5141</v>
+        <v>0.68210000000000004</v>
       </c>
       <c r="AC26" s="11">
-        <v>0.70079999999999998</v>
+        <v>0.81779999999999997</v>
       </c>
       <c r="AD26" s="11">
-        <v>0.1867</v>
+        <v>0.13569999999999999</v>
       </c>
       <c r="AE26" s="12">
-        <v>0.36320000000000002</v>
+        <v>0.19889999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.2">
@@ -3659,28 +4647,28 @@
         <v>-1</v>
       </c>
       <c r="X27" s="11">
-        <v>46.3</v>
+        <v>51.12</v>
       </c>
       <c r="Y27" s="11">
-        <v>23.85</v>
+        <v>28.57</v>
       </c>
       <c r="Z27" s="11">
-        <v>-22.45</v>
+        <v>-22.55</v>
       </c>
       <c r="AA27" s="12">
-        <v>-0.4849</v>
+        <v>-0.44109999999999999</v>
       </c>
       <c r="AB27" s="11">
         <v>0</v>
       </c>
       <c r="AC27" s="11">
-        <v>0</v>
+        <v>17.043700000000001</v>
       </c>
       <c r="AD27" s="11">
-        <v>0</v>
+        <v>17.043700000000001</v>
       </c>
       <c r="AE27" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.2">
@@ -3721,13 +4709,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="11">
         <v>0</v>
@@ -3745,13 +4733,13 @@
         <v>0</v>
       </c>
       <c r="U28" s="11">
-        <v>0</v>
+        <v>30.56</v>
       </c>
       <c r="V28" s="11">
-        <v>0</v>
+        <v>30.56</v>
       </c>
       <c r="W28" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" s="11">
         <v>3.09</v>
@@ -3813,64 +4801,64 @@
         <v>131</v>
       </c>
       <c r="L29" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M29" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N29" s="11">
         <v>-3</v>
       </c>
       <c r="O29" s="12">
-        <v>-0.75</v>
+        <v>-0.6</v>
       </c>
       <c r="P29" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q29" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29" s="11">
         <v>-3</v>
       </c>
       <c r="S29" s="12">
-        <v>-0.75</v>
+        <v>-0.6</v>
       </c>
       <c r="T29" s="11">
-        <v>175.1</v>
+        <v>236.49</v>
       </c>
       <c r="U29" s="11">
-        <v>20.6</v>
+        <v>50.28</v>
       </c>
       <c r="V29" s="11">
-        <v>-154.5</v>
+        <v>-186.21</v>
       </c>
       <c r="W29" s="12">
-        <v>-0.88239999999999996</v>
+        <v>-0.78739999999999999</v>
       </c>
       <c r="X29" s="11">
-        <v>215.39</v>
+        <v>262.24</v>
       </c>
       <c r="Y29" s="11">
-        <v>39.979999999999997</v>
+        <v>47.63</v>
       </c>
       <c r="Z29" s="11">
-        <v>-175.41</v>
+        <v>-214.61</v>
       </c>
       <c r="AA29" s="12">
-        <v>-0.81440000000000001</v>
+        <v>-0.81840000000000002</v>
       </c>
       <c r="AB29" s="11">
-        <v>1.528</v>
+        <v>1.8343</v>
       </c>
       <c r="AC29" s="11">
-        <v>3.9302000000000001</v>
+        <v>4.8116000000000003</v>
       </c>
       <c r="AD29" s="11">
-        <v>2.4022000000000001</v>
+        <v>2.9773000000000001</v>
       </c>
       <c r="AE29" s="12">
-        <v>1.5721000000000001</v>
+        <v>1.6231</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.2">
@@ -3884,7 +4872,7 @@
         <v>2043</v>
       </c>
       <c r="D30" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>126</v>
@@ -3908,52 +4896,52 @@
         <v>131</v>
       </c>
       <c r="L30" s="11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M30" s="11">
         <v>4</v>
       </c>
       <c r="N30" s="11">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="O30" s="12">
-        <v>-0.5</v>
+        <v>-0.66669999999999996</v>
       </c>
       <c r="P30" s="11">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q30" s="11">
         <v>4</v>
       </c>
       <c r="R30" s="11">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="S30" s="12">
-        <v>-0.42859999999999998</v>
+        <v>-0.63639999999999997</v>
       </c>
       <c r="T30" s="11">
-        <v>224.88</v>
+        <v>291.18</v>
       </c>
       <c r="U30" s="11">
         <v>112.57</v>
       </c>
       <c r="V30" s="11">
-        <v>-112.31</v>
+        <v>-178.61</v>
       </c>
       <c r="W30" s="12">
-        <v>-0.49940000000000001</v>
+        <v>-0.61339999999999995</v>
       </c>
       <c r="X30" s="11">
-        <v>227.28</v>
+        <v>316.83999999999997</v>
       </c>
       <c r="Y30" s="11">
-        <v>107.29</v>
+        <v>117.91</v>
       </c>
       <c r="Z30" s="11">
-        <v>-119.99</v>
+        <v>-198.93</v>
       </c>
       <c r="AA30" s="12">
-        <v>-0.52790000000000004</v>
+        <v>-0.62790000000000001</v>
       </c>
       <c r="AB30" s="11">
         <v>0.1235</v>
@@ -3979,7 +4967,7 @@
         <v>2043</v>
       </c>
       <c r="D31" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>126</v>
@@ -4003,64 +4991,64 @@
         <v>131</v>
       </c>
       <c r="L31" s="11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M31" s="11">
         <v>7</v>
       </c>
       <c r="N31" s="11">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="O31" s="12">
-        <v>0</v>
+        <v>-0.22220000000000001</v>
       </c>
       <c r="P31" s="11">
+        <v>9</v>
+      </c>
+      <c r="Q31" s="11">
         <v>7</v>
-      </c>
-      <c r="Q31" s="11">
-        <v>5</v>
       </c>
       <c r="R31" s="11">
         <v>-2</v>
       </c>
       <c r="S31" s="12">
-        <v>-0.28570000000000001</v>
+        <v>-0.22220000000000001</v>
       </c>
       <c r="T31" s="11">
-        <v>212.51</v>
+        <v>260.14999999999998</v>
       </c>
       <c r="U31" s="11">
         <v>185.33</v>
       </c>
       <c r="V31" s="11">
-        <v>-27.18</v>
+        <v>-74.819999999999993</v>
       </c>
       <c r="W31" s="12">
-        <v>-0.12790000000000001</v>
+        <v>-0.28760000000000002</v>
       </c>
       <c r="X31" s="11">
-        <v>187.2</v>
+        <v>234.63</v>
       </c>
       <c r="Y31" s="11">
-        <v>126.07</v>
+        <v>159.33000000000001</v>
       </c>
       <c r="Z31" s="11">
-        <v>-61.13</v>
+        <v>-75.3</v>
       </c>
       <c r="AA31" s="12">
-        <v>-0.32650000000000001</v>
+        <v>-0.32090000000000002</v>
       </c>
       <c r="AB31" s="11">
-        <v>0.79920000000000002</v>
+        <v>1.0677000000000001</v>
       </c>
       <c r="AC31" s="11">
-        <v>1.8523000000000001</v>
+        <v>2.2037</v>
       </c>
       <c r="AD31" s="11">
-        <v>1.0530999999999999</v>
+        <v>1.1359999999999999</v>
       </c>
       <c r="AE31" s="12">
-        <v>1.3177000000000001</v>
+        <v>1.0640000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.2">
@@ -4101,58 +5089,58 @@
         <v>2</v>
       </c>
       <c r="M32" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N32" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" s="12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P32" s="11">
         <v>2</v>
       </c>
       <c r="Q32" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R32" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T32" s="11">
         <v>49.3</v>
       </c>
       <c r="U32" s="11">
-        <v>99.07</v>
+        <v>123.69</v>
       </c>
       <c r="V32" s="11">
-        <v>49.77</v>
+        <v>74.39</v>
       </c>
       <c r="W32" s="12">
-        <v>1.0095000000000001</v>
+        <v>1.5088999999999999</v>
       </c>
       <c r="X32" s="11">
-        <v>80.510000000000005</v>
+        <v>89.3</v>
       </c>
       <c r="Y32" s="11">
-        <v>71.16</v>
+        <v>114.94</v>
       </c>
       <c r="Z32" s="11">
-        <v>-9.35</v>
+        <v>25.64</v>
       </c>
       <c r="AA32" s="12">
-        <v>-0.11609999999999999</v>
+        <v>0.28710000000000002</v>
       </c>
       <c r="AB32" s="11">
         <v>0</v>
       </c>
       <c r="AC32" s="11">
-        <v>0.89580000000000004</v>
+        <v>1.2112000000000001</v>
       </c>
       <c r="AD32" s="11">
-        <v>0.89580000000000004</v>
+        <v>1.2112000000000001</v>
       </c>
       <c r="AE32" s="12">
         <v>1</v>
@@ -4232,13 +5220,13 @@
         <v>73</v>
       </c>
       <c r="Y33" s="11">
-        <v>32.06</v>
+        <v>49.61</v>
       </c>
       <c r="Z33" s="11">
-        <v>-40.94</v>
+        <v>-23.39</v>
       </c>
       <c r="AA33" s="12">
-        <v>-0.56079999999999997</v>
+        <v>-0.32040000000000002</v>
       </c>
       <c r="AB33" s="11">
         <v>3.1848999999999998</v>
@@ -4288,52 +5276,52 @@
         <v>127</v>
       </c>
       <c r="L34" s="11">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="M34" s="11">
         <v>1</v>
       </c>
       <c r="N34" s="11">
-        <v>-7</v>
+        <v>-16</v>
       </c>
       <c r="O34" s="12">
-        <v>-0.875</v>
+        <v>-0.94120000000000004</v>
       </c>
       <c r="P34" s="11">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Q34" s="11">
         <v>0</v>
       </c>
       <c r="R34" s="11">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="S34" s="12">
         <v>-1</v>
       </c>
       <c r="T34" s="11">
-        <v>406.35</v>
+        <v>689.54</v>
       </c>
       <c r="U34" s="11">
         <v>-1319.02</v>
       </c>
       <c r="V34" s="11">
-        <v>-1725.37</v>
+        <v>-2008.56</v>
       </c>
       <c r="W34" s="12">
-        <v>-4.2460000000000004</v>
+        <v>-2.9129</v>
       </c>
       <c r="X34" s="11">
-        <v>63.59</v>
+        <v>349.84</v>
       </c>
       <c r="Y34" s="11">
-        <v>132.61000000000001</v>
+        <v>155.65</v>
       </c>
       <c r="Z34" s="11">
-        <v>69.02</v>
+        <v>-194.19</v>
       </c>
       <c r="AA34" s="12">
-        <v>1.0853999999999999</v>
+        <v>-0.55510000000000004</v>
       </c>
       <c r="AB34" s="11">
         <v>0</v>
@@ -4359,7 +5347,7 @@
         <v>2043</v>
       </c>
       <c r="D35" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>126</v>
@@ -4454,7 +5442,7 @@
         <v>2043</v>
       </c>
       <c r="D36" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>126</v>
@@ -4478,64 +5466,64 @@
         <v>127</v>
       </c>
       <c r="L36" s="11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M36" s="11">
         <v>1</v>
       </c>
       <c r="N36" s="11">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="O36" s="12">
-        <v>-0.85709999999999997</v>
+        <v>-0.88890000000000002</v>
       </c>
       <c r="P36" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q36" s="11">
         <v>1</v>
       </c>
       <c r="R36" s="11">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="S36" s="12">
-        <v>-0.83330000000000004</v>
+        <v>-0.875</v>
       </c>
       <c r="T36" s="11">
-        <v>223.13</v>
+        <v>274.5</v>
       </c>
       <c r="U36" s="11">
         <v>36.93</v>
       </c>
       <c r="V36" s="11">
-        <v>-186.2</v>
+        <v>-237.57</v>
       </c>
       <c r="W36" s="12">
-        <v>-0.83450000000000002</v>
+        <v>-0.86550000000000005</v>
       </c>
       <c r="X36" s="11">
-        <v>303.52999999999997</v>
+        <v>377.79</v>
       </c>
       <c r="Y36" s="11">
-        <v>64.989999999999995</v>
+        <v>72.89</v>
       </c>
       <c r="Z36" s="11">
-        <v>-238.54</v>
+        <v>-304.89999999999998</v>
       </c>
       <c r="AA36" s="12">
-        <v>-0.78590000000000004</v>
+        <v>-0.80710000000000004</v>
       </c>
       <c r="AB36" s="11">
-        <v>4.0427</v>
+        <v>5.3985000000000003</v>
       </c>
       <c r="AC36" s="11">
         <v>9.2260000000000009</v>
       </c>
       <c r="AD36" s="11">
-        <v>5.1833</v>
+        <v>3.8275000000000001</v>
       </c>
       <c r="AE36" s="12">
-        <v>1.2821</v>
+        <v>0.70899999999999996</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.2">
@@ -4549,7 +5537,7 @@
         <v>2043</v>
       </c>
       <c r="D37" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>126</v>
@@ -4573,52 +5561,52 @@
         <v>127</v>
       </c>
       <c r="L37" s="11">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M37" s="11">
         <v>1</v>
       </c>
       <c r="N37" s="11">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="O37" s="12">
-        <v>-0.8</v>
+        <v>-0.88890000000000002</v>
       </c>
       <c r="P37" s="11">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q37" s="11">
         <v>1</v>
       </c>
       <c r="R37" s="11">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="S37" s="12">
-        <v>-0.8</v>
+        <v>-0.88890000000000002</v>
       </c>
       <c r="T37" s="11">
-        <v>149.02000000000001</v>
+        <v>436.66</v>
       </c>
       <c r="U37" s="11">
         <v>36.159999999999997</v>
       </c>
       <c r="V37" s="11">
-        <v>-112.86</v>
+        <v>-400.5</v>
       </c>
       <c r="W37" s="12">
-        <v>-0.75729999999999997</v>
+        <v>-0.91720000000000002</v>
       </c>
       <c r="X37" s="11">
-        <v>86.18</v>
+        <v>185.17</v>
       </c>
       <c r="Y37" s="11">
-        <v>145.55000000000001</v>
+        <v>153.1</v>
       </c>
       <c r="Z37" s="11">
-        <v>59.37</v>
+        <v>-32.07</v>
       </c>
       <c r="AA37" s="12">
-        <v>0.68889999999999996</v>
+        <v>-0.17319999999999999</v>
       </c>
       <c r="AB37" s="11">
         <v>0</v>
@@ -4668,52 +5656,52 @@
         <v>127</v>
       </c>
       <c r="L38" s="11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M38" s="11">
         <v>0</v>
       </c>
       <c r="N38" s="11">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="O38" s="12">
         <v>-1</v>
       </c>
       <c r="P38" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q38" s="11">
         <v>0</v>
       </c>
       <c r="R38" s="11">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="S38" s="12">
         <v>-1</v>
       </c>
       <c r="T38" s="11">
-        <v>90.67</v>
+        <v>152.66</v>
       </c>
       <c r="U38" s="11">
         <v>0</v>
       </c>
       <c r="V38" s="11">
-        <v>-90.67</v>
+        <v>-152.66</v>
       </c>
       <c r="W38" s="12">
         <v>-1</v>
       </c>
       <c r="X38" s="11">
-        <v>103.45</v>
+        <v>135.86000000000001</v>
       </c>
       <c r="Y38" s="11">
         <v>10.45</v>
       </c>
       <c r="Z38" s="11">
-        <v>-93</v>
+        <v>-125.41</v>
       </c>
       <c r="AA38" s="12">
-        <v>-0.89900000000000002</v>
+        <v>-0.92310000000000003</v>
       </c>
       <c r="AB38" s="11">
         <v>3.3999999999999998E-3</v>
@@ -4739,7 +5727,7 @@
         <v>2043</v>
       </c>
       <c r="D39" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>126</v>
@@ -4799,28 +5787,28 @@
         <v>-1</v>
       </c>
       <c r="X39" s="11">
-        <v>44.5</v>
+        <v>48.47</v>
       </c>
       <c r="Y39" s="11">
         <v>0</v>
       </c>
       <c r="Z39" s="11">
-        <v>-44.5</v>
+        <v>-48.47</v>
       </c>
       <c r="AA39" s="12">
         <v>-1</v>
       </c>
       <c r="AB39" s="11">
-        <v>9.8100000000000007E-2</v>
+        <v>0.30480000000000002</v>
       </c>
       <c r="AC39" s="11">
         <v>0.1643</v>
       </c>
       <c r="AD39" s="11">
-        <v>6.6199999999999995E-2</v>
+        <v>-0.14050000000000001</v>
       </c>
       <c r="AE39" s="12">
-        <v>0.67479999999999996</v>
+        <v>-0.46100000000000002</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.2">
@@ -4894,16 +5882,16 @@
         <v>-1</v>
       </c>
       <c r="X40" s="11">
-        <v>29.29</v>
+        <v>43.61</v>
       </c>
       <c r="Y40" s="11">
-        <v>23.88</v>
+        <v>30.08</v>
       </c>
       <c r="Z40" s="11">
-        <v>-5.41</v>
+        <v>-13.53</v>
       </c>
       <c r="AA40" s="12">
-        <v>-0.1847</v>
+        <v>-0.31019999999999998</v>
       </c>
       <c r="AB40" s="11">
         <v>0</v>
@@ -4989,13 +5977,13 @@
         <v>0</v>
       </c>
       <c r="X41" s="11">
-        <v>4.46</v>
+        <v>5.95</v>
       </c>
       <c r="Y41" s="11">
         <v>0</v>
       </c>
       <c r="Z41" s="11">
-        <v>-4.46</v>
+        <v>-5.95</v>
       </c>
       <c r="AA41" s="12">
         <v>-1</v>
@@ -5084,13 +6072,13 @@
         <v>-1</v>
       </c>
       <c r="X42" s="11">
-        <v>140.68</v>
+        <v>152.91</v>
       </c>
       <c r="Y42" s="11">
         <v>0</v>
       </c>
       <c r="Z42" s="11">
-        <v>-140.68</v>
+        <v>-152.91</v>
       </c>
       <c r="AA42" s="12">
         <v>-1</v>
@@ -5143,52 +6131,52 @@
         <v>127</v>
       </c>
       <c r="L43" s="11">
+        <v>4</v>
+      </c>
+      <c r="M43" s="11">
+        <v>1</v>
+      </c>
+      <c r="N43" s="11">
+        <v>-3</v>
+      </c>
+      <c r="O43" s="12">
+        <v>-0.75</v>
+      </c>
+      <c r="P43" s="11">
         <v>3</v>
       </c>
-      <c r="M43" s="11">
-        <v>1</v>
-      </c>
-      <c r="N43" s="11">
-        <v>-2</v>
-      </c>
-      <c r="O43" s="12">
-        <v>-0.66669999999999996</v>
-      </c>
-      <c r="P43" s="11">
-        <v>2</v>
-      </c>
       <c r="Q43" s="11">
         <v>0</v>
       </c>
       <c r="R43" s="11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="S43" s="12">
         <v>-1</v>
       </c>
       <c r="T43" s="11">
-        <v>-35.53</v>
+        <v>17.11</v>
       </c>
       <c r="U43" s="11">
-        <v>28.7</v>
+        <v>-0.22</v>
       </c>
       <c r="V43" s="11">
-        <v>64.23</v>
+        <v>-17.329999999999998</v>
       </c>
       <c r="W43" s="12">
-        <v>1.8078000000000001</v>
+        <v>-1.0128999999999999</v>
       </c>
       <c r="X43" s="11">
-        <v>62.03</v>
+        <v>105.69</v>
       </c>
       <c r="Y43" s="11">
-        <v>8.5399999999999991</v>
+        <v>14.37</v>
       </c>
       <c r="Z43" s="11">
-        <v>-53.49</v>
+        <v>-91.32</v>
       </c>
       <c r="AA43" s="12">
-        <v>-0.86229999999999996</v>
+        <v>-0.86399999999999999</v>
       </c>
       <c r="AB43" s="11">
         <v>0</v>
@@ -5274,16 +6262,16 @@
         <v>-1</v>
       </c>
       <c r="X44" s="11">
-        <v>44.35</v>
+        <v>50.17</v>
       </c>
       <c r="Y44" s="11">
-        <v>26.61</v>
+        <v>35.53</v>
       </c>
       <c r="Z44" s="11">
-        <v>-17.739999999999998</v>
+        <v>-14.64</v>
       </c>
       <c r="AA44" s="12">
-        <v>-0.4</v>
+        <v>-0.2918</v>
       </c>
       <c r="AB44" s="11">
         <v>0</v>
@@ -5333,64 +6321,64 @@
         <v>127</v>
       </c>
       <c r="L45" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M45" s="11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N45" s="11">
+        <v>-4</v>
+      </c>
+      <c r="O45" s="12">
+        <v>-0.28570000000000001</v>
+      </c>
+      <c r="P45" s="11">
+        <v>14</v>
+      </c>
+      <c r="Q45" s="11">
+        <v>9</v>
+      </c>
+      <c r="R45" s="11">
         <v>-5</v>
       </c>
-      <c r="O45" s="12">
-        <v>-0.41670000000000001</v>
-      </c>
-      <c r="P45" s="11">
-        <v>12</v>
-      </c>
-      <c r="Q45" s="11">
-        <v>6</v>
-      </c>
-      <c r="R45" s="11">
-        <v>-6</v>
-      </c>
       <c r="S45" s="12">
-        <v>-0.5</v>
+        <v>-0.35709999999999997</v>
       </c>
       <c r="T45" s="11">
-        <v>272.62</v>
+        <v>446.24</v>
       </c>
       <c r="U45" s="11">
-        <v>227.99</v>
+        <v>301.42</v>
       </c>
       <c r="V45" s="11">
-        <v>-44.63</v>
+        <v>-144.82</v>
       </c>
       <c r="W45" s="12">
-        <v>-0.16370000000000001</v>
+        <v>-0.32450000000000001</v>
       </c>
       <c r="X45" s="11">
-        <v>156.13999999999999</v>
+        <v>198.56</v>
       </c>
       <c r="Y45" s="11">
-        <v>172.46</v>
+        <v>241.16</v>
       </c>
       <c r="Z45" s="11">
-        <v>16.32</v>
+        <v>42.6</v>
       </c>
       <c r="AA45" s="12">
-        <v>0.1045</v>
+        <v>0.2145</v>
       </c>
       <c r="AB45" s="11">
         <v>0.2029</v>
       </c>
       <c r="AC45" s="11">
-        <v>0.4375</v>
+        <v>1.087</v>
       </c>
       <c r="AD45" s="11">
-        <v>0.2346</v>
+        <v>0.8841</v>
       </c>
       <c r="AE45" s="12">
-        <v>1.1561999999999999</v>
+        <v>4.3573000000000004</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
@@ -5404,7 +6392,7 @@
         <v>2043</v>
       </c>
       <c r="D46" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>126</v>
@@ -5428,13 +6416,13 @@
         <v>127</v>
       </c>
       <c r="L46" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" s="11">
         <v>0</v>
       </c>
       <c r="N46" s="11">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O46" s="12">
         <v>-1</v>
@@ -5452,28 +6440,28 @@
         <v>-1</v>
       </c>
       <c r="T46" s="11">
-        <v>21.5</v>
+        <v>54.78</v>
       </c>
       <c r="U46" s="11">
         <v>0</v>
       </c>
       <c r="V46" s="11">
-        <v>-21.5</v>
+        <v>-54.78</v>
       </c>
       <c r="W46" s="12">
         <v>-1</v>
       </c>
       <c r="X46" s="11">
-        <v>208.83</v>
+        <v>276.66000000000003</v>
       </c>
       <c r="Y46" s="11">
-        <v>42.88</v>
+        <v>57.27</v>
       </c>
       <c r="Z46" s="11">
-        <v>-165.95</v>
+        <v>-219.39</v>
       </c>
       <c r="AA46" s="12">
-        <v>-0.79469999999999996</v>
+        <v>-0.79300000000000004</v>
       </c>
       <c r="AB46" s="11">
         <v>0</v>
@@ -5559,13 +6547,13 @@
         <v>0</v>
       </c>
       <c r="X47" s="11">
-        <v>9.74</v>
+        <v>12.87</v>
       </c>
       <c r="Y47" s="11">
         <v>0</v>
       </c>
       <c r="Z47" s="11">
-        <v>-9.74</v>
+        <v>-12.87</v>
       </c>
       <c r="AA47" s="12">
         <v>-1</v>
@@ -5594,7 +6582,7 @@
         <v>2043</v>
       </c>
       <c r="D48" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>126</v>
@@ -5621,49 +6609,49 @@
         <v>3</v>
       </c>
       <c r="M48" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="11">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="O48" s="12">
-        <v>-1</v>
+        <v>-0.66669999999999996</v>
       </c>
       <c r="P48" s="11">
         <v>3</v>
       </c>
       <c r="Q48" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="11">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="S48" s="12">
-        <v>-1</v>
+        <v>-0.66669999999999996</v>
       </c>
       <c r="T48" s="11">
         <v>169.31</v>
       </c>
       <c r="U48" s="11">
-        <v>0</v>
+        <v>61.75</v>
       </c>
       <c r="V48" s="11">
-        <v>-169.31</v>
+        <v>-107.56</v>
       </c>
       <c r="W48" s="12">
-        <v>-1</v>
+        <v>-0.63529999999999998</v>
       </c>
       <c r="X48" s="11">
-        <v>86.46</v>
+        <v>93.74</v>
       </c>
       <c r="Y48" s="11">
-        <v>33.9</v>
+        <v>95.65</v>
       </c>
       <c r="Z48" s="11">
-        <v>-52.56</v>
+        <v>1.91</v>
       </c>
       <c r="AA48" s="12">
-        <v>-0.6079</v>
+        <v>2.0400000000000001E-2</v>
       </c>
       <c r="AB48" s="11">
         <v>0</v>
@@ -5749,16 +6737,16 @@
         <v>-1</v>
       </c>
       <c r="X49" s="11">
-        <v>181.68</v>
+        <v>189.44</v>
       </c>
       <c r="Y49" s="11">
         <v>13.5</v>
       </c>
       <c r="Z49" s="11">
-        <v>-168.18</v>
+        <v>-175.94</v>
       </c>
       <c r="AA49" s="12">
-        <v>-0.92569999999999997</v>
+        <v>-0.92869999999999997</v>
       </c>
       <c r="AB49" s="11">
         <v>0</v>
@@ -5808,52 +6796,52 @@
         <v>132</v>
       </c>
       <c r="L50" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M50" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N50" s="11">
         <v>-3</v>
       </c>
       <c r="O50" s="12">
-        <v>-0.75</v>
+        <v>-0.6</v>
       </c>
       <c r="P50" s="11">
         <v>4</v>
       </c>
       <c r="Q50" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="S50" s="12">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="T50" s="11">
-        <v>133.03</v>
+        <v>185</v>
       </c>
       <c r="U50" s="11">
-        <v>20.48</v>
+        <v>21.55</v>
       </c>
       <c r="V50" s="11">
-        <v>-112.55</v>
+        <v>-163.44999999999999</v>
       </c>
       <c r="W50" s="12">
-        <v>-0.84599999999999997</v>
+        <v>-0.88349999999999995</v>
       </c>
       <c r="X50" s="11">
         <v>131.56</v>
       </c>
       <c r="Y50" s="11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z50" s="11">
-        <v>-131.56</v>
+        <v>-129.76</v>
       </c>
       <c r="AA50" s="12">
-        <v>-1</v>
+        <v>-0.98629999999999995</v>
       </c>
       <c r="AB50" s="11">
         <v>0</v>
@@ -5998,64 +6986,64 @@
         <v>132</v>
       </c>
       <c r="L52" s="11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M52" s="11">
         <v>0</v>
       </c>
       <c r="N52" s="11">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="O52" s="12">
         <v>-1</v>
       </c>
       <c r="P52" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q52" s="11">
         <v>0</v>
       </c>
       <c r="R52" s="11">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="S52" s="12">
         <v>-1</v>
       </c>
       <c r="T52" s="11">
-        <v>53.09</v>
+        <v>112.23</v>
       </c>
       <c r="U52" s="11">
         <v>0</v>
       </c>
       <c r="V52" s="11">
-        <v>-53.09</v>
+        <v>-112.23</v>
       </c>
       <c r="W52" s="12">
         <v>-1</v>
       </c>
       <c r="X52" s="11">
-        <v>2.4500000000000002</v>
+        <v>51.32</v>
       </c>
       <c r="Y52" s="11">
-        <v>15.06</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="Z52" s="11">
-        <v>12.61</v>
+        <v>-34.51</v>
       </c>
       <c r="AA52" s="12">
-        <v>5.1468999999999996</v>
+        <v>-0.6724</v>
       </c>
       <c r="AB52" s="11">
         <v>0</v>
       </c>
       <c r="AC52" s="11">
-        <v>0</v>
+        <v>3.8157000000000001</v>
       </c>
       <c r="AD52" s="11">
-        <v>0</v>
+        <v>3.8157000000000001</v>
       </c>
       <c r="AE52" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.2">
@@ -6093,52 +7081,52 @@
         <v>132</v>
       </c>
       <c r="L53" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M53" s="11">
         <v>0</v>
       </c>
       <c r="N53" s="11">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="O53" s="12">
         <v>-1</v>
       </c>
       <c r="P53" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q53" s="11">
         <v>0</v>
       </c>
       <c r="R53" s="11">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="S53" s="12">
         <v>-1</v>
       </c>
       <c r="T53" s="11">
-        <v>27.65</v>
+        <v>108.8</v>
       </c>
       <c r="U53" s="11">
         <v>0</v>
       </c>
       <c r="V53" s="11">
-        <v>-27.65</v>
+        <v>-108.8</v>
       </c>
       <c r="W53" s="12">
         <v>-1</v>
       </c>
       <c r="X53" s="11">
-        <v>13.82</v>
+        <v>81.27</v>
       </c>
       <c r="Y53" s="11">
-        <v>22.09</v>
+        <v>26.65</v>
       </c>
       <c r="Z53" s="11">
-        <v>8.27</v>
+        <v>-54.62</v>
       </c>
       <c r="AA53" s="12">
-        <v>0.59840000000000004</v>
+        <v>-0.67210000000000003</v>
       </c>
       <c r="AB53" s="11">
         <v>0</v>
@@ -6164,88 +7152,88 @@
         <v>2043</v>
       </c>
       <c r="D54" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F54" s="10">
-        <v>113450</v>
+        <v>113312</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="I54" s="22">
-        <v>45852</v>
+        <v>45440</v>
       </c>
       <c r="J54" s="22">
-        <v>45852</v>
+        <v>45440</v>
       </c>
       <c r="K54" s="23" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="L54" s="11">
         <v>0</v>
       </c>
       <c r="M54" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54" s="11">
         <v>0</v>
       </c>
       <c r="Q54" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" s="11">
         <v>0</v>
       </c>
       <c r="U54" s="11">
-        <v>58.06</v>
+        <v>0</v>
       </c>
       <c r="V54" s="11">
-        <v>58.06</v>
+        <v>0</v>
       </c>
       <c r="W54" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X54" s="11">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Y54" s="11">
-        <v>69.42</v>
+        <v>0</v>
       </c>
       <c r="Z54" s="11">
-        <v>69.42</v>
+        <v>-1.87</v>
       </c>
       <c r="AA54" s="12">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AB54" s="11">
         <v>0</v>
       </c>
       <c r="AC54" s="11">
-        <v>0.30030000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD54" s="11">
-        <v>0.30030000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE54" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.2">
@@ -6259,34 +7247,34 @@
         <v>2043</v>
       </c>
       <c r="D55" s="10">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F55" s="10">
-        <v>114100</v>
+        <v>113450</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H55" s="10" t="s">
         <v>127</v>
       </c>
       <c r="I55" s="22">
-        <v>45863</v>
+        <v>45852</v>
       </c>
       <c r="J55" s="22">
-        <v>45863</v>
+        <v>45852</v>
       </c>
       <c r="K55" s="23" t="s">
         <v>132</v>
       </c>
       <c r="L55" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" s="11">
         <v>0</v>
@@ -6295,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="P55" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="11">
         <v>0</v>
@@ -6307,40 +7295,40 @@
         <v>0</v>
       </c>
       <c r="T55" s="11">
-        <v>0</v>
+        <v>27.2</v>
       </c>
       <c r="U55" s="11">
-        <v>0</v>
+        <v>58.06</v>
       </c>
       <c r="V55" s="11">
-        <v>0</v>
+        <v>30.86</v>
       </c>
       <c r="W55" s="12">
-        <v>0</v>
+        <v>1.1346000000000001</v>
       </c>
       <c r="X55" s="11">
-        <v>0</v>
+        <v>13.61</v>
       </c>
       <c r="Y55" s="11">
-        <v>47.98</v>
+        <v>79.680000000000007</v>
       </c>
       <c r="Z55" s="11">
-        <v>47.98</v>
+        <v>66.069999999999993</v>
       </c>
       <c r="AA55" s="12">
-        <v>1</v>
+        <v>4.8544999999999998</v>
       </c>
       <c r="AB55" s="11">
         <v>0</v>
       </c>
       <c r="AC55" s="11">
-        <v>0</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="AD55" s="11">
-        <v>0</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="AE55" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.2">
@@ -6354,25 +7342,25 @@
         <v>2043</v>
       </c>
       <c r="D56" s="10">
-        <v>2692</v>
+        <v>2856</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F56" s="10">
-        <v>114157</v>
+        <v>114100</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H56" s="10" t="s">
         <v>127</v>
       </c>
       <c r="I56" s="22">
-        <v>45904</v>
+        <v>45863</v>
       </c>
       <c r="J56" s="22">
-        <v>45904</v>
+        <v>45863</v>
       </c>
       <c r="K56" s="23" t="s">
         <v>132</v>
@@ -6393,22 +7381,22 @@
         <v>0</v>
       </c>
       <c r="Q56" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" s="11">
         <v>0</v>
       </c>
       <c r="U56" s="11">
-        <v>20.37</v>
+        <v>40.83</v>
       </c>
       <c r="V56" s="11">
-        <v>20.37</v>
+        <v>40.83</v>
       </c>
       <c r="W56" s="12">
         <v>1</v>
@@ -6417,10 +7405,10 @@
         <v>0</v>
       </c>
       <c r="Y56" s="11">
-        <v>27.97</v>
+        <v>71.260000000000005</v>
       </c>
       <c r="Z56" s="11">
-        <v>27.97</v>
+        <v>71.260000000000005</v>
       </c>
       <c r="AA56" s="12">
         <v>1</v>
@@ -6449,25 +7437,25 @@
         <v>2043</v>
       </c>
       <c r="D57" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F57" s="10">
-        <v>114431</v>
+        <v>114157</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H57" s="10" t="s">
         <v>127</v>
       </c>
       <c r="I57" s="22">
-        <v>45930</v>
+        <v>45904</v>
       </c>
       <c r="J57" s="22">
-        <v>45930</v>
+        <v>45904</v>
       </c>
       <c r="K57" s="23" t="s">
         <v>132</v>
@@ -6476,46 +7464,46 @@
         <v>0</v>
       </c>
       <c r="M57" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P57" s="11">
         <v>0</v>
       </c>
       <c r="Q57" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="11">
         <v>0</v>
       </c>
       <c r="U57" s="11">
-        <v>0</v>
+        <v>20.37</v>
       </c>
       <c r="V57" s="11">
-        <v>0</v>
+        <v>20.37</v>
       </c>
       <c r="W57" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" s="11">
         <v>0</v>
       </c>
       <c r="Y57" s="11">
-        <v>22.36</v>
+        <v>31.3</v>
       </c>
       <c r="Z57" s="11">
-        <v>22.36</v>
+        <v>31.3</v>
       </c>
       <c r="AA57" s="12">
         <v>1</v>
@@ -6544,25 +7532,25 @@
         <v>2043</v>
       </c>
       <c r="D58" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F58" s="10">
-        <v>114664</v>
+        <v>114431</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I58" s="22">
-        <v>45950</v>
+        <v>45930</v>
       </c>
       <c r="J58" s="22">
-        <v>45950</v>
+        <v>45930</v>
       </c>
       <c r="K58" s="23" t="s">
         <v>132</v>
@@ -6607,13 +7595,13 @@
         <v>0</v>
       </c>
       <c r="Y58" s="11">
-        <v>0</v>
+        <v>22.36</v>
       </c>
       <c r="Z58" s="11">
-        <v>0</v>
+        <v>22.36</v>
       </c>
       <c r="AA58" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB58" s="11">
         <v>0</v>
@@ -6639,25 +7627,25 @@
         <v>2043</v>
       </c>
       <c r="D59" s="10">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F59" s="10">
-        <v>115047</v>
+        <v>114664</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I59" s="22">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="J59" s="22">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="K59" s="23" t="s">
         <v>132</v>
@@ -6666,61 +7654,61 @@
         <v>0</v>
       </c>
       <c r="M59" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N59" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O59" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" s="11">
         <v>0</v>
       </c>
       <c r="Q59" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R59" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S59" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" s="11">
         <v>0</v>
       </c>
       <c r="U59" s="11">
-        <v>76.040000000000006</v>
+        <v>0</v>
       </c>
       <c r="V59" s="11">
-        <v>76.040000000000006</v>
+        <v>0</v>
       </c>
       <c r="W59" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X59" s="11">
         <v>0</v>
       </c>
       <c r="Y59" s="11">
-        <v>143.38</v>
+        <v>0</v>
       </c>
       <c r="Z59" s="11">
-        <v>143.38</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="11">
         <v>0</v>
       </c>
       <c r="AC59" s="11">
-        <v>1.407</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="11">
-        <v>1.407</v>
+        <v>0</v>
       </c>
       <c r="AE59" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.2">
@@ -6734,25 +7722,25 @@
         <v>2043</v>
       </c>
       <c r="D60" s="10">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F60" s="10">
-        <v>115404</v>
+        <v>115047</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>127</v>
       </c>
       <c r="I60" s="22">
-        <v>45986</v>
+        <v>45944</v>
       </c>
       <c r="J60" s="22">
-        <v>45986</v>
+        <v>45944</v>
       </c>
       <c r="K60" s="23" t="s">
         <v>132</v>
@@ -6761,10 +7749,10 @@
         <v>0</v>
       </c>
       <c r="M60" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N60" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O60" s="12">
         <v>1</v>
@@ -6773,10 +7761,10 @@
         <v>0</v>
       </c>
       <c r="Q60" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S60" s="12">
         <v>1</v>
@@ -6785,10 +7773,10 @@
         <v>0</v>
       </c>
       <c r="U60" s="11">
-        <v>29.87</v>
+        <v>76.040000000000006</v>
       </c>
       <c r="V60" s="11">
-        <v>29.87</v>
+        <v>76.040000000000006</v>
       </c>
       <c r="W60" s="12">
         <v>1</v>
@@ -6797,10 +7785,10 @@
         <v>0</v>
       </c>
       <c r="Y60" s="11">
-        <v>53.86</v>
+        <v>148.4</v>
       </c>
       <c r="Z60" s="11">
-        <v>53.86</v>
+        <v>148.4</v>
       </c>
       <c r="AA60" s="12">
         <v>1</v>
@@ -6809,13 +7797,13 @@
         <v>0</v>
       </c>
       <c r="AC60" s="11">
-        <v>0</v>
+        <v>2.3195000000000001</v>
       </c>
       <c r="AD60" s="11">
-        <v>0</v>
+        <v>2.3195000000000001</v>
       </c>
       <c r="AE60" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.2">
@@ -6829,25 +7817,25 @@
         <v>2043</v>
       </c>
       <c r="D61" s="10">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F61" s="10">
-        <v>116060</v>
+        <v>115404</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>127</v>
       </c>
       <c r="I61" s="22">
-        <v>46010</v>
+        <v>45986</v>
       </c>
       <c r="J61" s="22">
-        <v>46010</v>
+        <v>45986</v>
       </c>
       <c r="K61" s="23" t="s">
         <v>132</v>
@@ -6856,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="M61" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N61" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O61" s="12">
         <v>1</v>
@@ -6868,10 +7856,10 @@
         <v>0</v>
       </c>
       <c r="Q61" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R61" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S61" s="12">
         <v>1</v>
@@ -6880,10 +7868,10 @@
         <v>0</v>
       </c>
       <c r="U61" s="11">
-        <v>52.1</v>
+        <v>29.87</v>
       </c>
       <c r="V61" s="11">
-        <v>52.1</v>
+        <v>29.87</v>
       </c>
       <c r="W61" s="12">
         <v>1</v>
@@ -6892,10 +7880,10 @@
         <v>0</v>
       </c>
       <c r="Y61" s="11">
-        <v>67.16</v>
+        <v>53.86</v>
       </c>
       <c r="Z61" s="11">
-        <v>67.16</v>
+        <v>53.86</v>
       </c>
       <c r="AA61" s="12">
         <v>1</v>
@@ -6924,73 +7912,73 @@
         <v>2043</v>
       </c>
       <c r="D62" s="10">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F62" s="10">
-        <v>116795</v>
+        <v>116060</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I62" s="22">
-        <v>46000</v>
+        <v>46010</v>
       </c>
       <c r="J62" s="22">
-        <v>46023</v>
+        <v>46010</v>
       </c>
       <c r="K62" s="23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="L62" s="11">
         <v>0</v>
       </c>
       <c r="M62" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N62" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O62" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P62" s="11">
         <v>0</v>
       </c>
       <c r="Q62" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R62" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S62" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="11">
         <v>0</v>
       </c>
       <c r="U62" s="11">
-        <v>0</v>
+        <v>52.1</v>
       </c>
       <c r="V62" s="11">
-        <v>0</v>
+        <v>52.1</v>
       </c>
       <c r="W62" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" s="11">
         <v>0</v>
       </c>
       <c r="Y62" s="11">
-        <v>4.76</v>
+        <v>73.959999999999994</v>
       </c>
       <c r="Z62" s="11">
-        <v>4.76</v>
+        <v>73.959999999999994</v>
       </c>
       <c r="AA62" s="12">
         <v>1</v>
@@ -7019,73 +8007,73 @@
         <v>2043</v>
       </c>
       <c r="D63" s="10">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F63" s="10">
-        <v>116876</v>
+        <v>116795</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I63" s="22">
-        <v>46111</v>
+        <v>46000</v>
       </c>
       <c r="J63" s="22">
-        <v>46111</v>
+        <v>46023</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="L63" s="11">
         <v>0</v>
       </c>
       <c r="M63" s="11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N63" s="11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O63" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P63" s="11">
         <v>0</v>
       </c>
       <c r="Q63" s="11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R63" s="11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S63" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63" s="11">
         <v>0</v>
       </c>
       <c r="U63" s="11">
-        <v>118.98</v>
+        <v>0</v>
       </c>
       <c r="V63" s="11">
-        <v>118.98</v>
+        <v>0</v>
       </c>
       <c r="W63" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X63" s="11">
         <v>0</v>
       </c>
       <c r="Y63" s="11">
-        <v>72.05</v>
+        <v>6.35</v>
       </c>
       <c r="Z63" s="11">
-        <v>72.05</v>
+        <v>6.35</v>
       </c>
       <c r="AA63" s="12">
         <v>1</v>
@@ -7120,31 +8108,31 @@
         <v>126</v>
       </c>
       <c r="F64" s="10">
-        <v>116883</v>
+        <v>116876</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>127</v>
       </c>
       <c r="I64" s="22">
-        <v>46007</v>
+        <v>46111</v>
       </c>
       <c r="J64" s="22">
-        <v>46023</v>
+        <v>46111</v>
       </c>
       <c r="K64" s="23" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="L64" s="11">
         <v>0</v>
       </c>
       <c r="M64" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N64" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O64" s="12">
         <v>1</v>
@@ -7153,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="Q64" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R64" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S64" s="12">
         <v>1</v>
@@ -7165,10 +8153,10 @@
         <v>0</v>
       </c>
       <c r="U64" s="11">
-        <v>142.31</v>
+        <v>118.98</v>
       </c>
       <c r="V64" s="11">
-        <v>142.31</v>
+        <v>118.98</v>
       </c>
       <c r="W64" s="12">
         <v>1</v>
@@ -7177,10 +8165,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="11">
-        <v>33.06</v>
+        <v>72.05</v>
       </c>
       <c r="Z64" s="11">
-        <v>33.06</v>
+        <v>72.05</v>
       </c>
       <c r="AA64" s="12">
         <v>1</v>
@@ -7209,37 +8197,37 @@
         <v>2043</v>
       </c>
       <c r="D65" s="10">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F65" s="10">
-        <v>117440</v>
+        <v>116883</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>127</v>
       </c>
       <c r="I65" s="22">
-        <v>46059</v>
+        <v>46126</v>
       </c>
       <c r="J65" s="22">
-        <v>46083</v>
+        <v>46126</v>
       </c>
       <c r="K65" s="23" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="L65" s="11">
         <v>0</v>
       </c>
       <c r="M65" s="11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N65" s="11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O65" s="12">
         <v>1</v>
@@ -7248,10 +8236,10 @@
         <v>0</v>
       </c>
       <c r="Q65" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R65" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S65" s="12">
         <v>1</v>
@@ -7260,10 +8248,10 @@
         <v>0</v>
       </c>
       <c r="U65" s="11">
-        <v>155.6</v>
+        <v>168.39</v>
       </c>
       <c r="V65" s="11">
-        <v>155.6</v>
+        <v>168.39</v>
       </c>
       <c r="W65" s="12">
         <v>1</v>
@@ -7272,10 +8260,10 @@
         <v>0</v>
       </c>
       <c r="Y65" s="11">
-        <v>15.45</v>
+        <v>34.89</v>
       </c>
       <c r="Z65" s="11">
-        <v>15.45</v>
+        <v>34.89</v>
       </c>
       <c r="AA65" s="12">
         <v>1</v>
@@ -7304,25 +8292,25 @@
         <v>2043</v>
       </c>
       <c r="D66" s="10">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F66" s="10">
-        <v>118069</v>
+        <v>117440</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H66" s="10" t="s">
         <v>127</v>
       </c>
       <c r="I66" s="22">
-        <v>46105</v>
+        <v>46059</v>
       </c>
       <c r="J66" s="22">
-        <v>46113</v>
+        <v>46083</v>
       </c>
       <c r="K66" s="23" t="s">
         <v>128</v>
@@ -7331,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="M66" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N66" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O66" s="12">
         <v>1</v>
@@ -7343,10 +8331,10 @@
         <v>0</v>
       </c>
       <c r="Q66" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R66" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S66" s="12">
         <v>1</v>
@@ -7355,36 +8343,131 @@
         <v>0</v>
       </c>
       <c r="U66" s="11">
+        <v>220.42</v>
+      </c>
+      <c r="V66" s="11">
+        <v>220.42</v>
+      </c>
+      <c r="W66" s="12">
+        <v>1</v>
+      </c>
+      <c r="X66" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="11">
+        <v>25.97</v>
+      </c>
+      <c r="Z66" s="11">
+        <v>25.97</v>
+      </c>
+      <c r="AA66" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A67" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="10">
+        <v>2043</v>
+      </c>
+      <c r="D67" s="10">
+        <v>2856</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F67" s="10">
+        <v>118069</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="I67" s="22">
+        <v>46105</v>
+      </c>
+      <c r="J67" s="22">
+        <v>46113</v>
+      </c>
+      <c r="K67" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="L67" s="11">
+        <v>0</v>
+      </c>
+      <c r="M67" s="11">
+        <v>1</v>
+      </c>
+      <c r="N67" s="11">
+        <v>1</v>
+      </c>
+      <c r="O67" s="12">
+        <v>1</v>
+      </c>
+      <c r="P67" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="11">
+        <v>1</v>
+      </c>
+      <c r="R67" s="11">
+        <v>1</v>
+      </c>
+      <c r="S67" s="12">
+        <v>1</v>
+      </c>
+      <c r="T67" s="11">
+        <v>0</v>
+      </c>
+      <c r="U67" s="11">
         <v>21.34</v>
       </c>
-      <c r="V66" s="11">
+      <c r="V67" s="11">
         <v>21.34</v>
       </c>
-      <c r="W66" s="12">
-        <v>1</v>
-      </c>
-      <c r="X66" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="11">
+      <c r="W67" s="12">
+        <v>1</v>
+      </c>
+      <c r="X67" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="11">
         <v>1.78</v>
       </c>
-      <c r="Z66" s="11">
+      <c r="Z67" s="11">
         <v>1.78</v>
       </c>
-      <c r="AA66" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB66" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC66" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD66" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE66" s="12">
+      <c r="AA67" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB67" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD67" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="12">
         <v>0</v>
       </c>
     </row>
@@ -7396,37 +8479,312 @@
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A7:C66">
-    <cfRule type="expression" dxfId="6" priority="29" stopIfTrue="1">
+  <conditionalFormatting sqref="AD7:AE67 N7:O67 R7:S67 V7:W67 Z7:AA67">
+    <cfRule type="cellIs" dxfId="61" priority="40" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:B67">
+    <cfRule type="expression" dxfId="60" priority="61" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:W66">
-    <cfRule type="expression" dxfId="5" priority="41" stopIfTrue="1">
+  <conditionalFormatting sqref="C7:C67">
+    <cfRule type="expression" dxfId="59" priority="60" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:V66">
-    <cfRule type="expression" dxfId="4" priority="10">
+  <conditionalFormatting sqref="D7:D67">
+    <cfRule type="expression" dxfId="58" priority="59" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N7:O66 R7:S66 V7:W66 Z7:AA66 AD7:AE66">
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="lessThan">
+  <conditionalFormatting sqref="E7:E67">
+    <cfRule type="expression" dxfId="57" priority="58" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F67">
+    <cfRule type="expression" dxfId="56" priority="57" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G67">
+    <cfRule type="expression" dxfId="55" priority="56" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H67">
+    <cfRule type="expression" dxfId="54" priority="55" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7:I67">
+    <cfRule type="expression" dxfId="53" priority="54" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7:J67">
+    <cfRule type="expression" dxfId="52" priority="53" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:K67">
+    <cfRule type="expression" dxfId="51" priority="52" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:L67">
+    <cfRule type="expression" dxfId="50" priority="51" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M67">
+    <cfRule type="expression" dxfId="49" priority="50" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:N67">
+    <cfRule type="expression" dxfId="48" priority="49" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O7:O67">
+    <cfRule type="expression" dxfId="47" priority="48" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:P67">
+    <cfRule type="expression" dxfId="46" priority="47" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q7:Q67">
+    <cfRule type="expression" dxfId="45" priority="46" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R7:R67">
+    <cfRule type="expression" dxfId="44" priority="45" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S67">
+    <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T7:T67">
+    <cfRule type="expression" dxfId="42" priority="43" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U7:U67">
+    <cfRule type="expression" dxfId="41" priority="42" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V7:V67">
+    <cfRule type="expression" dxfId="40" priority="41" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W7:W67">
+    <cfRule type="expression" dxfId="39" priority="62" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X7:X67">
+    <cfRule type="expression" dxfId="38" priority="39" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Y67">
+    <cfRule type="expression" dxfId="37" priority="38" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z7:Z67">
+    <cfRule type="expression" dxfId="36" priority="37" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA67">
+    <cfRule type="expression" dxfId="35" priority="36" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB7:AB67">
+    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC67">
+    <cfRule type="expression" dxfId="33" priority="34" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD67">
+    <cfRule type="expression" dxfId="32" priority="33" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AE67">
+    <cfRule type="expression" dxfId="31" priority="32" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AE67 N7:O67 R7:S67 V7:W67 Z7:AA67">
+    <cfRule type="cellIs" dxfId="30" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V7:W66 Z7:AA66 AD7:AE66 N7:O66 R7:S66">
-    <cfRule type="cellIs" dxfId="2" priority="40" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W7:AE66">
-    <cfRule type="expression" dxfId="1" priority="31" stopIfTrue="1">
+  <conditionalFormatting sqref="A7:B67">
+    <cfRule type="expression" dxfId="29" priority="30" stopIfTrue="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X7:AE66">
+  <conditionalFormatting sqref="C7:C67">
+    <cfRule type="expression" dxfId="28" priority="29" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7:D67">
+    <cfRule type="expression" dxfId="27" priority="28">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E67">
+    <cfRule type="expression" dxfId="26" priority="27">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F67">
+    <cfRule type="expression" dxfId="25" priority="26">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G67">
+    <cfRule type="expression" dxfId="24" priority="25">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H67">
+    <cfRule type="expression" dxfId="23" priority="24">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7:I67">
+    <cfRule type="expression" dxfId="22" priority="23">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7:J67">
+    <cfRule type="expression" dxfId="21" priority="22">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:K67">
+    <cfRule type="expression" dxfId="20" priority="21">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:L67">
+    <cfRule type="expression" dxfId="19" priority="20">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M67">
+    <cfRule type="expression" dxfId="18" priority="19">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:N67">
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O7:O67">
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:P67">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q7:Q67">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R7:R67">
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S67">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T7:T67">
+    <cfRule type="expression" dxfId="11" priority="12">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U7:U67">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V7:V67">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W7:W67">
+    <cfRule type="expression" dxfId="8" priority="31" stopIfTrue="1">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X7:X67">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Y67">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z7:Z67">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA67">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB7:AB67">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7:AC67">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD67">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AE67">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$B7&lt;&gt;""</formula>
     </cfRule>

--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925BE45E-FFF4-F940-8C22-AC81EADFF646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394FF3AD-AD04-C94A-992D-83E80F97060C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
@@ -672,14 +672,6 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -693,13 +685,21 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="72">
+  <dxfs count="136">
     <dxf>
       <border>
         <left style="hair">
@@ -1707,17 +1707,1181 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="double">
+          <color indexed="22"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="double">
           <color indexed="22"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="double">
-          <color indexed="22"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -1756,132 +2920,6 @@
       </border>
       <protection locked="1" hidden="1"/>
     </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1896,7 +2934,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="64" headerRowBorderDxfId="62" tableBorderDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="135" headerRowBorderDxfId="134" tableBorderDxfId="133">
   <autoFilter ref="A3:P5" xr:uid="{A29DCA76-5097-2F45-94DA-4B121F22F1F5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{A2D27468-D390-E245-85A6-B90C4BDF0CE1}" name="Polizas_Pagadas_Año_Anterior"/>
@@ -2245,7 +3283,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="1">
-        <v>46136</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="46" thickBot="1" x14ac:dyDescent="0.25">
@@ -2321,25 +3359,25 @@
         <v>168</v>
       </c>
       <c r="B5" s="15">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C5" s="15">
-        <v>-82</v>
+        <v>-67</v>
       </c>
       <c r="D5" s="16">
-        <v>-0.48809523809523814</v>
+        <v>-0.39880952380952384</v>
       </c>
       <c r="E5" s="15">
         <v>8098.38</v>
       </c>
       <c r="F5" s="15">
-        <v>4179.3500000000004</v>
+        <v>4768.13</v>
       </c>
       <c r="G5" s="15">
-        <v>-3919.03</v>
+        <v>-3330.25</v>
       </c>
       <c r="H5" s="16">
-        <v>-0.48392764972747637</v>
+        <v>-0.41122422015267246</v>
       </c>
       <c r="I5" s="15">
         <v>3</v>
@@ -2357,13 +3395,13 @@
         <v>372.32</v>
       </c>
       <c r="N5" s="15">
-        <v>106.9436</v>
+        <v>142.24350000000001</v>
       </c>
       <c r="O5" s="15">
-        <v>-265.37639999999999</v>
+        <v>-230.07650000000001</v>
       </c>
       <c r="P5" s="16">
-        <v>-0.7127642887838419</v>
+        <v>-0.61795364202836267</v>
       </c>
     </row>
   </sheetData>
@@ -2385,40 +3423,40 @@
   <sheetData>
     <row r="1" spans="1:31" ht="33" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>46136</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="L2" s="24" t="s">
+      <c r="L2" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="25" t="s">
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="24" t="s">
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="25" t="s">
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="24" t="s">
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
     </row>
     <row r="3" spans="1:31" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -2548,38 +3586,38 @@
       <c r="AD4" s="13"/>
       <c r="AE4" s="20"/>
     </row>
-    <row r="5" spans="1:31" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="27"/>
-      <c r="AC5" s="27"/>
-      <c r="AD5" s="27"/>
-      <c r="AE5" s="28"/>
+    <row r="5" spans="1:31" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="26"/>
+      <c r="X5" s="25"/>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="25"/>
+      <c r="AA5" s="26"/>
+      <c r="AB5" s="25"/>
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="26"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
@@ -2738,37 +3776,37 @@
         <v>278.72000000000003</v>
       </c>
       <c r="U7" s="11">
-        <v>186.68</v>
+        <v>186.97</v>
       </c>
       <c r="V7" s="11">
-        <v>-92.04</v>
+        <v>-91.75</v>
       </c>
       <c r="W7" s="12">
-        <v>-0.33019999999999999</v>
+        <v>-0.32919999999999999</v>
       </c>
       <c r="X7" s="11">
         <v>326.55</v>
       </c>
       <c r="Y7" s="11">
-        <v>215.54</v>
+        <v>221.78</v>
       </c>
       <c r="Z7" s="11">
-        <v>-111.01</v>
+        <v>-104.77</v>
       </c>
       <c r="AA7" s="12">
-        <v>-0.33989999999999998</v>
+        <v>-0.32079999999999997</v>
       </c>
       <c r="AB7" s="11">
         <v>8.8199000000000005</v>
       </c>
       <c r="AC7" s="11">
-        <v>17.076799999999999</v>
+        <v>17.4192</v>
       </c>
       <c r="AD7" s="11">
-        <v>8.2568999999999999</v>
+        <v>8.5992999999999995</v>
       </c>
       <c r="AE7" s="12">
-        <v>0.93620000000000003</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
@@ -3035,22 +4073,22 @@
         <v>31.17</v>
       </c>
       <c r="Y10" s="11">
-        <v>33.700000000000003</v>
+        <v>34.75</v>
       </c>
       <c r="Z10" s="11">
-        <v>2.5299999999999998</v>
+        <v>3.58</v>
       </c>
       <c r="AA10" s="12">
-        <v>8.1199999999999994E-2</v>
+        <v>0.1149</v>
       </c>
       <c r="AB10" s="11">
         <v>0</v>
       </c>
       <c r="AC10" s="11">
-        <v>0.2135</v>
+        <v>0.2147</v>
       </c>
       <c r="AD10" s="11">
-        <v>0.2135</v>
+        <v>0.2147</v>
       </c>
       <c r="AE10" s="12">
         <v>1</v>
@@ -3189,61 +4227,61 @@
         <v>13</v>
       </c>
       <c r="M12" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N12" s="11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O12" s="12">
-        <v>-7.6899999999999996E-2</v>
+        <v>7.6899999999999996E-2</v>
       </c>
       <c r="P12" s="11">
         <v>12</v>
       </c>
       <c r="Q12" s="11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R12" s="11">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="S12" s="12">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="T12" s="11">
         <v>619.97</v>
       </c>
       <c r="U12" s="11">
-        <v>570.01</v>
+        <v>701.65</v>
       </c>
       <c r="V12" s="11">
-        <v>-49.96</v>
+        <v>81.680000000000007</v>
       </c>
       <c r="W12" s="12">
-        <v>-8.0600000000000005E-2</v>
+        <v>0.13170000000000001</v>
       </c>
       <c r="X12" s="11">
         <v>876.03</v>
       </c>
       <c r="Y12" s="11">
-        <v>394.8</v>
+        <v>556.61</v>
       </c>
       <c r="Z12" s="11">
-        <v>-481.23</v>
+        <v>-319.42</v>
       </c>
       <c r="AA12" s="12">
-        <v>-0.54930000000000001</v>
+        <v>-0.36459999999999998</v>
       </c>
       <c r="AB12" s="11">
         <v>11.831099999999999</v>
       </c>
       <c r="AC12" s="11">
-        <v>21.471900000000002</v>
+        <v>21.480399999999999</v>
       </c>
       <c r="AD12" s="11">
-        <v>9.6408000000000005</v>
+        <v>9.6493000000000002</v>
       </c>
       <c r="AE12" s="12">
-        <v>0.81489999999999996</v>
+        <v>0.81559999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
@@ -3320,25 +4358,25 @@
         <v>116.4</v>
       </c>
       <c r="Y13" s="11">
-        <v>44.91</v>
+        <v>49.3</v>
       </c>
       <c r="Z13" s="11">
-        <v>-71.489999999999995</v>
+        <v>-67.099999999999994</v>
       </c>
       <c r="AA13" s="12">
-        <v>-0.61419999999999997</v>
+        <v>-0.57650000000000001</v>
       </c>
       <c r="AB13" s="11">
         <v>6.7163000000000004</v>
       </c>
       <c r="AC13" s="11">
-        <v>8.6708999999999996</v>
+        <v>8.7853999999999992</v>
       </c>
       <c r="AD13" s="11">
-        <v>1.9545999999999999</v>
+        <v>2.0691000000000002</v>
       </c>
       <c r="AE13" s="12">
-        <v>0.29099999999999998</v>
+        <v>0.30809999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
@@ -3664,61 +4702,61 @@
         <v>7</v>
       </c>
       <c r="M17" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N17" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O17" s="12">
-        <v>0.71430000000000005</v>
+        <v>0.85709999999999997</v>
       </c>
       <c r="P17" s="11">
         <v>8</v>
       </c>
       <c r="Q17" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R17" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S17" s="12">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="T17" s="11">
         <v>1032.33</v>
       </c>
       <c r="U17" s="11">
-        <v>788.19</v>
+        <v>864.93</v>
       </c>
       <c r="V17" s="11">
-        <v>-244.14</v>
+        <v>-167.4</v>
       </c>
       <c r="W17" s="12">
-        <v>-0.23649999999999999</v>
+        <v>-0.16220000000000001</v>
       </c>
       <c r="X17" s="11">
         <v>820.67</v>
       </c>
       <c r="Y17" s="11">
-        <v>941.95</v>
+        <v>1050.1300000000001</v>
       </c>
       <c r="Z17" s="11">
-        <v>121.28</v>
+        <v>229.46</v>
       </c>
       <c r="AA17" s="12">
-        <v>0.14779999999999999</v>
+        <v>0.27960000000000002</v>
       </c>
       <c r="AB17" s="11">
         <v>1.9245000000000001</v>
       </c>
       <c r="AC17" s="11">
-        <v>4.5960000000000001</v>
+        <v>4.6641000000000004</v>
       </c>
       <c r="AD17" s="11">
-        <v>2.6715</v>
+        <v>2.7395999999999998</v>
       </c>
       <c r="AE17" s="12">
-        <v>1.3882000000000001</v>
+        <v>1.4235</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -3771,49 +4809,49 @@
         <v>1</v>
       </c>
       <c r="Q18" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S18" s="12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T18" s="11">
         <v>19.260000000000002</v>
       </c>
       <c r="U18" s="11">
-        <v>41.45</v>
+        <v>41.68</v>
       </c>
       <c r="V18" s="11">
-        <v>22.19</v>
+        <v>22.42</v>
       </c>
       <c r="W18" s="12">
-        <v>1.1520999999999999</v>
+        <v>1.1640999999999999</v>
       </c>
       <c r="X18" s="11">
         <v>29.28</v>
       </c>
       <c r="Y18" s="11">
-        <v>16.89</v>
+        <v>20.39</v>
       </c>
       <c r="Z18" s="11">
-        <v>-12.39</v>
+        <v>-8.89</v>
       </c>
       <c r="AA18" s="12">
-        <v>-0.42320000000000002</v>
+        <v>-0.30359999999999998</v>
       </c>
       <c r="AB18" s="11">
         <v>2.0203000000000002</v>
       </c>
       <c r="AC18" s="11">
-        <v>2.1012</v>
+        <v>2.1046999999999998</v>
       </c>
       <c r="AD18" s="11">
-        <v>8.09E-2</v>
+        <v>8.4400000000000003E-2</v>
       </c>
       <c r="AE18" s="12">
-        <v>0.04</v>
+        <v>4.1799999999999997E-2</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.2">
@@ -3890,13 +4928,13 @@
         <v>6.52</v>
       </c>
       <c r="Y19" s="11">
-        <v>20.7</v>
+        <v>20.73</v>
       </c>
       <c r="Z19" s="11">
-        <v>14.18</v>
+        <v>14.21</v>
       </c>
       <c r="AA19" s="12">
-        <v>2.1747999999999998</v>
+        <v>2.1793999999999998</v>
       </c>
       <c r="AB19" s="11">
         <v>0</v>
@@ -3949,61 +4987,61 @@
         <v>11</v>
       </c>
       <c r="M20" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N20" s="11">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="O20" s="12">
-        <v>-0.2727</v>
+        <v>-0.18179999999999999</v>
       </c>
       <c r="P20" s="11">
         <v>11</v>
       </c>
       <c r="Q20" s="11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R20" s="11">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="S20" s="12">
-        <v>-0.63639999999999997</v>
+        <v>-0.2727</v>
       </c>
       <c r="T20" s="11">
         <v>429.71</v>
       </c>
       <c r="U20" s="11">
-        <v>360.76</v>
+        <v>407.52</v>
       </c>
       <c r="V20" s="11">
-        <v>-68.95</v>
+        <v>-22.19</v>
       </c>
       <c r="W20" s="12">
-        <v>-0.1605</v>
+        <v>-5.16E-2</v>
       </c>
       <c r="X20" s="11">
         <v>513.05999999999995</v>
       </c>
       <c r="Y20" s="11">
-        <v>243.25</v>
+        <v>393.63</v>
       </c>
       <c r="Z20" s="11">
-        <v>-269.81</v>
+        <v>-119.43</v>
       </c>
       <c r="AA20" s="12">
-        <v>-0.52590000000000003</v>
+        <v>-0.23280000000000001</v>
       </c>
       <c r="AB20" s="11">
         <v>1.8688</v>
       </c>
       <c r="AC20" s="11">
-        <v>0.62990000000000002</v>
+        <v>1.544</v>
       </c>
       <c r="AD20" s="11">
-        <v>-1.2388999999999999</v>
+        <v>-0.32479999999999998</v>
       </c>
       <c r="AE20" s="12">
-        <v>-0.66290000000000004</v>
+        <v>-0.17380000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.2">
@@ -4080,25 +5118,25 @@
         <v>15.44</v>
       </c>
       <c r="Y21" s="11">
-        <v>69.099999999999994</v>
+        <v>73.78</v>
       </c>
       <c r="Z21" s="11">
-        <v>53.66</v>
+        <v>58.34</v>
       </c>
       <c r="AA21" s="12">
-        <v>3.4754</v>
+        <v>3.7785000000000002</v>
       </c>
       <c r="AB21" s="11">
         <v>0.42049999999999998</v>
       </c>
       <c r="AC21" s="11">
-        <v>5.0438999999999998</v>
+        <v>5.0641999999999996</v>
       </c>
       <c r="AD21" s="11">
-        <v>4.6234000000000002</v>
+        <v>4.6436999999999999</v>
       </c>
       <c r="AE21" s="12">
-        <v>10.994999999999999</v>
+        <v>11.0433</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.2">
@@ -4270,10 +5308,10 @@
         <v>1468.63</v>
       </c>
       <c r="Y23" s="11">
-        <v>24.11</v>
+        <v>24.14</v>
       </c>
       <c r="Z23" s="11">
-        <v>-1444.52</v>
+        <v>-1444.49</v>
       </c>
       <c r="AA23" s="12">
         <v>-0.98360000000000003</v>
@@ -4555,25 +5593,25 @@
         <v>85.04</v>
       </c>
       <c r="Y26" s="11">
-        <v>59.82</v>
+        <v>68.03</v>
       </c>
       <c r="Z26" s="11">
-        <v>-25.22</v>
+        <v>-17.010000000000002</v>
       </c>
       <c r="AA26" s="12">
-        <v>-0.29659999999999997</v>
+        <v>-0.2</v>
       </c>
       <c r="AB26" s="11">
         <v>0.68210000000000004</v>
       </c>
       <c r="AC26" s="11">
-        <v>0.81779999999999997</v>
+        <v>1.4392</v>
       </c>
       <c r="AD26" s="11">
-        <v>0.13569999999999999</v>
+        <v>0.7571</v>
       </c>
       <c r="AE26" s="12">
-        <v>0.19889999999999999</v>
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.2">
@@ -4650,13 +5688,13 @@
         <v>51.12</v>
       </c>
       <c r="Y27" s="11">
-        <v>28.57</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="Z27" s="11">
-        <v>-22.55</v>
+        <v>-18.420000000000002</v>
       </c>
       <c r="AA27" s="12">
-        <v>-0.44109999999999999</v>
+        <v>-0.36030000000000001</v>
       </c>
       <c r="AB27" s="11">
         <v>0</v>
@@ -4733,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="U28" s="11">
-        <v>30.56</v>
+        <v>30.73</v>
       </c>
       <c r="V28" s="11">
-        <v>30.56</v>
+        <v>30.73</v>
       </c>
       <c r="W28" s="12">
         <v>1</v>
@@ -4745,13 +5783,13 @@
         <v>3.09</v>
       </c>
       <c r="Y28" s="11">
-        <v>13.24</v>
+        <v>21.33</v>
       </c>
       <c r="Z28" s="11">
-        <v>10.15</v>
+        <v>18.239999999999998</v>
       </c>
       <c r="AA28" s="12">
-        <v>3.2848000000000002</v>
+        <v>5.9028999999999998</v>
       </c>
       <c r="AB28" s="11">
         <v>0</v>
@@ -4828,37 +5866,37 @@
         <v>236.49</v>
       </c>
       <c r="U29" s="11">
-        <v>50.28</v>
+        <v>50.45</v>
       </c>
       <c r="V29" s="11">
-        <v>-186.21</v>
+        <v>-186.04</v>
       </c>
       <c r="W29" s="12">
-        <v>-0.78739999999999999</v>
+        <v>-0.78669999999999995</v>
       </c>
       <c r="X29" s="11">
         <v>262.24</v>
       </c>
       <c r="Y29" s="11">
-        <v>47.63</v>
+        <v>48.72</v>
       </c>
       <c r="Z29" s="11">
-        <v>-214.61</v>
+        <v>-213.52</v>
       </c>
       <c r="AA29" s="12">
-        <v>-0.81840000000000002</v>
+        <v>-0.81420000000000003</v>
       </c>
       <c r="AB29" s="11">
         <v>1.8343</v>
       </c>
       <c r="AC29" s="11">
-        <v>4.8116000000000003</v>
+        <v>6.0392999999999999</v>
       </c>
       <c r="AD29" s="11">
-        <v>2.9773000000000001</v>
+        <v>4.2050000000000001</v>
       </c>
       <c r="AE29" s="12">
-        <v>1.6231</v>
+        <v>2.2924000000000002</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.2">
@@ -4935,13 +5973,13 @@
         <v>316.83999999999997</v>
       </c>
       <c r="Y30" s="11">
-        <v>117.91</v>
+        <v>119.71</v>
       </c>
       <c r="Z30" s="11">
-        <v>-198.93</v>
+        <v>-197.13</v>
       </c>
       <c r="AA30" s="12">
-        <v>-0.62790000000000001</v>
+        <v>-0.62219999999999998</v>
       </c>
       <c r="AB30" s="11">
         <v>0.1235</v>
@@ -5018,37 +6056,37 @@
         <v>260.14999999999998</v>
       </c>
       <c r="U31" s="11">
-        <v>185.33</v>
+        <v>160.13</v>
       </c>
       <c r="V31" s="11">
-        <v>-74.819999999999993</v>
+        <v>-100.02</v>
       </c>
       <c r="W31" s="12">
-        <v>-0.28760000000000002</v>
+        <v>-0.38450000000000001</v>
       </c>
       <c r="X31" s="11">
         <v>234.63</v>
       </c>
       <c r="Y31" s="11">
-        <v>159.33000000000001</v>
+        <v>159.51</v>
       </c>
       <c r="Z31" s="11">
-        <v>-75.3</v>
+        <v>-75.12</v>
       </c>
       <c r="AA31" s="12">
-        <v>-0.32090000000000002</v>
+        <v>-0.32019999999999998</v>
       </c>
       <c r="AB31" s="11">
         <v>1.0677000000000001</v>
       </c>
       <c r="AC31" s="11">
-        <v>2.2037</v>
+        <v>2.4571000000000001</v>
       </c>
       <c r="AD31" s="11">
-        <v>1.1359999999999999</v>
+        <v>1.3894</v>
       </c>
       <c r="AE31" s="12">
-        <v>1.0640000000000001</v>
+        <v>1.3012999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.2">
@@ -5089,58 +6127,58 @@
         <v>2</v>
       </c>
       <c r="M32" s="11">
+        <v>6</v>
+      </c>
+      <c r="N32" s="11">
         <v>4</v>
       </c>
-      <c r="N32" s="11">
+      <c r="O32" s="12">
         <v>2</v>
-      </c>
-      <c r="O32" s="12">
-        <v>1</v>
       </c>
       <c r="P32" s="11">
         <v>2</v>
       </c>
       <c r="Q32" s="11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R32" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S32" s="12">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="T32" s="11">
         <v>49.3</v>
       </c>
       <c r="U32" s="11">
-        <v>123.69</v>
+        <v>174.68</v>
       </c>
       <c r="V32" s="11">
-        <v>74.39</v>
+        <v>125.38</v>
       </c>
       <c r="W32" s="12">
-        <v>1.5088999999999999</v>
+        <v>2.5432000000000001</v>
       </c>
       <c r="X32" s="11">
         <v>89.3</v>
       </c>
       <c r="Y32" s="11">
-        <v>114.94</v>
+        <v>130.19</v>
       </c>
       <c r="Z32" s="11">
-        <v>25.64</v>
+        <v>40.89</v>
       </c>
       <c r="AA32" s="12">
-        <v>0.28710000000000002</v>
+        <v>0.45789999999999997</v>
       </c>
       <c r="AB32" s="11">
         <v>0</v>
       </c>
       <c r="AC32" s="11">
-        <v>1.2112000000000001</v>
+        <v>1.2130000000000001</v>
       </c>
       <c r="AD32" s="11">
-        <v>1.2112000000000001</v>
+        <v>1.2130000000000001</v>
       </c>
       <c r="AE32" s="12">
         <v>1</v>
@@ -5220,13 +6258,13 @@
         <v>73</v>
       </c>
       <c r="Y33" s="11">
-        <v>49.61</v>
+        <v>49.71</v>
       </c>
       <c r="Z33" s="11">
-        <v>-23.39</v>
+        <v>-23.29</v>
       </c>
       <c r="AA33" s="12">
-        <v>-0.32040000000000002</v>
+        <v>-0.31900000000000001</v>
       </c>
       <c r="AB33" s="11">
         <v>3.1848999999999998</v>
@@ -5315,13 +6353,13 @@
         <v>349.84</v>
       </c>
       <c r="Y34" s="11">
-        <v>155.65</v>
+        <v>159.78</v>
       </c>
       <c r="Z34" s="11">
-        <v>-194.19</v>
+        <v>-190.06</v>
       </c>
       <c r="AA34" s="12">
-        <v>-0.55510000000000004</v>
+        <v>-0.54330000000000001</v>
       </c>
       <c r="AB34" s="11">
         <v>0</v>
@@ -5505,25 +6543,25 @@
         <v>377.79</v>
       </c>
       <c r="Y36" s="11">
-        <v>72.89</v>
+        <v>74.88</v>
       </c>
       <c r="Z36" s="11">
-        <v>-304.89999999999998</v>
+        <v>-302.91000000000003</v>
       </c>
       <c r="AA36" s="12">
-        <v>-0.80710000000000004</v>
+        <v>-0.80179999999999996</v>
       </c>
       <c r="AB36" s="11">
         <v>5.3985000000000003</v>
       </c>
       <c r="AC36" s="11">
-        <v>9.2260000000000009</v>
+        <v>10.6434</v>
       </c>
       <c r="AD36" s="11">
-        <v>3.8275000000000001</v>
+        <v>5.2449000000000003</v>
       </c>
       <c r="AE36" s="12">
-        <v>0.70899999999999996</v>
+        <v>0.97150000000000003</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.2">
@@ -5600,13 +6638,13 @@
         <v>185.17</v>
       </c>
       <c r="Y37" s="11">
-        <v>153.1</v>
+        <v>153.13999999999999</v>
       </c>
       <c r="Z37" s="11">
-        <v>-32.07</v>
+        <v>-32.03</v>
       </c>
       <c r="AA37" s="12">
-        <v>-0.17319999999999999</v>
+        <v>-0.17299999999999999</v>
       </c>
       <c r="AB37" s="11">
         <v>0</v>
@@ -5802,13 +6840,13 @@
         <v>0.30480000000000002</v>
       </c>
       <c r="AC39" s="11">
-        <v>0.1643</v>
+        <v>0.38040000000000002</v>
       </c>
       <c r="AD39" s="11">
-        <v>-0.14050000000000001</v>
+        <v>7.5600000000000001E-2</v>
       </c>
       <c r="AE39" s="12">
-        <v>-0.46100000000000002</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.2">
@@ -5885,13 +6923,13 @@
         <v>43.61</v>
       </c>
       <c r="Y40" s="11">
-        <v>30.08</v>
+        <v>30.98</v>
       </c>
       <c r="Z40" s="11">
-        <v>-13.53</v>
+        <v>-12.63</v>
       </c>
       <c r="AA40" s="12">
-        <v>-0.31019999999999998</v>
+        <v>-0.28960000000000002</v>
       </c>
       <c r="AB40" s="11">
         <v>0</v>
@@ -6158,25 +7196,25 @@
         <v>17.11</v>
       </c>
       <c r="U43" s="11">
-        <v>-0.22</v>
+        <v>-0.38</v>
       </c>
       <c r="V43" s="11">
-        <v>-17.329999999999998</v>
+        <v>-17.489999999999998</v>
       </c>
       <c r="W43" s="12">
-        <v>-1.0128999999999999</v>
+        <v>-1.0222</v>
       </c>
       <c r="X43" s="11">
         <v>105.69</v>
       </c>
       <c r="Y43" s="11">
-        <v>14.37</v>
+        <v>14.4</v>
       </c>
       <c r="Z43" s="11">
-        <v>-91.32</v>
+        <v>-91.29</v>
       </c>
       <c r="AA43" s="12">
-        <v>-0.86399999999999999</v>
+        <v>-0.86380000000000001</v>
       </c>
       <c r="AB43" s="11">
         <v>0</v>
@@ -6265,13 +7303,13 @@
         <v>50.17</v>
       </c>
       <c r="Y44" s="11">
-        <v>35.53</v>
+        <v>35.58</v>
       </c>
       <c r="Z44" s="11">
-        <v>-14.64</v>
+        <v>-14.59</v>
       </c>
       <c r="AA44" s="12">
-        <v>-0.2918</v>
+        <v>-0.2908</v>
       </c>
       <c r="AB44" s="11">
         <v>0</v>
@@ -6324,13 +7362,13 @@
         <v>14</v>
       </c>
       <c r="M45" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N45" s="11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="O45" s="12">
-        <v>-0.28570000000000001</v>
+        <v>-0.21429999999999999</v>
       </c>
       <c r="P45" s="11">
         <v>14</v>
@@ -6348,37 +7386,37 @@
         <v>446.24</v>
       </c>
       <c r="U45" s="11">
-        <v>301.42</v>
+        <v>335.91</v>
       </c>
       <c r="V45" s="11">
-        <v>-144.82</v>
+        <v>-110.33</v>
       </c>
       <c r="W45" s="12">
-        <v>-0.32450000000000001</v>
+        <v>-0.2472</v>
       </c>
       <c r="X45" s="11">
         <v>198.56</v>
       </c>
       <c r="Y45" s="11">
-        <v>241.16</v>
+        <v>243.51</v>
       </c>
       <c r="Z45" s="11">
-        <v>42.6</v>
+        <v>44.95</v>
       </c>
       <c r="AA45" s="12">
-        <v>0.2145</v>
+        <v>0.22639999999999999</v>
       </c>
       <c r="AB45" s="11">
         <v>0.2029</v>
       </c>
       <c r="AC45" s="11">
-        <v>1.087</v>
+        <v>1.0906</v>
       </c>
       <c r="AD45" s="11">
-        <v>0.8841</v>
+        <v>0.88770000000000004</v>
       </c>
       <c r="AE45" s="12">
-        <v>4.3573000000000004</v>
+        <v>4.3750999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
@@ -6455,13 +7493,13 @@
         <v>276.66000000000003</v>
       </c>
       <c r="Y46" s="11">
-        <v>57.27</v>
+        <v>71.81</v>
       </c>
       <c r="Z46" s="11">
-        <v>-219.39</v>
+        <v>-204.85</v>
       </c>
       <c r="AA46" s="12">
-        <v>-0.79300000000000004</v>
+        <v>-0.74039999999999995</v>
       </c>
       <c r="AB46" s="11">
         <v>0</v>
@@ -6633,25 +7671,25 @@
         <v>169.31</v>
       </c>
       <c r="U48" s="11">
-        <v>61.75</v>
+        <v>62.1</v>
       </c>
       <c r="V48" s="11">
-        <v>-107.56</v>
+        <v>-107.21</v>
       </c>
       <c r="W48" s="12">
-        <v>-0.63529999999999998</v>
+        <v>-0.63319999999999999</v>
       </c>
       <c r="X48" s="11">
         <v>93.74</v>
       </c>
       <c r="Y48" s="11">
-        <v>95.65</v>
+        <v>101.47</v>
       </c>
       <c r="Z48" s="11">
-        <v>1.91</v>
+        <v>7.73</v>
       </c>
       <c r="AA48" s="12">
-        <v>2.0400000000000001E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="AB48" s="11">
         <v>0</v>
@@ -6835,13 +7873,13 @@
         <v>131.56</v>
       </c>
       <c r="Y50" s="11">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Z50" s="11">
-        <v>-129.76</v>
+        <v>-129.75</v>
       </c>
       <c r="AA50" s="12">
-        <v>-0.98629999999999995</v>
+        <v>-0.98619999999999997</v>
       </c>
       <c r="AB50" s="11">
         <v>0</v>
@@ -7025,22 +8063,22 @@
         <v>51.32</v>
       </c>
       <c r="Y52" s="11">
-        <v>16.809999999999999</v>
+        <v>16.82</v>
       </c>
       <c r="Z52" s="11">
-        <v>-34.51</v>
+        <v>-34.5</v>
       </c>
       <c r="AA52" s="12">
-        <v>-0.6724</v>
+        <v>-0.67230000000000001</v>
       </c>
       <c r="AB52" s="11">
         <v>0</v>
       </c>
       <c r="AC52" s="11">
-        <v>3.8157000000000001</v>
+        <v>3.8371</v>
       </c>
       <c r="AD52" s="11">
-        <v>3.8157000000000001</v>
+        <v>3.8371</v>
       </c>
       <c r="AE52" s="12">
         <v>1</v>
@@ -7120,25 +8158,25 @@
         <v>81.27</v>
       </c>
       <c r="Y53" s="11">
-        <v>26.65</v>
+        <v>31.26</v>
       </c>
       <c r="Z53" s="11">
-        <v>-54.62</v>
+        <v>-50.01</v>
       </c>
       <c r="AA53" s="12">
-        <v>-0.67210000000000003</v>
+        <v>-0.61539999999999995</v>
       </c>
       <c r="AB53" s="11">
         <v>0</v>
       </c>
       <c r="AC53" s="11">
-        <v>0</v>
+        <v>0.4395</v>
       </c>
       <c r="AD53" s="11">
-        <v>0</v>
+        <v>0.4395</v>
       </c>
       <c r="AE53" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.2">
@@ -7310,13 +8348,13 @@
         <v>13.61</v>
       </c>
       <c r="Y55" s="11">
-        <v>79.680000000000007</v>
+        <v>79.69</v>
       </c>
       <c r="Z55" s="11">
-        <v>66.069999999999993</v>
+        <v>66.08</v>
       </c>
       <c r="AA55" s="12">
-        <v>4.8544999999999998</v>
+        <v>4.8552999999999997</v>
       </c>
       <c r="AB55" s="11">
         <v>0</v>
@@ -7393,10 +8431,10 @@
         <v>0</v>
       </c>
       <c r="U56" s="11">
-        <v>40.83</v>
+        <v>41.06</v>
       </c>
       <c r="V56" s="11">
-        <v>40.83</v>
+        <v>41.06</v>
       </c>
       <c r="W56" s="12">
         <v>1</v>
@@ -7405,10 +8443,10 @@
         <v>0</v>
       </c>
       <c r="Y56" s="11">
-        <v>71.260000000000005</v>
+        <v>80.680000000000007</v>
       </c>
       <c r="Z56" s="11">
-        <v>71.260000000000005</v>
+        <v>80.680000000000007</v>
       </c>
       <c r="AA56" s="12">
         <v>1</v>
@@ -7500,10 +8538,10 @@
         <v>0</v>
       </c>
       <c r="Y57" s="11">
-        <v>31.3</v>
+        <v>31.32</v>
       </c>
       <c r="Z57" s="11">
-        <v>31.3</v>
+        <v>31.32</v>
       </c>
       <c r="AA57" s="12">
         <v>1</v>
@@ -7595,10 +8633,10 @@
         <v>0</v>
       </c>
       <c r="Y58" s="11">
-        <v>22.36</v>
+        <v>24.06</v>
       </c>
       <c r="Z58" s="11">
-        <v>22.36</v>
+        <v>24.06</v>
       </c>
       <c r="AA58" s="12">
         <v>1</v>
@@ -7785,10 +8823,10 @@
         <v>0</v>
       </c>
       <c r="Y60" s="11">
-        <v>148.4</v>
+        <v>150.26</v>
       </c>
       <c r="Z60" s="11">
-        <v>148.4</v>
+        <v>150.26</v>
       </c>
       <c r="AA60" s="12">
         <v>1</v>
@@ -7797,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="AC60" s="11">
-        <v>2.3195000000000001</v>
+        <v>2.5602</v>
       </c>
       <c r="AD60" s="11">
-        <v>2.3195000000000001</v>
+        <v>2.5602</v>
       </c>
       <c r="AE60" s="12">
         <v>1</v>
@@ -7880,10 +8918,10 @@
         <v>0</v>
       </c>
       <c r="Y61" s="11">
-        <v>53.86</v>
+        <v>55.61</v>
       </c>
       <c r="Z61" s="11">
-        <v>53.86</v>
+        <v>55.61</v>
       </c>
       <c r="AA61" s="12">
         <v>1</v>
@@ -7975,10 +9013,10 @@
         <v>0</v>
       </c>
       <c r="Y62" s="11">
-        <v>73.959999999999994</v>
+        <v>89.29</v>
       </c>
       <c r="Z62" s="11">
-        <v>73.959999999999994</v>
+        <v>89.29</v>
       </c>
       <c r="AA62" s="12">
         <v>1</v>
@@ -8070,10 +9108,10 @@
         <v>0</v>
       </c>
       <c r="Y63" s="11">
-        <v>6.35</v>
+        <v>6.36</v>
       </c>
       <c r="Z63" s="11">
-        <v>6.35</v>
+        <v>6.36</v>
       </c>
       <c r="AA63" s="12">
         <v>1</v>
@@ -8165,10 +9203,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="11">
-        <v>72.05</v>
+        <v>74.08</v>
       </c>
       <c r="Z64" s="11">
-        <v>72.05</v>
+        <v>74.08</v>
       </c>
       <c r="AA64" s="12">
         <v>1</v>
@@ -8224,10 +9262,10 @@
         <v>0</v>
       </c>
       <c r="M65" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N65" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O65" s="12">
         <v>1</v>
@@ -8236,10 +9274,10 @@
         <v>0</v>
       </c>
       <c r="Q65" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R65" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S65" s="12">
         <v>1</v>
@@ -8248,10 +9286,10 @@
         <v>0</v>
       </c>
       <c r="U65" s="11">
-        <v>168.39</v>
+        <v>193.8</v>
       </c>
       <c r="V65" s="11">
-        <v>168.39</v>
+        <v>193.8</v>
       </c>
       <c r="W65" s="12">
         <v>1</v>
@@ -8260,10 +9298,10 @@
         <v>0</v>
       </c>
       <c r="Y65" s="11">
-        <v>34.89</v>
+        <v>68.16</v>
       </c>
       <c r="Z65" s="11">
-        <v>34.89</v>
+        <v>68.16</v>
       </c>
       <c r="AA65" s="12">
         <v>1</v>
@@ -8331,10 +9369,10 @@
         <v>0</v>
       </c>
       <c r="Q66" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R66" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S66" s="12">
         <v>1</v>
@@ -8343,10 +9381,10 @@
         <v>0</v>
       </c>
       <c r="U66" s="11">
-        <v>220.42</v>
+        <v>220.78</v>
       </c>
       <c r="V66" s="11">
-        <v>220.42</v>
+        <v>220.78</v>
       </c>
       <c r="W66" s="12">
         <v>1</v>
@@ -8355,10 +9393,10 @@
         <v>0</v>
       </c>
       <c r="Y66" s="11">
-        <v>25.97</v>
+        <v>33.94</v>
       </c>
       <c r="Z66" s="11">
-        <v>25.97</v>
+        <v>33.94</v>
       </c>
       <c r="AA66" s="12">
         <v>1</v>
@@ -8450,10 +9488,10 @@
         <v>0</v>
       </c>
       <c r="Y67" s="11">
-        <v>1.78</v>
+        <v>3.57</v>
       </c>
       <c r="Z67" s="11">
-        <v>1.78</v>
+        <v>3.57</v>
       </c>
       <c r="AA67" s="12">
         <v>1</v>

--- a/administrador/comparativo_vida/comparativo vida.xlsx
+++ b/administrador/comparativo_vida/comparativo vida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/administrador/comparativo_vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394FF3AD-AD04-C94A-992D-83E80F97060C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8CA1DC-96AD-E24E-B39A-4E58ABB441F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" activeTab="1" xr2:uid="{E1D9733C-3B37-8B4F-9120-34426D0B6D20}"/>
   </bookViews>
   <sheets>
     <sheet name="promotoria" sheetId="2" r:id="rId1"/>
@@ -90,6 +90,291 @@
     <t>%_Crec_Prima_Pagada_Reclutas</t>
   </si>
   <si>
+    <t>GABRIELA CASTAÐEDA SALAZAR</t>
+  </si>
+  <si>
+    <t>MIREYA LIZETTE TORRES GARCIA</t>
+  </si>
+  <si>
+    <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
+  </si>
+  <si>
+    <t>ARMANDO JONATHAN DE LA CRUZ DIAZ</t>
+  </si>
+  <si>
+    <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
+  </si>
+  <si>
+    <t>ROCIO IVON RUIZ GARCIA</t>
+  </si>
+  <si>
+    <t>ANGELICA YADIRA ROMERO JAUREGUI</t>
+  </si>
+  <si>
+    <t>ISAI ANTONIO ROJAS MARTINEZ</t>
+  </si>
+  <si>
+    <t>RODRIGO RAMON ALVAREZ JIMENEZ</t>
+  </si>
+  <si>
+    <t>MIRIAM ROCIO LOMELI CHAVEZ</t>
+  </si>
+  <si>
+    <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
+  </si>
+  <si>
+    <t>ROCIO YANETH OCHOA IBARRA</t>
+  </si>
+  <si>
+    <t>ANAIS LUA MORENO</t>
+  </si>
+  <si>
+    <t>JOSE RENE DE ALBA MORALES</t>
+  </si>
+  <si>
+    <t>LUIS FERNANDO HERNANDEZ AYALA</t>
+  </si>
+  <si>
+    <t>JORGE ANTONIO LUNA LARA</t>
+  </si>
+  <si>
+    <t>CLAUDIA VALERIA HERNANDEZ MACIAS</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARIO ALBERTO VILLASEÐOR SANCHEZ</t>
+  </si>
+  <si>
+    <t>LAURA DOLORES MONTAÐO MONTAÐO</t>
+  </si>
+  <si>
+    <t>BRUNO BRAULIO MACIAS ALVAREZ</t>
+  </si>
+  <si>
+    <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
+  </si>
+  <si>
+    <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
+  </si>
+  <si>
+    <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
+  </si>
+  <si>
+    <t>MARIA JOSE GUZMAN ZAMORA</t>
+  </si>
+  <si>
+    <t>LINDA TANIA MIROSLAVA ENRIQUEZ PRECIADO</t>
+  </si>
+  <si>
+    <t>VELIA PATRICIA BERNAL RAMOS</t>
+  </si>
+  <si>
+    <t>ANA VERONICA GONZALEZ GAYTAN</t>
+  </si>
+  <si>
+    <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
+  </si>
+  <si>
+    <t>GERARDO DANIEL BARAJAS TORRES</t>
+  </si>
+  <si>
+    <t>PAULA ANGELICA LOMELI CAZARES</t>
+  </si>
+  <si>
+    <t>SOFIA CAMPILLO VASCONCELOS</t>
+  </si>
+  <si>
+    <t>Pólizas Emitidas</t>
+  </si>
+  <si>
+    <t>Pólizas Pagadas</t>
+  </si>
+  <si>
+    <t>Prima Emitida Anualizada (Neta)</t>
+  </si>
+  <si>
+    <t>Prima Pagada</t>
+  </si>
+  <si>
+    <t>Dumpin al 10%</t>
+  </si>
+  <si>
+    <t>Oficina</t>
+  </si>
+  <si>
+    <t>Gerencia</t>
+  </si>
+  <si>
+    <t>Mat</t>
+  </si>
+  <si>
+    <t>Suc</t>
+  </si>
+  <si>
+    <t>Promotor</t>
+  </si>
+  <si>
+    <t>Nombre del Asesor</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Conexión</t>
+  </si>
+  <si>
+    <t>Concurso</t>
+  </si>
+  <si>
+    <t>Clase</t>
+  </si>
+  <si>
+    <t>Año Anterior</t>
+  </si>
+  <si>
+    <t>Añoa Actual</t>
+  </si>
+  <si>
+    <t>Crec</t>
+  </si>
+  <si>
+    <t>% Crec</t>
+  </si>
+  <si>
+    <t>a2</t>
+  </si>
+  <si>
+    <t>a3</t>
+  </si>
+  <si>
+    <t>a4</t>
+  </si>
+  <si>
+    <t>a5</t>
+  </si>
+  <si>
+    <t>a6</t>
+  </si>
+  <si>
+    <t>a7</t>
+  </si>
+  <si>
+    <t>a8</t>
+  </si>
+  <si>
+    <t>a9</t>
+  </si>
+  <si>
+    <t>a10</t>
+  </si>
+  <si>
+    <t>a11</t>
+  </si>
+  <si>
+    <t>a12</t>
+  </si>
+  <si>
+    <t>a13</t>
+  </si>
+  <si>
+    <t>a14</t>
+  </si>
+  <si>
+    <t>a15</t>
+  </si>
+  <si>
+    <t>a16</t>
+  </si>
+  <si>
+    <t>a17</t>
+  </si>
+  <si>
+    <t>a18</t>
+  </si>
+  <si>
+    <t>a19</t>
+  </si>
+  <si>
+    <t>a20</t>
+  </si>
+  <si>
+    <t>a21</t>
+  </si>
+  <si>
+    <t>a22</t>
+  </si>
+  <si>
+    <t>a23</t>
+  </si>
+  <si>
+    <t>a24</t>
+  </si>
+  <si>
+    <t>a25</t>
+  </si>
+  <si>
+    <t>a26</t>
+  </si>
+  <si>
+    <t>a27</t>
+  </si>
+  <si>
+    <t>a28</t>
+  </si>
+  <si>
+    <t>a29</t>
+  </si>
+  <si>
+    <t>a30</t>
+  </si>
+  <si>
+    <t>a31</t>
+  </si>
+  <si>
+    <t>GUADALAJARA</t>
+  </si>
+  <si>
+    <t>GUADALAJARA (A. RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ALEJANDRA GABRIELA AMBRIZ GOMEZ</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>MONSERRAT VELASCO SANTOS</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>MARIO IVAN ROMERO GONZALEZ</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>RAFAEL ALBERTO SUAREZ BAQUEDANO</t>
   </si>
   <si>
@@ -163,291 +448,6 @@
   </si>
   <si>
     <t>PAULINA LIZBETH SOTO MUÐIZ</t>
-  </si>
-  <si>
-    <t>GABRIELA CASTAÐEDA SALAZAR</t>
-  </si>
-  <si>
-    <t>MIREYA LIZETTE TORRES GARCIA</t>
-  </si>
-  <si>
-    <t>ORLANDA JIMENA CERVANTES NUÐEZ</t>
-  </si>
-  <si>
-    <t>ARMANDO JONATHAN DE LA CRUZ DIAZ</t>
-  </si>
-  <si>
-    <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
-  </si>
-  <si>
-    <t>MARIA ELIZABETH LLAMAS LOPEZ</t>
-  </si>
-  <si>
-    <t>ROCIO IVON RUIZ GARCIA</t>
-  </si>
-  <si>
-    <t>ANGELICA YADIRA ROMERO JAUREGUI</t>
-  </si>
-  <si>
-    <t>ISAI ANTONIO ROJAS MARTINEZ</t>
-  </si>
-  <si>
-    <t>RODRIGO RAMON ALVAREZ JIMENEZ</t>
-  </si>
-  <si>
-    <t>MIRIAM ROCIO LOMELI CHAVEZ</t>
-  </si>
-  <si>
-    <t>EVELYN CAROLINA VENEGAS IÐIGUEZ</t>
-  </si>
-  <si>
-    <t>ROCIO YANETH OCHOA IBARRA</t>
-  </si>
-  <si>
-    <t>ANAIS LUA MORENO</t>
-  </si>
-  <si>
-    <t>JOSE RENE DE ALBA MORALES</t>
-  </si>
-  <si>
-    <t>LUIS FERNANDO HERNANDEZ AYALA</t>
-  </si>
-  <si>
-    <t>JORGE ANTONIO LUNA LARA</t>
-  </si>
-  <si>
-    <t>CLAUDIA VALERIA HERNANDEZ MACIAS</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARIO ALBERTO VILLASEÐOR SANCHEZ</t>
-  </si>
-  <si>
-    <t>LAURA DOLORES MONTAÐO MONTAÐO</t>
-  </si>
-  <si>
-    <t>BRUNO BRAULIO MACIAS ALVAREZ</t>
-  </si>
-  <si>
-    <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
-  </si>
-  <si>
-    <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
-  </si>
-  <si>
-    <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
-  </si>
-  <si>
-    <t>MARIA JOSE GUZMAN ZAMORA</t>
-  </si>
-  <si>
-    <t>LINDA TANIA MIROSLAVA ENRIQUEZ PRECIADO</t>
-  </si>
-  <si>
-    <t>VELIA PATRICIA BERNAL RAMOS</t>
-  </si>
-  <si>
-    <t>ANA VERONICA GONZALEZ GAYTAN</t>
-  </si>
-  <si>
-    <t>LUVIA PATRICIA FIGUEROA CASTRO</t>
-  </si>
-  <si>
-    <t>GERARDO DANIEL BARAJAS TORRES</t>
-  </si>
-  <si>
-    <t>PAULA ANGELICA LOMELI CAZARES</t>
-  </si>
-  <si>
-    <t>SOFIA CAMPILLO VASCONCELOS</t>
-  </si>
-  <si>
-    <t>Pólizas Emitidas</t>
-  </si>
-  <si>
-    <t>Pólizas Pagadas</t>
-  </si>
-  <si>
-    <t>Prima Emitida Anualizada (Neta)</t>
-  </si>
-  <si>
-    <t>Prima Pagada</t>
-  </si>
-  <si>
-    <t>Dumpin al 10%</t>
-  </si>
-  <si>
-    <t>Oficina</t>
-  </si>
-  <si>
-    <t>Gerencia</t>
-  </si>
-  <si>
-    <t>Mat</t>
-  </si>
-  <si>
-    <t>Suc</t>
-  </si>
-  <si>
-    <t>Promotor</t>
-  </si>
-  <si>
-    <t>Nombre del Asesor</t>
-  </si>
-  <si>
-    <t>Grupo</t>
-  </si>
-  <si>
-    <t>Conexión</t>
-  </si>
-  <si>
-    <t>Concurso</t>
-  </si>
-  <si>
-    <t>Clase</t>
-  </si>
-  <si>
-    <t>Año Anterior</t>
-  </si>
-  <si>
-    <t>Añoa Actual</t>
-  </si>
-  <si>
-    <t>Crec</t>
-  </si>
-  <si>
-    <t>% Crec</t>
-  </si>
-  <si>
-    <t>a2</t>
-  </si>
-  <si>
-    <t>a3</t>
-  </si>
-  <si>
-    <t>a4</t>
-  </si>
-  <si>
-    <t>a5</t>
-  </si>
-  <si>
-    <t>a6</t>
-  </si>
-  <si>
-    <t>a7</t>
-  </si>
-  <si>
-    <t>a8</t>
-  </si>
-  <si>
-    <t>a9</t>
-  </si>
-  <si>
-    <t>a10</t>
-  </si>
-  <si>
-    <t>a11</t>
-  </si>
-  <si>
-    <t>a12</t>
-  </si>
-  <si>
-    <t>a13</t>
-  </si>
-  <si>
-    <t>a14</t>
-  </si>
-  <si>
-    <t>a15</t>
-  </si>
-  <si>
-    <t>a16</t>
-  </si>
-  <si>
-    <t>a17</t>
-  </si>
-  <si>
-    <t>a18</t>
-  </si>
-  <si>
-    <t>a19</t>
-  </si>
-  <si>
-    <t>a20</t>
-  </si>
-  <si>
-    <t>a21</t>
-  </si>
-  <si>
-    <t>a22</t>
-  </si>
-  <si>
-    <t>a23</t>
-  </si>
-  <si>
-    <t>a24</t>
-  </si>
-  <si>
-    <t>a25</t>
-  </si>
-  <si>
-    <t>a26</t>
-  </si>
-  <si>
-    <t>a27</t>
-  </si>
-  <si>
-    <t>a28</t>
-  </si>
-  <si>
-    <t>a29</t>
-  </si>
-  <si>
-    <t>a30</t>
-  </si>
-  <si>
-    <t>a31</t>
-  </si>
-  <si>
-    <t>GUADALAJARA</t>
-  </si>
-  <si>
-    <t>GUADALAJARA (A. RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ALEJANDRA GABRIELA AMBRIZ GOMEZ</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>MONSERRAT VELASCO SANTOS</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>MARIO IVAN ROMERO GONZALEZ</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
 </sst>
 </file>
@@ -699,7 +699,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="136">
+  <dxfs count="72">
     <dxf>
       <border>
         <left style="hair">
@@ -1188,1044 +1188,6 @@
         <extend val="0"/>
         <color indexed="10"/>
       </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border>
         <left style="hair">
           <color indexed="64"/>
@@ -2934,7 +1896,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="135" headerRowBorderDxfId="134" tableBorderDxfId="133">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA801B-A74C-1349-A3D4-C6A1109DE591}" name="Tabla10" displayName="Tabla10" ref="A3:P5" totalsRowShown="0" headerRowDxfId="71" headerRowBorderDxfId="70" tableBorderDxfId="69">
   <autoFilter ref="A3:P5" xr:uid="{A29DCA76-5097-2F45-94DA-4B121F22F1F5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{A2D27468-D390-E245-85A6-B90C4BDF0CE1}" name="Polizas_Pagadas_Año_Anterior"/>
@@ -3283,7 +2245,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="1">
-        <v>46142</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="46" thickBot="1" x14ac:dyDescent="0.25">
@@ -3356,52 +2318,52 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="15">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="B5" s="15">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C5" s="15">
-        <v>-67</v>
+        <v>-86</v>
       </c>
       <c r="D5" s="16">
-        <v>-0.39880952380952384</v>
+        <v>-0.43216080402010049</v>
       </c>
       <c r="E5" s="15">
-        <v>8098.38</v>
+        <v>9434.75</v>
       </c>
       <c r="F5" s="15">
-        <v>4768.13</v>
+        <v>5253.44</v>
       </c>
       <c r="G5" s="15">
-        <v>-3330.25</v>
+        <v>-4181.3100000000004</v>
       </c>
       <c r="H5" s="16">
-        <v>-0.41122422015267246</v>
+        <v>-0.44318185431516477</v>
       </c>
       <c r="I5" s="15">
+        <v>4</v>
+      </c>
+      <c r="J5" s="15">
         <v>3</v>
-      </c>
-      <c r="J5" s="15">
-        <v>2</v>
       </c>
       <c r="K5" s="15">
         <v>-1</v>
       </c>
       <c r="L5" s="16">
-        <v>-0.33333333333333337</v>
+        <v>-0.25</v>
       </c>
       <c r="M5" s="15">
-        <v>372.32</v>
+        <v>524.92999999999995</v>
       </c>
       <c r="N5" s="15">
-        <v>142.24350000000001</v>
+        <v>183.75559999999999</v>
       </c>
       <c r="O5" s="15">
-        <v>-230.07650000000001</v>
+        <v>-341.17439999999999</v>
       </c>
       <c r="P5" s="16">
-        <v>-0.61795364202836267</v>
+        <v>-0.64994265902120274</v>
       </c>
     </row>
   </sheetData>
@@ -3423,36 +2385,36 @@
   <sheetData>
     <row r="1" spans="1:31" ht="33" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>46142</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L2" s="28" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M2" s="28"/>
       <c r="N2" s="28"/>
       <c r="O2" s="28"/>
       <c r="P2" s="29" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="Q2" s="29"/>
       <c r="R2" s="29"/>
       <c r="S2" s="29"/>
       <c r="T2" s="28" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="U2" s="28"/>
       <c r="V2" s="28"/>
       <c r="W2" s="28"/>
       <c r="X2" s="29" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="Y2" s="29"/>
       <c r="Z2" s="29"/>
       <c r="AA2" s="29"/>
       <c r="AB2" s="28" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="AC2" s="28"/>
       <c r="AD2" s="28"/>
@@ -3460,97 +2422,97 @@
     </row>
     <row r="3" spans="1:31" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="T3" s="17" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="U3" s="17" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="V3" s="17" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="W3" s="18" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="AB3" s="17" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AC3" s="17" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="AD3" s="17" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="AE3" s="18" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="17" thickTop="1" x14ac:dyDescent="0.2">
@@ -3621,105 +2583,105 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="M6" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="P6" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q6" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="S6" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="T6" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="U6" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="V6" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="W6" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="X6" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y6" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z6" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA6" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="21" t="s">
+      <c r="AB6" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="AC6" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="AD6" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="AE6" s="21" t="s">
         <v>98</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="M6" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="N6" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="O6" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="P6" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q6" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="R6" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="S6" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="T6" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="U6" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="V6" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="W6" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="X6" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y6" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z6" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA6" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB6" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="AC6" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD6" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE6" s="21" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C7" s="10">
         <v>2043</v>
@@ -3728,16 +2690,16 @@
         <v>2043</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F7" s="10">
         <v>47116</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I7" s="22">
         <v>44616</v>
@@ -3746,75 +2708,75 @@
         <v>44616</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L7" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="M7" s="11">
+        <v>8</v>
+      </c>
+      <c r="N7" s="11">
+        <v>-0.5</v>
+      </c>
+      <c r="O7" s="12">
+        <v>-5.8799999999999998E-2</v>
+      </c>
+      <c r="P7" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="Q7" s="11">
         <v>7</v>
       </c>
-      <c r="M7" s="11">
-        <v>6</v>
-      </c>
-      <c r="N7" s="11">
-        <v>-1</v>
-      </c>
-      <c r="O7" s="12">
-        <v>-0.1429</v>
-      </c>
-      <c r="P7" s="11">
-        <v>7</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>5</v>
-      </c>
       <c r="R7" s="11">
-        <v>-2</v>
+        <v>-1.5</v>
       </c>
       <c r="S7" s="12">
-        <v>-0.28570000000000001</v>
+        <v>-0.17649999999999999</v>
       </c>
       <c r="T7" s="11">
-        <v>278.72000000000003</v>
+        <v>325.7</v>
       </c>
       <c r="U7" s="11">
-        <v>186.97</v>
+        <v>210.32</v>
       </c>
       <c r="V7" s="11">
-        <v>-91.75</v>
+        <v>-115.38</v>
       </c>
       <c r="W7" s="12">
-        <v>-0.32919999999999999</v>
+        <v>-0.3543</v>
       </c>
       <c r="X7" s="11">
-        <v>326.55</v>
+        <v>392.62</v>
       </c>
       <c r="Y7" s="11">
-        <v>221.78</v>
+        <v>275.27</v>
       </c>
       <c r="Z7" s="11">
-        <v>-104.77</v>
+        <v>-117.35</v>
       </c>
       <c r="AA7" s="12">
-        <v>-0.32079999999999997</v>
+        <v>-0.2989</v>
       </c>
       <c r="AB7" s="11">
-        <v>8.8199000000000005</v>
+        <v>10.642300000000001</v>
       </c>
       <c r="AC7" s="11">
-        <v>17.4192</v>
+        <v>19.323799999999999</v>
       </c>
       <c r="AD7" s="11">
-        <v>8.5992999999999995</v>
+        <v>8.6814999999999998</v>
       </c>
       <c r="AE7" s="12">
-        <v>0.97499999999999998</v>
+        <v>0.81579999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C8" s="10">
         <v>2043</v>
@@ -3823,16 +2785,16 @@
         <v>2043</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F8" s="10">
         <v>49227</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="I8" s="22">
         <v>44377</v>
@@ -3841,7 +2803,7 @@
         <v>44377</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L8" s="11">
         <v>0</v>
@@ -3906,10 +2868,10 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C9" s="10">
         <v>2043</v>
@@ -3918,16 +2880,16 @@
         <v>2511</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F9" s="10">
         <v>63441</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I9" s="22">
         <v>44733</v>
@@ -3936,7 +2898,7 @@
         <v>44733</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L9" s="11">
         <v>1</v>
@@ -3975,36 +2937,36 @@
         <v>-1</v>
       </c>
       <c r="X9" s="11">
-        <v>38.99</v>
+        <v>45.05</v>
       </c>
       <c r="Y9" s="11">
-        <v>9.02</v>
+        <v>10.87</v>
       </c>
       <c r="Z9" s="11">
-        <v>-29.97</v>
+        <v>-34.18</v>
       </c>
       <c r="AA9" s="12">
-        <v>-0.76870000000000005</v>
+        <v>-0.75870000000000004</v>
       </c>
       <c r="AB9" s="11">
         <v>0</v>
       </c>
       <c r="AC9" s="11">
-        <v>0</v>
+        <v>0.33589999999999998</v>
       </c>
       <c r="AD9" s="11">
-        <v>0</v>
+        <v>0.33589999999999998</v>
       </c>
       <c r="AE9" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C10" s="10">
         <v>2043</v>
@@ -4013,16 +2975,16 @@
         <v>2043</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F10" s="10">
         <v>65046</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I10" s="22">
         <v>44763</v>
@@ -4031,7 +2993,7 @@
         <v>44763</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L10" s="11">
         <v>1</v>
@@ -4073,13 +3035,13 @@
         <v>31.17</v>
       </c>
       <c r="Y10" s="11">
-        <v>34.75</v>
+        <v>36.5</v>
       </c>
       <c r="Z10" s="11">
-        <v>3.58</v>
+        <v>5.33</v>
       </c>
       <c r="AA10" s="12">
-        <v>0.1149</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="AB10" s="11">
         <v>0</v>
@@ -4096,10 +3058,10 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C11" s="10">
         <v>2043</v>
@@ -4108,16 +3070,16 @@
         <v>2511</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F11" s="10">
         <v>69684</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I11" s="22">
         <v>44771</v>
@@ -4126,7 +3088,7 @@
         <v>44771</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L11" s="11">
         <v>0</v>
@@ -4191,10 +3153,10 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C12" s="10">
         <v>2043</v>
@@ -4203,16 +3165,16 @@
         <v>2043</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F12" s="10">
         <v>80122</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I12" s="22">
         <v>43371</v>
@@ -4221,75 +3183,75 @@
         <v>43371</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L12" s="11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M12" s="11">
         <v>14</v>
       </c>
       <c r="N12" s="11">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="O12" s="12">
-        <v>7.6899999999999996E-2</v>
+        <v>-0.125</v>
       </c>
       <c r="P12" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="11">
         <v>12</v>
       </c>
       <c r="R12" s="11">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S12" s="12">
-        <v>0</v>
+        <v>-0.1429</v>
       </c>
       <c r="T12" s="11">
-        <v>619.97</v>
+        <v>697.7</v>
       </c>
       <c r="U12" s="11">
-        <v>701.65</v>
+        <v>616.71</v>
       </c>
       <c r="V12" s="11">
-        <v>81.680000000000007</v>
+        <v>-80.989999999999995</v>
       </c>
       <c r="W12" s="12">
-        <v>0.13170000000000001</v>
+        <v>-0.11609999999999999</v>
       </c>
       <c r="X12" s="11">
-        <v>876.03</v>
+        <v>995.37</v>
       </c>
       <c r="Y12" s="11">
-        <v>556.61</v>
+        <v>577.79999999999995</v>
       </c>
       <c r="Z12" s="11">
-        <v>-319.42</v>
+        <v>-417.57</v>
       </c>
       <c r="AA12" s="12">
-        <v>-0.36459999999999998</v>
+        <v>-0.41949999999999998</v>
       </c>
       <c r="AB12" s="11">
-        <v>11.831099999999999</v>
+        <v>6.4795999999999996</v>
       </c>
       <c r="AC12" s="11">
         <v>21.480399999999999</v>
       </c>
       <c r="AD12" s="11">
-        <v>9.6493000000000002</v>
+        <v>15.0008</v>
       </c>
       <c r="AE12" s="12">
-        <v>0.81559999999999999</v>
+        <v>2.3151000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C13" s="10">
         <v>2043</v>
@@ -4298,16 +3260,16 @@
         <v>2043</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F13" s="10">
         <v>80925</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I13" s="22">
         <v>43439</v>
@@ -4316,75 +3278,75 @@
         <v>43439</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L13" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="11">
         <v>-4</v>
       </c>
       <c r="O13" s="12">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="P13" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q13" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="11">
         <v>-4</v>
       </c>
       <c r="S13" s="12">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="T13" s="11">
-        <v>94.04</v>
+        <v>142.94999999999999</v>
       </c>
       <c r="U13" s="11">
-        <v>0</v>
+        <v>22.7</v>
       </c>
       <c r="V13" s="11">
-        <v>-94.04</v>
+        <v>-120.25</v>
       </c>
       <c r="W13" s="12">
-        <v>-1</v>
+        <v>-0.84119999999999995</v>
       </c>
       <c r="X13" s="11">
-        <v>116.4</v>
+        <v>160.61000000000001</v>
       </c>
       <c r="Y13" s="11">
-        <v>49.3</v>
+        <v>72</v>
       </c>
       <c r="Z13" s="11">
-        <v>-67.099999999999994</v>
+        <v>-88.61</v>
       </c>
       <c r="AA13" s="12">
-        <v>-0.57650000000000001</v>
+        <v>-0.55169999999999997</v>
       </c>
       <c r="AB13" s="11">
-        <v>6.7163000000000004</v>
+        <v>7.4029999999999996</v>
       </c>
       <c r="AC13" s="11">
-        <v>8.7853999999999992</v>
+        <v>9.0097000000000005</v>
       </c>
       <c r="AD13" s="11">
-        <v>2.0691000000000002</v>
+        <v>1.6067</v>
       </c>
       <c r="AE13" s="12">
-        <v>0.30809999999999998</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C14" s="10">
         <v>2043</v>
@@ -4393,16 +3355,16 @@
         <v>2511</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F14" s="10">
         <v>81044</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I14" s="22">
         <v>44872</v>
@@ -4411,7 +3373,7 @@
         <v>44872</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L14" s="11">
         <v>0</v>
@@ -4450,16 +3412,16 @@
         <v>0</v>
       </c>
       <c r="X14" s="11">
-        <v>30.5</v>
+        <v>31.44</v>
       </c>
       <c r="Y14" s="11">
         <v>2.4</v>
       </c>
       <c r="Z14" s="11">
-        <v>-28.1</v>
+        <v>-29.04</v>
       </c>
       <c r="AA14" s="12">
-        <v>-0.92130000000000001</v>
+        <v>-0.92369999999999997</v>
       </c>
       <c r="AB14" s="11">
         <v>0</v>
@@ -4476,10 +3438,10 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C15" s="10">
         <v>2043</v>
@@ -4488,16 +3450,16 @@
         <v>2043</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F15" s="10">
         <v>81618</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="I15" s="22">
         <v>43447</v>
@@ -4506,7 +3468,7 @@
         <v>43447</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L15" s="11">
         <v>0</v>
@@ -4548,22 +3510,22 @@
         <v>2.87</v>
       </c>
       <c r="Y15" s="11">
-        <v>14.95</v>
+        <v>30.1</v>
       </c>
       <c r="Z15" s="11">
-        <v>12.08</v>
+        <v>27.23</v>
       </c>
       <c r="AA15" s="12">
-        <v>4.2091000000000003</v>
+        <v>9.4878</v>
       </c>
       <c r="AB15" s="11">
         <v>0</v>
       </c>
       <c r="AC15" s="11">
-        <v>6.7150999999999996</v>
+        <v>9.2150999999999996</v>
       </c>
       <c r="AD15" s="11">
-        <v>6.7150999999999996</v>
+        <v>9.2150999999999996</v>
       </c>
       <c r="AE15" s="12">
         <v>1</v>
@@ -4571,10 +3533,10 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C16" s="10">
         <v>2043</v>
@@ -4583,16 +3545,16 @@
         <v>2043</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F16" s="10">
         <v>83407</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="I16" s="22">
         <v>43488</v>
@@ -4601,7 +3563,7 @@
         <v>43497</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L16" s="11">
         <v>0</v>
@@ -4666,10 +3628,10 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C17" s="10">
         <v>2043</v>
@@ -4678,16 +3640,16 @@
         <v>2043</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F17" s="10">
         <v>87538</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I17" s="22">
         <v>43731</v>
@@ -4696,75 +3658,75 @@
         <v>43731</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L17" s="11">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M17" s="11">
         <v>13</v>
       </c>
       <c r="N17" s="11">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="O17" s="12">
-        <v>0.85709999999999997</v>
+        <v>-7.1400000000000005E-2</v>
       </c>
       <c r="P17" s="11">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q17" s="11">
         <v>13</v>
       </c>
       <c r="R17" s="11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S17" s="12">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="T17" s="11">
-        <v>1032.33</v>
+        <v>1445.77</v>
       </c>
       <c r="U17" s="11">
         <v>864.93</v>
       </c>
       <c r="V17" s="11">
-        <v>-167.4</v>
+        <v>-580.84</v>
       </c>
       <c r="W17" s="12">
-        <v>-0.16220000000000001</v>
+        <v>-0.40179999999999999</v>
       </c>
       <c r="X17" s="11">
-        <v>820.67</v>
+        <v>1042.5899999999999</v>
       </c>
       <c r="Y17" s="11">
-        <v>1050.1300000000001</v>
+        <v>1099.08</v>
       </c>
       <c r="Z17" s="11">
-        <v>229.46</v>
+        <v>56.49</v>
       </c>
       <c r="AA17" s="12">
-        <v>0.27960000000000002</v>
+        <v>5.4199999999999998E-2</v>
       </c>
       <c r="AB17" s="11">
         <v>1.9245000000000001</v>
       </c>
       <c r="AC17" s="11">
-        <v>4.6641000000000004</v>
+        <v>10.214</v>
       </c>
       <c r="AD17" s="11">
-        <v>2.7395999999999998</v>
+        <v>8.2895000000000003</v>
       </c>
       <c r="AE17" s="12">
-        <v>1.4235</v>
+        <v>4.3074000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C18" s="10">
         <v>2043</v>
@@ -4773,16 +3735,16 @@
         <v>2043</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F18" s="10">
         <v>88234</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I18" s="22">
         <v>43794</v>
@@ -4791,7 +3753,7 @@
         <v>43794</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L18" s="11">
         <v>1</v>
@@ -4830,16 +3792,16 @@
         <v>1.1640999999999999</v>
       </c>
       <c r="X18" s="11">
-        <v>29.28</v>
+        <v>32.67</v>
       </c>
       <c r="Y18" s="11">
-        <v>20.39</v>
+        <v>28.12</v>
       </c>
       <c r="Z18" s="11">
-        <v>-8.89</v>
+        <v>-4.55</v>
       </c>
       <c r="AA18" s="12">
-        <v>-0.30359999999999998</v>
+        <v>-0.13930000000000001</v>
       </c>
       <c r="AB18" s="11">
         <v>2.0203000000000002</v>
@@ -4856,10 +3818,10 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C19" s="10">
         <v>2043</v>
@@ -4868,16 +3830,16 @@
         <v>2043</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F19" s="10">
         <v>90177</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I19" s="22">
         <v>43949</v>
@@ -4886,55 +3848,55 @@
         <v>43949</v>
       </c>
       <c r="K19" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L19" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="11">
         <v>0</v>
       </c>
       <c r="N19" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O19" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P19" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="11">
         <v>0</v>
       </c>
       <c r="R19" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S19" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T19" s="11">
-        <v>0</v>
+        <v>60.2</v>
       </c>
       <c r="U19" s="11">
         <v>0</v>
       </c>
       <c r="V19" s="11">
-        <v>0</v>
+        <v>-60.2</v>
       </c>
       <c r="W19" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X19" s="11">
-        <v>6.52</v>
+        <v>11.53</v>
       </c>
       <c r="Y19" s="11">
         <v>20.73</v>
       </c>
       <c r="Z19" s="11">
-        <v>14.21</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AA19" s="12">
-        <v>2.1793999999999998</v>
+        <v>0.79790000000000005</v>
       </c>
       <c r="AB19" s="11">
         <v>0</v>
@@ -4951,10 +3913,10 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C20" s="10">
         <v>2043</v>
@@ -4963,16 +3925,16 @@
         <v>2043</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F20" s="10">
         <v>90355</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I20" s="22">
         <v>43949</v>
@@ -4981,75 +3943,75 @@
         <v>43949</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L20" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M20" s="11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N20" s="11">
+        <v>0</v>
+      </c>
+      <c r="O20" s="12">
+        <v>0</v>
+      </c>
+      <c r="P20" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>10</v>
+      </c>
+      <c r="R20" s="11">
         <v>-2</v>
       </c>
-      <c r="O20" s="12">
-        <v>-0.18179999999999999</v>
-      </c>
-      <c r="P20" s="11">
-        <v>11</v>
-      </c>
-      <c r="Q20" s="11">
-        <v>8</v>
-      </c>
-      <c r="R20" s="11">
-        <v>-3</v>
-      </c>
       <c r="S20" s="12">
-        <v>-0.2727</v>
+        <v>-0.16669999999999999</v>
       </c>
       <c r="T20" s="11">
-        <v>429.71</v>
+        <v>465.4</v>
       </c>
       <c r="U20" s="11">
-        <v>407.52</v>
+        <v>577.07000000000005</v>
       </c>
       <c r="V20" s="11">
-        <v>-22.19</v>
+        <v>111.67</v>
       </c>
       <c r="W20" s="12">
-        <v>-5.16E-2</v>
+        <v>0.2399</v>
       </c>
       <c r="X20" s="11">
-        <v>513.05999999999995</v>
+        <v>582.91</v>
       </c>
       <c r="Y20" s="11">
-        <v>393.63</v>
+        <v>458.62</v>
       </c>
       <c r="Z20" s="11">
-        <v>-119.43</v>
+        <v>-124.29</v>
       </c>
       <c r="AA20" s="12">
-        <v>-0.23280000000000001</v>
+        <v>-0.2132</v>
       </c>
       <c r="AB20" s="11">
         <v>1.8688</v>
       </c>
       <c r="AC20" s="11">
-        <v>1.544</v>
+        <v>4.6801000000000004</v>
       </c>
       <c r="AD20" s="11">
-        <v>-0.32479999999999998</v>
+        <v>2.8113000000000001</v>
       </c>
       <c r="AE20" s="12">
-        <v>-0.17380000000000001</v>
+        <v>1.5043</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C21" s="10">
         <v>2043</v>
@@ -5058,16 +4020,16 @@
         <v>2043</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F21" s="10">
         <v>94156</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I21" s="22">
         <v>44159</v>
@@ -5076,75 +4038,75 @@
         <v>44159</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="11">
         <v>3</v>
       </c>
       <c r="N21" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O21" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="11">
         <v>3</v>
       </c>
       <c r="R21" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S21" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T21" s="11">
-        <v>0</v>
+        <v>28.68</v>
       </c>
       <c r="U21" s="11">
         <v>139.21</v>
       </c>
       <c r="V21" s="11">
-        <v>139.21</v>
+        <v>110.53</v>
       </c>
       <c r="W21" s="12">
-        <v>1</v>
+        <v>3.8538999999999999</v>
       </c>
       <c r="X21" s="11">
-        <v>15.44</v>
+        <v>22.28</v>
       </c>
       <c r="Y21" s="11">
         <v>73.78</v>
       </c>
       <c r="Z21" s="11">
-        <v>58.34</v>
+        <v>51.5</v>
       </c>
       <c r="AA21" s="12">
-        <v>3.7785000000000002</v>
+        <v>2.3115000000000001</v>
       </c>
       <c r="AB21" s="11">
-        <v>0.42049999999999998</v>
+        <v>0.52649999999999997</v>
       </c>
       <c r="AC21" s="11">
-        <v>5.0641999999999996</v>
+        <v>5.4142000000000001</v>
       </c>
       <c r="AD21" s="11">
-        <v>4.6436999999999999</v>
+        <v>4.8876999999999997</v>
       </c>
       <c r="AE21" s="12">
-        <v>11.0433</v>
+        <v>9.2834000000000003</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C22" s="10">
         <v>2043</v>
@@ -5153,16 +4115,16 @@
         <v>2043</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F22" s="10">
         <v>94205</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="I22" s="22">
         <v>44116</v>
@@ -5171,7 +4133,7 @@
         <v>44116</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L22" s="11">
         <v>0</v>
@@ -5236,10 +4198,10 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C23" s="10">
         <v>2043</v>
@@ -5248,16 +4210,16 @@
         <v>2043</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F23" s="10">
         <v>95148</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="I23" s="22">
         <v>44916</v>
@@ -5266,75 +4228,75 @@
         <v>44916</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L23" s="11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M23" s="11">
         <v>1</v>
       </c>
       <c r="N23" s="11">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="O23" s="12">
-        <v>-0.66669999999999996</v>
+        <v>-0.83330000000000004</v>
       </c>
       <c r="P23" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="11">
         <v>1</v>
       </c>
       <c r="R23" s="11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="S23" s="12">
-        <v>-0.66669999999999996</v>
+        <v>-0.75</v>
       </c>
       <c r="T23" s="11">
-        <v>1620.14</v>
+        <v>1712.85</v>
       </c>
       <c r="U23" s="11">
         <v>46.1</v>
       </c>
       <c r="V23" s="11">
-        <v>-1574.04</v>
+        <v>-1666.75</v>
       </c>
       <c r="W23" s="12">
-        <v>-0.97150000000000003</v>
+        <v>-0.97309999999999997</v>
       </c>
       <c r="X23" s="11">
-        <v>1468.63</v>
+        <v>1507.86</v>
       </c>
       <c r="Y23" s="11">
         <v>24.14</v>
       </c>
       <c r="Z23" s="11">
-        <v>-1444.49</v>
+        <v>-1483.72</v>
       </c>
       <c r="AA23" s="12">
-        <v>-0.98360000000000003</v>
+        <v>-0.98399999999999999</v>
       </c>
       <c r="AB23" s="11">
-        <v>0</v>
+        <v>0.50860000000000005</v>
       </c>
       <c r="AC23" s="11">
         <v>0</v>
       </c>
       <c r="AD23" s="11">
-        <v>0</v>
+        <v>-0.50860000000000005</v>
       </c>
       <c r="AE23" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C24" s="10">
         <v>2043</v>
@@ -5343,16 +4305,16 @@
         <v>2043</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F24" s="10">
         <v>98797</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I24" s="22">
         <v>44342</v>
@@ -5361,7 +4323,7 @@
         <v>44342</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L24" s="11">
         <v>1</v>
@@ -5400,13 +4362,13 @@
         <v>-1</v>
       </c>
       <c r="X24" s="11">
-        <v>109.19</v>
+        <v>111.18</v>
       </c>
       <c r="Y24" s="11">
         <v>0</v>
       </c>
       <c r="Z24" s="11">
-        <v>-109.19</v>
+        <v>-111.18</v>
       </c>
       <c r="AA24" s="12">
         <v>-1</v>
@@ -5426,10 +4388,10 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C25" s="10">
         <v>2043</v>
@@ -5438,16 +4400,16 @@
         <v>2043</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10">
         <v>100323</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="I25" s="22">
         <v>45042</v>
@@ -5456,7 +4418,7 @@
         <v>45042</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="L25" s="11">
         <v>0</v>
@@ -5521,10 +4483,10 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C26" s="10">
         <v>2043</v>
@@ -5533,16 +4495,16 @@
         <v>2043</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F26" s="10">
         <v>100677</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I26" s="22">
         <v>44999</v>
@@ -5551,75 +4513,75 @@
         <v>44999</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="L26" s="11">
         <v>5</v>
       </c>
       <c r="M26" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" s="11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="O26" s="12">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="P26" s="11">
         <v>4</v>
       </c>
       <c r="Q26" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" s="11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="S26" s="12">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="T26" s="11">
         <v>78.38</v>
       </c>
       <c r="U26" s="11">
-        <v>-0.28999999999999998</v>
+        <v>65.34</v>
       </c>
       <c r="V26" s="11">
-        <v>-78.67</v>
+        <v>-13.04</v>
       </c>
       <c r="W26" s="12">
-        <v>-1.0037</v>
+        <v>-0.16639999999999999</v>
       </c>
       <c r="X26" s="11">
-        <v>85.04</v>
+        <v>90.18</v>
       </c>
       <c r="Y26" s="11">
-        <v>68.03</v>
+        <v>98.67</v>
       </c>
       <c r="Z26" s="11">
-        <v>-17.010000000000002</v>
+        <v>8.49</v>
       </c>
       <c r="AA26" s="12">
-        <v>-0.2</v>
+        <v>9.4100000000000003E-2</v>
       </c>
       <c r="AB26" s="11">
-        <v>0.68210000000000004</v>
+        <v>0.95789999999999997</v>
       </c>
       <c r="AC26" s="11">
         <v>1.4392</v>
       </c>
       <c r="AD26" s="11">
-        <v>0.7571</v>
+        <v>0.48130000000000001</v>
       </c>
       <c r="AE26" s="12">
-        <v>1.1100000000000001</v>
+        <v>0.50249999999999995</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C27" s="10">
         <v>2043</v>
@@ -5628,16 +4590,16 @@
         <v>2043</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F27" s="10">
         <v>101640</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I27" s="22">
         <v>45104</v>
@@ -5646,75 +4608,75 @@
         <v>45104</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="L27" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M27" s="11">
         <v>0</v>
       </c>
       <c r="N27" s="11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O27" s="12">
         <v>-1</v>
       </c>
       <c r="P27" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="11">
         <v>0</v>
       </c>
       <c r="R27" s="11">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S27" s="12">
         <v>-1</v>
       </c>
       <c r="T27" s="11">
-        <v>9.4</v>
+        <v>123.9</v>
       </c>
       <c r="U27" s="11">
         <v>0</v>
       </c>
       <c r="V27" s="11">
-        <v>-9.4</v>
+        <v>-123.9</v>
       </c>
       <c r="W27" s="12">
         <v>-1</v>
       </c>
       <c r="X27" s="11">
-        <v>51.12</v>
+        <v>162.13</v>
       </c>
       <c r="Y27" s="11">
-        <v>32.700000000000003</v>
+        <v>37.450000000000003</v>
       </c>
       <c r="Z27" s="11">
-        <v>-18.420000000000002</v>
+        <v>-124.68</v>
       </c>
       <c r="AA27" s="12">
-        <v>-0.36030000000000001</v>
+        <v>-0.76900000000000002</v>
       </c>
       <c r="AB27" s="11">
-        <v>0</v>
+        <v>2.0920000000000001</v>
       </c>
       <c r="AC27" s="11">
         <v>17.043700000000001</v>
       </c>
       <c r="AD27" s="11">
-        <v>17.043700000000001</v>
+        <v>14.951700000000001</v>
       </c>
       <c r="AE27" s="12">
-        <v>1</v>
+        <v>7.1471</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C28" s="10">
         <v>2043</v>
@@ -5723,16 +4685,16 @@
         <v>2043</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F28" s="10">
         <v>102825</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I28" s="22">
         <v>45117</v>
@@ -5741,7 +4703,7 @@
         <v>45139</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="L28" s="11">
         <v>0</v>
@@ -5759,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="Q28" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="11">
         <v>0</v>
@@ -5783,13 +4745,13 @@
         <v>3.09</v>
       </c>
       <c r="Y28" s="11">
-        <v>21.33</v>
+        <v>44.06</v>
       </c>
       <c r="Z28" s="11">
-        <v>18.239999999999998</v>
+        <v>40.97</v>
       </c>
       <c r="AA28" s="12">
-        <v>5.9028999999999998</v>
+        <v>13.258900000000001</v>
       </c>
       <c r="AB28" s="11">
         <v>0</v>
@@ -5806,10 +4768,10 @@
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C29" s="10">
         <v>2043</v>
@@ -5818,16 +4780,16 @@
         <v>2043</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F29" s="10">
         <v>104343</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I29" s="22">
         <v>45201</v>
@@ -5836,7 +4798,7 @@
         <v>45201</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="L29" s="11">
         <v>5</v>
@@ -5875,36 +4837,36 @@
         <v>-0.78669999999999995</v>
       </c>
       <c r="X29" s="11">
-        <v>262.24</v>
+        <v>288.69</v>
       </c>
       <c r="Y29" s="11">
-        <v>48.72</v>
+        <v>56</v>
       </c>
       <c r="Z29" s="11">
-        <v>-213.52</v>
+        <v>-232.69</v>
       </c>
       <c r="AA29" s="12">
-        <v>-0.81420000000000003</v>
+        <v>-0.80600000000000005</v>
       </c>
       <c r="AB29" s="11">
-        <v>1.8343</v>
+        <v>2.3889999999999998</v>
       </c>
       <c r="AC29" s="11">
-        <v>6.0392999999999999</v>
+        <v>7.4409000000000001</v>
       </c>
       <c r="AD29" s="11">
-        <v>4.2050000000000001</v>
+        <v>5.0518999999999998</v>
       </c>
       <c r="AE29" s="12">
-        <v>2.2924000000000002</v>
+        <v>2.1147</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C30" s="10">
         <v>2043</v>
@@ -5913,16 +4875,16 @@
         <v>2043</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F30" s="10">
         <v>104718</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I30" s="22">
         <v>45264</v>
@@ -5931,7 +4893,7 @@
         <v>45264</v>
       </c>
       <c r="K30" s="23" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="L30" s="11">
         <v>12</v>
@@ -5970,36 +4932,36 @@
         <v>-0.61339999999999995</v>
       </c>
       <c r="X30" s="11">
-        <v>316.83999999999997</v>
+        <v>358.34</v>
       </c>
       <c r="Y30" s="11">
-        <v>119.71</v>
+        <v>126.89</v>
       </c>
       <c r="Z30" s="11">
-        <v>-197.13</v>
+        <v>-231.45</v>
       </c>
       <c r="AA30" s="12">
-        <v>-0.62219999999999998</v>
+        <v>-0.64590000000000003</v>
       </c>
       <c r="AB30" s="11">
         <v>0.1235</v>
       </c>
       <c r="AC30" s="11">
-        <v>3.3654000000000002</v>
+        <v>3.5846</v>
       </c>
       <c r="AD30" s="11">
-        <v>3.2418999999999998</v>
+        <v>3.4611000000000001</v>
       </c>
       <c r="AE30" s="12">
-        <v>26.2502</v>
+        <v>28.025099999999998</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C31" s="10">
         <v>2043</v>
@@ -6008,16 +4970,16 @@
         <v>2043</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F31" s="10">
         <v>104750</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I31" s="22">
         <v>45236</v>
@@ -6026,75 +4988,75 @@
         <v>45236</v>
       </c>
       <c r="K31" s="23" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="L31" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M31" s="11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N31" s="11">
         <v>-2</v>
       </c>
       <c r="O31" s="12">
-        <v>-0.22220000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="P31" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q31" s="11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R31" s="11">
         <v>-2</v>
       </c>
       <c r="S31" s="12">
-        <v>-0.22220000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="T31" s="11">
-        <v>260.14999999999998</v>
+        <v>287.43</v>
       </c>
       <c r="U31" s="11">
-        <v>160.13</v>
+        <v>182.59</v>
       </c>
       <c r="V31" s="11">
-        <v>-100.02</v>
+        <v>-104.84</v>
       </c>
       <c r="W31" s="12">
-        <v>-0.38450000000000001</v>
+        <v>-0.36470000000000002</v>
       </c>
       <c r="X31" s="11">
-        <v>234.63</v>
+        <v>277.25</v>
       </c>
       <c r="Y31" s="11">
-        <v>159.51</v>
+        <v>177.66</v>
       </c>
       <c r="Z31" s="11">
-        <v>-75.12</v>
+        <v>-99.59</v>
       </c>
       <c r="AA31" s="12">
-        <v>-0.32019999999999998</v>
+        <v>-0.35920000000000002</v>
       </c>
       <c r="AB31" s="11">
-        <v>1.0677000000000001</v>
+        <v>1.5203</v>
       </c>
       <c r="AC31" s="11">
-        <v>2.4571000000000001</v>
+        <v>2.8401999999999998</v>
       </c>
       <c r="AD31" s="11">
-        <v>1.3894</v>
+        <v>1.3199000000000001</v>
       </c>
       <c r="AE31" s="12">
-        <v>1.3012999999999999</v>
+        <v>0.86819999999999997</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C32" s="10">
         <v>2043</v>
@@ -6103,16 +5065,16 @@
         <v>2043</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F32" s="10">
         <v>105696</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I32" s="22">
         <v>45279</v>
@@ -6121,75 +5083,75 @@
         <v>45279</v>
       </c>
       <c r="K32" s="23" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="L32" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M32" s="11">
         <v>6</v>
       </c>
       <c r="N32" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O32" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="11">
         <v>6</v>
       </c>
       <c r="R32" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S32" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T32" s="11">
-        <v>49.3</v>
+        <v>69.37</v>
       </c>
       <c r="U32" s="11">
         <v>174.68</v>
       </c>
       <c r="V32" s="11">
-        <v>125.38</v>
+        <v>105.31</v>
       </c>
       <c r="W32" s="12">
-        <v>2.5432000000000001</v>
+        <v>1.5181</v>
       </c>
       <c r="X32" s="11">
-        <v>89.3</v>
+        <v>99.79</v>
       </c>
       <c r="Y32" s="11">
-        <v>130.19</v>
+        <v>131.94</v>
       </c>
       <c r="Z32" s="11">
-        <v>40.89</v>
+        <v>32.15</v>
       </c>
       <c r="AA32" s="12">
-        <v>0.45789999999999997</v>
+        <v>0.32219999999999999</v>
       </c>
       <c r="AB32" s="11">
-        <v>0</v>
+        <v>0.84750000000000003</v>
       </c>
       <c r="AC32" s="11">
         <v>1.2130000000000001</v>
       </c>
       <c r="AD32" s="11">
-        <v>1.2130000000000001</v>
+        <v>0.36549999999999999</v>
       </c>
       <c r="AE32" s="12">
-        <v>1</v>
+        <v>0.43130000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C33" s="10">
         <v>2043</v>
@@ -6198,16 +5160,16 @@
         <v>2043</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F33" s="10">
         <v>106018</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="I33" s="22">
         <v>45344</v>
@@ -6216,7 +5178,7 @@
         <v>45344</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L33" s="11">
         <v>2</v>
@@ -6258,13 +5220,13 @@
         <v>73</v>
       </c>
       <c r="Y33" s="11">
-        <v>49.71</v>
+        <v>52.82</v>
       </c>
       <c r="Z33" s="11">
-        <v>-23.29</v>
+        <v>-20.18</v>
       </c>
       <c r="AA33" s="12">
-        <v>-0.31900000000000001</v>
+        <v>-0.27639999999999998</v>
       </c>
       <c r="AB33" s="11">
         <v>3.1848999999999998</v>
@@ -6281,10 +5243,10 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C34" s="10">
         <v>2043</v>
@@ -6293,16 +5255,16 @@
         <v>2043</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F34" s="10">
         <v>107488</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I34" s="22">
         <v>45440</v>
@@ -6311,55 +5273,55 @@
         <v>45440</v>
       </c>
       <c r="K34" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L34" s="11">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M34" s="11">
         <v>1</v>
       </c>
       <c r="N34" s="11">
+        <v>-18</v>
+      </c>
+      <c r="O34" s="12">
+        <v>-0.94740000000000002</v>
+      </c>
+      <c r="P34" s="11">
+        <v>16</v>
+      </c>
+      <c r="Q34" s="11">
+        <v>0</v>
+      </c>
+      <c r="R34" s="11">
         <v>-16</v>
-      </c>
-      <c r="O34" s="12">
-        <v>-0.94120000000000004</v>
-      </c>
-      <c r="P34" s="11">
-        <v>14</v>
-      </c>
-      <c r="Q34" s="11">
-        <v>0</v>
-      </c>
-      <c r="R34" s="11">
-        <v>-14</v>
       </c>
       <c r="S34" s="12">
         <v>-1</v>
       </c>
       <c r="T34" s="11">
-        <v>689.54</v>
+        <v>746.04</v>
       </c>
       <c r="U34" s="11">
         <v>-1319.02</v>
       </c>
       <c r="V34" s="11">
-        <v>-2008.56</v>
+        <v>-2065.06</v>
       </c>
       <c r="W34" s="12">
-        <v>-2.9129</v>
+        <v>-2.7679999999999998</v>
       </c>
       <c r="X34" s="11">
-        <v>349.84</v>
+        <v>389.34</v>
       </c>
       <c r="Y34" s="11">
-        <v>159.78</v>
+        <v>169.23</v>
       </c>
       <c r="Z34" s="11">
-        <v>-190.06</v>
+        <v>-220.11</v>
       </c>
       <c r="AA34" s="12">
-        <v>-0.54330000000000001</v>
+        <v>-0.56530000000000002</v>
       </c>
       <c r="AB34" s="11">
         <v>0</v>
@@ -6376,10 +5338,10 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C35" s="10">
         <v>2043</v>
@@ -6388,16 +5350,16 @@
         <v>2043</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F35" s="10">
         <v>107660</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="I35" s="22">
         <v>45471</v>
@@ -6406,7 +5368,7 @@
         <v>45471</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L35" s="11">
         <v>0</v>
@@ -6471,10 +5433,10 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C36" s="10">
         <v>2043</v>
@@ -6483,16 +5445,16 @@
         <v>2043</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F36" s="10">
         <v>108404</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I36" s="22">
         <v>45467</v>
@@ -6501,75 +5463,75 @@
         <v>45467</v>
       </c>
       <c r="K36" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L36" s="11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M36" s="11">
         <v>1</v>
       </c>
       <c r="N36" s="11">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="O36" s="12">
-        <v>-0.88890000000000002</v>
+        <v>-0.91669999999999996</v>
       </c>
       <c r="P36" s="11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q36" s="11">
         <v>1</v>
       </c>
       <c r="R36" s="11">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="S36" s="12">
-        <v>-0.875</v>
+        <v>-0.90910000000000002</v>
       </c>
       <c r="T36" s="11">
-        <v>274.5</v>
+        <v>406.68</v>
       </c>
       <c r="U36" s="11">
         <v>36.93</v>
       </c>
       <c r="V36" s="11">
-        <v>-237.57</v>
+        <v>-369.75</v>
       </c>
       <c r="W36" s="12">
-        <v>-0.86550000000000005</v>
+        <v>-0.90920000000000001</v>
       </c>
       <c r="X36" s="11">
-        <v>377.79</v>
+        <v>462.03</v>
       </c>
       <c r="Y36" s="11">
-        <v>74.88</v>
+        <v>78.86</v>
       </c>
       <c r="Z36" s="11">
-        <v>-302.91000000000003</v>
+        <v>-383.17</v>
       </c>
       <c r="AA36" s="12">
-        <v>-0.80179999999999996</v>
+        <v>-0.82930000000000004</v>
       </c>
       <c r="AB36" s="11">
-        <v>5.3985000000000003</v>
+        <v>6.7584999999999997</v>
       </c>
       <c r="AC36" s="11">
         <v>10.6434</v>
       </c>
       <c r="AD36" s="11">
-        <v>5.2449000000000003</v>
+        <v>3.8849</v>
       </c>
       <c r="AE36" s="12">
-        <v>0.97150000000000003</v>
+        <v>0.57479999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C37" s="10">
         <v>2043</v>
@@ -6578,16 +5540,16 @@
         <v>2043</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F37" s="10">
         <v>108405</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I37" s="22">
         <v>45471</v>
@@ -6596,7 +5558,7 @@
         <v>45471</v>
       </c>
       <c r="K37" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L37" s="11">
         <v>9</v>
@@ -6635,16 +5597,16 @@
         <v>-0.91720000000000002</v>
       </c>
       <c r="X37" s="11">
-        <v>185.17</v>
+        <v>192.24</v>
       </c>
       <c r="Y37" s="11">
-        <v>153.13999999999999</v>
+        <v>155.65</v>
       </c>
       <c r="Z37" s="11">
-        <v>-32.03</v>
+        <v>-36.590000000000003</v>
       </c>
       <c r="AA37" s="12">
-        <v>-0.17299999999999999</v>
+        <v>-0.1903</v>
       </c>
       <c r="AB37" s="11">
         <v>0</v>
@@ -6661,10 +5623,10 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C38" s="10">
         <v>2043</v>
@@ -6673,16 +5635,16 @@
         <v>2043</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F38" s="10">
         <v>108658</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="I38" s="22">
         <v>45497</v>
@@ -6691,7 +5653,7 @@
         <v>45497</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L38" s="11">
         <v>6</v>
@@ -6706,13 +5668,13 @@
         <v>-1</v>
       </c>
       <c r="P38" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q38" s="11">
         <v>0</v>
       </c>
       <c r="R38" s="11">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S38" s="12">
         <v>-1</v>
@@ -6730,25 +5692,25 @@
         <v>-1</v>
       </c>
       <c r="X38" s="11">
-        <v>135.86000000000001</v>
+        <v>172.99</v>
       </c>
       <c r="Y38" s="11">
         <v>10.45</v>
       </c>
       <c r="Z38" s="11">
-        <v>-125.41</v>
+        <v>-162.54</v>
       </c>
       <c r="AA38" s="12">
-        <v>-0.92310000000000003</v>
+        <v>-0.93959999999999999</v>
       </c>
       <c r="AB38" s="11">
-        <v>3.3999999999999998E-3</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="AC38" s="11">
         <v>0</v>
       </c>
       <c r="AD38" s="11">
-        <v>-3.3999999999999998E-3</v>
+        <v>-7.1999999999999998E-3</v>
       </c>
       <c r="AE38" s="12">
         <v>-1</v>
@@ -6756,10 +5718,10 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C39" s="10">
         <v>2043</v>
@@ -6768,16 +5730,16 @@
         <v>2043</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F39" s="10">
         <v>108920</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="I39" s="22">
         <v>45526</v>
@@ -6786,7 +5748,7 @@
         <v>45526</v>
       </c>
       <c r="K39" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L39" s="11">
         <v>3</v>
@@ -6825,36 +5787,36 @@
         <v>-1</v>
       </c>
       <c r="X39" s="11">
-        <v>48.47</v>
+        <v>54.52</v>
       </c>
       <c r="Y39" s="11">
         <v>0</v>
       </c>
       <c r="Z39" s="11">
-        <v>-48.47</v>
+        <v>-54.52</v>
       </c>
       <c r="AA39" s="12">
         <v>-1</v>
       </c>
       <c r="AB39" s="11">
-        <v>0.30480000000000002</v>
+        <v>0.51219999999999999</v>
       </c>
       <c r="AC39" s="11">
         <v>0.38040000000000002</v>
       </c>
       <c r="AD39" s="11">
-        <v>7.5600000000000001E-2</v>
+        <v>-0.1318</v>
       </c>
       <c r="AE39" s="12">
-        <v>0.248</v>
+        <v>-0.25729999999999997</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C40" s="10">
         <v>2043</v>
@@ -6863,16 +5825,16 @@
         <v>2043</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F40" s="10">
         <v>109007</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I40" s="22">
         <v>45525</v>
@@ -6881,7 +5843,7 @@
         <v>45525</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L40" s="11">
         <v>1</v>
@@ -6920,16 +5882,16 @@
         <v>-1</v>
       </c>
       <c r="X40" s="11">
-        <v>43.61</v>
+        <v>54.83</v>
       </c>
       <c r="Y40" s="11">
         <v>30.98</v>
       </c>
       <c r="Z40" s="11">
-        <v>-12.63</v>
+        <v>-23.85</v>
       </c>
       <c r="AA40" s="12">
-        <v>-0.28960000000000002</v>
+        <v>-0.435</v>
       </c>
       <c r="AB40" s="11">
         <v>0</v>
@@ -6946,10 +5908,10 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C41" s="10">
         <v>2043</v>
@@ -6958,16 +5920,16 @@
         <v>2043</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F41" s="10">
         <v>109141</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="I41" s="22">
         <v>45453</v>
@@ -6976,7 +5938,7 @@
         <v>45474</v>
       </c>
       <c r="K41" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L41" s="11">
         <v>0</v>
@@ -7015,13 +5977,13 @@
         <v>0</v>
       </c>
       <c r="X41" s="11">
-        <v>5.95</v>
+        <v>7.45</v>
       </c>
       <c r="Y41" s="11">
         <v>0</v>
       </c>
       <c r="Z41" s="11">
-        <v>-5.95</v>
+        <v>-7.45</v>
       </c>
       <c r="AA41" s="12">
         <v>-1</v>
@@ -7041,10 +6003,10 @@
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C42" s="10">
         <v>2043</v>
@@ -7053,16 +6015,16 @@
         <v>2856</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F42" s="10">
         <v>109819</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I42" s="22">
         <v>45562</v>
@@ -7071,52 +6033,52 @@
         <v>45562</v>
       </c>
       <c r="K42" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L42" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" s="11">
         <v>0</v>
       </c>
       <c r="N42" s="11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O42" s="12">
         <v>-1</v>
       </c>
       <c r="P42" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" s="11">
         <v>0</v>
       </c>
       <c r="R42" s="11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="S42" s="12">
         <v>-1</v>
       </c>
       <c r="T42" s="11">
-        <v>97.1</v>
+        <v>127.42</v>
       </c>
       <c r="U42" s="11">
         <v>0</v>
       </c>
       <c r="V42" s="11">
-        <v>-97.1</v>
+        <v>-127.42</v>
       </c>
       <c r="W42" s="12">
         <v>-1</v>
       </c>
       <c r="X42" s="11">
-        <v>152.91</v>
+        <v>193.76</v>
       </c>
       <c r="Y42" s="11">
         <v>0</v>
       </c>
       <c r="Z42" s="11">
-        <v>-152.91</v>
+        <v>-193.76</v>
       </c>
       <c r="AA42" s="12">
         <v>-1</v>
@@ -7136,10 +6098,10 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C43" s="10">
         <v>2043</v>
@@ -7148,16 +6110,16 @@
         <v>2043</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F43" s="10">
         <v>109998</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I43" s="22">
         <v>45596</v>
@@ -7166,55 +6128,55 @@
         <v>45596</v>
       </c>
       <c r="K43" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L43" s="11">
+        <v>5</v>
+      </c>
+      <c r="M43" s="11">
+        <v>1</v>
+      </c>
+      <c r="N43" s="11">
+        <v>-4</v>
+      </c>
+      <c r="O43" s="12">
+        <v>-0.8</v>
+      </c>
+      <c r="P43" s="11">
         <v>4</v>
       </c>
-      <c r="M43" s="11">
-        <v>1</v>
-      </c>
-      <c r="N43" s="11">
-        <v>-3</v>
-      </c>
-      <c r="O43" s="12">
-        <v>-0.75</v>
-      </c>
-      <c r="P43" s="11">
-        <v>3</v>
-      </c>
       <c r="Q43" s="11">
         <v>0</v>
       </c>
       <c r="R43" s="11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="S43" s="12">
         <v>-1</v>
       </c>
       <c r="T43" s="11">
-        <v>17.11</v>
+        <v>50.3</v>
       </c>
       <c r="U43" s="11">
         <v>-0.38</v>
       </c>
       <c r="V43" s="11">
-        <v>-17.489999999999998</v>
+        <v>-50.68</v>
       </c>
       <c r="W43" s="12">
-        <v>-1.0222</v>
+        <v>-1.0076000000000001</v>
       </c>
       <c r="X43" s="11">
-        <v>105.69</v>
+        <v>116.89</v>
       </c>
       <c r="Y43" s="11">
-        <v>14.4</v>
+        <v>17.38</v>
       </c>
       <c r="Z43" s="11">
-        <v>-91.29</v>
+        <v>-99.51</v>
       </c>
       <c r="AA43" s="12">
-        <v>-0.86380000000000001</v>
+        <v>-0.85129999999999995</v>
       </c>
       <c r="AB43" s="11">
         <v>0</v>
@@ -7231,10 +6193,10 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C44" s="10">
         <v>2043</v>
@@ -7243,16 +6205,16 @@
         <v>2043</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F44" s="10">
         <v>110105</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I44" s="22">
         <v>45560</v>
@@ -7261,55 +6223,55 @@
         <v>45560</v>
       </c>
       <c r="K44" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L44" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M44" s="11">
         <v>0</v>
       </c>
       <c r="N44" s="11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O44" s="12">
         <v>-1</v>
       </c>
       <c r="P44" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q44" s="11">
         <v>0</v>
       </c>
       <c r="R44" s="11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="S44" s="12">
         <v>-1</v>
       </c>
       <c r="T44" s="11">
-        <v>50.61</v>
+        <v>68.58</v>
       </c>
       <c r="U44" s="11">
         <v>0</v>
       </c>
       <c r="V44" s="11">
-        <v>-50.61</v>
+        <v>-68.58</v>
       </c>
       <c r="W44" s="12">
         <v>-1</v>
       </c>
       <c r="X44" s="11">
-        <v>50.17</v>
+        <v>57.5</v>
       </c>
       <c r="Y44" s="11">
         <v>35.58</v>
       </c>
       <c r="Z44" s="11">
-        <v>-14.59</v>
+        <v>-21.92</v>
       </c>
       <c r="AA44" s="12">
-        <v>-0.2908</v>
+        <v>-0.38119999999999998</v>
       </c>
       <c r="AB44" s="11">
         <v>0</v>
@@ -7326,10 +6288,10 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C45" s="10">
         <v>2043</v>
@@ -7338,16 +6300,16 @@
         <v>2856</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F45" s="10">
         <v>110453</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I45" s="22">
         <v>45600</v>
@@ -7356,75 +6318,75 @@
         <v>45600</v>
       </c>
       <c r="K45" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L45" s="11">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="M45" s="11">
         <v>11</v>
       </c>
       <c r="N45" s="11">
-        <v>-3</v>
+        <v>-5.5</v>
       </c>
       <c r="O45" s="12">
-        <v>-0.21429999999999999</v>
+        <v>-0.33329999999999999</v>
       </c>
       <c r="P45" s="11">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Q45" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R45" s="11">
-        <v>-5</v>
+        <v>-5.5</v>
       </c>
       <c r="S45" s="12">
-        <v>-0.35709999999999997</v>
+        <v>-0.3548</v>
       </c>
       <c r="T45" s="11">
-        <v>446.24</v>
+        <v>543.65</v>
       </c>
       <c r="U45" s="11">
         <v>335.91</v>
       </c>
       <c r="V45" s="11">
-        <v>-110.33</v>
+        <v>-207.74</v>
       </c>
       <c r="W45" s="12">
-        <v>-0.2472</v>
+        <v>-0.3821</v>
       </c>
       <c r="X45" s="11">
-        <v>198.56</v>
+        <v>290.86</v>
       </c>
       <c r="Y45" s="11">
-        <v>243.51</v>
+        <v>288.83999999999997</v>
       </c>
       <c r="Z45" s="11">
-        <v>44.95</v>
+        <v>-2.02</v>
       </c>
       <c r="AA45" s="12">
-        <v>0.22639999999999999</v>
+        <v>-6.8999999999999999E-3</v>
       </c>
       <c r="AB45" s="11">
-        <v>0.2029</v>
+        <v>1.5004999999999999</v>
       </c>
       <c r="AC45" s="11">
-        <v>1.0906</v>
+        <v>1.2110000000000001</v>
       </c>
       <c r="AD45" s="11">
-        <v>0.88770000000000004</v>
+        <v>-0.28949999999999998</v>
       </c>
       <c r="AE45" s="12">
-        <v>4.3750999999999998</v>
+        <v>-0.19289999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C46" s="10">
         <v>2043</v>
@@ -7433,16 +6395,16 @@
         <v>2043</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F46" s="10">
         <v>110575</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I46" s="22">
         <v>45583</v>
@@ -7451,7 +6413,7 @@
         <v>45583</v>
       </c>
       <c r="K46" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L46" s="11">
         <v>2</v>
@@ -7466,13 +6428,13 @@
         <v>-1</v>
       </c>
       <c r="P46" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" s="11">
         <v>0</v>
       </c>
       <c r="R46" s="11">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S46" s="12">
         <v>-1</v>
@@ -7490,16 +6452,16 @@
         <v>-1</v>
       </c>
       <c r="X46" s="11">
-        <v>276.66000000000003</v>
+        <v>358.71</v>
       </c>
       <c r="Y46" s="11">
         <v>71.81</v>
       </c>
       <c r="Z46" s="11">
-        <v>-204.85</v>
+        <v>-286.89999999999998</v>
       </c>
       <c r="AA46" s="12">
-        <v>-0.74039999999999995</v>
+        <v>-0.79979999999999996</v>
       </c>
       <c r="AB46" s="11">
         <v>0</v>
@@ -7516,10 +6478,10 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C47" s="10">
         <v>2043</v>
@@ -7528,16 +6490,16 @@
         <v>2043</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F47" s="10">
         <v>110740</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="I47" s="22">
         <v>45616</v>
@@ -7546,7 +6508,7 @@
         <v>45616</v>
       </c>
       <c r="K47" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L47" s="11">
         <v>0</v>
@@ -7585,13 +6547,13 @@
         <v>0</v>
       </c>
       <c r="X47" s="11">
-        <v>12.87</v>
+        <v>16.010000000000002</v>
       </c>
       <c r="Y47" s="11">
         <v>0</v>
       </c>
       <c r="Z47" s="11">
-        <v>-12.87</v>
+        <v>-16.010000000000002</v>
       </c>
       <c r="AA47" s="12">
         <v>-1</v>
@@ -7611,10 +6573,10 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C48" s="10">
         <v>2043</v>
@@ -7623,16 +6585,16 @@
         <v>2043</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F48" s="10">
         <v>111056</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I48" s="22">
         <v>45639</v>
@@ -7641,7 +6603,7 @@
         <v>45639</v>
       </c>
       <c r="K48" s="23" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L48" s="11">
         <v>3</v>
@@ -7680,16 +6642,16 @@
         <v>-0.63319999999999999</v>
       </c>
       <c r="X48" s="11">
-        <v>93.74</v>
+        <v>109.52</v>
       </c>
       <c r="Y48" s="11">
         <v>101.47</v>
       </c>
       <c r="Z48" s="11">
-        <v>7.73</v>
+        <v>-8.0500000000000007</v>
       </c>
       <c r="AA48" s="12">
-        <v>8.2500000000000004E-2</v>
+        <v>-7.3499999999999996E-2</v>
       </c>
       <c r="AB48" s="11">
         <v>0</v>
@@ -7706,10 +6668,10 @@
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C49" s="10">
         <v>2043</v>
@@ -7718,16 +6680,16 @@
         <v>2856</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F49" s="10">
         <v>111960</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="I49" s="22">
         <v>45707</v>
@@ -7736,7 +6698,7 @@
         <v>45707</v>
       </c>
       <c r="K49" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L49" s="11">
         <v>6</v>
@@ -7775,16 +6737,16 @@
         <v>-1</v>
       </c>
       <c r="X49" s="11">
-        <v>189.44</v>
+        <v>205.32</v>
       </c>
       <c r="Y49" s="11">
         <v>13.5</v>
       </c>
       <c r="Z49" s="11">
-        <v>-175.94</v>
+        <v>-191.82</v>
       </c>
       <c r="AA49" s="12">
-        <v>-0.92869999999999997</v>
+        <v>-0.93420000000000003</v>
       </c>
       <c r="AB49" s="11">
         <v>0</v>
@@ -7801,10 +6763,10 @@
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C50" s="10">
         <v>2043</v>
@@ -7813,16 +6775,16 @@
         <v>2043</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F50" s="10">
         <v>112083</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I50" s="22">
         <v>45736</v>
@@ -7831,7 +6793,7 @@
         <v>45736</v>
       </c>
       <c r="K50" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L50" s="11">
         <v>5</v>
@@ -7846,40 +6808,40 @@
         <v>-0.6</v>
       </c>
       <c r="P50" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q50" s="11">
         <v>1</v>
       </c>
       <c r="R50" s="11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="S50" s="12">
-        <v>-0.75</v>
+        <v>-0.8</v>
       </c>
       <c r="T50" s="11">
-        <v>185</v>
+        <v>154.62</v>
       </c>
       <c r="U50" s="11">
         <v>21.55</v>
       </c>
       <c r="V50" s="11">
-        <v>-163.44999999999999</v>
+        <v>-133.07</v>
       </c>
       <c r="W50" s="12">
-        <v>-0.88349999999999995</v>
+        <v>-0.86060000000000003</v>
       </c>
       <c r="X50" s="11">
-        <v>131.56</v>
+        <v>153.30000000000001</v>
       </c>
       <c r="Y50" s="11">
-        <v>1.81</v>
+        <v>3.61</v>
       </c>
       <c r="Z50" s="11">
-        <v>-129.75</v>
+        <v>-149.69</v>
       </c>
       <c r="AA50" s="12">
-        <v>-0.98619999999999997</v>
+        <v>-0.97650000000000003</v>
       </c>
       <c r="AB50" s="11">
         <v>0</v>
@@ -7896,10 +6858,10 @@
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C51" s="10">
         <v>2043</v>
@@ -7908,16 +6870,16 @@
         <v>2692</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F51" s="10">
         <v>112192</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="I51" s="22">
         <v>45660</v>
@@ -7926,7 +6888,7 @@
         <v>45691</v>
       </c>
       <c r="K51" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L51" s="11">
         <v>1</v>
@@ -7991,10 +6953,10 @@
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C52" s="10">
         <v>2043</v>
@@ -8003,16 +6965,16 @@
         <v>2856</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F52" s="10">
         <v>112522</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I52" s="22">
         <v>45776</v>
@@ -8021,7 +6983,7 @@
         <v>45776</v>
       </c>
       <c r="K52" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L52" s="11">
         <v>5</v>
@@ -8060,16 +7022,16 @@
         <v>-1</v>
       </c>
       <c r="X52" s="11">
-        <v>51.32</v>
+        <v>59.74</v>
       </c>
       <c r="Y52" s="11">
         <v>16.82</v>
       </c>
       <c r="Z52" s="11">
-        <v>-34.5</v>
+        <v>-42.92</v>
       </c>
       <c r="AA52" s="12">
-        <v>-0.67230000000000001</v>
+        <v>-0.71840000000000004</v>
       </c>
       <c r="AB52" s="11">
         <v>0</v>
@@ -8086,10 +7048,10 @@
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C53" s="10">
         <v>2043</v>
@@ -8098,16 +7060,16 @@
         <v>2043</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F53" s="10">
         <v>113076</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="I53" s="22">
         <v>45806</v>
@@ -8116,55 +7078,55 @@
         <v>45806</v>
       </c>
       <c r="K53" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L53" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M53" s="11">
         <v>0</v>
       </c>
       <c r="N53" s="11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O53" s="12">
         <v>-1</v>
       </c>
       <c r="P53" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q53" s="11">
         <v>0</v>
       </c>
       <c r="R53" s="11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="S53" s="12">
         <v>-1</v>
       </c>
       <c r="T53" s="11">
-        <v>108.8</v>
+        <v>159.41</v>
       </c>
       <c r="U53" s="11">
         <v>0</v>
       </c>
       <c r="V53" s="11">
-        <v>-108.8</v>
+        <v>-159.41</v>
       </c>
       <c r="W53" s="12">
         <v>-1</v>
       </c>
       <c r="X53" s="11">
-        <v>81.27</v>
+        <v>106.57</v>
       </c>
       <c r="Y53" s="11">
         <v>31.26</v>
       </c>
       <c r="Z53" s="11">
-        <v>-50.01</v>
+        <v>-75.31</v>
       </c>
       <c r="AA53" s="12">
-        <v>-0.61539999999999995</v>
+        <v>-0.70669999999999999</v>
       </c>
       <c r="AB53" s="11">
         <v>0</v>
@@ -8181,10 +7143,10 @@
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C54" s="10">
         <v>2043</v>
@@ -8193,16 +7155,16 @@
         <v>2043</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F54" s="10">
         <v>113312</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="I54" s="22">
         <v>45440</v>
@@ -8211,7 +7173,7 @@
         <v>45440</v>
       </c>
       <c r="K54" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L54" s="11">
         <v>0</v>
@@ -8250,13 +7212,13 @@
         <v>0</v>
       </c>
       <c r="X54" s="11">
-        <v>1.87</v>
+        <v>3.75</v>
       </c>
       <c r="Y54" s="11">
         <v>0</v>
       </c>
       <c r="Z54" s="11">
-        <v>-1.87</v>
+        <v>-3.75</v>
       </c>
       <c r="AA54" s="12">
         <v>-1</v>
@@ -8276,10 +7238,10 @@
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C55" s="10">
         <v>2043</v>
@@ -8288,16 +7250,16 @@
         <v>2043</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F55" s="10">
         <v>113450</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I55" s="22">
         <v>45852</v>
@@ -8306,55 +7268,55 @@
         <v>45852</v>
       </c>
       <c r="K55" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L55" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55" s="11">
         <v>1</v>
       </c>
       <c r="N55" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O55" s="12">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="P55" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q55" s="11">
         <v>1</v>
       </c>
       <c r="R55" s="11">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S55" s="12">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T55" s="11">
-        <v>27.2</v>
+        <v>47.96</v>
       </c>
       <c r="U55" s="11">
         <v>58.06</v>
       </c>
       <c r="V55" s="11">
-        <v>30.86</v>
+        <v>10.1</v>
       </c>
       <c r="W55" s="12">
-        <v>1.1346000000000001</v>
+        <v>0.21060000000000001</v>
       </c>
       <c r="X55" s="11">
-        <v>13.61</v>
+        <v>15.34</v>
       </c>
       <c r="Y55" s="11">
         <v>79.69</v>
       </c>
       <c r="Z55" s="11">
-        <v>66.08</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="AA55" s="12">
-        <v>4.8552999999999997</v>
+        <v>4.1948999999999996</v>
       </c>
       <c r="AB55" s="11">
         <v>0</v>
@@ -8371,10 +7333,10 @@
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C56" s="10">
         <v>2043</v>
@@ -8383,16 +7345,16 @@
         <v>2856</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F56" s="10">
         <v>114100</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I56" s="22">
         <v>45863</v>
@@ -8401,7 +7363,7 @@
         <v>45863</v>
       </c>
       <c r="K56" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L56" s="11">
         <v>0</v>
@@ -8419,13 +7381,13 @@
         <v>0</v>
       </c>
       <c r="Q56" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="11">
         <v>0</v>
@@ -8443,10 +7405,10 @@
         <v>0</v>
       </c>
       <c r="Y56" s="11">
-        <v>80.680000000000007</v>
+        <v>107.61</v>
       </c>
       <c r="Z56" s="11">
-        <v>80.680000000000007</v>
+        <v>107.61</v>
       </c>
       <c r="AA56" s="12">
         <v>1</v>
@@ -8466,10 +7428,10 @@
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C57" s="10">
         <v>2043</v>
@@ -8478,16 +7440,16 @@
         <v>2043</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F57" s="10">
         <v>114157</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I57" s="22">
         <v>45904</v>
@@ -8496,7 +7458,7 @@
         <v>45904</v>
       </c>
       <c r="K57" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L57" s="11">
         <v>0</v>
@@ -8538,10 +7500,10 @@
         <v>0</v>
       </c>
       <c r="Y57" s="11">
-        <v>31.32</v>
+        <v>32.97</v>
       </c>
       <c r="Z57" s="11">
-        <v>31.32</v>
+        <v>32.97</v>
       </c>
       <c r="AA57" s="12">
         <v>1</v>
@@ -8561,10 +7523,10 @@
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C58" s="10">
         <v>2043</v>
@@ -8573,16 +7535,16 @@
         <v>2043</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F58" s="10">
         <v>114431</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="I58" s="22">
         <v>45930</v>
@@ -8591,7 +7553,7 @@
         <v>45930</v>
       </c>
       <c r="K58" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L58" s="11">
         <v>0</v>
@@ -8633,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y58" s="11">
-        <v>24.06</v>
+        <v>25.81</v>
       </c>
       <c r="Z58" s="11">
-        <v>24.06</v>
+        <v>25.81</v>
       </c>
       <c r="AA58" s="12">
         <v>1</v>
@@ -8656,10 +7618,10 @@
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A59" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C59" s="10">
         <v>2043</v>
@@ -8668,16 +7630,16 @@
         <v>2043</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F59" s="10">
         <v>114664</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="I59" s="22">
         <v>45950</v>
@@ -8686,7 +7648,7 @@
         <v>45950</v>
       </c>
       <c r="K59" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L59" s="11">
         <v>0</v>
@@ -8751,10 +7713,10 @@
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A60" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C60" s="10">
         <v>2043</v>
@@ -8763,16 +7725,16 @@
         <v>2856</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F60" s="10">
         <v>115047</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I60" s="22">
         <v>45944</v>
@@ -8781,7 +7743,7 @@
         <v>45944</v>
       </c>
       <c r="K60" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L60" s="11">
         <v>0</v>
@@ -8823,10 +7785,10 @@
         <v>0</v>
       </c>
       <c r="Y60" s="11">
-        <v>150.26</v>
+        <v>159.76</v>
       </c>
       <c r="Z60" s="11">
-        <v>150.26</v>
+        <v>159.76</v>
       </c>
       <c r="AA60" s="12">
         <v>1</v>
@@ -8835,10 +7797,10 @@
         <v>0</v>
       </c>
       <c r="AC60" s="11">
-        <v>2.5602</v>
+        <v>3.4779</v>
       </c>
       <c r="AD60" s="11">
-        <v>2.5602</v>
+        <v>3.4779</v>
       </c>
       <c r="AE60" s="12">
         <v>1</v>
@@ -8846,10 +7808,10 @@
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A61" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C61" s="10">
         <v>2043</v>
@@ -8858,16 +7820,16 @@
         <v>2043</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F61" s="10">
         <v>115404</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I61" s="22">
         <v>45986</v>
@@ -8876,7 +7838,7 @@
         <v>45986</v>
       </c>
       <c r="K61" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L61" s="11">
         <v>0</v>
@@ -8918,10 +7880,10 @@
         <v>0</v>
       </c>
       <c r="Y61" s="11">
-        <v>55.61</v>
+        <v>56.27</v>
       </c>
       <c r="Z61" s="11">
-        <v>55.61</v>
+        <v>56.27</v>
       </c>
       <c r="AA61" s="12">
         <v>1</v>
@@ -8941,10 +7903,10 @@
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A62" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C62" s="10">
         <v>2043</v>
@@ -8953,16 +7915,16 @@
         <v>2856</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F62" s="10">
         <v>116060</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I62" s="22">
         <v>46010</v>
@@ -8971,7 +7933,7 @@
         <v>46010</v>
       </c>
       <c r="K62" s="23" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L62" s="11">
         <v>0</v>
@@ -9013,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="Y62" s="11">
-        <v>89.29</v>
+        <v>92.5</v>
       </c>
       <c r="Z62" s="11">
-        <v>89.29</v>
+        <v>92.5</v>
       </c>
       <c r="AA62" s="12">
         <v>1</v>
@@ -9036,10 +7998,10 @@
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A63" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C63" s="10">
         <v>2043</v>
@@ -9048,16 +8010,16 @@
         <v>2043</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F63" s="10">
         <v>116795</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="I63" s="22">
         <v>46000</v>
@@ -9066,7 +8028,7 @@
         <v>46023</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L63" s="11">
         <v>0</v>
@@ -9131,10 +8093,10 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A64" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C64" s="10">
         <v>2043</v>
@@ -9143,16 +8105,16 @@
         <v>2856</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F64" s="10">
         <v>116876</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I64" s="22">
         <v>46111</v>
@@ -9161,7 +8123,7 @@
         <v>46111</v>
       </c>
       <c r="K64" s="23" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L64" s="11">
         <v>0</v>
@@ -9226,10 +8188,10 @@
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A65" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C65" s="10">
         <v>2043</v>
@@ -9238,16 +8200,16 @@
         <v>2856</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F65" s="10">
         <v>116883</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I65" s="22">
         <v>46126</v>
@@ -9256,7 +8218,7 @@
         <v>46126</v>
       </c>
       <c r="K65" s="23" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L65" s="11">
         <v>0</v>
@@ -9321,10 +8283,10 @@
     </row>
     <row r="66" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A66" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C66" s="10">
         <v>2043</v>
@@ -9333,25 +8295,25 @@
         <v>2043</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F66" s="10">
         <v>117440</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I66" s="22">
-        <v>46059</v>
+        <v>46149</v>
       </c>
       <c r="J66" s="22">
-        <v>46083</v>
+        <v>46149</v>
       </c>
       <c r="K66" s="23" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="L66" s="11">
         <v>0</v>
@@ -9393,10 +8355,10 @@
         <v>0</v>
       </c>
       <c r="Y66" s="11">
-        <v>33.94</v>
+        <v>41.51</v>
       </c>
       <c r="Z66" s="11">
-        <v>33.94</v>
+        <v>41.51</v>
       </c>
       <c r="AA66" s="12">
         <v>1</v>
@@ -9416,10 +8378,10 @@
     </row>
     <row r="67" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A67" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C67" s="10">
         <v>2043</v>
@@ -9428,16 +8390,16 @@
         <v>2856</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F67" s="10">
         <v>118069</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I67" s="22">
         <v>46105</v>
@@ -9446,16 +8408,16 @@
         <v>46113</v>
       </c>
       <c r="K67" s="23" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L67" s="11">
         <v>0</v>
       </c>
       <c r="M67" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N67" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O67" s="12">
         <v>1</v>
@@ -9464,10 +8426,10 @@
         <v>0</v>
       </c>
       <c r="Q67" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R67" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S67" s="12">
         <v>1</v>
@@ -9476,10 +8438,10 @@
         <v>0</v>
       </c>
       <c r="U67" s="11">
-        <v>21.34</v>
+        <v>92.09</v>
       </c>
       <c r="V67" s="11">
-        <v>21.34</v>
+        <v>92.09</v>
       </c>
       <c r="W67" s="12">
         <v>1</v>
@@ -9488,10 +8450,10 @@
         <v>0</v>
       </c>
       <c r="Y67" s="11">
-        <v>3.57</v>
+        <v>38.17</v>
       </c>
       <c r="Z67" s="11">
-        <v>3.57</v>
+        <v>38.17</v>
       </c>
       <c r="AA67" s="12">
         <v>1</v>
